--- a/customers/cpall/excel_templates/logistic_plan_มหาชัย.xlsx
+++ b/customers/cpall/excel_templates/logistic_plan_มหาชัย.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gtdit\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User7\Desktop\PRD-Plan\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4757063E-6FC7-4499-AF94-0C86570EC451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AAB3F39-B8D1-44D4-892A-7DCE732D9A24}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="399" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="399" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="มหาชัย-ผลิต" sheetId="5" r:id="rId1"/>
@@ -21,9 +21,9 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'คันที่ 1'!$A$2:$F$49</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'คันที่ 2'!$A$1:$F$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'มหาชัย-ผลิต'!$B$4:$I$56</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'มหาชัย-ผลิต'!$B$4:$H$56</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,12 +31,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -44,10 +39,9 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="2">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="1">
     <bk>
@@ -58,20 +52,6 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="2" v="0"/>
-    </bk>
-  </cellMetadata>
   <valueMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
@@ -81,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="148">
   <si>
     <t>PO1</t>
   </si>
@@ -553,18 +533,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="83">
+  <fonts count="84">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -572,14 +552,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -665,7 +645,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -957,6 +937,14 @@
     </font>
     <font>
       <b/>
+      <u/>
+      <sz val="60"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="40"/>
       <name val="Arial Narrow"/>
       <family val="2"/>
@@ -1151,7 +1139,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="44">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -1643,58 +1631,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1709,7 +1645,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="253">
+  <cellXfs count="254">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1927,43 +1863,43 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="5" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="5" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1972,7 +1908,7 @@
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1987,19 +1923,19 @@
     <xf numFmtId="0" fontId="49" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2008,6 +1944,9 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2020,88 +1959,97 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="29" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="80" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="29" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="81" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="30" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="13" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="30" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="13" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="30" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2110,46 +2058,70 @@
     <xf numFmtId="0" fontId="53" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="5" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="5" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="5" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="5" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="5" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="5" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2167,79 +2139,133 @@
     <xf numFmtId="0" fontId="55" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="5" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="5" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="5" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="5" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="5" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="5" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="5" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="5" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="5" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="82" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="82" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="5" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="5" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="5" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="5" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="5" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2251,64 +2277,82 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2344,127 +2388,22 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="5" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="5" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="5" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="5" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="5" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2639,7 +2578,7 @@
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <global>
     <keyFlags>
       <key name="_Self">
@@ -2665,9 +2604,6 @@
         <flag name="ExcludeFromCalcComparison" value="1"/>
       </key>
       <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
         <flag name="ExcludeFromCalcComparison" value="1"/>
       </key>
       <key name="_ClassificationId">
@@ -3019,1021 +2955,893 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:K136"/>
-  <sheetFormatPr defaultColWidth="5.77734375" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="B2:J136"/>
+  <sheetFormatPr defaultColWidth="5.75" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.77734375" style="64"/>
-    <col min="2" max="2" width="15.6640625" style="64" customWidth="1"/>
+    <col min="1" max="1" width="5.75" style="64"/>
+    <col min="2" max="2" width="15.625" style="64" customWidth="1"/>
     <col min="3" max="3" width="135" style="72" customWidth="1"/>
-    <col min="4" max="4" width="28.21875" style="64" customWidth="1"/>
-    <col min="5" max="6" width="116.109375" style="64" customWidth="1"/>
-    <col min="7" max="7" width="30.88671875" style="64" customWidth="1"/>
-    <col min="8" max="8" width="33.88671875" style="64" customWidth="1"/>
-    <col min="9" max="9" width="45.88671875" style="64" customWidth="1"/>
-    <col min="10" max="10" width="11.6640625" style="64" customWidth="1"/>
-    <col min="11" max="16384" width="5.77734375" style="64"/>
+    <col min="4" max="4" width="28.25" style="64" customWidth="1"/>
+    <col min="5" max="5" width="116.125" style="64" customWidth="1"/>
+    <col min="6" max="6" width="30.875" style="64" customWidth="1"/>
+    <col min="7" max="7" width="33.875" style="64" customWidth="1"/>
+    <col min="8" max="8" width="45.875" style="64" customWidth="1"/>
+    <col min="9" max="9" width="11.625" style="64" customWidth="1"/>
+    <col min="10" max="16384" width="5.75" style="64"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="58.95" customHeight="1"/>
-    <row r="3" spans="2:11" ht="30.75" customHeight="1" thickBot="1">
+    <row r="2" spans="2:10" ht="58.9" customHeight="1"/>
+    <row r="3" spans="2:10" ht="30.75" customHeight="1" thickBot="1">
       <c r="E3" s="65"/>
       <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
       <c r="I3" s="65"/>
       <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-    </row>
-    <row r="4" spans="2:11" ht="103.95" customHeight="1" thickBot="1">
-      <c r="B4" s="136" t="s">
+    </row>
+    <row r="4" spans="2:10" ht="103.9" customHeight="1" thickBot="1">
+      <c r="B4" s="175" t="s">
         <v>147</v>
       </c>
-      <c r="C4" s="137"/>
-      <c r="D4" s="148" t="s">
+      <c r="C4" s="176"/>
+      <c r="D4" s="160" t="s">
         <v>143</v>
       </c>
-      <c r="E4" s="149"/>
-      <c r="F4" s="149"/>
-      <c r="G4" s="149"/>
-      <c r="H4" s="149"/>
-      <c r="I4" s="150"/>
-    </row>
-    <row r="5" spans="2:11" s="67" customFormat="1" ht="31.2" customHeight="1">
-      <c r="B5" s="140" t="s">
+      <c r="E4" s="161"/>
+      <c r="F4" s="161"/>
+      <c r="G4" s="161"/>
+      <c r="H4" s="162"/>
+    </row>
+    <row r="5" spans="2:10" s="67" customFormat="1" ht="15" customHeight="1">
+      <c r="B5" s="179" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="141"/>
-      <c r="D5" s="144" t="s">
+      <c r="C5" s="180"/>
+      <c r="D5" s="183" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="248" t="s">
+      <c r="E5" s="165" t="s">
         <v>111</v>
       </c>
-      <c r="F5" s="249"/>
-      <c r="G5" s="153" t="s">
+      <c r="F5" s="167" t="s">
         <v>72</v>
       </c>
-      <c r="H5" s="154"/>
-      <c r="I5" s="151" t="s">
+      <c r="G5" s="168"/>
+      <c r="H5" s="163" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="2:11" s="67" customFormat="1" ht="30.6" customHeight="1" thickBot="1">
-      <c r="B6" s="142"/>
-      <c r="C6" s="143"/>
-      <c r="D6" s="145"/>
-      <c r="E6" s="250"/>
-      <c r="F6" s="251"/>
-      <c r="G6" s="155"/>
-      <c r="H6" s="156"/>
-      <c r="I6" s="152"/>
-    </row>
-    <row r="7" spans="2:11" s="67" customFormat="1" ht="58.5" customHeight="1" thickBot="1">
-      <c r="B7" s="142"/>
-      <c r="C7" s="143"/>
-      <c r="D7" s="145"/>
-      <c r="E7" s="252" t="s">
-        <v>0</v>
-      </c>
-      <c r="F7" s="252" t="s">
+    <row r="6" spans="2:10" s="67" customFormat="1" ht="30.6" customHeight="1" thickBot="1">
+      <c r="B6" s="181"/>
+      <c r="C6" s="182"/>
+      <c r="D6" s="184"/>
+      <c r="E6" s="166"/>
+      <c r="F6" s="169"/>
+      <c r="G6" s="170"/>
+      <c r="H6" s="164"/>
+    </row>
+    <row r="7" spans="2:10" s="67" customFormat="1" ht="58.5" customHeight="1" thickBot="1">
+      <c r="B7" s="181"/>
+      <c r="C7" s="182"/>
+      <c r="D7" s="184"/>
+      <c r="E7" s="166"/>
+      <c r="F7" s="73" t="s">
+        <v>75</v>
+      </c>
+      <c r="G7" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="H7" s="164"/>
+    </row>
+    <row r="8" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1">
+      <c r="B8" s="171">
         <v>1</v>
       </c>
-      <c r="G7" s="73" t="s">
-        <v>75</v>
-      </c>
-      <c r="H7" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="I7" s="152"/>
-    </row>
-    <row r="8" spans="2:11" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B8" s="146">
-        <v>1</v>
-      </c>
-      <c r="C8" s="104" t="s">
+      <c r="C8" s="106" t="s">
         <v>115</v>
       </c>
-      <c r="D8" s="146">
+      <c r="D8" s="171">
         <v>36</v>
       </c>
-      <c r="E8" s="247">
-        <v>50</v>
-      </c>
-      <c r="F8" s="247">
-        <v>50</v>
-      </c>
-      <c r="G8" s="128">
-        <f t="shared" ref="G8" si="0">SUM(E8:F8)</f>
-        <v>100</v>
-      </c>
-      <c r="H8" s="130">
+      <c r="E8" s="125"/>
+      <c r="F8" s="158">
+        <f>SUM(E8:E8)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="134">
         <f>มหาชัย!C10</f>
-        <v>4</v>
-      </c>
-      <c r="I8" s="132"/>
-    </row>
-    <row r="9" spans="2:11" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B9" s="147"/>
-      <c r="C9" s="108" t="s">
+        <v>0</v>
+      </c>
+      <c r="H8" s="136"/>
+    </row>
+    <row r="9" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
+      <c r="B9" s="172"/>
+      <c r="C9" s="110" t="s">
         <v>116</v>
       </c>
-      <c r="D9" s="147"/>
-      <c r="E9" s="121" t="str">
+      <c r="D9" s="172"/>
+      <c r="E9" s="126" t="str">
         <f>IF(E8=0, "", IF(MOD(E8, $D$8) = 0, E8 / $D$8, IF(INT(E8 / $D$8) = 0, MOD(E8, $D$8) &amp; " P", INT(E8 / $D$8) &amp; " + " &amp; MOD(E8, $D$8) &amp; " P")))</f>
-        <v>1 + 14 P</v>
-      </c>
-      <c r="F9" s="121" t="str">
-        <f>IF(F8=0, "", IF(MOD(F8, $D$8) = 0, F8 / $D$8, IF(INT(F8 / $D$8) = 0, MOD(F8, $D$8) &amp; " P", INT(F8 / $D$8) &amp; " + " &amp; MOD(F8, $D$8) &amp; " P")))</f>
-        <v>1 + 14 P</v>
-      </c>
-      <c r="G9" s="129"/>
-      <c r="H9" s="131"/>
-      <c r="I9" s="133"/>
-    </row>
-    <row r="10" spans="2:11" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B10" s="146">
+        <v/>
+      </c>
+      <c r="F9" s="159"/>
+      <c r="G9" s="135"/>
+      <c r="H9" s="137"/>
+    </row>
+    <row r="10" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1">
+      <c r="B10" s="171">
         <v>2</v>
       </c>
-      <c r="C10" s="105" t="s">
+      <c r="C10" s="107" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="146">
+      <c r="D10" s="171">
         <v>32</v>
       </c>
-      <c r="E10" s="120"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="128">
-        <f t="shared" ref="G10" si="1">SUM(E10:F10)</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="130">
+      <c r="E10" s="125"/>
+      <c r="F10" s="158">
+        <f>SUM(E10:E10)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="134">
         <f>มหาชัย!C11</f>
         <v>0</v>
       </c>
-      <c r="I10" s="132"/>
-    </row>
-    <row r="11" spans="2:11" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B11" s="147"/>
-      <c r="C11" s="108" t="s">
+      <c r="H10" s="136"/>
+    </row>
+    <row r="11" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
+      <c r="B11" s="172"/>
+      <c r="C11" s="110" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="147"/>
-      <c r="E11" s="121" t="str">
+      <c r="D11" s="172"/>
+      <c r="E11" s="126" t="str">
         <f>IF(E10=0, "", IF(MOD(E10, $D$10) = 0, E10 / $D$10, IF(INT(E10 / $D$10) = 0, MOD(E10, $D$10) &amp; " P", INT(E10 / $D$10) &amp; " + " &amp; MOD(E10, $D$10) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F11" s="121" t="str">
-        <f>IF(F10=0, "", IF(MOD(F10, $D$10) = 0, F10 / $D$10, IF(INT(F10 / $D$10) = 0, MOD(F10, $D$10) &amp; " P", INT(F10 / $D$10) &amp; " + " &amp; MOD(F10, $D$10) &amp; " P")))</f>
-        <v/>
-      </c>
-      <c r="G11" s="129"/>
-      <c r="H11" s="131"/>
-      <c r="I11" s="133"/>
-    </row>
-    <row r="12" spans="2:11" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B12" s="146">
+      <c r="F11" s="159"/>
+      <c r="G11" s="135"/>
+      <c r="H11" s="137"/>
+    </row>
+    <row r="12" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1">
+      <c r="B12" s="171">
         <v>3</v>
       </c>
-      <c r="C12" s="105" t="s">
+      <c r="C12" s="107" t="s">
         <v>127</v>
       </c>
-      <c r="D12" s="134">
+      <c r="D12" s="138">
         <v>36</v>
       </c>
-      <c r="E12" s="120"/>
-      <c r="F12" s="120"/>
-      <c r="G12" s="128">
-        <f t="shared" ref="G12" si="2">SUM(E12:F12)</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="130">
+      <c r="E12" s="125"/>
+      <c r="F12" s="158">
+        <f>SUM(E12:E12)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="134">
         <f>มหาชัย!C12</f>
         <v>0</v>
       </c>
-      <c r="I12" s="132"/>
-    </row>
-    <row r="13" spans="2:11" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B13" s="147"/>
-      <c r="C13" s="108" t="s">
+      <c r="H12" s="136"/>
+    </row>
+    <row r="13" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
+      <c r="B13" s="172"/>
+      <c r="C13" s="110" t="s">
         <v>128</v>
       </c>
-      <c r="D13" s="135"/>
-      <c r="E13" s="121" t="str">
+      <c r="D13" s="139"/>
+      <c r="E13" s="126" t="str">
         <f>IF(E12=0, "", IF(MOD(E12, $D$12) = 0, E12/ $D$12, IF(INT(E12 / $D$12) = 0, MOD(E12, $D$12) &amp; " P", INT(E12 / $D$12) &amp; " + " &amp; MOD(E12, $D$12) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F13" s="121" t="str">
-        <f>IF(F12=0, "", IF(MOD(F12, $D$12) = 0, F12/ $D$12, IF(INT(F12 / $D$12) = 0, MOD(F12, $D$12) &amp; " P", INT(F12 / $D$12) &amp; " + " &amp; MOD(F12, $D$12) &amp; " P")))</f>
-        <v/>
-      </c>
-      <c r="G13" s="129"/>
-      <c r="H13" s="131"/>
-      <c r="I13" s="133"/>
-    </row>
-    <row r="14" spans="2:11" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B14" s="116">
+      <c r="F13" s="159"/>
+      <c r="G13" s="135"/>
+      <c r="H13" s="137"/>
+    </row>
+    <row r="14" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1">
+      <c r="B14" s="120">
         <v>4</v>
       </c>
-      <c r="C14" s="105" t="s">
+      <c r="C14" s="107" t="s">
         <v>138</v>
       </c>
-      <c r="D14" s="146">
+      <c r="D14" s="171">
         <v>14</v>
       </c>
-      <c r="E14" s="120"/>
-      <c r="F14" s="120"/>
-      <c r="G14" s="128">
-        <f t="shared" ref="G14" si="3">SUM(E14:F14)</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="130">
+      <c r="E14" s="125"/>
+      <c r="F14" s="158">
+        <f>SUM(E14:E14)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="134">
         <f>มหาชัย!C13</f>
         <v>0</v>
       </c>
-      <c r="I14" s="132"/>
-    </row>
-    <row r="15" spans="2:11" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B15" s="117"/>
-      <c r="C15" s="108" t="s">
+      <c r="H14" s="136"/>
+    </row>
+    <row r="15" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
+      <c r="B15" s="121"/>
+      <c r="C15" s="110" t="s">
         <v>139</v>
       </c>
-      <c r="D15" s="147"/>
-      <c r="E15" s="121" t="str">
+      <c r="D15" s="172"/>
+      <c r="E15" s="126" t="str">
         <f>IF(E14=0, "", IF(MOD(E14, $D$14) = 0, E14/ $D$14, IF(INT(E14 / $D$14) = 0, MOD(E14, $D$14) &amp; " P", INT(E14 / $D$14) &amp; " + " &amp; MOD(E14, $D$14) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F15" s="121" t="str">
-        <f>IF(F14=0, "", IF(MOD(F14, $D$14) = 0, F14/ $D$14, IF(INT(F14 / $D$14) = 0, MOD(F14, $D$14) &amp; " P", INT(F14 / $D$14) &amp; " + " &amp; MOD(F14, $D$14) &amp; " P")))</f>
-        <v/>
-      </c>
-      <c r="G15" s="129"/>
-      <c r="H15" s="131"/>
-      <c r="I15" s="133"/>
-    </row>
-    <row r="16" spans="2:11" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B16" s="116">
+      <c r="F15" s="159"/>
+      <c r="G15" s="135"/>
+      <c r="H15" s="137"/>
+    </row>
+    <row r="16" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1">
+      <c r="B16" s="120">
         <v>5</v>
       </c>
-      <c r="C16" s="105" t="s">
+      <c r="C16" s="107" t="s">
         <v>140</v>
       </c>
-      <c r="D16" s="146">
+      <c r="D16" s="171">
         <v>14</v>
       </c>
-      <c r="E16" s="120"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="128">
-        <f t="shared" ref="G16" si="4">SUM(E16:F16)</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="130">
+      <c r="E16" s="125"/>
+      <c r="F16" s="158">
+        <f>SUM(E16:E16)</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="134">
         <f>มหาชัย!C14</f>
         <v>0</v>
       </c>
-      <c r="I16" s="132"/>
-    </row>
-    <row r="17" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B17" s="117"/>
-      <c r="C17" s="108" t="s">
+      <c r="H16" s="136"/>
+    </row>
+    <row r="17" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
+      <c r="B17" s="121"/>
+      <c r="C17" s="110" t="s">
         <v>141</v>
       </c>
-      <c r="D17" s="147"/>
-      <c r="E17" s="121" t="str">
+      <c r="D17" s="172"/>
+      <c r="E17" s="126" t="str">
         <f>IF(E16=0, "", IF(MOD(E16, $D$16) = 0, E16/ $D$16, IF(INT(E16 / $D$16) = 0, MOD(E16, $D$16) &amp; " P", INT(E16 / $D$16) &amp; " + " &amp; MOD(E16, $D$16) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F17" s="121" t="str">
-        <f>IF(F16=0, "", IF(MOD(F16, $D$16) = 0, F16/ $D$16, IF(INT(F16 / $D$16) = 0, MOD(F16, $D$16) &amp; " P", INT(F16 / $D$16) &amp; " + " &amp; MOD(F16, $D$16) &amp; " P")))</f>
-        <v/>
-      </c>
-      <c r="G17" s="129"/>
-      <c r="H17" s="131"/>
-      <c r="I17" s="133"/>
-    </row>
-    <row r="18" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B18" s="114">
+      <c r="F17" s="159"/>
+      <c r="G17" s="135"/>
+      <c r="H17" s="137"/>
+    </row>
+    <row r="18" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1">
+      <c r="B18" s="118">
         <v>6</v>
       </c>
-      <c r="C18" s="105" t="s">
+      <c r="C18" s="107" t="s">
         <v>62</v>
       </c>
-      <c r="D18" s="134">
+      <c r="D18" s="138">
         <v>32</v>
       </c>
-      <c r="E18" s="120"/>
-      <c r="F18" s="120"/>
-      <c r="G18" s="128">
-        <f t="shared" ref="G18" si="5">SUM(E18:F18)</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="130">
+      <c r="E18" s="125"/>
+      <c r="F18" s="158">
+        <f>SUM(E18:E18)</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="134">
         <f>มหาชัย!C15</f>
         <v>0</v>
       </c>
-      <c r="I18" s="132"/>
-    </row>
-    <row r="19" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B19" s="115"/>
-      <c r="C19" s="108" t="s">
+      <c r="H18" s="136"/>
+    </row>
+    <row r="19" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
+      <c r="B19" s="119"/>
+      <c r="C19" s="110" t="s">
         <v>120</v>
       </c>
-      <c r="D19" s="135"/>
-      <c r="E19" s="121" t="str">
+      <c r="D19" s="139"/>
+      <c r="E19" s="126" t="str">
         <f>IF(E18=0, "", IF(MOD(E18, $D$18) = 0, E18/ $D$18, IF(INT(E18 / $D$18) = 0, MOD(E18, $D$18) &amp; " P", INT(E18 / $D$18) &amp; " + " &amp; MOD(E18, $D$18) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F19" s="121" t="str">
-        <f>IF(F18=0, "", IF(MOD(F18, $D$18) = 0, F18/ $D$18, IF(INT(F18 / $D$18) = 0, MOD(F18, $D$18) &amp; " P", INT(F18 / $D$18) &amp; " + " &amp; MOD(F18, $D$18) &amp; " P")))</f>
-        <v/>
-      </c>
-      <c r="G19" s="129"/>
-      <c r="H19" s="131"/>
-      <c r="I19" s="133"/>
-    </row>
-    <row r="20" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B20" s="118">
+      <c r="F19" s="159"/>
+      <c r="G19" s="135"/>
+      <c r="H19" s="137"/>
+    </row>
+    <row r="20" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1">
+      <c r="B20" s="123">
         <v>7</v>
       </c>
-      <c r="C20" s="104" t="s">
+      <c r="C20" s="106" t="s">
         <v>136</v>
       </c>
-      <c r="D20" s="134">
+      <c r="D20" s="138">
         <v>27</v>
       </c>
-      <c r="E20" s="122"/>
-      <c r="F20" s="122"/>
-      <c r="G20" s="128">
-        <f t="shared" ref="G20" si="6">SUM(E20:F20)</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="130">
+      <c r="E20" s="127"/>
+      <c r="F20" s="173">
+        <f>SUM(E20:E20)</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="134">
         <f>มหาชัย!C16</f>
         <v>0</v>
       </c>
-      <c r="I20" s="132"/>
-    </row>
-    <row r="21" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B21" s="119"/>
-      <c r="C21" s="108" t="s">
+      <c r="H20" s="136"/>
+    </row>
+    <row r="21" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
+      <c r="B21" s="124"/>
+      <c r="C21" s="110" t="s">
         <v>137</v>
       </c>
-      <c r="D21" s="135"/>
-      <c r="E21" s="121" t="str">
+      <c r="D21" s="139"/>
+      <c r="E21" s="126" t="str">
         <f>IF(E20=0, "", IF(MOD(E20, $D$20) = 0, E20/ $D$20, IF(INT(E20 / $D$20) = 0, MOD(E20, $D$20) &amp; " P", INT(E20 / $D$20) &amp; " + " &amp; MOD(E20, $D$20) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F21" s="121" t="str">
-        <f>IF(F20=0, "", IF(MOD(F20, $D$20) = 0, F20/ $D$20, IF(INT(F20 / $D$20) = 0, MOD(F20, $D$20) &amp; " P", INT(F20 / $D$20) &amp; " + " &amp; MOD(F20, $D$20) &amp; " P")))</f>
-        <v/>
-      </c>
-      <c r="G21" s="129"/>
-      <c r="H21" s="131"/>
-      <c r="I21" s="133"/>
-    </row>
-    <row r="22" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B22" s="116">
+      <c r="F21" s="174"/>
+      <c r="G21" s="135"/>
+      <c r="H21" s="137"/>
+    </row>
+    <row r="22" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1">
+      <c r="B22" s="120">
         <v>8</v>
       </c>
-      <c r="C22" s="106" t="s">
+      <c r="C22" s="108" t="s">
         <v>142</v>
       </c>
-      <c r="D22" s="134">
+      <c r="D22" s="138">
         <v>27</v>
       </c>
-      <c r="E22" s="120"/>
-      <c r="F22" s="120"/>
-      <c r="G22" s="128">
-        <f t="shared" ref="G22" si="7">SUM(E22:F22)</f>
-        <v>0</v>
-      </c>
-      <c r="H22" s="130">
+      <c r="E22" s="125"/>
+      <c r="F22" s="158">
+        <f>SUM(E22:E22)</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="134">
         <f>มหาชัย!C17</f>
         <v>0</v>
       </c>
-      <c r="I22" s="132"/>
-    </row>
-    <row r="23" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B23" s="117"/>
-      <c r="C23" s="108" t="s">
+      <c r="H22" s="136"/>
+    </row>
+    <row r="23" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
+      <c r="B23" s="121"/>
+      <c r="C23" s="110" t="s">
         <v>122</v>
       </c>
-      <c r="D23" s="135"/>
-      <c r="E23" s="121" t="str">
+      <c r="D23" s="139"/>
+      <c r="E23" s="126" t="str">
         <f>IF(E22=0, "", IF(MOD(E22, $D$22) = 0, E22/ $D$22, IF(INT(E22 / $D$22) = 0, MOD(E22, $D$22) &amp; " P", INT(E22 / $D$22) &amp; " + " &amp; MOD(E22, $D$22) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F23" s="121" t="str">
-        <f>IF(F22=0, "", IF(MOD(F22, $D$22) = 0, F22/ $D$22, IF(INT(F22 / $D$22) = 0, MOD(F22, $D$22) &amp; " P", INT(F22 / $D$22) &amp; " + " &amp; MOD(F22, $D$22) &amp; " P")))</f>
-        <v/>
-      </c>
-      <c r="G23" s="129"/>
-      <c r="H23" s="131"/>
-      <c r="I23" s="133"/>
-    </row>
-    <row r="24" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B24" s="116">
+      <c r="F23" s="159"/>
+      <c r="G23" s="135"/>
+      <c r="H23" s="137"/>
+    </row>
+    <row r="24" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1">
+      <c r="B24" s="120">
         <v>9</v>
       </c>
-      <c r="C24" s="107" t="s">
+      <c r="C24" s="109" t="s">
         <v>63</v>
       </c>
-      <c r="D24" s="134">
+      <c r="D24" s="138">
         <v>36</v>
       </c>
-      <c r="E24" s="120"/>
-      <c r="F24" s="120"/>
-      <c r="G24" s="128">
-        <f t="shared" ref="G24" si="8">SUM(E24:F24)</f>
-        <v>0</v>
-      </c>
-      <c r="H24" s="130">
+      <c r="E24" s="125"/>
+      <c r="F24" s="158">
+        <f>SUM(E24:E24)</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="134">
         <f>มหาชัย!C18</f>
         <v>0</v>
       </c>
-      <c r="I24" s="132"/>
-    </row>
-    <row r="25" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B25" s="117"/>
-      <c r="C25" s="123" t="s">
+      <c r="H24" s="136"/>
+    </row>
+    <row r="25" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
+      <c r="B25" s="121"/>
+      <c r="C25" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="D25" s="135"/>
-      <c r="E25" s="121" t="str">
+      <c r="D25" s="139"/>
+      <c r="E25" s="126" t="str">
         <f>IF(E24=0, "", IF(MOD(E24, $D$24) = 0, E24/ $D$24, IF(INT(E24 / $D$24) = 0, MOD(E24, $D$24) &amp; " P", INT(E24 / $D$24) &amp; " + " &amp; MOD(E24, $D$24) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F25" s="121" t="str">
-        <f>IF(F24=0, "", IF(MOD(F24, $D$24) = 0, F24/ $D$24, IF(INT(F24 / $D$24) = 0, MOD(F24, $D$24) &amp; " P", INT(F24 / $D$24) &amp; " + " &amp; MOD(F24, $D$24) &amp; " P")))</f>
-        <v/>
-      </c>
-      <c r="G25" s="129"/>
-      <c r="H25" s="131"/>
-      <c r="I25" s="133"/>
-    </row>
-    <row r="26" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B26" s="116">
+      <c r="F25" s="159"/>
+      <c r="G25" s="135"/>
+      <c r="H25" s="137"/>
+    </row>
+    <row r="26" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1">
+      <c r="B26" s="120">
         <v>10</v>
       </c>
-      <c r="C26" s="105" t="s">
+      <c r="C26" s="107" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="134">
+      <c r="D26" s="138">
         <v>20</v>
       </c>
-      <c r="E26" s="120"/>
-      <c r="F26" s="120"/>
-      <c r="G26" s="128">
-        <f t="shared" ref="G26" si="9">SUM(E26:F26)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="130">
+      <c r="E26" s="125"/>
+      <c r="F26" s="158">
+        <f>SUM(E26:E26)</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="134">
         <f>มหาชัย!C19</f>
         <v>0</v>
       </c>
-      <c r="I26" s="132"/>
-    </row>
-    <row r="27" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B27" s="117"/>
-      <c r="C27" s="108" t="s">
+      <c r="H26" s="136"/>
+    </row>
+    <row r="27" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
+      <c r="B27" s="121"/>
+      <c r="C27" s="110" t="s">
         <v>117</v>
       </c>
-      <c r="D27" s="135"/>
-      <c r="E27" s="121" t="str">
+      <c r="D27" s="139"/>
+      <c r="E27" s="126" t="str">
         <f>IF(E26=0, "", IF(MOD(E26, $D$26) = 0, E26/ $D$26, IF(INT(E26 / $D$26) = 0, MOD(E26, $D$26) &amp; " P", INT(E26 / $D$26) &amp; " + " &amp; MOD(E26, $D$26) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F27" s="121" t="str">
-        <f>IF(F26=0, "", IF(MOD(F26, $D$26) = 0, F26/ $D$26, IF(INT(F26 / $D$26) = 0, MOD(F26, $D$26) &amp; " P", INT(F26 / $D$26) &amp; " + " &amp; MOD(F26, $D$26) &amp; " P")))</f>
-        <v/>
-      </c>
-      <c r="G27" s="129"/>
-      <c r="H27" s="131"/>
-      <c r="I27" s="133"/>
-    </row>
-    <row r="28" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B28" s="116">
+      <c r="F27" s="159"/>
+      <c r="G27" s="135"/>
+      <c r="H27" s="137"/>
+    </row>
+    <row r="28" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1">
+      <c r="B28" s="120">
         <v>11</v>
       </c>
-      <c r="C28" s="107" t="s">
+      <c r="C28" s="109" t="s">
         <v>129</v>
       </c>
-      <c r="D28" s="138">
+      <c r="D28" s="177">
         <v>15</v>
       </c>
-      <c r="E28" s="124"/>
-      <c r="F28" s="124"/>
-      <c r="G28" s="128">
-        <f t="shared" ref="G28" si="10">SUM(E28:F28)</f>
-        <v>0</v>
-      </c>
-      <c r="H28" s="130">
+      <c r="E28" s="129"/>
+      <c r="F28" s="158">
+        <f>SUM(E28:E28)</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="134">
         <f>มหาชัย!C20</f>
         <v>0</v>
       </c>
-      <c r="I28" s="132"/>
-    </row>
-    <row r="29" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B29" s="117"/>
-      <c r="C29" s="108" t="s">
+      <c r="H28" s="136"/>
+    </row>
+    <row r="29" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
+      <c r="B29" s="121"/>
+      <c r="C29" s="110" t="s">
         <v>130</v>
       </c>
-      <c r="D29" s="139"/>
-      <c r="E29" s="125" t="str">
+      <c r="D29" s="178"/>
+      <c r="E29" s="130" t="str">
         <f>IF(E28=0, "", IF(MOD(E28, $D$28) = 0, E28/ $D$28, IF(INT(E28 / $D$28) = 0, MOD(E28, $D$28) &amp; " P", INT(E28 / $D$28) &amp; " + " &amp; MOD(E28, $D$28) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F29" s="125" t="str">
-        <f>IF(F28=0, "", IF(MOD(F28, $D$28) = 0, F28/ $D$28, IF(INT(F28 / $D$28) = 0, MOD(F28, $D$28) &amp; " P", INT(F28 / $D$28) &amp; " + " &amp; MOD(F28, $D$28) &amp; " P")))</f>
-        <v/>
-      </c>
-      <c r="G29" s="129"/>
-      <c r="H29" s="131"/>
-      <c r="I29" s="133"/>
-    </row>
-    <row r="30" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B30" s="116">
+      <c r="F29" s="159"/>
+      <c r="G29" s="135"/>
+      <c r="H29" s="137"/>
+    </row>
+    <row r="30" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1">
+      <c r="B30" s="120">
         <v>12</v>
       </c>
-      <c r="C30" s="107" t="s">
+      <c r="C30" s="109" t="s">
         <v>65</v>
       </c>
-      <c r="D30" s="134">
+      <c r="D30" s="138">
         <v>45</v>
       </c>
-      <c r="E30" s="124"/>
-      <c r="F30" s="124"/>
-      <c r="G30" s="128">
-        <f t="shared" ref="G30" si="11">SUM(E30:F30)</f>
-        <v>0</v>
-      </c>
-      <c r="H30" s="130">
+      <c r="E30" s="131"/>
+      <c r="F30" s="158">
+        <f>SUM(E30:E30)</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="134">
         <f>มหาชัย!C21</f>
         <v>0</v>
       </c>
-      <c r="I30" s="132"/>
-    </row>
-    <row r="31" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B31" s="117"/>
-      <c r="C31" s="108" t="s">
+      <c r="H30" s="136"/>
+    </row>
+    <row r="31" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
+      <c r="B31" s="121"/>
+      <c r="C31" s="110" t="s">
         <v>118</v>
       </c>
-      <c r="D31" s="135"/>
-      <c r="E31" s="125" t="str">
+      <c r="D31" s="139"/>
+      <c r="E31" s="130" t="str">
         <f>IF(E30=0, "", IF(MOD(E30, $D$30) = 0, E30/ $D$30, IF(INT(E30 / $D$30) = 0, MOD(E30, $D$30) &amp; " P", INT(E30 / $D$30) &amp; " + " &amp; MOD(E30, $D$30) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F31" s="125" t="str">
-        <f>IF(F30=0, "", IF(MOD(F30, $D$30) = 0, F30/ $D$30, IF(INT(F30 / $D$30) = 0, MOD(F30, $D$30) &amp; " P", INT(F30 / $D$30) &amp; " + " &amp; MOD(F30, $D$30) &amp; " P")))</f>
-        <v/>
-      </c>
-      <c r="G31" s="129"/>
-      <c r="H31" s="131"/>
-      <c r="I31" s="133"/>
-    </row>
-    <row r="32" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B32" s="116">
+      <c r="F31" s="159"/>
+      <c r="G31" s="135"/>
+      <c r="H31" s="137"/>
+    </row>
+    <row r="32" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1">
+      <c r="B32" s="120">
         <v>13</v>
       </c>
-      <c r="C32" s="107" t="s">
+      <c r="C32" s="109" t="s">
         <v>134</v>
       </c>
-      <c r="D32" s="134">
+      <c r="D32" s="138">
         <v>15</v>
       </c>
-      <c r="E32" s="124"/>
-      <c r="F32" s="124"/>
-      <c r="G32" s="128">
-        <f t="shared" ref="G32" si="12">SUM(E32:F32)</f>
-        <v>0</v>
-      </c>
-      <c r="H32" s="130">
+      <c r="E32" s="131"/>
+      <c r="F32" s="158">
+        <f>SUM(E32:E32)</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="134">
         <f>มหาชัย!C22</f>
         <v>0</v>
       </c>
-      <c r="I32" s="132"/>
-    </row>
-    <row r="33" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B33" s="117"/>
-      <c r="C33" s="108" t="s">
+      <c r="H32" s="136"/>
+    </row>
+    <row r="33" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
+      <c r="B33" s="121"/>
+      <c r="C33" s="110" t="s">
         <v>135</v>
       </c>
-      <c r="D33" s="135"/>
-      <c r="E33" s="125" t="str">
+      <c r="D33" s="139"/>
+      <c r="E33" s="130" t="str">
         <f>IF(E32=0, "", IF(MOD(E32, $D$32) = 0, E32/ $D$32, IF(INT(E32 / $D$32) = 0, MOD(E32, $D$32) &amp; " P", INT(E32 / $D$32) &amp; " + " &amp; MOD(E32, $D$32) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F33" s="125" t="str">
-        <f>IF(F32=0, "", IF(MOD(F32, $D$32) = 0, F32/ $D$32, IF(INT(F32 / $D$32) = 0, MOD(F32, $D$32) &amp; " P", INT(F32 / $D$32) &amp; " + " &amp; MOD(F32, $D$32) &amp; " P")))</f>
-        <v/>
-      </c>
-      <c r="G33" s="129"/>
-      <c r="H33" s="131"/>
-      <c r="I33" s="133"/>
-    </row>
-    <row r="34" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B34" s="126">
+      <c r="F33" s="159"/>
+      <c r="G33" s="135"/>
+      <c r="H33" s="137"/>
+    </row>
+    <row r="34" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
+      <c r="B34" s="132">
         <v>14</v>
       </c>
-      <c r="C34" s="105" t="s">
+      <c r="C34" s="107" t="s">
         <v>66</v>
       </c>
-      <c r="D34" s="134">
+      <c r="D34" s="138">
         <v>15</v>
       </c>
-      <c r="E34" s="124"/>
-      <c r="F34" s="124"/>
-      <c r="G34" s="128">
-        <f t="shared" ref="G34" si="13">SUM(E34:F34)</f>
-        <v>0</v>
-      </c>
-      <c r="H34" s="130">
+      <c r="E34" s="131"/>
+      <c r="F34" s="158">
+        <f>SUM(E34:E34)</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="134">
         <f>มหาชัย!C23</f>
         <v>0</v>
       </c>
-      <c r="I34" s="132"/>
-    </row>
-    <row r="35" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B35" s="119"/>
-      <c r="C35" s="108" t="s">
+      <c r="H34" s="136"/>
+    </row>
+    <row r="35" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
+      <c r="B35" s="124"/>
+      <c r="C35" s="110" t="s">
         <v>123</v>
       </c>
-      <c r="D35" s="135"/>
-      <c r="E35" s="125" t="str">
+      <c r="D35" s="139"/>
+      <c r="E35" s="130" t="str">
         <f>IF(E34=0, "", IF(MOD(E34, $D$34) = 0, E34/ $D$34, IF(INT(E34 / $D$34) = 0, MOD(E34, $D$34) &amp; " P", INT(E34 / $D$34) &amp; " + " &amp; MOD(E34, $D$34) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F35" s="125" t="str">
-        <f>IF(F34=0, "", IF(MOD(F34, $D$34) = 0, F34/ $D$34, IF(INT(F34 / $D$34) = 0, MOD(F34, $D$34) &amp; " P", INT(F34 / $D$34) &amp; " + " &amp; MOD(F34, $D$34) &amp; " P")))</f>
-        <v/>
-      </c>
-      <c r="G35" s="129"/>
-      <c r="H35" s="131"/>
-      <c r="I35" s="133"/>
-    </row>
-    <row r="36" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B36" s="126">
+      <c r="F35" s="159"/>
+      <c r="G35" s="135"/>
+      <c r="H35" s="137"/>
+    </row>
+    <row r="36" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
+      <c r="B36" s="132">
         <v>15</v>
       </c>
-      <c r="C36" s="107" t="s">
+      <c r="C36" s="109" t="s">
         <v>132</v>
       </c>
-      <c r="D36" s="134">
+      <c r="D36" s="138">
         <v>27</v>
       </c>
-      <c r="E36" s="124"/>
-      <c r="F36" s="124"/>
-      <c r="G36" s="128">
-        <f t="shared" ref="G36" si="14">SUM(E36:F36)</f>
-        <v>0</v>
-      </c>
-      <c r="H36" s="130">
+      <c r="E36" s="131"/>
+      <c r="F36" s="158">
+        <f>SUM(E36:E36)</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="134">
         <f>มหาชัย!C24</f>
         <v>0</v>
       </c>
-      <c r="I36" s="132"/>
-    </row>
-    <row r="37" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B37" s="119"/>
-      <c r="C37" s="108" t="s">
+      <c r="H36" s="136"/>
+    </row>
+    <row r="37" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
+      <c r="B37" s="124"/>
+      <c r="C37" s="110" t="s">
         <v>133</v>
       </c>
-      <c r="D37" s="135"/>
-      <c r="E37" s="125" t="str">
+      <c r="D37" s="139"/>
+      <c r="E37" s="130" t="str">
         <f>IF(E36=0, "", IF(MOD(E36, $D$36) = 0, E36/ $D$36, IF(INT(E36 / $D$36) = 0, MOD(E36, $D$36) &amp; " P", INT(E36 / $D$36) &amp; " + " &amp; MOD(E36, $D$36) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F37" s="125" t="str">
-        <f>IF(F36=0, "", IF(MOD(F36, $D$36) = 0, F36/ $D$36, IF(INT(F36 / $D$36) = 0, MOD(F36, $D$36) &amp; " P", INT(F36 / $D$36) &amp; " + " &amp; MOD(F36, $D$36) &amp; " P")))</f>
-        <v/>
-      </c>
-      <c r="G37" s="129"/>
-      <c r="H37" s="131"/>
-      <c r="I37" s="133"/>
-    </row>
-    <row r="38" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B38" s="126">
+      <c r="F37" s="159"/>
+      <c r="G37" s="135"/>
+      <c r="H37" s="137"/>
+    </row>
+    <row r="38" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
+      <c r="B38" s="132">
         <v>16</v>
       </c>
-      <c r="C38" s="107" t="s">
+      <c r="C38" s="109" t="s">
         <v>68</v>
       </c>
-      <c r="D38" s="134">
+      <c r="D38" s="138">
         <v>20</v>
       </c>
-      <c r="E38" s="124"/>
-      <c r="F38" s="124"/>
-      <c r="G38" s="128">
-        <f t="shared" ref="G38" si="15">SUM(E38:F38)</f>
-        <v>0</v>
-      </c>
-      <c r="H38" s="130">
+      <c r="E38" s="131"/>
+      <c r="F38" s="158">
+        <f>SUM(E38:E38)</f>
+        <v>0</v>
+      </c>
+      <c r="G38" s="134">
         <f>มหาชัย!C25</f>
         <v>0</v>
       </c>
-      <c r="I38" s="132"/>
-    </row>
-    <row r="39" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B39" s="119"/>
-      <c r="C39" s="108" t="s">
+      <c r="H38" s="136"/>
+    </row>
+    <row r="39" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
+      <c r="B39" s="124"/>
+      <c r="C39" s="110" t="s">
         <v>124</v>
       </c>
-      <c r="D39" s="135"/>
-      <c r="E39" s="125" t="str">
+      <c r="D39" s="139"/>
+      <c r="E39" s="130" t="str">
         <f>IF(E38=0, "", IF(MOD(E38, $D$38) = 0, E38/ $D$38, IF(INT(E38 / $D$38) = 0, MOD(E38, $D$38) &amp; " P", INT(E38 / $D$38) &amp; " + " &amp; MOD(E38, $D$38) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F39" s="125" t="str">
-        <f>IF(F38=0, "", IF(MOD(F38, $D$38) = 0, F38/ $D$38, IF(INT(F38 / $D$38) = 0, MOD(F38, $D$38) &amp; " P", INT(F38 / $D$38) &amp; " + " &amp; MOD(F38, $D$38) &amp; " P")))</f>
-        <v/>
-      </c>
-      <c r="G39" s="129"/>
-      <c r="H39" s="131"/>
-      <c r="I39" s="133"/>
-    </row>
-    <row r="40" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B40" s="126">
+      <c r="F39" s="159"/>
+      <c r="G39" s="135"/>
+      <c r="H39" s="137"/>
+    </row>
+    <row r="40" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
+      <c r="B40" s="132">
         <v>17</v>
       </c>
-      <c r="C40" s="106" t="s">
+      <c r="C40" s="108" t="s">
         <v>69</v>
       </c>
-      <c r="D40" s="134">
+      <c r="D40" s="138">
         <v>32</v>
       </c>
-      <c r="E40" s="124"/>
-      <c r="F40" s="124"/>
-      <c r="G40" s="128">
-        <f t="shared" ref="G40" si="16">SUM(E40:F40)</f>
-        <v>0</v>
-      </c>
-      <c r="H40" s="130">
+      <c r="E40" s="131"/>
+      <c r="F40" s="158">
+        <f>SUM(E40:E40)</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="134">
         <f>มหาชัย!C26</f>
         <v>0</v>
       </c>
-      <c r="I40" s="132"/>
-    </row>
-    <row r="41" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B41" s="119"/>
-      <c r="C41" s="108" t="s">
+      <c r="H40" s="136"/>
+    </row>
+    <row r="41" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
+      <c r="B41" s="124"/>
+      <c r="C41" s="110" t="s">
         <v>125</v>
       </c>
-      <c r="D41" s="135"/>
-      <c r="E41" s="125" t="str">
+      <c r="D41" s="139"/>
+      <c r="E41" s="130" t="str">
         <f>IF(E40=0, "", IF(MOD(E40, $D$40) = 0, E40/ $D$40, IF(INT(E40 / $D$40) = 0, MOD(E40, $D$40) &amp; " P", INT(E40 / $D$40) &amp; " + " &amp; MOD(E40, $D$40) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F41" s="125" t="str">
-        <f>IF(F40=0, "", IF(MOD(F40, $D$40) = 0, F40/ $D$40, IF(INT(F40 / $D$40) = 0, MOD(F40, $D$40) &amp; " P", INT(F40 / $D$40) &amp; " + " &amp; MOD(F40, $D$40) &amp; " P")))</f>
-        <v/>
-      </c>
-      <c r="G41" s="129"/>
-      <c r="H41" s="131"/>
-      <c r="I41" s="133"/>
-    </row>
-    <row r="42" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B42" s="126">
+      <c r="F41" s="159"/>
+      <c r="G41" s="135"/>
+      <c r="H41" s="137"/>
+    </row>
+    <row r="42" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
+      <c r="B42" s="132">
         <v>18</v>
       </c>
-      <c r="C42" s="105" t="s">
+      <c r="C42" s="107" t="s">
         <v>113</v>
       </c>
-      <c r="D42" s="134">
+      <c r="D42" s="138">
         <v>15</v>
       </c>
-      <c r="E42" s="124"/>
-      <c r="F42" s="124"/>
-      <c r="G42" s="128">
-        <f t="shared" ref="G42" si="17">SUM(E42:F42)</f>
-        <v>0</v>
-      </c>
-      <c r="H42" s="130">
+      <c r="E42" s="131"/>
+      <c r="F42" s="158">
+        <f>SUM(E42:E42)</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="134">
         <f>มหาชัย!C27</f>
         <v>0</v>
       </c>
-      <c r="I42" s="132"/>
-    </row>
-    <row r="43" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B43" s="119"/>
-      <c r="C43" s="108" t="s">
+      <c r="H42" s="136"/>
+    </row>
+    <row r="43" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
+      <c r="B43" s="124"/>
+      <c r="C43" s="110" t="s">
         <v>126</v>
       </c>
-      <c r="D43" s="135"/>
-      <c r="E43" s="125" t="str">
+      <c r="D43" s="139"/>
+      <c r="E43" s="130" t="str">
         <f>IF(E42=0, "", IF(MOD(E42, $D$42) = 0, E42/ $D$42, IF(INT(E42 / $D$42) = 0, MOD(E42, $D$42) &amp; " P", INT(E42 / $D$42) &amp; " + " &amp; MOD(E42, $D$42) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F43" s="125" t="str">
-        <f>IF(F42=0, "", IF(MOD(F42, $D$42) = 0, F42/ $D$42, IF(INT(F42 / $D$42) = 0, MOD(F42, $D$42) &amp; " P", INT(F42 / $D$42) &amp; " + " &amp; MOD(F42, $D$42) &amp; " P")))</f>
+      <c r="F43" s="159"/>
+      <c r="G43" s="135"/>
+      <c r="H43" s="137"/>
+    </row>
+    <row r="44" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
+      <c r="B44" s="132">
+        <v>19</v>
+      </c>
+      <c r="C44" s="107" t="s">
+        <v>144</v>
+      </c>
+      <c r="D44" s="138">
+        <v>8</v>
+      </c>
+      <c r="E44" s="131"/>
+      <c r="F44" s="158">
+        <f>SUM(E44:E44)</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="134">
+        <f>มหาชัย!C28</f>
+        <v>0</v>
+      </c>
+      <c r="H44" s="136"/>
+    </row>
+    <row r="45" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
+      <c r="B45" s="124"/>
+      <c r="C45" s="110" t="s">
+        <v>145</v>
+      </c>
+      <c r="D45" s="139"/>
+      <c r="E45" s="130" t="str">
+        <f>IF(E44=0, "", IF(MOD(E44, $D$44) = 0, E44/ $D$44, IF(INT(E44 / $D$44) = 0, MOD(E44, $D$44) &amp; " P", INT(E44 / $D$44) &amp; " + " &amp; MOD(E44, $D$44) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="G43" s="129"/>
-      <c r="H43" s="131"/>
-      <c r="I43" s="133"/>
-    </row>
-    <row r="44" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B44" s="126">
-        <v>19</v>
-      </c>
-      <c r="C44" s="105" t="s">
-        <v>144</v>
-      </c>
-      <c r="D44" s="134">
-        <v>8</v>
-      </c>
-      <c r="E44" s="124">
-        <v>50</v>
-      </c>
-      <c r="F44" s="124">
-        <v>50</v>
-      </c>
-      <c r="G44" s="128">
-        <f>SUM(E44:F44)</f>
-        <v>100</v>
-      </c>
-      <c r="H44" s="130">
-        <f>มหาชัย!C28</f>
-        <v>14</v>
-      </c>
-      <c r="I44" s="132"/>
-    </row>
-    <row r="45" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B45" s="119"/>
-      <c r="C45" s="108" t="s">
-        <v>145</v>
-      </c>
-      <c r="D45" s="135"/>
-      <c r="E45" s="125" t="str">
-        <f>IF(E44=0, "", IF(MOD(E44, $D$44) = 0, E44/ $D$44, IF(INT(E44 / $D$44) = 0, MOD(E44, $D$44) &amp; " P", INT(E44 / $D$44) &amp; " + " &amp; MOD(E44, $D$44) &amp; " P")))</f>
-        <v>6 + 2 P</v>
-      </c>
-      <c r="F45" s="125" t="str">
-        <f>IF(F44=0, "", IF(MOD(F44, $D$44) = 0, F44/ $D$44, IF(INT(F44 / $D$44) = 0, MOD(F44, $D$44) &amp; " P", INT(F44 / $D$44) &amp; " + " &amp; MOD(F44, $D$44) &amp; " P")))</f>
-        <v>6 + 2 P</v>
-      </c>
-      <c r="G45" s="129"/>
-      <c r="H45" s="131"/>
-      <c r="I45" s="133"/>
-    </row>
-    <row r="46" spans="2:10" s="67" customFormat="1" ht="102" customHeight="1" thickBot="1">
-      <c r="B46" s="172" t="s">
+      <c r="F45" s="159"/>
+      <c r="G45" s="135"/>
+      <c r="H45" s="137"/>
+    </row>
+    <row r="46" spans="2:9" s="67" customFormat="1" ht="102" customHeight="1" thickBot="1">
+      <c r="B46" s="155" t="s">
         <v>88</v>
       </c>
-      <c r="C46" s="173"/>
-      <c r="D46" s="174"/>
+      <c r="C46" s="156"/>
+      <c r="D46" s="157"/>
       <c r="E46" s="77">
         <f>-SUM(ROUNDUP(E8/$D$8,0), ROUNDUP(E10/$D$10,0), ROUNDUP(E12/$D$12,0), ROUNDUP(E14/$D$14,0), ROUNDUP(E16/$D$16,0), ROUNDUP(E18/$D$18,0), ROUNDUP(E20/$D$20,0), ROUNDUP(E22/$D$22,0), ROUNDUP(E24/$D$24,0), ROUNDUP(E26/$D$26,0), ROUNDUP(E28/$D$28,0), ROUNDUP(E30/$D$30,0), ROUNDUP(E32/$D$32,0), ROUNDUP(E34/$D$34,0), ROUNDUP(E36/$D$36,0), ROUNDUP(E38/$D$38,0), ROUNDUP(E40/$D$40,0), ROUNDUP(E42/$D$42,0), ROUNDUP(E44/$D$44,0))</f>
-        <v>-9</v>
-      </c>
-      <c r="F46" s="77">
-        <f>-SUM(ROUNDUP(F8/$D$8,0), ROUNDUP(F10/$D$10,0), ROUNDUP(F12/$D$12,0), ROUNDUP(F14/$D$14,0), ROUNDUP(F16/$D$16,0), ROUNDUP(F18/$D$18,0), ROUNDUP(F20/$D$20,0), ROUNDUP(F22/$D$22,0), ROUNDUP(F24/$D$24,0), ROUNDUP(F26/$D$26,0), ROUNDUP(F28/$D$28,0), ROUNDUP(F30/$D$30,0), ROUNDUP(F32/$D$32,0), ROUNDUP(F34/$D$34,0), ROUNDUP(F36/$D$36,0), ROUNDUP(F38/$D$38,0), ROUNDUP(F40/$D$40,0), ROUNDUP(F42/$D$42,0), ROUNDUP(F44/$D$44,0))</f>
-        <v>-9</v>
-      </c>
-      <c r="G46" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="F46" s="78" t="s">
         <v>90</v>
       </c>
-      <c r="H46" s="79">
-        <f>SUM(H8:H45)</f>
-        <v>18</v>
-      </c>
-      <c r="I46" s="70"/>
-      <c r="J46" s="69"/>
-    </row>
-    <row r="47" spans="2:10" ht="17.399999999999999" customHeight="1" thickBot="1">
+      <c r="G46" s="79">
+        <f>SUM(G8:G45)</f>
+        <v>0</v>
+      </c>
+      <c r="H46" s="70"/>
+      <c r="I46" s="69"/>
+    </row>
+    <row r="47" spans="2:9" ht="17.45" customHeight="1" thickBot="1">
       <c r="E47" s="80"/>
-      <c r="F47" s="80"/>
-      <c r="G47" s="81"/>
-      <c r="H47" s="82"/>
+      <c r="F47" s="81"/>
+      <c r="G47" s="82"/>
+      <c r="H47" s="66"/>
       <c r="I47" s="66"/>
-      <c r="J47" s="66"/>
-    </row>
-    <row r="48" spans="2:10" ht="105" customHeight="1" thickBot="1">
-      <c r="B48" s="163" t="s">
+    </row>
+    <row r="48" spans="2:9" ht="105" customHeight="1" thickBot="1">
+      <c r="B48" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="C48" s="171"/>
-      <c r="D48" s="164"/>
+      <c r="C48" s="154"/>
+      <c r="D48" s="147"/>
       <c r="E48" s="84" t="s">
         <v>53</v>
       </c>
-      <c r="F48" s="127"/>
-      <c r="G48" s="163" t="s">
+      <c r="F48" s="146" t="s">
         <v>54</v>
       </c>
-      <c r="H48" s="164"/>
-      <c r="I48" s="84" t="s">
+      <c r="G48" s="147"/>
+      <c r="H48" s="84" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="62.4" customHeight="1">
+    <row r="49" spans="2:8" ht="62.45" customHeight="1">
       <c r="B49" s="92" t="s">
         <v>78</v>
       </c>
-      <c r="C49" s="169"/>
-      <c r="D49" s="170"/>
+      <c r="C49" s="152"/>
+      <c r="D49" s="153"/>
       <c r="E49" s="93"/>
-      <c r="F49" s="244"/>
-      <c r="G49" s="161"/>
-      <c r="H49" s="162"/>
-      <c r="I49" s="93"/>
-    </row>
-    <row r="50" spans="2:9" ht="62.4" customHeight="1">
+      <c r="F49" s="144"/>
+      <c r="G49" s="145"/>
+      <c r="H49" s="93"/>
+    </row>
+    <row r="50" spans="2:8" ht="62.45" customHeight="1">
       <c r="B50" s="94" t="s">
         <v>80</v>
       </c>
-      <c r="C50" s="167"/>
-      <c r="D50" s="168"/>
+      <c r="C50" s="150"/>
+      <c r="D50" s="151"/>
       <c r="E50" s="95"/>
-      <c r="F50" s="245"/>
-      <c r="G50" s="159"/>
-      <c r="H50" s="160"/>
-      <c r="I50" s="95"/>
-    </row>
-    <row r="51" spans="2:9" ht="62.4" customHeight="1" thickBot="1">
+      <c r="F50" s="142"/>
+      <c r="G50" s="143"/>
+      <c r="H50" s="95"/>
+    </row>
+    <row r="51" spans="2:8" ht="62.45" customHeight="1" thickBot="1">
       <c r="B51" s="96" t="s">
         <v>82</v>
       </c>
-      <c r="C51" s="165"/>
-      <c r="D51" s="166"/>
+      <c r="C51" s="148"/>
+      <c r="D51" s="149"/>
       <c r="E51" s="97"/>
-      <c r="F51" s="246"/>
-      <c r="G51" s="157"/>
-      <c r="H51" s="158"/>
-      <c r="I51" s="97"/>
-    </row>
-    <row r="53" spans="2:9" ht="102.6" customHeight="1">
+      <c r="F51" s="140"/>
+      <c r="G51" s="141"/>
+      <c r="H51" s="97"/>
+    </row>
+    <row r="53" spans="2:8" ht="102.6" customHeight="1">
       <c r="C53" s="85"/>
       <c r="D53" s="86" t="s">
         <v>91</v>
       </c>
       <c r="E53" s="86"/>
-      <c r="F53" s="86"/>
-      <c r="G53" s="76">
-        <f>SUM(H46)</f>
-        <v>18</v>
-      </c>
-      <c r="H53" s="87" t="s">
+      <c r="F53" s="76">
+        <f>SUM(G46)</f>
+        <v>0</v>
+      </c>
+      <c r="G53" s="87" t="s">
         <v>92</v>
       </c>
-      <c r="I53" s="85"/>
-    </row>
-    <row r="54" spans="2:9" ht="55.95" customHeight="1" thickBot="1">
+      <c r="H53" s="85"/>
+    </row>
+    <row r="54" spans="2:8" ht="55.9" customHeight="1" thickBot="1">
       <c r="C54" s="85"/>
       <c r="D54" s="85"/>
       <c r="E54" s="86"/>
-      <c r="F54" s="86"/>
-      <c r="G54" s="86" t="s">
+      <c r="F54" s="86" t="s">
         <v>79</v>
       </c>
-      <c r="H54" s="86"/>
-      <c r="I54" s="85"/>
-    </row>
-    <row r="55" spans="2:9" ht="55.95" customHeight="1" thickBot="1">
+      <c r="G54" s="86"/>
+      <c r="H54" s="85"/>
+    </row>
+    <row r="55" spans="2:8" ht="55.9" customHeight="1" thickBot="1">
       <c r="C55" s="88"/>
       <c r="D55" s="85"/>
       <c r="E55" s="85"/>
-      <c r="F55" s="85"/>
+      <c r="F55" s="89" t="s">
+        <v>81</v>
+      </c>
       <c r="G55" s="89" t="s">
-        <v>81</v>
-      </c>
-      <c r="H55" s="89" t="s">
         <v>59</v>
       </c>
-      <c r="I55" s="85"/>
-    </row>
-    <row r="56" spans="2:9" ht="55.95" customHeight="1" thickBot="1">
+      <c r="H55" s="85"/>
+    </row>
+    <row r="56" spans="2:8" ht="55.9" customHeight="1" thickBot="1">
       <c r="C56" s="88"/>
       <c r="D56" s="85"/>
       <c r="E56" s="85"/>
-      <c r="F56" s="85"/>
+      <c r="F56" s="89"/>
       <c r="G56" s="89"/>
-      <c r="H56" s="89"/>
-      <c r="I56" s="85"/>
-    </row>
-    <row r="57" spans="2:9" ht="108.6" customHeight="1" thickBot="1">
+      <c r="H56" s="85"/>
+    </row>
+    <row r="57" spans="2:8" ht="108.6" customHeight="1" thickBot="1">
       <c r="C57" s="85"/>
       <c r="D57" s="85"/>
       <c r="E57" s="90" t="s">
         <v>83</v>
       </c>
-      <c r="F57" s="90"/>
+      <c r="F57" s="91"/>
       <c r="G57" s="91"/>
-      <c r="H57" s="91"/>
-      <c r="I57" s="85"/>
-    </row>
-    <row r="58" spans="2:9" ht="87.6" customHeight="1">
+      <c r="H57" s="85"/>
+    </row>
+    <row r="58" spans="2:8" ht="87.6" customHeight="1">
       <c r="C58" s="74"/>
       <c r="D58" s="74"/>
       <c r="E58" s="74"/>
-      <c r="F58" s="74"/>
+      <c r="F58" s="75"/>
       <c r="G58" s="75"/>
-      <c r="H58" s="75"/>
-      <c r="I58" s="67"/>
-    </row>
-    <row r="59" spans="2:9" ht="15" customHeight="1">
+      <c r="H58" s="67"/>
+    </row>
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="E59" s="67"/>
       <c r="F59" s="67"/>
       <c r="G59" s="67"/>
       <c r="H59" s="67"/>
-      <c r="I59" s="67"/>
     </row>
     <row r="75" spans="3:3" ht="15" customHeight="1">
       <c r="C75" s="64"/>
@@ -4223,54 +4031,38 @@
     </row>
   </sheetData>
   <mergeCells count="95">
-    <mergeCell ref="E5:F6"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="I38:I39"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="I42:I43"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="I5:I7"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="G5:H6"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="H28:H29"/>
     <mergeCell ref="G28:G29"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="H32:H33"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="D22:D23"/>
     <mergeCell ref="D24:D25"/>
@@ -4286,42 +4078,61 @@
     <mergeCell ref="D20:D21"/>
     <mergeCell ref="D16:D17"/>
     <mergeCell ref="D14:D15"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="H32:H33"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="I34:I35"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="H5:H7"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="F5:G6"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="F42:F43"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="20" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="F8 F18 F12" formulaRange="1"/>
+  </ignoredErrors>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -4330,44 +4141,44 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:AV51"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="35.77734375" style="3" customWidth="1"/>
-    <col min="2" max="3" width="11.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="7.21875" style="3" customWidth="1"/>
-    <col min="5" max="13" width="5.77734375" style="3" customWidth="1"/>
-    <col min="14" max="14" width="20.109375" style="3" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="10.77734375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="15.77734375" style="3" customWidth="1"/>
-    <col min="18" max="47" width="3.77734375" style="3" hidden="1" customWidth="1"/>
-    <col min="48" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="35.75" style="3" customWidth="1"/>
+    <col min="2" max="3" width="11.625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="7.25" style="3" customWidth="1"/>
+    <col min="5" max="13" width="5.75" style="3" customWidth="1"/>
+    <col min="14" max="14" width="20.125" style="3" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="10.75" style="3" customWidth="1"/>
+    <col min="17" max="17" width="15.75" style="3" customWidth="1"/>
+    <col min="18" max="47" width="3.75" style="3" hidden="1" customWidth="1"/>
+    <col min="48" max="16384" width="8.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" ht="49.95" customHeight="1">
+    <row r="1" spans="1:48" ht="49.9" customHeight="1">
       <c r="A1" s="3" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="175" t="s">
+      <c r="B1" s="206" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
-      <c r="F1" s="176"/>
-      <c r="G1" s="176"/>
-      <c r="H1" s="176"/>
-      <c r="I1" s="176"/>
-      <c r="J1" s="176"/>
-      <c r="K1" s="176"/>
-      <c r="L1" s="176"/>
-      <c r="M1" s="176"/>
-      <c r="O1" s="177" t="s">
+      <c r="C1" s="200"/>
+      <c r="D1" s="200"/>
+      <c r="E1" s="200"/>
+      <c r="F1" s="200"/>
+      <c r="G1" s="200"/>
+      <c r="H1" s="200"/>
+      <c r="I1" s="200"/>
+      <c r="J1" s="200"/>
+      <c r="K1" s="200"/>
+      <c r="L1" s="200"/>
+      <c r="M1" s="200"/>
+      <c r="O1" s="207" t="s">
         <v>18</v>
       </c>
-      <c r="P1" s="177"/>
-      <c r="Q1" s="177"/>
-    </row>
-    <row r="2" spans="1:48" ht="10.199999999999999" customHeight="1">
+      <c r="P1" s="207"/>
+      <c r="Q1" s="207"/>
+    </row>
+    <row r="2" spans="1:48" ht="10.15" customHeight="1">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -4389,23 +4200,23 @@
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="9"/>
-      <c r="O3" s="177" t="s">
+      <c r="O3" s="207" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="177"/>
-      <c r="Q3" s="177"/>
-    </row>
-    <row r="4" spans="1:48" ht="25.2" customHeight="1">
+      <c r="P3" s="207"/>
+      <c r="Q3" s="207"/>
+    </row>
+    <row r="4" spans="1:48" ht="25.15" customHeight="1">
       <c r="A4" s="63" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="O4" s="177"/>
-      <c r="P4" s="177"/>
-      <c r="Q4" s="177"/>
-    </row>
-    <row r="5" spans="1:48" ht="4.95" customHeight="1">
+      <c r="O4" s="207"/>
+      <c r="P4" s="207"/>
+      <c r="Q4" s="207"/>
+    </row>
+    <row r="5" spans="1:48" ht="4.9000000000000004" customHeight="1">
       <c r="A5" s="63"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -4413,171 +4224,171 @@
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
     </row>
-    <row r="6" spans="1:48" ht="25.2" customHeight="1">
-      <c r="A6" s="178" t="s">
+    <row r="6" spans="1:48" ht="25.15" customHeight="1">
+      <c r="A6" s="208" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="178"/>
-      <c r="C6" s="180" t="s">
+      <c r="B6" s="208"/>
+      <c r="C6" s="210" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="180"/>
-      <c r="E6" s="180"/>
-      <c r="F6" s="180"/>
-      <c r="G6" s="180"/>
-      <c r="H6" s="180"/>
-      <c r="I6" s="180"/>
-      <c r="J6" s="180"/>
-      <c r="K6" s="180"/>
-      <c r="L6" s="180"/>
-      <c r="M6" s="180"/>
-      <c r="N6" s="180"/>
-      <c r="O6" s="180"/>
-      <c r="P6" s="180"/>
-      <c r="Q6" s="180"/>
-    </row>
-    <row r="7" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A7" s="178"/>
-      <c r="B7" s="178"/>
-      <c r="C7" s="184" t="s">
+      <c r="D6" s="210"/>
+      <c r="E6" s="210"/>
+      <c r="F6" s="210"/>
+      <c r="G6" s="210"/>
+      <c r="H6" s="210"/>
+      <c r="I6" s="210"/>
+      <c r="J6" s="210"/>
+      <c r="K6" s="210"/>
+      <c r="L6" s="210"/>
+      <c r="M6" s="210"/>
+      <c r="N6" s="210"/>
+      <c r="O6" s="210"/>
+      <c r="P6" s="210"/>
+      <c r="Q6" s="210"/>
+    </row>
+    <row r="7" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A7" s="208"/>
+      <c r="B7" s="208"/>
+      <c r="C7" s="204" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="186" t="s">
+      <c r="D7" s="185" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="187"/>
-      <c r="F7" s="187"/>
-      <c r="G7" s="187"/>
-      <c r="H7" s="187"/>
-      <c r="I7" s="187"/>
-      <c r="J7" s="187"/>
-      <c r="K7" s="187"/>
-      <c r="L7" s="187"/>
-      <c r="M7" s="187"/>
-      <c r="N7" s="187"/>
-      <c r="O7" s="187"/>
-      <c r="P7" s="187"/>
-      <c r="Q7" s="188"/>
+      <c r="E7" s="186"/>
+      <c r="F7" s="186"/>
+      <c r="G7" s="186"/>
+      <c r="H7" s="186"/>
+      <c r="I7" s="186"/>
+      <c r="J7" s="186"/>
+      <c r="K7" s="186"/>
+      <c r="L7" s="186"/>
+      <c r="M7" s="186"/>
+      <c r="N7" s="186"/>
+      <c r="O7" s="186"/>
+      <c r="P7" s="186"/>
+      <c r="Q7" s="187"/>
     </row>
     <row r="8" spans="1:48" ht="15" customHeight="1">
-      <c r="A8" s="179"/>
-      <c r="B8" s="178"/>
-      <c r="C8" s="185"/>
-      <c r="D8" s="181" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="181" t="s">
+      <c r="A8" s="209"/>
+      <c r="B8" s="208"/>
+      <c r="C8" s="205"/>
+      <c r="D8" s="190" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="190" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="181" t="s">
+      <c r="F8" s="190" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="181" t="s">
+      <c r="G8" s="190" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="181" t="s">
+      <c r="H8" s="190" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="181" t="s">
+      <c r="I8" s="190" t="s">
         <v>28</v>
       </c>
-      <c r="J8" s="181" t="s">
+      <c r="J8" s="190" t="s">
         <v>29</v>
       </c>
-      <c r="K8" s="181" t="s">
+      <c r="K8" s="190" t="s">
         <v>30</v>
       </c>
-      <c r="L8" s="181" t="s">
+      <c r="L8" s="190" t="s">
         <v>31</v>
       </c>
-      <c r="M8" s="181" t="s">
+      <c r="M8" s="190" t="s">
         <v>32</v>
       </c>
       <c r="N8" s="10"/>
-      <c r="O8" s="181" t="s">
+      <c r="O8" s="190" t="s">
         <v>35</v>
       </c>
-      <c r="P8" s="181" t="s">
+      <c r="P8" s="190" t="s">
         <v>36</v>
       </c>
-      <c r="Q8" s="181" t="s">
+      <c r="Q8" s="190" t="s">
         <v>37</v>
       </c>
-      <c r="R8" s="176" t="s">
+      <c r="R8" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="S8" s="176"/>
-      <c r="T8" s="176"/>
-      <c r="U8" s="176" t="s">
+      <c r="S8" s="200"/>
+      <c r="T8" s="200"/>
+      <c r="U8" s="200" t="s">
         <v>5</v>
       </c>
-      <c r="V8" s="176"/>
-      <c r="W8" s="176"/>
-      <c r="X8" s="176" t="s">
+      <c r="V8" s="200"/>
+      <c r="W8" s="200"/>
+      <c r="X8" s="200" t="s">
         <v>7</v>
       </c>
-      <c r="Y8" s="176"/>
-      <c r="Z8" s="176"/>
-      <c r="AA8" s="176" t="s">
+      <c r="Y8" s="200"/>
+      <c r="Z8" s="200"/>
+      <c r="AA8" s="200" t="s">
         <v>8</v>
       </c>
-      <c r="AB8" s="176"/>
-      <c r="AC8" s="176"/>
-      <c r="AD8" s="176" t="s">
+      <c r="AB8" s="200"/>
+      <c r="AC8" s="200"/>
+      <c r="AD8" s="200" t="s">
         <v>9</v>
       </c>
-      <c r="AE8" s="176"/>
-      <c r="AF8" s="176"/>
-      <c r="AG8" s="176" t="s">
+      <c r="AE8" s="200"/>
+      <c r="AF8" s="200"/>
+      <c r="AG8" s="200" t="s">
         <v>10</v>
       </c>
-      <c r="AH8" s="176"/>
-      <c r="AI8" s="176"/>
-      <c r="AJ8" s="176" t="s">
+      <c r="AH8" s="200"/>
+      <c r="AI8" s="200"/>
+      <c r="AJ8" s="200" t="s">
         <v>11</v>
       </c>
-      <c r="AK8" s="176"/>
-      <c r="AL8" s="176"/>
-      <c r="AM8" s="176" t="s">
+      <c r="AK8" s="200"/>
+      <c r="AL8" s="200"/>
+      <c r="AM8" s="200" t="s">
         <v>12</v>
       </c>
-      <c r="AN8" s="176"/>
-      <c r="AO8" s="176"/>
-      <c r="AP8" s="176" t="s">
+      <c r="AN8" s="200"/>
+      <c r="AO8" s="200"/>
+      <c r="AP8" s="200" t="s">
         <v>13</v>
       </c>
-      <c r="AQ8" s="176"/>
-      <c r="AR8" s="176"/>
-      <c r="AS8" s="176" t="s">
+      <c r="AQ8" s="200"/>
+      <c r="AR8" s="200"/>
+      <c r="AS8" s="200" t="s">
         <v>14</v>
       </c>
-      <c r="AT8" s="176"/>
-      <c r="AU8" s="176"/>
-    </row>
-    <row r="9" spans="1:48" ht="25.2" customHeight="1">
-      <c r="A9" s="3" t="s">
+      <c r="AT8" s="200"/>
+      <c r="AU8" s="200"/>
+    </row>
+    <row r="9" spans="1:48" ht="25.15" customHeight="1">
+      <c r="A9" s="113" t="s">
         <v>38</v>
       </c>
       <c r="B9" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="185"/>
-      <c r="D9" s="182"/>
-      <c r="E9" s="182"/>
-      <c r="F9" s="182"/>
-      <c r="G9" s="182"/>
-      <c r="H9" s="182"/>
-      <c r="I9" s="182"/>
-      <c r="J9" s="182"/>
-      <c r="K9" s="182"/>
-      <c r="L9" s="182"/>
-      <c r="M9" s="182"/>
+      <c r="C9" s="205"/>
+      <c r="D9" s="191"/>
+      <c r="E9" s="191"/>
+      <c r="F9" s="191"/>
+      <c r="G9" s="191"/>
+      <c r="H9" s="191"/>
+      <c r="I9" s="191"/>
+      <c r="J9" s="191"/>
+      <c r="K9" s="191"/>
+      <c r="L9" s="191"/>
+      <c r="M9" s="191"/>
       <c r="N9" s="98" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="182"/>
-      <c r="P9" s="182"/>
-      <c r="Q9" s="182"/>
+      <c r="O9" s="191"/>
+      <c r="P9" s="191"/>
+      <c r="Q9" s="191"/>
       <c r="R9" s="2" t="s">
         <v>2</v>
       </c>
@@ -4669,2438 +4480,2378 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A10" s="110" t="s">
+    <row r="10" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A10" s="114" t="s">
         <v>115</v>
       </c>
-      <c r="B10" s="109">
+      <c r="B10" s="112">
         <v>36</v>
       </c>
-      <c r="C10" s="83" cm="1">
-        <f t="array" ref="C10">SUMPRODUCT(ROUNDUP(D10:M10/B10,0))</f>
-        <v>4</v>
+      <c r="C10" s="83">
+        <f>SUMPRODUCT(ROUNDUP(D10/B10,0))</f>
+        <v>0</v>
       </c>
       <c r="D10" s="83">
         <f>'มหาชัย-ผลิต'!E8</f>
-        <v>50</v>
-      </c>
-      <c r="E10" s="83">
+        <v>0</v>
+      </c>
+      <c r="E10" s="83"/>
+      <c r="F10" s="100"/>
+      <c r="G10" s="100"/>
+      <c r="H10" s="100"/>
+      <c r="I10" s="100"/>
+      <c r="J10" s="100"/>
+      <c r="K10" s="100"/>
+      <c r="L10" s="100"/>
+      <c r="M10" s="100"/>
+      <c r="N10" s="100">
         <f>'มหาชัย-ผลิต'!F8</f>
-        <v>50</v>
-      </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11">
-        <f>'มหาชัย-ผลิต'!G8</f>
-        <v>100</v>
-      </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="101">
+        <v>0</v>
+      </c>
+      <c r="O10" s="100"/>
+      <c r="P10" s="100"/>
+      <c r="Q10" s="100"/>
+      <c r="R10" s="102">
         <f t="shared" ref="R10:R23" si="0">INT(D10/B10)</f>
-        <v>1</v>
-      </c>
-      <c r="S10" s="102">
+        <v>0</v>
+      </c>
+      <c r="S10" s="103">
         <f t="shared" ref="S10:S23" si="1">IF(MOD(D10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="T10" s="103">
+      <c r="T10" s="104">
         <f t="shared" ref="T10:T23" si="2">IF(AND(MOD(D10,B10)/B10&lt;=0.5,MOD(D10,B10)&lt;&gt;0),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="U10" s="101">
+        <v>0</v>
+      </c>
+      <c r="U10" s="102">
         <f>INT(E10/B10)</f>
-        <v>1</v>
-      </c>
-      <c r="V10" s="102">
+        <v>0</v>
+      </c>
+      <c r="V10" s="103">
         <f>IF(MOD(E10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="W10" s="103">
+      <c r="W10" s="104">
         <f>IF(AND(MOD(E10,B10)/B10&lt;=0.5,MOD(E10,B10)&lt;&gt;0),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="X10" s="101">
+        <v>0</v>
+      </c>
+      <c r="X10" s="102">
         <f t="shared" ref="X10:X24" si="3">INT(F10/B10)</f>
         <v>0</v>
       </c>
-      <c r="Y10" s="102">
+      <c r="Y10" s="103">
         <f t="shared" ref="Y10:Y24" si="4">IF(MOD(F10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="Z10" s="103">
+      <c r="Z10" s="104">
         <f t="shared" ref="Z10:Z24" si="5">IF(AND(MOD(F10,B10)/B10&lt;=0.5,MOD(F10,B10)&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="AA10" s="101">
+      <c r="AA10" s="102">
         <f>INT(G10/B10)</f>
         <v>0</v>
       </c>
-      <c r="AB10" s="102">
+      <c r="AB10" s="103">
         <f>IF(MOD(G10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AC10" s="103">
+      <c r="AC10" s="104">
         <f>IF(AND(MOD(G10,B10)/B10&lt;=0.5,MOD(G10,B10)&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="AD10" s="101">
+      <c r="AD10" s="102">
         <f>INT(H10/B10)</f>
         <v>0</v>
       </c>
-      <c r="AE10" s="102">
+      <c r="AE10" s="103">
         <f>IF(MOD(H10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AF10" s="103">
+      <c r="AF10" s="104">
         <f>IF(AND(MOD(H10,B10)/B10&lt;=0.5,MOD(H10,B10)&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="AG10" s="101">
+      <c r="AG10" s="102">
         <f>INT(I10/B10)</f>
         <v>0</v>
       </c>
-      <c r="AH10" s="102">
+      <c r="AH10" s="103">
         <f>IF(MOD(I10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AI10" s="103">
+      <c r="AI10" s="104">
         <f>IF(AND(MOD(I10,B10)/B10&lt;=0.5,MOD(I10,B10)&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="AJ10" s="101">
+      <c r="AJ10" s="102">
         <f>INT(J10/B10)</f>
         <v>0</v>
       </c>
-      <c r="AK10" s="102">
+      <c r="AK10" s="103">
         <f>IF(MOD(J10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AL10" s="103">
+      <c r="AL10" s="104">
         <f>IF(AND(MOD(J10,B10)/B10&lt;=0.5,MOD(J10,B10)&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="AM10" s="101">
+      <c r="AM10" s="102">
         <f>INT(K10/B10)</f>
         <v>0</v>
       </c>
-      <c r="AN10" s="102">
+      <c r="AN10" s="103">
         <f>IF(MOD(K10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO10" s="103">
+      <c r="AO10" s="104">
         <f>IF(AND(MOD(K10,B10)/B10&lt;=0.5,MOD(K10,B10)&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="AP10" s="101">
+      <c r="AP10" s="102">
         <f>INT(L10/B10)</f>
         <v>0</v>
       </c>
-      <c r="AQ10" s="102">
+      <c r="AQ10" s="103">
         <f>IF(MOD(L10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AR10" s="103">
+      <c r="AR10" s="104">
         <f>IF(AND(MOD(L10,B10)/B10&lt;=0.5,MOD(L10,B10)&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS10" s="101">
+      <c r="AS10" s="102">
         <f>INT(M10/B10)</f>
         <v>0</v>
       </c>
-      <c r="AT10" s="102">
+      <c r="AT10" s="103">
         <f>IF(MOD(M10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AU10" s="103">
+      <c r="AU10" s="104">
         <f>IF(AND(MOD(M10,B10)/B10&lt;=0.5,MOD(M10,B10)&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="AV10" s="11"/>
-    </row>
-    <row r="11" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A11" s="110" t="s">
+      <c r="AV10" s="100"/>
+    </row>
+    <row r="11" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A11" s="114" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="109">
+      <c r="B11" s="112">
         <v>32</v>
       </c>
-      <c r="C11" s="83" cm="1">
-        <f t="array" ref="C11">SUMPRODUCT(ROUNDUP(D11:M11/B11,0))</f>
+      <c r="C11" s="83">
+        <f t="shared" ref="C11:C17" si="6">SUMPRODUCT(ROUNDUP(D11/B11,0))</f>
         <v>0</v>
       </c>
       <c r="D11" s="83">
         <f>'มหาชัย-ผลิต'!E10</f>
         <v>0</v>
       </c>
-      <c r="E11" s="83">
-        <f>'มหาชัย-ผลิต'!F10</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11" t="str">
-        <f t="shared" ref="N11:N18" si="6">INT(SUM(D11:M11)/B11) &amp; " full, " &amp; IF(MOD(SUM(D11:M11), B11)/B11 &lt;= 0.5, "1 less than half", IF(MOD(SUM(D11:M11), B11)/B11 &gt; 0.5, "1 more than half", ""))</f>
+      <c r="E11" s="83"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="100"/>
+      <c r="H11" s="100"/>
+      <c r="I11" s="100"/>
+      <c r="J11" s="100"/>
+      <c r="K11" s="100"/>
+      <c r="L11" s="100"/>
+      <c r="M11" s="100"/>
+      <c r="N11" s="100" t="str">
+        <f t="shared" ref="N11:N18" si="7">INT(SUM(D11:M11)/B11) &amp; " full, " &amp; IF(MOD(SUM(D11:M11), B11)/B11 &lt;= 0.5, "1 less than half", IF(MOD(SUM(D11:M11), B11)/B11 &gt; 0.5, "1 more than half", ""))</f>
         <v>0 full, 1 less than half</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="101">
+      <c r="O11" s="100"/>
+      <c r="P11" s="100"/>
+      <c r="Q11" s="100"/>
+      <c r="R11" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S11" s="102">
+      <c r="S11" s="103">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T11" s="103">
+      <c r="T11" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U11" s="101">
-        <f t="shared" ref="U11:U24" si="7">INT(E11/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="V11" s="102">
-        <f t="shared" ref="V11:V24" si="8">IF(MOD(E11,B11)/B11&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="W11" s="103">
-        <f t="shared" ref="W11:W24" si="9">IF(AND(MOD(E11,B11)/B11&lt;=0.5,MOD(E11,B11)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X11" s="101">
+      <c r="U11" s="102">
+        <f t="shared" ref="U11:U24" si="8">INT(E11/B11)</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="103">
+        <f t="shared" ref="V11:V24" si="9">IF(MOD(E11,B11)/B11&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="104">
+        <f t="shared" ref="W11:W24" si="10">IF(AND(MOD(E11,B11)/B11&lt;=0.5,MOD(E11,B11)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X11" s="102">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y11" s="102">
+      <c r="Y11" s="103">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Z11" s="103">
+      <c r="Z11" s="104">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA11" s="101">
-        <f t="shared" ref="AA11:AA24" si="10">INT(G11/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="AB11" s="102">
-        <f t="shared" ref="AB11:AB24" si="11">IF(MOD(G11,B11)/B11&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AC11" s="103">
-        <f t="shared" ref="AC11:AC24" si="12">IF(AND(MOD(G11,B11)/B11&lt;=0.5,MOD(G11,B11)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AD11" s="101">
-        <f t="shared" ref="AD11:AD24" si="13">INT(H11/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="AE11" s="102">
-        <f t="shared" ref="AE11:AE24" si="14">IF(MOD(H11,B11)/B11&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF11" s="103">
-        <f t="shared" ref="AF11:AF24" si="15">IF(AND(MOD(H11,B11)/B11&lt;=0.5,MOD(H11,B11)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AG11" s="101">
-        <f t="shared" ref="AG11:AG24" si="16">INT(I11/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="AH11" s="102">
-        <f t="shared" ref="AH11:AH24" si="17">IF(MOD(I11,B11)/B11&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AI11" s="103">
-        <f t="shared" ref="AI11:AI24" si="18">IF(AND(MOD(I11,B11)/B11&lt;=0.5,MOD(I11,B11)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ11" s="101">
-        <f t="shared" ref="AJ11:AJ24" si="19">INT(J11/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="AK11" s="102">
-        <f t="shared" ref="AK11:AK24" si="20">IF(MOD(J11,B11)/B11&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AL11" s="103">
-        <f t="shared" ref="AL11:AL24" si="21">IF(AND(MOD(J11,B11)/B11&lt;=0.5,MOD(J11,B11)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AM11" s="101">
-        <f t="shared" ref="AM11:AM24" si="22">INT(K11/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="AN11" s="102">
-        <f t="shared" ref="AN11:AN24" si="23">IF(MOD(K11,B11)/B11&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AO11" s="103">
-        <f t="shared" ref="AO11:AO24" si="24">IF(AND(MOD(K11,B11)/B11&lt;=0.5,MOD(K11,B11)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AP11" s="101">
-        <f t="shared" ref="AP11:AP24" si="25">INT(L11/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="102">
-        <f t="shared" ref="AQ11:AQ24" si="26">IF(MOD(L11,B11)/B11&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AR11" s="103">
-        <f t="shared" ref="AR11:AR24" si="27">IF(AND(MOD(L11,B11)/B11&lt;=0.5,MOD(L11,B11)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AS11" s="101">
-        <f t="shared" ref="AS11:AS24" si="28">INT(M11/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="AT11" s="102">
-        <f t="shared" ref="AT11:AT24" si="29">IF(MOD(M11,B11)/B11&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AU11" s="103">
-        <f t="shared" ref="AU11:AU24" si="30">IF(AND(MOD(M11,B11)/B11&lt;=0.5,MOD(M11,B11)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AV11" s="11"/>
-    </row>
-    <row r="12" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A12" s="110" t="s">
+      <c r="AA11" s="102">
+        <f t="shared" ref="AA11:AA24" si="11">INT(G11/B11)</f>
+        <v>0</v>
+      </c>
+      <c r="AB11" s="103">
+        <f t="shared" ref="AB11:AB24" si="12">IF(MOD(G11,B11)/B11&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC11" s="104">
+        <f t="shared" ref="AC11:AC24" si="13">IF(AND(MOD(G11,B11)/B11&lt;=0.5,MOD(G11,B11)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD11" s="102">
+        <f t="shared" ref="AD11:AD24" si="14">INT(H11/B11)</f>
+        <v>0</v>
+      </c>
+      <c r="AE11" s="103">
+        <f t="shared" ref="AE11:AE24" si="15">IF(MOD(H11,B11)/B11&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="104">
+        <f t="shared" ref="AF11:AF24" si="16">IF(AND(MOD(H11,B11)/B11&lt;=0.5,MOD(H11,B11)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG11" s="102">
+        <f t="shared" ref="AG11:AG24" si="17">INT(I11/B11)</f>
+        <v>0</v>
+      </c>
+      <c r="AH11" s="103">
+        <f t="shared" ref="AH11:AH24" si="18">IF(MOD(I11,B11)/B11&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI11" s="104">
+        <f t="shared" ref="AI11:AI24" si="19">IF(AND(MOD(I11,B11)/B11&lt;=0.5,MOD(I11,B11)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="102">
+        <f t="shared" ref="AJ11:AJ24" si="20">INT(J11/B11)</f>
+        <v>0</v>
+      </c>
+      <c r="AK11" s="103">
+        <f t="shared" ref="AK11:AK24" si="21">IF(MOD(J11,B11)/B11&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL11" s="104">
+        <f t="shared" ref="AL11:AL24" si="22">IF(AND(MOD(J11,B11)/B11&lt;=0.5,MOD(J11,B11)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM11" s="102">
+        <f t="shared" ref="AM11:AM24" si="23">INT(K11/B11)</f>
+        <v>0</v>
+      </c>
+      <c r="AN11" s="103">
+        <f t="shared" ref="AN11:AN24" si="24">IF(MOD(K11,B11)/B11&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO11" s="104">
+        <f t="shared" ref="AO11:AO24" si="25">IF(AND(MOD(K11,B11)/B11&lt;=0.5,MOD(K11,B11)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP11" s="102">
+        <f t="shared" ref="AP11:AP24" si="26">INT(L11/B11)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="103">
+        <f t="shared" ref="AQ11:AQ24" si="27">IF(MOD(L11,B11)/B11&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR11" s="104">
+        <f t="shared" ref="AR11:AR24" si="28">IF(AND(MOD(L11,B11)/B11&lt;=0.5,MOD(L11,B11)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS11" s="102">
+        <f t="shared" ref="AS11:AS24" si="29">INT(M11/B11)</f>
+        <v>0</v>
+      </c>
+      <c r="AT11" s="103">
+        <f t="shared" ref="AT11:AT24" si="30">IF(MOD(M11,B11)/B11&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU11" s="104">
+        <f t="shared" ref="AU11:AU24" si="31">IF(AND(MOD(M11,B11)/B11&lt;=0.5,MOD(M11,B11)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV11" s="100"/>
+    </row>
+    <row r="12" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A12" s="114" t="s">
         <v>127</v>
       </c>
-      <c r="B12" s="109">
+      <c r="B12" s="112">
         <v>36</v>
       </c>
-      <c r="C12" s="83" cm="1">
-        <f t="array" ref="C12">SUMPRODUCT(ROUNDUP(D12:M12/B12,0))</f>
+      <c r="C12" s="83">
+        <f>SUMPRODUCT(ROUNDUP(D12/B12,0))</f>
         <v>0</v>
       </c>
       <c r="D12" s="83">
         <f>'มหาชัย-ผลิต'!E12</f>
         <v>0</v>
       </c>
-      <c r="E12" s="83">
-        <f>'มหาชัย-ผลิต'!F12</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11" t="str">
-        <f t="shared" si="6"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="100"/>
+      <c r="G12" s="100"/>
+      <c r="H12" s="100"/>
+      <c r="I12" s="100"/>
+      <c r="J12" s="100"/>
+      <c r="K12" s="100"/>
+      <c r="L12" s="100"/>
+      <c r="M12" s="100"/>
+      <c r="N12" s="100" t="str">
+        <f t="shared" si="7"/>
         <v>0 full, 1 less than half</v>
       </c>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="101">
+      <c r="O12" s="100"/>
+      <c r="P12" s="100"/>
+      <c r="Q12" s="100"/>
+      <c r="R12" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S12" s="102">
+      <c r="S12" s="103">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T12" s="103">
+      <c r="T12" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U12" s="101">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V12" s="102">
+      <c r="U12" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W12" s="103">
+      <c r="V12" s="103">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="X12" s="101">
+      <c r="W12" s="104">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="102">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y12" s="102">
+      <c r="Y12" s="103">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Z12" s="103">
+      <c r="Z12" s="104">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA12" s="101">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AB12" s="102">
+      <c r="AA12" s="102">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AC12" s="103">
+      <c r="AB12" s="103">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AD12" s="101">
+      <c r="AC12" s="104">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AE12" s="102">
+      <c r="AD12" s="102">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AF12" s="103">
+      <c r="AE12" s="103">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AG12" s="101">
+      <c r="AF12" s="104">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AH12" s="102">
+      <c r="AG12" s="102">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AI12" s="103">
+      <c r="AH12" s="103">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ12" s="101">
+      <c r="AI12" s="104">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK12" s="102">
+      <c r="AJ12" s="102">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AL12" s="103">
+      <c r="AK12" s="103">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="AM12" s="101">
+      <c r="AL12" s="104">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AN12" s="102">
+      <c r="AM12" s="102">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AO12" s="103">
+      <c r="AN12" s="103">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP12" s="101">
+      <c r="AO12" s="104">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AQ12" s="102">
+      <c r="AP12" s="102">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AR12" s="103">
+      <c r="AQ12" s="103">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AS12" s="101">
+      <c r="AR12" s="104">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AT12" s="102">
+      <c r="AS12" s="102">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AU12" s="103">
+      <c r="AT12" s="103">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AV12" s="11"/>
-    </row>
-    <row r="13" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A13" s="110" t="s">
+      <c r="AU12" s="104">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AV12" s="100"/>
+    </row>
+    <row r="13" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A13" s="114" t="s">
         <v>138</v>
       </c>
-      <c r="B13" s="109">
+      <c r="B13" s="112">
         <v>14</v>
       </c>
-      <c r="C13" s="83" cm="1">
-        <f t="array" ref="C13">SUMPRODUCT(ROUNDUP(D13:M13/B13,0))</f>
+      <c r="C13" s="83">
+        <f t="shared" ref="C13:C14" si="32">SUMPRODUCT(ROUNDUP(D13/B13,0))</f>
         <v>0</v>
       </c>
       <c r="D13" s="83">
         <f>'มหาชัย-ผลิต'!E14</f>
         <v>0</v>
       </c>
-      <c r="E13" s="83">
-        <f>'มหาชัย-ผลิต'!F14</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="101"/>
-      <c r="S13" s="102"/>
-      <c r="T13" s="103"/>
-      <c r="U13" s="101"/>
-      <c r="V13" s="102"/>
-      <c r="W13" s="103"/>
-      <c r="X13" s="101"/>
-      <c r="Y13" s="102"/>
-      <c r="Z13" s="103"/>
-      <c r="AA13" s="101"/>
-      <c r="AB13" s="102"/>
-      <c r="AC13" s="103"/>
-      <c r="AD13" s="101"/>
-      <c r="AE13" s="102"/>
-      <c r="AF13" s="103"/>
-      <c r="AG13" s="101"/>
-      <c r="AH13" s="102"/>
-      <c r="AI13" s="103"/>
-      <c r="AJ13" s="101"/>
-      <c r="AK13" s="102"/>
-      <c r="AL13" s="103"/>
-      <c r="AM13" s="101"/>
-      <c r="AN13" s="102"/>
-      <c r="AO13" s="103"/>
-      <c r="AP13" s="101"/>
-      <c r="AQ13" s="102"/>
-      <c r="AR13" s="103"/>
-      <c r="AS13" s="101"/>
-      <c r="AT13" s="102"/>
-      <c r="AU13" s="103"/>
-      <c r="AV13" s="11"/>
-    </row>
-    <row r="14" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A14" s="110" t="s">
+      <c r="E13" s="83"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="122"/>
+      <c r="H13" s="122"/>
+      <c r="I13" s="122"/>
+      <c r="J13" s="122"/>
+      <c r="K13" s="122"/>
+      <c r="L13" s="122"/>
+      <c r="M13" s="122"/>
+      <c r="N13" s="122"/>
+      <c r="O13" s="122"/>
+      <c r="P13" s="122"/>
+      <c r="Q13" s="122"/>
+      <c r="R13" s="102"/>
+      <c r="S13" s="103"/>
+      <c r="T13" s="104"/>
+      <c r="U13" s="102"/>
+      <c r="V13" s="103"/>
+      <c r="W13" s="104"/>
+      <c r="X13" s="102"/>
+      <c r="Y13" s="103"/>
+      <c r="Z13" s="104"/>
+      <c r="AA13" s="102"/>
+      <c r="AB13" s="103"/>
+      <c r="AC13" s="104"/>
+      <c r="AD13" s="102"/>
+      <c r="AE13" s="103"/>
+      <c r="AF13" s="104"/>
+      <c r="AG13" s="102"/>
+      <c r="AH13" s="103"/>
+      <c r="AI13" s="104"/>
+      <c r="AJ13" s="102"/>
+      <c r="AK13" s="103"/>
+      <c r="AL13" s="104"/>
+      <c r="AM13" s="102"/>
+      <c r="AN13" s="103"/>
+      <c r="AO13" s="104"/>
+      <c r="AP13" s="102"/>
+      <c r="AQ13" s="103"/>
+      <c r="AR13" s="104"/>
+      <c r="AS13" s="102"/>
+      <c r="AT13" s="103"/>
+      <c r="AU13" s="104"/>
+      <c r="AV13" s="122"/>
+    </row>
+    <row r="14" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A14" s="114" t="s">
         <v>140</v>
       </c>
-      <c r="B14" s="109">
+      <c r="B14" s="112">
         <v>14</v>
       </c>
-      <c r="C14" s="83" cm="1">
-        <f t="array" ref="C14">SUMPRODUCT(ROUNDUP(D14:M14/B14,0))</f>
+      <c r="C14" s="83">
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="D14" s="83">
         <f>'มหาชัย-ผลิต'!E16</f>
         <v>0</v>
       </c>
-      <c r="E14" s="83">
-        <f>'มหาชัย-ผลิต'!F16</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="101"/>
-      <c r="S14" s="102"/>
-      <c r="T14" s="103"/>
-      <c r="U14" s="101"/>
-      <c r="V14" s="102"/>
-      <c r="W14" s="103"/>
-      <c r="X14" s="101"/>
-      <c r="Y14" s="102"/>
-      <c r="Z14" s="103"/>
-      <c r="AA14" s="101"/>
-      <c r="AB14" s="102"/>
-      <c r="AC14" s="103"/>
-      <c r="AD14" s="101"/>
-      <c r="AE14" s="102"/>
-      <c r="AF14" s="103"/>
-      <c r="AG14" s="101"/>
-      <c r="AH14" s="102"/>
-      <c r="AI14" s="103"/>
-      <c r="AJ14" s="101"/>
-      <c r="AK14" s="102"/>
-      <c r="AL14" s="103"/>
-      <c r="AM14" s="101"/>
-      <c r="AN14" s="102"/>
-      <c r="AO14" s="103"/>
-      <c r="AP14" s="101"/>
-      <c r="AQ14" s="102"/>
-      <c r="AR14" s="103"/>
-      <c r="AS14" s="101"/>
-      <c r="AT14" s="102"/>
-      <c r="AU14" s="103"/>
-      <c r="AV14" s="11"/>
-    </row>
-    <row r="15" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A15" s="110" t="s">
+      <c r="E14" s="83"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="122"/>
+      <c r="H14" s="122"/>
+      <c r="I14" s="122"/>
+      <c r="J14" s="122"/>
+      <c r="K14" s="122"/>
+      <c r="L14" s="122"/>
+      <c r="M14" s="122"/>
+      <c r="N14" s="122"/>
+      <c r="O14" s="122"/>
+      <c r="P14" s="122"/>
+      <c r="Q14" s="122"/>
+      <c r="R14" s="102"/>
+      <c r="S14" s="103"/>
+      <c r="T14" s="104"/>
+      <c r="U14" s="102"/>
+      <c r="V14" s="103"/>
+      <c r="W14" s="104"/>
+      <c r="X14" s="102"/>
+      <c r="Y14" s="103"/>
+      <c r="Z14" s="104"/>
+      <c r="AA14" s="102"/>
+      <c r="AB14" s="103"/>
+      <c r="AC14" s="104"/>
+      <c r="AD14" s="102"/>
+      <c r="AE14" s="103"/>
+      <c r="AF14" s="104"/>
+      <c r="AG14" s="102"/>
+      <c r="AH14" s="103"/>
+      <c r="AI14" s="104"/>
+      <c r="AJ14" s="102"/>
+      <c r="AK14" s="103"/>
+      <c r="AL14" s="104"/>
+      <c r="AM14" s="102"/>
+      <c r="AN14" s="103"/>
+      <c r="AO14" s="104"/>
+      <c r="AP14" s="102"/>
+      <c r="AQ14" s="103"/>
+      <c r="AR14" s="104"/>
+      <c r="AS14" s="102"/>
+      <c r="AT14" s="103"/>
+      <c r="AU14" s="104"/>
+      <c r="AV14" s="122"/>
+    </row>
+    <row r="15" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A15" s="114" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="109">
+      <c r="B15" s="112">
         <v>32</v>
       </c>
-      <c r="C15" s="83" cm="1">
-        <f t="array" ref="C15">SUMPRODUCT(ROUNDUP(D15:M15/B15,0))</f>
+      <c r="C15" s="83">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="D15" s="83">
         <f>'มหาชัย-ผลิต'!E18</f>
         <v>0</v>
       </c>
-      <c r="E15" s="83">
-        <f>'มหาชัย-ผลิต'!F18</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11" t="str">
+      <c r="E15" s="83"/>
+      <c r="F15" s="100"/>
+      <c r="G15" s="100"/>
+      <c r="H15" s="100"/>
+      <c r="I15" s="100"/>
+      <c r="J15" s="100"/>
+      <c r="K15" s="100"/>
+      <c r="L15" s="100"/>
+      <c r="M15" s="100"/>
+      <c r="N15" s="100" t="str">
+        <f t="shared" si="7"/>
+        <v>0 full, 1 less than half</v>
+      </c>
+      <c r="O15" s="100"/>
+      <c r="P15" s="100"/>
+      <c r="Q15" s="100"/>
+      <c r="R15" s="102">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="103">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="104">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="102">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="103">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="104">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="102">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z15" s="104">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA15" s="102">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB15" s="103">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AC15" s="104">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AD15" s="102">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AE15" s="103">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="104">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AG15" s="102">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AH15" s="103">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AI15" s="104">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="102">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AK15" s="103">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AL15" s="104">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AM15" s="102">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN15" s="103">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AO15" s="104">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AP15" s="102">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="103">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AR15" s="104">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AS15" s="102">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AT15" s="103">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AU15" s="104">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AV15" s="100"/>
+    </row>
+    <row r="16" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A16" s="115" t="s">
+        <v>136</v>
+      </c>
+      <c r="B16" s="112">
+        <v>27</v>
+      </c>
+      <c r="C16" s="83">
         <f t="shared" si="6"/>
-        <v>0 full, 1 less than half</v>
-      </c>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="101">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S15" s="102">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T15" s="103">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="101">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="102">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="W15" s="103">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="X15" s="101">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="102">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Z15" s="103">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AA15" s="101">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AB15" s="102">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AC15" s="103">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AD15" s="101">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AE15" s="102">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AF15" s="103">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AG15" s="101">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AH15" s="102">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AI15" s="103">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="101">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AK15" s="102">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AL15" s="103">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AM15" s="101">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AN15" s="102">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AO15" s="103">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AP15" s="101">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="102">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AR15" s="103">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AS15" s="101">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AT15" s="102">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AU15" s="103">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AV15" s="11"/>
-    </row>
-    <row r="16" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A16" s="111" t="s">
-        <v>136</v>
-      </c>
-      <c r="B16" s="109">
-        <v>27</v>
-      </c>
-      <c r="C16" s="83" cm="1">
-        <f t="array" ref="C16">SUMPRODUCT(ROUNDUP(D16:M16/B16,0))</f>
         <v>0</v>
       </c>
       <c r="D16" s="83">
         <f>'มหาชัย-ผลิต'!E20</f>
         <v>0</v>
       </c>
-      <c r="E16" s="83">
-        <f>'มหาชัย-ผลิต'!F20</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="101"/>
-      <c r="S16" s="102"/>
-      <c r="T16" s="103"/>
-      <c r="U16" s="101">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="102">
+      <c r="E16" s="83"/>
+      <c r="F16" s="111"/>
+      <c r="G16" s="111"/>
+      <c r="H16" s="111"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="111"/>
+      <c r="L16" s="111"/>
+      <c r="M16" s="111"/>
+      <c r="N16" s="111"/>
+      <c r="O16" s="111"/>
+      <c r="P16" s="111"/>
+      <c r="Q16" s="111"/>
+      <c r="R16" s="102"/>
+      <c r="S16" s="103"/>
+      <c r="T16" s="104"/>
+      <c r="U16" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W16" s="103">
+      <c r="V16" s="103">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="X16" s="101">
+      <c r="W16" s="104">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="102">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y16" s="102">
+      <c r="Y16" s="103">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Z16" s="103">
+      <c r="Z16" s="104">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA16" s="101">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AB16" s="102">
+      <c r="AA16" s="102">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AC16" s="103">
+      <c r="AB16" s="103">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AD16" s="101">
+      <c r="AC16" s="104">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AE16" s="102">
+      <c r="AD16" s="102">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AF16" s="103">
+      <c r="AE16" s="103">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AG16" s="101">
+      <c r="AF16" s="104">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AH16" s="102">
+      <c r="AG16" s="102">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AI16" s="103">
+      <c r="AH16" s="103">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ16" s="101">
+      <c r="AI16" s="104">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK16" s="102">
+      <c r="AJ16" s="102">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AL16" s="103">
+      <c r="AK16" s="103">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="AM16" s="101">
+      <c r="AL16" s="104">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AN16" s="102">
+      <c r="AM16" s="102">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AO16" s="103">
+      <c r="AN16" s="103">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP16" s="101">
+      <c r="AO16" s="104">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AQ16" s="102">
+      <c r="AP16" s="102">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AR16" s="103">
+      <c r="AQ16" s="103">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AS16" s="101">
+      <c r="AR16" s="104">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AT16" s="102">
+      <c r="AS16" s="102">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AU16" s="103">
+      <c r="AT16" s="103">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AV16" s="11"/>
-    </row>
-    <row r="17" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A17" s="112" t="s">
+      <c r="AU16" s="104">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AV16" s="111"/>
+    </row>
+    <row r="17" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A17" s="116" t="s">
         <v>142</v>
       </c>
-      <c r="B17" s="109">
+      <c r="B17" s="112">
         <v>27</v>
       </c>
-      <c r="C17" s="83" cm="1">
-        <f t="array" ref="C17">SUMPRODUCT(ROUNDUP(D17:M17/B17,0))</f>
+      <c r="C17" s="83">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="D17" s="83">
         <f>'มหาชัย-ผลิต'!E22</f>
         <v>0</v>
       </c>
-      <c r="E17" s="83">
-        <f>'มหาชัย-ผลิต'!F22</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="101"/>
-      <c r="S17" s="102"/>
-      <c r="T17" s="103"/>
-      <c r="U17" s="101">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="102">
+      <c r="E17" s="83"/>
+      <c r="F17" s="100"/>
+      <c r="G17" s="100"/>
+      <c r="H17" s="100"/>
+      <c r="I17" s="100"/>
+      <c r="J17" s="100"/>
+      <c r="K17" s="100"/>
+      <c r="L17" s="100"/>
+      <c r="M17" s="100"/>
+      <c r="N17" s="100"/>
+      <c r="O17" s="100"/>
+      <c r="P17" s="100"/>
+      <c r="Q17" s="100"/>
+      <c r="R17" s="102"/>
+      <c r="S17" s="103"/>
+      <c r="T17" s="104"/>
+      <c r="U17" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W17" s="103">
+      <c r="V17" s="103">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="X17" s="101">
+      <c r="W17" s="104">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="102">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y17" s="102">
+      <c r="Y17" s="103">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Z17" s="103">
+      <c r="Z17" s="104">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA17" s="101">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AB17" s="102">
+      <c r="AA17" s="102">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AC17" s="103">
+      <c r="AB17" s="103">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AD17" s="101">
+      <c r="AC17" s="104">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AE17" s="102">
+      <c r="AD17" s="102">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AF17" s="103">
+      <c r="AE17" s="103">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AG17" s="101">
+      <c r="AF17" s="104">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AH17" s="102">
+      <c r="AG17" s="102">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AI17" s="103">
+      <c r="AH17" s="103">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ17" s="101">
+      <c r="AI17" s="104">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK17" s="102">
+      <c r="AJ17" s="102">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AL17" s="103">
+      <c r="AK17" s="103">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="AM17" s="101">
+      <c r="AL17" s="104">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AN17" s="102">
+      <c r="AM17" s="102">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AO17" s="103">
+      <c r="AN17" s="103">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP17" s="101">
+      <c r="AO17" s="104">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AQ17" s="102">
+      <c r="AP17" s="102">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AR17" s="103">
+      <c r="AQ17" s="103">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AS17" s="101">
+      <c r="AR17" s="104">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AT17" s="102">
+      <c r="AS17" s="102">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AU17" s="103">
+      <c r="AT17" s="103">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AV17" s="11"/>
-    </row>
-    <row r="18" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A18" s="113" t="s">
+      <c r="AU17" s="104">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AV17" s="100"/>
+    </row>
+    <row r="18" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A18" s="117" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="109">
+      <c r="B18" s="112">
         <v>36</v>
       </c>
-      <c r="C18" s="83" cm="1">
-        <f t="array" ref="C18">SUMPRODUCT(ROUNDUP(D18:M18/B18,0))</f>
+      <c r="C18" s="83">
+        <f>SUMPRODUCT(ROUNDUP(D18/B18,0))</f>
         <v>0</v>
       </c>
       <c r="D18" s="83">
         <f>'มหาชัย-ผลิต'!E24</f>
         <v>0</v>
       </c>
-      <c r="E18" s="83">
-        <f>'มหาชัย-ผลิต'!F24</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11" t="str">
-        <f t="shared" si="6"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="100"/>
+      <c r="G18" s="100"/>
+      <c r="H18" s="100"/>
+      <c r="I18" s="100"/>
+      <c r="J18" s="100"/>
+      <c r="K18" s="100"/>
+      <c r="L18" s="100"/>
+      <c r="M18" s="100"/>
+      <c r="N18" s="100" t="str">
+        <f t="shared" si="7"/>
         <v>0 full, 1 less than half</v>
       </c>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="101">
+      <c r="O18" s="100"/>
+      <c r="P18" s="100"/>
+      <c r="Q18" s="100"/>
+      <c r="R18" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S18" s="102">
+      <c r="S18" s="103">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T18" s="103">
+      <c r="T18" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U18" s="101">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V18" s="102">
+      <c r="U18" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W18" s="103">
+      <c r="V18" s="103">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="X18" s="101">
+      <c r="W18" s="104">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X18" s="102">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y18" s="102">
+      <c r="Y18" s="103">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Z18" s="103">
+      <c r="Z18" s="104">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA18" s="101">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AB18" s="102">
+      <c r="AA18" s="102">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AC18" s="103">
+      <c r="AB18" s="103">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AD18" s="101">
+      <c r="AC18" s="104">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AE18" s="102">
+      <c r="AD18" s="102">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AF18" s="103">
+      <c r="AE18" s="103">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AG18" s="101">
+      <c r="AF18" s="104">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AH18" s="102">
+      <c r="AG18" s="102">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AI18" s="103">
+      <c r="AH18" s="103">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ18" s="101">
+      <c r="AI18" s="104">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK18" s="102">
+      <c r="AJ18" s="102">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AL18" s="103">
+      <c r="AK18" s="103">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="AM18" s="101">
+      <c r="AL18" s="104">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AN18" s="102">
+      <c r="AM18" s="102">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AO18" s="103">
+      <c r="AN18" s="103">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP18" s="101">
+      <c r="AO18" s="104">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AQ18" s="102">
+      <c r="AP18" s="102">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AR18" s="103">
+      <c r="AQ18" s="103">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AS18" s="101">
+      <c r="AR18" s="104">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AT18" s="102">
+      <c r="AS18" s="102">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AU18" s="103">
+      <c r="AT18" s="103">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AV18" s="11"/>
-    </row>
-    <row r="19" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A19" s="110" t="s">
+      <c r="AU18" s="104">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AV18" s="100"/>
+    </row>
+    <row r="19" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A19" s="114" t="s">
         <v>114</v>
       </c>
-      <c r="B19" s="109">
+      <c r="B19" s="112">
         <v>20</v>
       </c>
-      <c r="C19" s="83" cm="1">
-        <f t="array" ref="C19">SUMPRODUCT(ROUNDUP(D19:M19/B19,0))</f>
+      <c r="C19" s="83">
+        <f>SUMPRODUCT(ROUNDUP(D19/B19,0))</f>
         <v>0</v>
       </c>
       <c r="D19" s="83">
         <f>'มหาชัย-ผลิต'!E26</f>
         <v>0</v>
       </c>
-      <c r="E19" s="83">
-        <f>'มหาชัย-ผลิต'!F26</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11" t="e">
+      <c r="E19" s="83"/>
+      <c r="F19" s="100"/>
+      <c r="G19" s="100"/>
+      <c r="H19" s="100"/>
+      <c r="I19" s="100"/>
+      <c r="J19" s="100"/>
+      <c r="K19" s="100"/>
+      <c r="L19" s="100"/>
+      <c r="M19" s="100"/>
+      <c r="N19" s="100" t="e">
         <f>'มหาชัย-ผลิต'!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="101">
-        <f t="shared" ref="R19" si="31">INT(D19/B19)</f>
-        <v>0</v>
-      </c>
-      <c r="S19" s="102">
-        <f t="shared" ref="S19" si="32">IF(MOD(D19,B19)/B19&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T19" s="103">
-        <f t="shared" ref="T19" si="33">IF(AND(MOD(D19,B19)/B19&lt;=0.5,MOD(D19,B19)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U19" s="101">
-        <f t="shared" ref="U19:U21" si="34">INT(E19/B19)</f>
-        <v>0</v>
-      </c>
-      <c r="V19" s="102">
-        <f t="shared" ref="V19:V21" si="35">IF(MOD(E19,B19)/B19&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="W19" s="103">
-        <f t="shared" ref="W19:W21" si="36">IF(AND(MOD(E19,B19)/B19&lt;=0.5,MOD(E19,B19)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X19" s="101">
-        <f t="shared" ref="X19:X21" si="37">INT(F19/B19)</f>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="102">
-        <f t="shared" ref="Y19:Y21" si="38">IF(MOD(F19,B19)/B19&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z19" s="103">
-        <f t="shared" ref="Z19:Z21" si="39">IF(AND(MOD(F19,B19)/B19&lt;=0.5,MOD(F19,B19)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AA19" s="101">
-        <f t="shared" ref="AA19:AA21" si="40">INT(G19/B19)</f>
-        <v>0</v>
-      </c>
-      <c r="AB19" s="102">
-        <f t="shared" ref="AB19:AB21" si="41">IF(MOD(G19,B19)/B19&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AC19" s="103">
-        <f t="shared" ref="AC19:AC21" si="42">IF(AND(MOD(G19,B19)/B19&lt;=0.5,MOD(G19,B19)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AD19" s="101">
-        <f t="shared" ref="AD19:AD21" si="43">INT(H19/B19)</f>
-        <v>0</v>
-      </c>
-      <c r="AE19" s="102">
-        <f t="shared" ref="AE19:AE21" si="44">IF(MOD(H19,B19)/B19&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF19" s="103">
-        <f t="shared" ref="AF19:AF21" si="45">IF(AND(MOD(H19,B19)/B19&lt;=0.5,MOD(H19,B19)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AG19" s="101">
-        <f t="shared" ref="AG19:AG21" si="46">INT(I19/B19)</f>
-        <v>0</v>
-      </c>
-      <c r="AH19" s="102">
-        <f t="shared" ref="AH19:AH21" si="47">IF(MOD(I19,B19)/B19&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AI19" s="103">
-        <f t="shared" ref="AI19:AI21" si="48">IF(AND(MOD(I19,B19)/B19&lt;=0.5,MOD(I19,B19)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ19" s="101">
-        <f t="shared" ref="AJ19:AJ21" si="49">INT(J19/B19)</f>
-        <v>0</v>
-      </c>
-      <c r="AK19" s="102">
-        <f t="shared" ref="AK19:AK21" si="50">IF(MOD(J19,B19)/B19&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AL19" s="103">
-        <f t="shared" ref="AL19:AL21" si="51">IF(AND(MOD(J19,B19)/B19&lt;=0.5,MOD(J19,B19)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AM19" s="101">
-        <f t="shared" ref="AM19:AM21" si="52">INT(K19/B19)</f>
-        <v>0</v>
-      </c>
-      <c r="AN19" s="102">
-        <f t="shared" ref="AN19:AN21" si="53">IF(MOD(K19,B19)/B19&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AO19" s="103">
-        <f t="shared" ref="AO19:AO21" si="54">IF(AND(MOD(K19,B19)/B19&lt;=0.5,MOD(K19,B19)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AP19" s="101">
-        <f t="shared" ref="AP19:AP21" si="55">INT(L19/B19)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ19" s="102">
-        <f t="shared" ref="AQ19:AQ21" si="56">IF(MOD(L19,B19)/B19&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AR19" s="103">
-        <f t="shared" ref="AR19:AR21" si="57">IF(AND(MOD(L19,B19)/B19&lt;=0.5,MOD(L19,B19)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AS19" s="101">
-        <f t="shared" ref="AS19:AS21" si="58">INT(M19/B19)</f>
-        <v>0</v>
-      </c>
-      <c r="AT19" s="102">
-        <f t="shared" ref="AT19:AT21" si="59">IF(MOD(M19,B19)/B19&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AU19" s="103">
-        <f t="shared" ref="AU19:AU21" si="60">IF(AND(MOD(M19,B19)/B19&lt;=0.5,MOD(M19,B19)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AV19" s="11"/>
-    </row>
-    <row r="20" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A20" s="113" t="s">
+      <c r="O19" s="100"/>
+      <c r="P19" s="100"/>
+      <c r="Q19" s="100"/>
+      <c r="R19" s="102">
+        <f t="shared" ref="R19" si="33">INT(D19/B19)</f>
+        <v>0</v>
+      </c>
+      <c r="S19" s="103">
+        <f t="shared" ref="S19" si="34">IF(MOD(D19,B19)/B19&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T19" s="104">
+        <f t="shared" ref="T19" si="35">IF(AND(MOD(D19,B19)/B19&lt;=0.5,MOD(D19,B19)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U19" s="102">
+        <f t="shared" ref="U19:U21" si="36">INT(E19/B19)</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="103">
+        <f t="shared" ref="V19:V21" si="37">IF(MOD(E19,B19)/B19&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W19" s="104">
+        <f t="shared" ref="W19:W21" si="38">IF(AND(MOD(E19,B19)/B19&lt;=0.5,MOD(E19,B19)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X19" s="102">
+        <f t="shared" ref="X19:X21" si="39">INT(F19/B19)</f>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="103">
+        <f t="shared" ref="Y19:Y21" si="40">IF(MOD(F19,B19)/B19&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="104">
+        <f t="shared" ref="Z19:Z21" si="41">IF(AND(MOD(F19,B19)/B19&lt;=0.5,MOD(F19,B19)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA19" s="102">
+        <f t="shared" ref="AA19:AA21" si="42">INT(G19/B19)</f>
+        <v>0</v>
+      </c>
+      <c r="AB19" s="103">
+        <f t="shared" ref="AB19:AB21" si="43">IF(MOD(G19,B19)/B19&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC19" s="104">
+        <f t="shared" ref="AC19:AC21" si="44">IF(AND(MOD(G19,B19)/B19&lt;=0.5,MOD(G19,B19)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD19" s="102">
+        <f t="shared" ref="AD19:AD21" si="45">INT(H19/B19)</f>
+        <v>0</v>
+      </c>
+      <c r="AE19" s="103">
+        <f t="shared" ref="AE19:AE21" si="46">IF(MOD(H19,B19)/B19&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="104">
+        <f t="shared" ref="AF19:AF21" si="47">IF(AND(MOD(H19,B19)/B19&lt;=0.5,MOD(H19,B19)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG19" s="102">
+        <f t="shared" ref="AG19:AG21" si="48">INT(I19/B19)</f>
+        <v>0</v>
+      </c>
+      <c r="AH19" s="103">
+        <f t="shared" ref="AH19:AH21" si="49">IF(MOD(I19,B19)/B19&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI19" s="104">
+        <f t="shared" ref="AI19:AI21" si="50">IF(AND(MOD(I19,B19)/B19&lt;=0.5,MOD(I19,B19)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="102">
+        <f t="shared" ref="AJ19:AJ21" si="51">INT(J19/B19)</f>
+        <v>0</v>
+      </c>
+      <c r="AK19" s="103">
+        <f t="shared" ref="AK19:AK21" si="52">IF(MOD(J19,B19)/B19&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL19" s="104">
+        <f t="shared" ref="AL19:AL21" si="53">IF(AND(MOD(J19,B19)/B19&lt;=0.5,MOD(J19,B19)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM19" s="102">
+        <f t="shared" ref="AM19:AM21" si="54">INT(K19/B19)</f>
+        <v>0</v>
+      </c>
+      <c r="AN19" s="103">
+        <f t="shared" ref="AN19:AN21" si="55">IF(MOD(K19,B19)/B19&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO19" s="104">
+        <f t="shared" ref="AO19:AO21" si="56">IF(AND(MOD(K19,B19)/B19&lt;=0.5,MOD(K19,B19)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP19" s="102">
+        <f t="shared" ref="AP19:AP21" si="57">INT(L19/B19)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ19" s="103">
+        <f t="shared" ref="AQ19:AQ21" si="58">IF(MOD(L19,B19)/B19&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR19" s="104">
+        <f t="shared" ref="AR19:AR21" si="59">IF(AND(MOD(L19,B19)/B19&lt;=0.5,MOD(L19,B19)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS19" s="102">
+        <f t="shared" ref="AS19:AS21" si="60">INT(M19/B19)</f>
+        <v>0</v>
+      </c>
+      <c r="AT19" s="103">
+        <f t="shared" ref="AT19:AT21" si="61">IF(MOD(M19,B19)/B19&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU19" s="104">
+        <f t="shared" ref="AU19:AU21" si="62">IF(AND(MOD(M19,B19)/B19&lt;=0.5,MOD(M19,B19)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV19" s="100"/>
+    </row>
+    <row r="20" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A20" s="117" t="s">
         <v>131</v>
       </c>
-      <c r="B20" s="109">
+      <c r="B20" s="112">
         <v>15</v>
       </c>
-      <c r="C20" s="83" cm="1">
-        <f t="array" ref="C20">SUMPRODUCT(ROUNDUP(D20:M20/B20,0))</f>
+      <c r="C20" s="83">
+        <f>SUMPRODUCT(ROUNDUP(D20/B20,0))</f>
         <v>0</v>
       </c>
       <c r="D20" s="83">
         <f>'มหาชัย-ผลิต'!E28</f>
         <v>0</v>
       </c>
-      <c r="E20" s="83">
-        <f>'มหาชัย-ผลิต'!F28</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="101"/>
-      <c r="S20" s="102"/>
-      <c r="T20" s="103"/>
-      <c r="U20" s="101">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="V20" s="102">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="W20" s="103">
+      <c r="E20" s="83"/>
+      <c r="F20" s="100"/>
+      <c r="G20" s="100"/>
+      <c r="H20" s="100"/>
+      <c r="I20" s="100"/>
+      <c r="J20" s="100"/>
+      <c r="K20" s="100"/>
+      <c r="L20" s="100"/>
+      <c r="M20" s="100"/>
+      <c r="N20" s="100"/>
+      <c r="O20" s="100"/>
+      <c r="P20" s="100"/>
+      <c r="Q20" s="100"/>
+      <c r="R20" s="102"/>
+      <c r="S20" s="103"/>
+      <c r="T20" s="104"/>
+      <c r="U20" s="102">
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="X20" s="101">
+      <c r="V20" s="103">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="Y20" s="102">
+      <c r="W20" s="104">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="Z20" s="103">
+      <c r="X20" s="102">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AA20" s="101">
+      <c r="Y20" s="103">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="AB20" s="102">
+      <c r="Z20" s="104">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="AC20" s="103">
+      <c r="AA20" s="102">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="AD20" s="101">
+      <c r="AB20" s="103">
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="AE20" s="102">
+      <c r="AC20" s="104">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="AF20" s="103">
+      <c r="AD20" s="102">
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="AG20" s="101">
+      <c r="AE20" s="103">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="AH20" s="102">
+      <c r="AF20" s="104">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
-      <c r="AI20" s="103">
+      <c r="AG20" s="102">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="AJ20" s="101">
+      <c r="AH20" s="103">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="AK20" s="102">
+      <c r="AI20" s="104">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="AL20" s="103">
+      <c r="AJ20" s="102">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
-      <c r="AM20" s="101">
+      <c r="AK20" s="103">
         <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="AN20" s="102">
+      <c r="AL20" s="104">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="AO20" s="103">
+      <c r="AM20" s="102">
         <f t="shared" si="54"/>
         <v>0</v>
       </c>
-      <c r="AP20" s="101">
+      <c r="AN20" s="103">
         <f t="shared" si="55"/>
         <v>0</v>
       </c>
-      <c r="AQ20" s="102">
+      <c r="AO20" s="104">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="AR20" s="103">
+      <c r="AP20" s="102">
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AS20" s="101">
+      <c r="AQ20" s="103">
         <f t="shared" si="58"/>
         <v>0</v>
       </c>
-      <c r="AT20" s="102">
+      <c r="AR20" s="104">
         <f t="shared" si="59"/>
         <v>0</v>
       </c>
-      <c r="AU20" s="103">
+      <c r="AS20" s="102">
         <f t="shared" si="60"/>
         <v>0</v>
       </c>
-      <c r="AV20" s="11"/>
-    </row>
-    <row r="21" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A21" s="113" t="s">
+      <c r="AT20" s="103">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="AU20" s="104">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="AV20" s="100"/>
+    </row>
+    <row r="21" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A21" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="B21" s="109">
+      <c r="B21" s="112">
         <v>45</v>
       </c>
-      <c r="C21" s="83" cm="1">
-        <f t="array" ref="C21">SUMPRODUCT(ROUNDUP(D21:M21/B21,0))</f>
+      <c r="C21" s="83">
+        <f t="shared" ref="C21" si="63">SUMPRODUCT(ROUNDUP(D21/B21,0))</f>
         <v>0</v>
       </c>
       <c r="D21" s="83">
         <f>'มหาชัย-ผลิต'!E30</f>
         <v>0</v>
       </c>
-      <c r="E21" s="83">
-        <f>'มหาชัย-ผลิต'!F30</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="11"/>
-      <c r="R21" s="101"/>
-      <c r="S21" s="102"/>
-      <c r="T21" s="103"/>
-      <c r="U21" s="101">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="V21" s="102">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="W21" s="103">
+      <c r="E21" s="83"/>
+      <c r="F21" s="100"/>
+      <c r="G21" s="100"/>
+      <c r="H21" s="100"/>
+      <c r="I21" s="100"/>
+      <c r="J21" s="100"/>
+      <c r="K21" s="100"/>
+      <c r="L21" s="100"/>
+      <c r="M21" s="100"/>
+      <c r="N21" s="100"/>
+      <c r="O21" s="100"/>
+      <c r="P21" s="100"/>
+      <c r="Q21" s="100"/>
+      <c r="R21" s="102"/>
+      <c r="S21" s="103"/>
+      <c r="T21" s="104"/>
+      <c r="U21" s="102">
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="X21" s="101">
+      <c r="V21" s="103">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="Y21" s="102">
+      <c r="W21" s="104">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="Z21" s="103">
+      <c r="X21" s="102">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="AA21" s="101">
+      <c r="Y21" s="103">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="AB21" s="102">
+      <c r="Z21" s="104">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="AC21" s="103">
+      <c r="AA21" s="102">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="AD21" s="101">
+      <c r="AB21" s="103">
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="AE21" s="102">
+      <c r="AC21" s="104">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="AF21" s="103">
+      <c r="AD21" s="102">
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="AG21" s="101">
+      <c r="AE21" s="103">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="AH21" s="102">
+      <c r="AF21" s="104">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
-      <c r="AI21" s="103">
+      <c r="AG21" s="102">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="AJ21" s="101">
+      <c r="AH21" s="103">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="AK21" s="102">
+      <c r="AI21" s="104">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="AL21" s="103">
+      <c r="AJ21" s="102">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
-      <c r="AM21" s="101">
+      <c r="AK21" s="103">
         <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="AN21" s="102">
+      <c r="AL21" s="104">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="AO21" s="103">
+      <c r="AM21" s="102">
         <f t="shared" si="54"/>
         <v>0</v>
       </c>
-      <c r="AP21" s="101">
+      <c r="AN21" s="103">
         <f t="shared" si="55"/>
         <v>0</v>
       </c>
-      <c r="AQ21" s="102">
+      <c r="AO21" s="104">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="AR21" s="103">
+      <c r="AP21" s="102">
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AS21" s="101">
+      <c r="AQ21" s="103">
         <f t="shared" si="58"/>
         <v>0</v>
       </c>
-      <c r="AT21" s="102">
+      <c r="AR21" s="104">
         <f t="shared" si="59"/>
         <v>0</v>
       </c>
-      <c r="AU21" s="103">
+      <c r="AS21" s="102">
         <f t="shared" si="60"/>
         <v>0</v>
       </c>
-      <c r="AV21" s="11"/>
-    </row>
-    <row r="22" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A22" s="113" t="s">
+      <c r="AT21" s="103">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="AU21" s="104">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="AV21" s="100"/>
+    </row>
+    <row r="22" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A22" s="117" t="s">
         <v>134</v>
       </c>
-      <c r="B22" s="109">
+      <c r="B22" s="112">
         <v>15</v>
       </c>
-      <c r="C22" s="83" cm="1">
-        <f t="array" ref="C22">SUMPRODUCT(ROUNDUP(D22:M22/B22,0))</f>
+      <c r="C22" s="83">
+        <f t="shared" ref="C22" si="64">SUMPRODUCT(ROUNDUP(D22/B22,0))</f>
         <v>0</v>
       </c>
       <c r="D22" s="83">
         <f>'มหาชัย-ผลิต'!E32</f>
         <v>0</v>
       </c>
-      <c r="E22" s="83">
-        <f>'มหาชัย-ผลิต'!F32</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="11"/>
-      <c r="R22" s="101"/>
-      <c r="S22" s="102"/>
-      <c r="T22" s="103"/>
-      <c r="U22" s="101">
-        <f t="shared" ref="U22" si="61">INT(E22/B22)</f>
-        <v>0</v>
-      </c>
-      <c r="V22" s="102">
-        <f t="shared" ref="V22" si="62">IF(MOD(E22,B22)/B22&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="W22" s="103">
-        <f t="shared" ref="W22" si="63">IF(AND(MOD(E22,B22)/B22&lt;=0.5,MOD(E22,B22)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X22" s="101">
-        <f t="shared" ref="X22" si="64">INT(F22/B22)</f>
-        <v>0</v>
-      </c>
-      <c r="Y22" s="102">
-        <f t="shared" ref="Y22" si="65">IF(MOD(F22,B22)/B22&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z22" s="103">
-        <f t="shared" ref="Z22" si="66">IF(AND(MOD(F22,B22)/B22&lt;=0.5,MOD(F22,B22)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AA22" s="101">
-        <f t="shared" ref="AA22" si="67">INT(G22/B22)</f>
-        <v>0</v>
-      </c>
-      <c r="AB22" s="102">
-        <f t="shared" ref="AB22" si="68">IF(MOD(G22,B22)/B22&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AC22" s="103">
-        <f t="shared" ref="AC22" si="69">IF(AND(MOD(G22,B22)/B22&lt;=0.5,MOD(G22,B22)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AD22" s="101">
-        <f t="shared" ref="AD22" si="70">INT(H22/B22)</f>
-        <v>0</v>
-      </c>
-      <c r="AE22" s="102">
-        <f t="shared" ref="AE22" si="71">IF(MOD(H22,B22)/B22&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF22" s="103">
-        <f t="shared" ref="AF22" si="72">IF(AND(MOD(H22,B22)/B22&lt;=0.5,MOD(H22,B22)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AG22" s="101">
-        <f t="shared" ref="AG22" si="73">INT(I22/B22)</f>
-        <v>0</v>
-      </c>
-      <c r="AH22" s="102">
-        <f t="shared" ref="AH22" si="74">IF(MOD(I22,B22)/B22&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AI22" s="103">
-        <f t="shared" ref="AI22" si="75">IF(AND(MOD(I22,B22)/B22&lt;=0.5,MOD(I22,B22)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ22" s="101">
-        <f t="shared" ref="AJ22" si="76">INT(J22/B22)</f>
-        <v>0</v>
-      </c>
-      <c r="AK22" s="102">
-        <f t="shared" ref="AK22" si="77">IF(MOD(J22,B22)/B22&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AL22" s="103">
-        <f t="shared" ref="AL22" si="78">IF(AND(MOD(J22,B22)/B22&lt;=0.5,MOD(J22,B22)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AM22" s="101">
-        <f t="shared" ref="AM22" si="79">INT(K22/B22)</f>
-        <v>0</v>
-      </c>
-      <c r="AN22" s="102">
-        <f t="shared" ref="AN22" si="80">IF(MOD(K22,B22)/B22&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AO22" s="103">
-        <f t="shared" ref="AO22" si="81">IF(AND(MOD(K22,B22)/B22&lt;=0.5,MOD(K22,B22)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AP22" s="101">
-        <f t="shared" ref="AP22" si="82">INT(L22/B22)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ22" s="102">
-        <f t="shared" ref="AQ22" si="83">IF(MOD(L22,B22)/B22&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AR22" s="103">
-        <f t="shared" ref="AR22" si="84">IF(AND(MOD(L22,B22)/B22&lt;=0.5,MOD(L22,B22)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AS22" s="101">
-        <f t="shared" ref="AS22" si="85">INT(M22/B22)</f>
-        <v>0</v>
-      </c>
-      <c r="AT22" s="102">
-        <f t="shared" ref="AT22" si="86">IF(MOD(M22,B22)/B22&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AU22" s="103">
-        <f t="shared" ref="AU22" si="87">IF(AND(MOD(M22,B22)/B22&lt;=0.5,MOD(M22,B22)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AV22" s="11"/>
-    </row>
-    <row r="23" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A23" s="113" t="s">
+      <c r="E22" s="83"/>
+      <c r="F22" s="105"/>
+      <c r="G22" s="105"/>
+      <c r="H22" s="105"/>
+      <c r="I22" s="105"/>
+      <c r="J22" s="105"/>
+      <c r="K22" s="105"/>
+      <c r="L22" s="105"/>
+      <c r="M22" s="105"/>
+      <c r="N22" s="105"/>
+      <c r="O22" s="105"/>
+      <c r="P22" s="105"/>
+      <c r="Q22" s="105"/>
+      <c r="R22" s="102"/>
+      <c r="S22" s="103"/>
+      <c r="T22" s="104"/>
+      <c r="U22" s="102">
+        <f t="shared" ref="U22" si="65">INT(E22/B22)</f>
+        <v>0</v>
+      </c>
+      <c r="V22" s="103">
+        <f t="shared" ref="V22" si="66">IF(MOD(E22,B22)/B22&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W22" s="104">
+        <f t="shared" ref="W22" si="67">IF(AND(MOD(E22,B22)/B22&lt;=0.5,MOD(E22,B22)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X22" s="102">
+        <f t="shared" ref="X22" si="68">INT(F22/B22)</f>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="103">
+        <f t="shared" ref="Y22" si="69">IF(MOD(F22,B22)/B22&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z22" s="104">
+        <f t="shared" ref="Z22" si="70">IF(AND(MOD(F22,B22)/B22&lt;=0.5,MOD(F22,B22)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA22" s="102">
+        <f t="shared" ref="AA22" si="71">INT(G22/B22)</f>
+        <v>0</v>
+      </c>
+      <c r="AB22" s="103">
+        <f t="shared" ref="AB22" si="72">IF(MOD(G22,B22)/B22&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC22" s="104">
+        <f t="shared" ref="AC22" si="73">IF(AND(MOD(G22,B22)/B22&lt;=0.5,MOD(G22,B22)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD22" s="102">
+        <f t="shared" ref="AD22" si="74">INT(H22/B22)</f>
+        <v>0</v>
+      </c>
+      <c r="AE22" s="103">
+        <f t="shared" ref="AE22" si="75">IF(MOD(H22,B22)/B22&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF22" s="104">
+        <f t="shared" ref="AF22" si="76">IF(AND(MOD(H22,B22)/B22&lt;=0.5,MOD(H22,B22)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG22" s="102">
+        <f t="shared" ref="AG22" si="77">INT(I22/B22)</f>
+        <v>0</v>
+      </c>
+      <c r="AH22" s="103">
+        <f t="shared" ref="AH22" si="78">IF(MOD(I22,B22)/B22&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI22" s="104">
+        <f t="shared" ref="AI22" si="79">IF(AND(MOD(I22,B22)/B22&lt;=0.5,MOD(I22,B22)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="102">
+        <f t="shared" ref="AJ22" si="80">INT(J22/B22)</f>
+        <v>0</v>
+      </c>
+      <c r="AK22" s="103">
+        <f t="shared" ref="AK22" si="81">IF(MOD(J22,B22)/B22&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL22" s="104">
+        <f t="shared" ref="AL22" si="82">IF(AND(MOD(J22,B22)/B22&lt;=0.5,MOD(J22,B22)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM22" s="102">
+        <f t="shared" ref="AM22" si="83">INT(K22/B22)</f>
+        <v>0</v>
+      </c>
+      <c r="AN22" s="103">
+        <f t="shared" ref="AN22" si="84">IF(MOD(K22,B22)/B22&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO22" s="104">
+        <f t="shared" ref="AO22" si="85">IF(AND(MOD(K22,B22)/B22&lt;=0.5,MOD(K22,B22)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP22" s="102">
+        <f t="shared" ref="AP22" si="86">INT(L22/B22)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="103">
+        <f t="shared" ref="AQ22" si="87">IF(MOD(L22,B22)/B22&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR22" s="104">
+        <f t="shared" ref="AR22" si="88">IF(AND(MOD(L22,B22)/B22&lt;=0.5,MOD(L22,B22)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS22" s="102">
+        <f t="shared" ref="AS22" si="89">INT(M22/B22)</f>
+        <v>0</v>
+      </c>
+      <c r="AT22" s="103">
+        <f t="shared" ref="AT22" si="90">IF(MOD(M22,B22)/B22&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU22" s="104">
+        <f t="shared" ref="AU22" si="91">IF(AND(MOD(M22,B22)/B22&lt;=0.5,MOD(M22,B22)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV22" s="105"/>
+    </row>
+    <row r="23" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A23" s="117" t="s">
         <v>66</v>
       </c>
-      <c r="B23" s="109">
+      <c r="B23" s="112">
         <v>15</v>
       </c>
-      <c r="C23" s="83" cm="1">
-        <f t="array" ref="C23">SUMPRODUCT(ROUNDUP(D23:M23/B23,0))</f>
+      <c r="C23" s="83">
+        <f t="shared" ref="C23:C24" si="92">SUMPRODUCT(ROUNDUP(D23/B23,0))</f>
         <v>0</v>
       </c>
       <c r="D23" s="83">
         <f>'มหาชัย-ผลิต'!E34</f>
         <v>0</v>
       </c>
-      <c r="E23" s="83">
-        <f>'มหาชัย-ผลิต'!F34</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11" t="e">
+      <c r="E23" s="83"/>
+      <c r="F23" s="100"/>
+      <c r="G23" s="100"/>
+      <c r="H23" s="100"/>
+      <c r="I23" s="100"/>
+      <c r="J23" s="100"/>
+      <c r="K23" s="100"/>
+      <c r="L23" s="100"/>
+      <c r="M23" s="100"/>
+      <c r="N23" s="100" t="e">
         <f>'มหาชัย-ผลิต'!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="11"/>
-      <c r="R23" s="101">
+      <c r="O23" s="100"/>
+      <c r="P23" s="100"/>
+      <c r="Q23" s="100"/>
+      <c r="R23" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S23" s="102">
+      <c r="S23" s="103">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T23" s="103">
+      <c r="T23" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U23" s="101">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V23" s="102">
+      <c r="U23" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W23" s="103">
+      <c r="V23" s="103">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="X23" s="101">
+      <c r="W23" s="104">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X23" s="102">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y23" s="102">
+      <c r="Y23" s="103">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Z23" s="103">
+      <c r="Z23" s="104">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA23" s="101">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AB23" s="102">
+      <c r="AA23" s="102">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AC23" s="103">
+      <c r="AB23" s="103">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AD23" s="101">
+      <c r="AC23" s="104">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AE23" s="102">
+      <c r="AD23" s="102">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AF23" s="103">
+      <c r="AE23" s="103">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AG23" s="101">
+      <c r="AF23" s="104">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AH23" s="102">
+      <c r="AG23" s="102">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AI23" s="103">
+      <c r="AH23" s="103">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ23" s="101">
+      <c r="AI23" s="104">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK23" s="102">
+      <c r="AJ23" s="102">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AL23" s="103">
+      <c r="AK23" s="103">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="AM23" s="101">
+      <c r="AL23" s="104">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AN23" s="102">
+      <c r="AM23" s="102">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AO23" s="103">
+      <c r="AN23" s="103">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP23" s="101">
+      <c r="AO23" s="104">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AQ23" s="102">
+      <c r="AP23" s="102">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AR23" s="103">
+      <c r="AQ23" s="103">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AS23" s="101">
+      <c r="AR23" s="104">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AT23" s="102">
+      <c r="AS23" s="102">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AU23" s="103">
+      <c r="AT23" s="103">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AV23" s="11"/>
-    </row>
-    <row r="24" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A24" s="113" t="s">
+      <c r="AU23" s="104">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AV23" s="100"/>
+    </row>
+    <row r="24" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A24" s="117" t="s">
         <v>132</v>
       </c>
-      <c r="B24" s="109">
+      <c r="B24" s="112">
         <v>27</v>
       </c>
-      <c r="C24" s="83" cm="1">
-        <f t="array" ref="C24">SUMPRODUCT(ROUNDUP(D24:M24/B24,0))</f>
+      <c r="C24" s="83">
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="D24" s="83">
         <f>'มหาชัย-ผลิต'!E36</f>
         <v>0</v>
       </c>
-      <c r="E24" s="83">
-        <f>'มหาชัย-ผลิต'!F36</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="11"/>
-      <c r="R24" s="101"/>
-      <c r="S24" s="102"/>
-      <c r="T24" s="103"/>
-      <c r="U24" s="101">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V24" s="102">
+      <c r="E24" s="83"/>
+      <c r="F24" s="100"/>
+      <c r="G24" s="100"/>
+      <c r="H24" s="100"/>
+      <c r="I24" s="100"/>
+      <c r="J24" s="100"/>
+      <c r="K24" s="100"/>
+      <c r="L24" s="100"/>
+      <c r="M24" s="100"/>
+      <c r="N24" s="100"/>
+      <c r="O24" s="100"/>
+      <c r="P24" s="100"/>
+      <c r="Q24" s="100"/>
+      <c r="R24" s="102"/>
+      <c r="S24" s="103"/>
+      <c r="T24" s="104"/>
+      <c r="U24" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W24" s="103">
+      <c r="V24" s="103">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="X24" s="101">
+      <c r="W24" s="104">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X24" s="102">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y24" s="102">
+      <c r="Y24" s="103">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Z24" s="103">
+      <c r="Z24" s="104">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA24" s="101">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AB24" s="102">
+      <c r="AA24" s="102">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AC24" s="103">
+      <c r="AB24" s="103">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AD24" s="101">
+      <c r="AC24" s="104">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AE24" s="102">
+      <c r="AD24" s="102">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AF24" s="103">
+      <c r="AE24" s="103">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AG24" s="101">
+      <c r="AF24" s="104">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AH24" s="102">
+      <c r="AG24" s="102">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AI24" s="103">
+      <c r="AH24" s="103">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ24" s="101">
+      <c r="AI24" s="104">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK24" s="102">
+      <c r="AJ24" s="102">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AL24" s="103">
+      <c r="AK24" s="103">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="AM24" s="101">
+      <c r="AL24" s="104">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AN24" s="102">
+      <c r="AM24" s="102">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AO24" s="103">
+      <c r="AN24" s="103">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AP24" s="101">
+      <c r="AO24" s="104">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AQ24" s="102">
+      <c r="AP24" s="102">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AR24" s="103">
+      <c r="AQ24" s="103">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AS24" s="101">
+      <c r="AR24" s="104">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AT24" s="102">
+      <c r="AS24" s="102">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AU24" s="103">
+      <c r="AT24" s="103">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AV24" s="11"/>
-    </row>
-    <row r="25" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A25" s="113" t="s">
+      <c r="AU24" s="104">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AV24" s="100"/>
+    </row>
+    <row r="25" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A25" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="B25" s="109">
+      <c r="B25" s="112">
         <v>20</v>
       </c>
-      <c r="C25" s="83" cm="1">
-        <f t="array" ref="C25">SUMPRODUCT(ROUNDUP(D25:M25/B25,0))</f>
+      <c r="C25" s="83">
+        <f t="shared" ref="C25:C27" si="93">SUMPRODUCT(ROUNDUP(D25/B25,0))</f>
         <v>0</v>
       </c>
       <c r="D25" s="83">
         <f>'มหาชัย-ผลิต'!E38</f>
         <v>0</v>
       </c>
-      <c r="E25" s="83">
-        <f>'มหาชัย-ผลิต'!F38</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="11"/>
-      <c r="R25" s="101"/>
-      <c r="S25" s="102"/>
-      <c r="T25" s="103"/>
-      <c r="U25" s="101">
-        <f t="shared" ref="U25" si="88">INT(E25/B25)</f>
-        <v>0</v>
-      </c>
-      <c r="V25" s="102">
-        <f t="shared" ref="V25" si="89">IF(MOD(E25,B25)/B25&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="W25" s="103">
-        <f t="shared" ref="W25" si="90">IF(AND(MOD(E25,B25)/B25&lt;=0.5,MOD(E25,B25)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X25" s="101">
-        <f t="shared" ref="X25" si="91">INT(F25/B25)</f>
-        <v>0</v>
-      </c>
-      <c r="Y25" s="102">
-        <f t="shared" ref="Y25" si="92">IF(MOD(F25,B25)/B25&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z25" s="103">
-        <f t="shared" ref="Z25" si="93">IF(AND(MOD(F25,B25)/B25&lt;=0.5,MOD(F25,B25)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AA25" s="101">
-        <f t="shared" ref="AA25" si="94">INT(G25/B25)</f>
-        <v>0</v>
-      </c>
-      <c r="AB25" s="102">
-        <f t="shared" ref="AB25" si="95">IF(MOD(G25,B25)/B25&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AC25" s="103">
-        <f t="shared" ref="AC25" si="96">IF(AND(MOD(G25,B25)/B25&lt;=0.5,MOD(G25,B25)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AD25" s="101">
-        <f t="shared" ref="AD25" si="97">INT(H25/B25)</f>
-        <v>0</v>
-      </c>
-      <c r="AE25" s="102">
-        <f t="shared" ref="AE25" si="98">IF(MOD(H25,B25)/B25&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF25" s="103">
-        <f t="shared" ref="AF25" si="99">IF(AND(MOD(H25,B25)/B25&lt;=0.5,MOD(H25,B25)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AG25" s="101">
-        <f t="shared" ref="AG25" si="100">INT(I25/B25)</f>
-        <v>0</v>
-      </c>
-      <c r="AH25" s="102">
-        <f t="shared" ref="AH25" si="101">IF(MOD(I25,B25)/B25&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AI25" s="103">
-        <f t="shared" ref="AI25" si="102">IF(AND(MOD(I25,B25)/B25&lt;=0.5,MOD(I25,B25)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ25" s="101">
-        <f t="shared" ref="AJ25" si="103">INT(J25/B25)</f>
-        <v>0</v>
-      </c>
-      <c r="AK25" s="102">
-        <f t="shared" ref="AK25" si="104">IF(MOD(J25,B25)/B25&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AL25" s="103">
-        <f t="shared" ref="AL25" si="105">IF(AND(MOD(J25,B25)/B25&lt;=0.5,MOD(J25,B25)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AM25" s="101">
-        <f t="shared" ref="AM25" si="106">INT(K25/B25)</f>
-        <v>0</v>
-      </c>
-      <c r="AN25" s="102">
-        <f t="shared" ref="AN25" si="107">IF(MOD(K25,B25)/B25&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AO25" s="103">
-        <f t="shared" ref="AO25" si="108">IF(AND(MOD(K25,B25)/B25&lt;=0.5,MOD(K25,B25)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AP25" s="101">
-        <f t="shared" ref="AP25" si="109">INT(L25/B25)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ25" s="102">
-        <f t="shared" ref="AQ25" si="110">IF(MOD(L25,B25)/B25&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AR25" s="103">
-        <f t="shared" ref="AR25" si="111">IF(AND(MOD(L25,B25)/B25&lt;=0.5,MOD(L25,B25)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AS25" s="101">
-        <f t="shared" ref="AS25" si="112">INT(M25/B25)</f>
-        <v>0</v>
-      </c>
-      <c r="AT25" s="102">
-        <f t="shared" ref="AT25" si="113">IF(MOD(M25,B25)/B25&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AU25" s="103">
-        <f t="shared" ref="AU25" si="114">IF(AND(MOD(M25,B25)/B25&lt;=0.5,MOD(M25,B25)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AV25" s="11"/>
-    </row>
-    <row r="26" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A26" s="112" t="s">
+      <c r="E25" s="83"/>
+      <c r="F25" s="100"/>
+      <c r="G25" s="100"/>
+      <c r="H25" s="100"/>
+      <c r="I25" s="100"/>
+      <c r="J25" s="100"/>
+      <c r="K25" s="100"/>
+      <c r="L25" s="100"/>
+      <c r="M25" s="100"/>
+      <c r="N25" s="100"/>
+      <c r="O25" s="100"/>
+      <c r="P25" s="100"/>
+      <c r="Q25" s="100"/>
+      <c r="R25" s="102"/>
+      <c r="S25" s="103"/>
+      <c r="T25" s="104"/>
+      <c r="U25" s="102">
+        <f t="shared" ref="U25" si="94">INT(E25/B25)</f>
+        <v>0</v>
+      </c>
+      <c r="V25" s="103">
+        <f t="shared" ref="V25" si="95">IF(MOD(E25,B25)/B25&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W25" s="104">
+        <f t="shared" ref="W25" si="96">IF(AND(MOD(E25,B25)/B25&lt;=0.5,MOD(E25,B25)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X25" s="102">
+        <f t="shared" ref="X25" si="97">INT(F25/B25)</f>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="103">
+        <f t="shared" ref="Y25" si="98">IF(MOD(F25,B25)/B25&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z25" s="104">
+        <f t="shared" ref="Z25" si="99">IF(AND(MOD(F25,B25)/B25&lt;=0.5,MOD(F25,B25)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA25" s="102">
+        <f t="shared" ref="AA25" si="100">INT(G25/B25)</f>
+        <v>0</v>
+      </c>
+      <c r="AB25" s="103">
+        <f t="shared" ref="AB25" si="101">IF(MOD(G25,B25)/B25&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC25" s="104">
+        <f t="shared" ref="AC25" si="102">IF(AND(MOD(G25,B25)/B25&lt;=0.5,MOD(G25,B25)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD25" s="102">
+        <f t="shared" ref="AD25" si="103">INT(H25/B25)</f>
+        <v>0</v>
+      </c>
+      <c r="AE25" s="103">
+        <f t="shared" ref="AE25" si="104">IF(MOD(H25,B25)/B25&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF25" s="104">
+        <f t="shared" ref="AF25" si="105">IF(AND(MOD(H25,B25)/B25&lt;=0.5,MOD(H25,B25)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG25" s="102">
+        <f t="shared" ref="AG25" si="106">INT(I25/B25)</f>
+        <v>0</v>
+      </c>
+      <c r="AH25" s="103">
+        <f t="shared" ref="AH25" si="107">IF(MOD(I25,B25)/B25&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI25" s="104">
+        <f t="shared" ref="AI25" si="108">IF(AND(MOD(I25,B25)/B25&lt;=0.5,MOD(I25,B25)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="102">
+        <f t="shared" ref="AJ25" si="109">INT(J25/B25)</f>
+        <v>0</v>
+      </c>
+      <c r="AK25" s="103">
+        <f t="shared" ref="AK25" si="110">IF(MOD(J25,B25)/B25&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL25" s="104">
+        <f t="shared" ref="AL25" si="111">IF(AND(MOD(J25,B25)/B25&lt;=0.5,MOD(J25,B25)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM25" s="102">
+        <f t="shared" ref="AM25" si="112">INT(K25/B25)</f>
+        <v>0</v>
+      </c>
+      <c r="AN25" s="103">
+        <f t="shared" ref="AN25" si="113">IF(MOD(K25,B25)/B25&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO25" s="104">
+        <f t="shared" ref="AO25" si="114">IF(AND(MOD(K25,B25)/B25&lt;=0.5,MOD(K25,B25)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP25" s="102">
+        <f t="shared" ref="AP25" si="115">INT(L25/B25)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="103">
+        <f t="shared" ref="AQ25" si="116">IF(MOD(L25,B25)/B25&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR25" s="104">
+        <f t="shared" ref="AR25" si="117">IF(AND(MOD(L25,B25)/B25&lt;=0.5,MOD(L25,B25)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS25" s="102">
+        <f t="shared" ref="AS25" si="118">INT(M25/B25)</f>
+        <v>0</v>
+      </c>
+      <c r="AT25" s="103">
+        <f t="shared" ref="AT25" si="119">IF(MOD(M25,B25)/B25&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU25" s="104">
+        <f t="shared" ref="AU25" si="120">IF(AND(MOD(M25,B25)/B25&lt;=0.5,MOD(M25,B25)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV25" s="100"/>
+    </row>
+    <row r="26" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A26" s="116" t="s">
         <v>69</v>
       </c>
-      <c r="B26" s="109">
+      <c r="B26" s="112">
         <v>32</v>
       </c>
-      <c r="C26" s="83" cm="1">
-        <f t="array" ref="C26">SUMPRODUCT(ROUNDUP(D26:M26/B26,0))</f>
+      <c r="C26" s="83">
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="D26" s="83">
         <f>'มหาชัย-ผลิต'!E40</f>
         <v>0</v>
       </c>
-      <c r="E26" s="83">
-        <f>'มหาชัย-ผลิต'!F40</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
-      <c r="Q26" s="11"/>
-      <c r="R26" s="101"/>
-      <c r="S26" s="102"/>
-      <c r="T26" s="103"/>
-      <c r="U26" s="101"/>
-      <c r="V26" s="102"/>
-      <c r="W26" s="103"/>
-      <c r="X26" s="101"/>
-      <c r="Y26" s="102"/>
-      <c r="Z26" s="103"/>
-      <c r="AA26" s="101"/>
-      <c r="AB26" s="102"/>
-      <c r="AC26" s="103"/>
-      <c r="AD26" s="101"/>
-      <c r="AE26" s="102"/>
-      <c r="AF26" s="103"/>
-      <c r="AG26" s="101"/>
-      <c r="AH26" s="102"/>
-      <c r="AI26" s="103"/>
-      <c r="AJ26" s="101"/>
-      <c r="AK26" s="102"/>
-      <c r="AL26" s="103"/>
-      <c r="AM26" s="101"/>
-      <c r="AN26" s="102"/>
-      <c r="AO26" s="103"/>
-      <c r="AP26" s="101"/>
-      <c r="AQ26" s="102"/>
-      <c r="AR26" s="103"/>
-      <c r="AS26" s="101"/>
-      <c r="AT26" s="102"/>
-      <c r="AU26" s="103"/>
-      <c r="AV26" s="11"/>
-    </row>
-    <row r="27" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A27" s="110" t="s">
+      <c r="E26" s="83"/>
+      <c r="F26" s="100"/>
+      <c r="G26" s="100"/>
+      <c r="H26" s="100"/>
+      <c r="I26" s="100"/>
+      <c r="J26" s="100"/>
+      <c r="K26" s="100"/>
+      <c r="L26" s="100"/>
+      <c r="M26" s="100"/>
+      <c r="N26" s="100"/>
+      <c r="O26" s="100"/>
+      <c r="P26" s="100"/>
+      <c r="Q26" s="100"/>
+      <c r="R26" s="102"/>
+      <c r="S26" s="103"/>
+      <c r="T26" s="104"/>
+      <c r="U26" s="102"/>
+      <c r="V26" s="103"/>
+      <c r="W26" s="104"/>
+      <c r="X26" s="102"/>
+      <c r="Y26" s="103"/>
+      <c r="Z26" s="104"/>
+      <c r="AA26" s="102"/>
+      <c r="AB26" s="103"/>
+      <c r="AC26" s="104"/>
+      <c r="AD26" s="102"/>
+      <c r="AE26" s="103"/>
+      <c r="AF26" s="104"/>
+      <c r="AG26" s="102"/>
+      <c r="AH26" s="103"/>
+      <c r="AI26" s="104"/>
+      <c r="AJ26" s="102"/>
+      <c r="AK26" s="103"/>
+      <c r="AL26" s="104"/>
+      <c r="AM26" s="102"/>
+      <c r="AN26" s="103"/>
+      <c r="AO26" s="104"/>
+      <c r="AP26" s="102"/>
+      <c r="AQ26" s="103"/>
+      <c r="AR26" s="104"/>
+      <c r="AS26" s="102"/>
+      <c r="AT26" s="103"/>
+      <c r="AU26" s="104"/>
+      <c r="AV26" s="100"/>
+    </row>
+    <row r="27" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A27" s="114" t="s">
         <v>113</v>
       </c>
-      <c r="B27" s="109">
+      <c r="B27" s="112">
         <v>15</v>
       </c>
-      <c r="C27" s="83" cm="1">
-        <f t="array" ref="C27">SUMPRODUCT(ROUNDUP(D27:M27/B27,0))</f>
+      <c r="C27" s="83">
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="D27" s="83">
         <f>'มหาชัย-ผลิต'!E42</f>
         <v>0</v>
       </c>
-      <c r="E27" s="83">
-        <f>'มหาชัย-ผลิต'!F42</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="11"/>
-      <c r="P27" s="11"/>
-      <c r="Q27" s="11"/>
-      <c r="R27" s="101"/>
-      <c r="S27" s="102"/>
-      <c r="T27" s="103"/>
-      <c r="U27" s="101"/>
-      <c r="V27" s="102"/>
-      <c r="W27" s="103"/>
-      <c r="X27" s="101"/>
-      <c r="Y27" s="102"/>
-      <c r="Z27" s="103"/>
-      <c r="AA27" s="101"/>
-      <c r="AB27" s="102"/>
-      <c r="AC27" s="103"/>
-      <c r="AD27" s="101"/>
-      <c r="AE27" s="102"/>
-      <c r="AF27" s="103"/>
-      <c r="AG27" s="101"/>
-      <c r="AH27" s="102"/>
-      <c r="AI27" s="103"/>
-      <c r="AJ27" s="101"/>
-      <c r="AK27" s="102"/>
-      <c r="AL27" s="103"/>
-      <c r="AM27" s="101"/>
-      <c r="AN27" s="102"/>
-      <c r="AO27" s="103"/>
-      <c r="AP27" s="101"/>
-      <c r="AQ27" s="102"/>
-      <c r="AR27" s="103"/>
-      <c r="AS27" s="101"/>
-      <c r="AT27" s="102"/>
-      <c r="AU27" s="103"/>
-      <c r="AV27" s="11"/>
-    </row>
-    <row r="28" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A28" s="110" t="s">
+      <c r="E27" s="83"/>
+      <c r="F27" s="100"/>
+      <c r="G27" s="100"/>
+      <c r="H27" s="100"/>
+      <c r="I27" s="100"/>
+      <c r="J27" s="100"/>
+      <c r="K27" s="100"/>
+      <c r="L27" s="100"/>
+      <c r="M27" s="100"/>
+      <c r="N27" s="100"/>
+      <c r="O27" s="100"/>
+      <c r="P27" s="100"/>
+      <c r="Q27" s="100"/>
+      <c r="R27" s="102"/>
+      <c r="S27" s="103"/>
+      <c r="T27" s="104"/>
+      <c r="U27" s="102"/>
+      <c r="V27" s="103"/>
+      <c r="W27" s="104"/>
+      <c r="X27" s="102"/>
+      <c r="Y27" s="103"/>
+      <c r="Z27" s="104"/>
+      <c r="AA27" s="102"/>
+      <c r="AB27" s="103"/>
+      <c r="AC27" s="104"/>
+      <c r="AD27" s="102"/>
+      <c r="AE27" s="103"/>
+      <c r="AF27" s="104"/>
+      <c r="AG27" s="102"/>
+      <c r="AH27" s="103"/>
+      <c r="AI27" s="104"/>
+      <c r="AJ27" s="102"/>
+      <c r="AK27" s="103"/>
+      <c r="AL27" s="104"/>
+      <c r="AM27" s="102"/>
+      <c r="AN27" s="103"/>
+      <c r="AO27" s="104"/>
+      <c r="AP27" s="102"/>
+      <c r="AQ27" s="103"/>
+      <c r="AR27" s="104"/>
+      <c r="AS27" s="102"/>
+      <c r="AT27" s="103"/>
+      <c r="AU27" s="104"/>
+      <c r="AV27" s="100"/>
+    </row>
+    <row r="28" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A28" s="114" t="s">
         <v>146</v>
       </c>
-      <c r="B28" s="109">
+      <c r="B28" s="112">
         <v>8</v>
       </c>
-      <c r="C28" s="83" cm="1">
-        <f t="array" ref="C28">SUMPRODUCT(ROUNDUP(D28:M28/B28,0))</f>
-        <v>14</v>
+      <c r="C28" s="83">
+        <f t="shared" ref="C28" si="121">SUMPRODUCT(ROUNDUP(D28/B28,0))</f>
+        <v>0</v>
       </c>
       <c r="D28" s="83">
         <f>'มหาชัย-ผลิต'!E44</f>
-        <v>50</v>
-      </c>
-      <c r="E28" s="83">
-        <f>'มหาชัย-ผลิต'!F44</f>
-        <v>50</v>
-      </c>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="11"/>
-      <c r="O28" s="11"/>
-      <c r="P28" s="11"/>
-      <c r="Q28" s="11"/>
-      <c r="R28" s="101"/>
-      <c r="S28" s="102"/>
-      <c r="T28" s="103"/>
-      <c r="U28" s="101"/>
-      <c r="V28" s="102"/>
-      <c r="W28" s="103"/>
-      <c r="X28" s="101"/>
-      <c r="Y28" s="102"/>
-      <c r="Z28" s="103"/>
-      <c r="AA28" s="101"/>
-      <c r="AB28" s="102"/>
-      <c r="AC28" s="103"/>
-      <c r="AD28" s="101"/>
-      <c r="AE28" s="102"/>
-      <c r="AF28" s="103"/>
-      <c r="AG28" s="101"/>
-      <c r="AH28" s="102"/>
-      <c r="AI28" s="103"/>
-      <c r="AJ28" s="101"/>
-      <c r="AK28" s="102"/>
-      <c r="AL28" s="103"/>
-      <c r="AM28" s="101"/>
-      <c r="AN28" s="102"/>
-      <c r="AO28" s="103"/>
-      <c r="AP28" s="101"/>
-      <c r="AQ28" s="102"/>
-      <c r="AR28" s="103"/>
-      <c r="AS28" s="101"/>
-      <c r="AT28" s="102"/>
-      <c r="AU28" s="103"/>
-      <c r="AV28" s="11"/>
-    </row>
-    <row r="29" spans="1:48" s="23" customFormat="1" ht="25.2" customHeight="1">
-      <c r="A29" s="189" t="s">
+        <v>0</v>
+      </c>
+      <c r="E28" s="83"/>
+      <c r="F28" s="133"/>
+      <c r="G28" s="133"/>
+      <c r="H28" s="133"/>
+      <c r="I28" s="133"/>
+      <c r="J28" s="133"/>
+      <c r="K28" s="133"/>
+      <c r="L28" s="133"/>
+      <c r="M28" s="133"/>
+      <c r="N28" s="133"/>
+      <c r="O28" s="133"/>
+      <c r="P28" s="133"/>
+      <c r="Q28" s="133"/>
+      <c r="R28" s="102"/>
+      <c r="S28" s="103"/>
+      <c r="T28" s="104"/>
+      <c r="U28" s="102"/>
+      <c r="V28" s="103"/>
+      <c r="W28" s="104"/>
+      <c r="X28" s="102"/>
+      <c r="Y28" s="103"/>
+      <c r="Z28" s="104"/>
+      <c r="AA28" s="102"/>
+      <c r="AB28" s="103"/>
+      <c r="AC28" s="104"/>
+      <c r="AD28" s="102"/>
+      <c r="AE28" s="103"/>
+      <c r="AF28" s="104"/>
+      <c r="AG28" s="102"/>
+      <c r="AH28" s="103"/>
+      <c r="AI28" s="104"/>
+      <c r="AJ28" s="102"/>
+      <c r="AK28" s="103"/>
+      <c r="AL28" s="104"/>
+      <c r="AM28" s="102"/>
+      <c r="AN28" s="103"/>
+      <c r="AO28" s="104"/>
+      <c r="AP28" s="102"/>
+      <c r="AQ28" s="103"/>
+      <c r="AR28" s="104"/>
+      <c r="AS28" s="102"/>
+      <c r="AT28" s="103"/>
+      <c r="AU28" s="104"/>
+      <c r="AV28" s="133"/>
+    </row>
+    <row r="29" spans="1:48" s="23" customFormat="1" ht="25.15" customHeight="1">
+      <c r="A29" s="201" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="190"/>
+      <c r="B29" s="202"/>
       <c r="C29" s="99">
         <f>SUM(C10:C28)</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D29" s="61">
         <f>SUM(D30:D32)*-1</f>
-        <v>-2</v>
-      </c>
-      <c r="E29" s="61">
-        <f>SUM(E30:E32)*-1</f>
-        <v>-2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E29" s="21"/>
       <c r="F29" s="21"/>
       <c r="G29" s="21"/>
       <c r="H29" s="21"/>
@@ -7146,46 +6897,40 @@
       <c r="AV29" s="22"/>
     </row>
     <row r="30" spans="1:48" ht="21" customHeight="1">
-      <c r="A30" s="183" t="s">
+      <c r="A30" s="203" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="183"/>
-      <c r="C30" s="183"/>
-      <c r="D30" s="100">
+      <c r="B30" s="203"/>
+      <c r="C30" s="203"/>
+      <c r="D30" s="101">
         <f>SUM(R10:R23)</f>
-        <v>1</v>
-      </c>
-      <c r="E30" s="100">
-        <f>SUM(S10:S23)</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="100"/>
-      <c r="G30" s="100"/>
-      <c r="H30" s="100"/>
-      <c r="I30" s="100"/>
-      <c r="J30" s="100"/>
-      <c r="K30" s="100"/>
-      <c r="L30" s="100"/>
-      <c r="M30" s="100"/>
-      <c r="N30" s="100"/>
-      <c r="O30" s="100"/>
-      <c r="P30" s="100"/>
-      <c r="Q30" s="100"/>
+        <v>0</v>
+      </c>
+      <c r="E30" s="101"/>
+      <c r="F30" s="101"/>
+      <c r="G30" s="101"/>
+      <c r="H30" s="101"/>
+      <c r="I30" s="101"/>
+      <c r="J30" s="101"/>
+      <c r="K30" s="101"/>
+      <c r="L30" s="101"/>
+      <c r="M30" s="101"/>
+      <c r="N30" s="101"/>
+      <c r="O30" s="101"/>
+      <c r="P30" s="101"/>
+      <c r="Q30" s="101"/>
     </row>
     <row r="31" spans="1:48" ht="21" customHeight="1">
-      <c r="A31" s="191" t="s">
+      <c r="A31" s="198" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="191"/>
-      <c r="C31" s="191"/>
+      <c r="B31" s="198"/>
+      <c r="C31" s="198"/>
       <c r="D31" s="11">
         <f>SUM(S10:S23)</f>
         <v>0</v>
       </c>
-      <c r="E31" s="11">
-        <f>SUM(T10:T23)</f>
-        <v>1</v>
-      </c>
+      <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
@@ -7200,19 +6945,16 @@
       <c r="Q31" s="11"/>
     </row>
     <row r="32" spans="1:48" ht="21" customHeight="1">
-      <c r="A32" s="191" t="s">
+      <c r="A32" s="198" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="191"/>
-      <c r="C32" s="191"/>
+      <c r="B32" s="198"/>
+      <c r="C32" s="198"/>
       <c r="D32" s="11">
         <f>SUM(T10:T23)</f>
-        <v>1</v>
-      </c>
-      <c r="E32" s="11">
-        <f>SUM(U10:U23)</f>
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="11"/>
       <c r="H32" s="11"/>
@@ -7237,7 +6979,7 @@
       <c r="C34" s="8"/>
     </row>
     <row r="35" spans="1:17" ht="18" customHeight="1">
-      <c r="A35" s="192" t="s">
+      <c r="A35" s="197" t="s">
         <v>44</v>
       </c>
       <c r="B35" s="12" t="s">
@@ -7248,14 +6990,14 @@
       </c>
       <c r="D35" s="11">
         <f>IF(C35=0, 0, ((SUM(D30:M30)+SUM(D31:M31))/C35)*100)</f>
-        <v>1.4925373134328357</v>
+        <v>0</v>
       </c>
       <c r="E35" s="11" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="18" customHeight="1">
-      <c r="A36" s="192"/>
+      <c r="A36" s="197"/>
       <c r="B36" s="12" t="s">
         <v>46</v>
       </c>
@@ -7264,32 +7006,32 @@
       </c>
       <c r="D36" s="11">
         <f>IF(C36=0, 0, ((SUM(D32:M32))/C36)*100)</f>
-        <v>0.82644628099173556</v>
+        <v>0</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="18" customHeight="1">
-      <c r="A37" s="192"/>
-      <c r="B37" s="191" t="s">
+      <c r="A37" s="197"/>
+      <c r="B37" s="198" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="191"/>
+      <c r="C37" s="198"/>
       <c r="D37" s="11">
         <f>D35+D36</f>
-        <v>2.3189835944245711</v>
+        <v>0</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="18" customHeight="1">
-      <c r="A38" s="192"/>
-      <c r="B38" s="191" t="s">
+      <c r="A38" s="197"/>
+      <c r="B38" s="198" t="s">
         <v>47</v>
       </c>
-      <c r="C38" s="191"/>
+      <c r="C38" s="198"/>
       <c r="D38" s="11">
         <v>100</v>
       </c>
@@ -7298,21 +7040,21 @@
       </c>
     </row>
     <row r="39" spans="1:17" ht="18" customHeight="1">
-      <c r="A39" s="192"/>
-      <c r="B39" s="191" t="s">
+      <c r="A39" s="197"/>
+      <c r="B39" s="198" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="191"/>
+      <c r="C39" s="198"/>
       <c r="D39" s="11">
         <f>CEILING(D37 /D38, 1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" s="13" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="18" customHeight="1">
-      <c r="A40" s="192" t="s">
+      <c r="A40" s="197" t="s">
         <v>45</v>
       </c>
       <c r="B40" s="12" t="s">
@@ -7323,14 +7065,14 @@
       </c>
       <c r="D40" s="11">
         <f>IF(C40=0, 0, ((SUM(D30:M30)+SUM(D31:M31))/C40)*100)</f>
-        <v>1.2987012987012987</v>
+        <v>0</v>
       </c>
       <c r="E40" s="11" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:17" ht="18" customHeight="1">
-      <c r="A41" s="192"/>
+      <c r="A41" s="197"/>
       <c r="B41" s="12" t="s">
         <v>46</v>
       </c>
@@ -7339,32 +7081,32 @@
       </c>
       <c r="D41" s="11">
         <f>IF(C41=0, 0, ((SUM(D32:M32))/C41)*100)</f>
-        <v>0.71942446043165476</v>
+        <v>0</v>
       </c>
       <c r="E41" s="11" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:17" ht="18" customHeight="1">
-      <c r="A42" s="192"/>
-      <c r="B42" s="191" t="s">
+      <c r="A42" s="197"/>
+      <c r="B42" s="198" t="s">
         <v>48</v>
       </c>
-      <c r="C42" s="191"/>
+      <c r="C42" s="198"/>
       <c r="D42" s="11">
         <f>D40+D41</f>
-        <v>2.0181257591329533</v>
+        <v>0</v>
       </c>
       <c r="E42" s="11" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="43" spans="1:17" ht="18" customHeight="1">
-      <c r="A43" s="192"/>
-      <c r="B43" s="191" t="s">
+      <c r="A43" s="197"/>
+      <c r="B43" s="198" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="191"/>
+      <c r="C43" s="198"/>
       <c r="D43" s="11">
         <v>100</v>
       </c>
@@ -7372,76 +7114,76 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="25.2" customHeight="1">
-      <c r="A44" s="192"/>
-      <c r="B44" s="191" t="s">
+    <row r="44" spans="1:17" ht="25.15" customHeight="1">
+      <c r="A44" s="197"/>
+      <c r="B44" s="198" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="191"/>
+      <c r="C44" s="198"/>
       <c r="D44" s="11">
         <f>CEILING(D42 /D43, 1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" s="13" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="25.2" customHeight="1">
+    <row r="45" spans="1:17" ht="25.15" customHeight="1">
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
       <c r="E45" s="9"/>
     </row>
-    <row r="46" spans="1:17" ht="4.95" customHeight="1">
+    <row r="46" spans="1:17" ht="4.9000000000000004" customHeight="1">
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
       <c r="E46" s="9"/>
     </row>
     <row r="47" spans="1:17" ht="21" customHeight="1">
-      <c r="A47" s="198" t="s">
+      <c r="A47" s="199" t="s">
         <v>15</v>
       </c>
-      <c r="B47" s="192"/>
+      <c r="B47" s="197"/>
       <c r="C47" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D47" s="198" t="s">
+      <c r="D47" s="199" t="s">
         <v>53</v>
       </c>
-      <c r="E47" s="198"/>
-      <c r="F47" s="198"/>
-      <c r="G47" s="198" t="s">
+      <c r="E47" s="199"/>
+      <c r="F47" s="199"/>
+      <c r="G47" s="199" t="s">
         <v>54</v>
       </c>
-      <c r="H47" s="198"/>
-      <c r="I47" s="198"/>
-      <c r="J47" s="186" t="s">
+      <c r="H47" s="199"/>
+      <c r="I47" s="199"/>
+      <c r="J47" s="185" t="s">
         <v>55</v>
       </c>
-      <c r="K47" s="187"/>
-      <c r="L47" s="187"/>
-      <c r="M47" s="188"/>
+      <c r="K47" s="186"/>
+      <c r="L47" s="186"/>
+      <c r="M47" s="187"/>
       <c r="N47" s="14"/>
-      <c r="O47" s="199" t="s">
+      <c r="O47" s="188" t="s">
         <v>60</v>
       </c>
-      <c r="P47" s="200"/>
+      <c r="P47" s="189"/>
     </row>
     <row r="48" spans="1:17" ht="21" customHeight="1">
-      <c r="A48" s="193" t="s">
+      <c r="A48" s="192" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="194"/>
+      <c r="B48" s="193"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="186"/>
-      <c r="E48" s="187"/>
-      <c r="F48" s="188"/>
-      <c r="G48" s="186"/>
-      <c r="H48" s="187"/>
-      <c r="I48" s="188"/>
-      <c r="J48" s="195"/>
-      <c r="K48" s="196"/>
-      <c r="L48" s="196"/>
-      <c r="M48" s="197"/>
+      <c r="D48" s="185"/>
+      <c r="E48" s="186"/>
+      <c r="F48" s="187"/>
+      <c r="G48" s="185"/>
+      <c r="H48" s="186"/>
+      <c r="I48" s="187"/>
+      <c r="J48" s="194"/>
+      <c r="K48" s="195"/>
+      <c r="L48" s="195"/>
+      <c r="M48" s="196"/>
       <c r="N48" s="15"/>
       <c r="O48" s="19" t="s">
         <v>56</v>
@@ -7452,21 +7194,21 @@
       <c r="Q48" s="5"/>
     </row>
     <row r="49" spans="1:17" ht="21" customHeight="1">
-      <c r="A49" s="193" t="s">
+      <c r="A49" s="192" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="194"/>
+      <c r="B49" s="193"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="186"/>
-      <c r="E49" s="187"/>
-      <c r="F49" s="188"/>
-      <c r="G49" s="186"/>
-      <c r="H49" s="187"/>
-      <c r="I49" s="188"/>
-      <c r="J49" s="195"/>
-      <c r="K49" s="196"/>
-      <c r="L49" s="196"/>
-      <c r="M49" s="197"/>
+      <c r="D49" s="185"/>
+      <c r="E49" s="186"/>
+      <c r="F49" s="187"/>
+      <c r="G49" s="185"/>
+      <c r="H49" s="186"/>
+      <c r="I49" s="187"/>
+      <c r="J49" s="194"/>
+      <c r="K49" s="195"/>
+      <c r="L49" s="195"/>
+      <c r="M49" s="196"/>
       <c r="N49" s="15"/>
       <c r="O49" s="19" t="s">
         <v>58</v>
@@ -7477,21 +7219,21 @@
       <c r="Q49" s="16"/>
     </row>
     <row r="50" spans="1:17" ht="21" customHeight="1">
-      <c r="A50" s="193" t="s">
+      <c r="A50" s="192" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="193"/>
+      <c r="B50" s="192"/>
       <c r="C50" s="11"/>
-      <c r="D50" s="186"/>
-      <c r="E50" s="187"/>
-      <c r="F50" s="188"/>
-      <c r="G50" s="186"/>
-      <c r="H50" s="187"/>
-      <c r="I50" s="188"/>
-      <c r="J50" s="195"/>
-      <c r="K50" s="196"/>
-      <c r="L50" s="196"/>
-      <c r="M50" s="197"/>
+      <c r="D50" s="185"/>
+      <c r="E50" s="186"/>
+      <c r="F50" s="187"/>
+      <c r="G50" s="185"/>
+      <c r="H50" s="186"/>
+      <c r="I50" s="187"/>
+      <c r="J50" s="194"/>
+      <c r="K50" s="195"/>
+      <c r="L50" s="195"/>
+      <c r="M50" s="196"/>
       <c r="N50" s="15"/>
       <c r="O50" s="17" t="s">
         <v>59</v>
@@ -7508,14 +7250,41 @@
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="G48:I48"/>
-    <mergeCell ref="G49:I49"/>
-    <mergeCell ref="G50:I50"/>
-    <mergeCell ref="O47:P47"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="J47:M47"/>
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="O3:Q4"/>
+    <mergeCell ref="A6:B8"/>
+    <mergeCell ref="C6:Q6"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="D7:Q7"/>
+    <mergeCell ref="AJ8:AL8"/>
+    <mergeCell ref="AM8:AO8"/>
+    <mergeCell ref="AP8:AR8"/>
+    <mergeCell ref="AS8:AU8"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="U8:W8"/>
+    <mergeCell ref="X8:Z8"/>
+    <mergeCell ref="AA8:AC8"/>
+    <mergeCell ref="AD8:AF8"/>
+    <mergeCell ref="AG8:AI8"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A35:A39"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A49:B49"/>
     <mergeCell ref="A50:B50"/>
@@ -7532,41 +7301,14 @@
     <mergeCell ref="D48:F48"/>
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="D50:F50"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A35:A39"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="AJ8:AL8"/>
-    <mergeCell ref="AM8:AO8"/>
-    <mergeCell ref="AP8:AR8"/>
-    <mergeCell ref="AS8:AU8"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="U8:W8"/>
-    <mergeCell ref="X8:Z8"/>
-    <mergeCell ref="AA8:AC8"/>
-    <mergeCell ref="AD8:AF8"/>
-    <mergeCell ref="AG8:AI8"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="D7:Q7"/>
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="O3:Q4"/>
-    <mergeCell ref="A6:B8"/>
-    <mergeCell ref="C6:Q6"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="G49:I49"/>
+    <mergeCell ref="G50:I50"/>
+    <mergeCell ref="O47:P47"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="J47:M47"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7577,29 +7319,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:I25"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="51.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" customWidth="1"/>
-    <col min="6" max="6" width="11.77734375" customWidth="1"/>
+    <col min="2" max="2" width="51.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.125" customWidth="1"/>
+    <col min="6" max="6" width="11.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:9" s="3" customFormat="1" ht="15" customHeight="1"/>
     <row r="3" spans="1:9" s="3" customFormat="1" ht="30.75" customHeight="1">
       <c r="D3" s="43"/>
       <c r="E3" s="43"/>
-      <c r="G3" s="216"/>
-      <c r="H3" s="216"/>
-      <c r="I3" s="216"/>
+      <c r="G3" s="215"/>
+      <c r="H3" s="215"/>
+      <c r="I3" s="215"/>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
       <c r="D4" s="42"/>
       <c r="E4" s="42"/>
       <c r="F4" s="41"/>
-      <c r="G4" s="216"/>
-      <c r="H4" s="216"/>
-      <c r="I4" s="216"/>
+      <c r="G4" s="215"/>
+      <c r="H4" s="215"/>
+      <c r="I4" s="215"/>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" ht="56.25" customHeight="1" thickBot="1">
       <c r="A5" s="51" t="s">
@@ -7608,52 +7350,52 @@
       <c r="B5" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="217" t="s">
+      <c r="C5" s="216" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="218"/>
-      <c r="E5" s="218"/>
-      <c r="F5" s="219"/>
+      <c r="D5" s="217"/>
+      <c r="E5" s="217"/>
+      <c r="F5" s="218"/>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A6" s="220" t="s">
+      <c r="A6" s="219" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="221"/>
-      <c r="C6" s="226" t="s">
+      <c r="B6" s="220"/>
+      <c r="C6" s="225" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="229" t="s">
+      <c r="D6" s="228" t="s">
         <v>94</v>
       </c>
-      <c r="E6" s="231" t="s">
+      <c r="E6" s="230" t="s">
         <v>72</v>
       </c>
-      <c r="F6" s="232"/>
+      <c r="F6" s="231"/>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" ht="30.6" customHeight="1" thickBot="1">
-      <c r="A7" s="222"/>
-      <c r="B7" s="223"/>
-      <c r="C7" s="227"/>
-      <c r="D7" s="230"/>
-      <c r="E7" s="233"/>
-      <c r="F7" s="234"/>
+      <c r="A7" s="221"/>
+      <c r="B7" s="222"/>
+      <c r="C7" s="226"/>
+      <c r="D7" s="229"/>
+      <c r="E7" s="232"/>
+      <c r="F7" s="233"/>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A8" s="222"/>
-      <c r="B8" s="223"/>
-      <c r="C8" s="227"/>
-      <c r="D8" s="236" t="s">
+      <c r="A8" s="221"/>
+      <c r="B8" s="222"/>
+      <c r="C8" s="226"/>
+      <c r="D8" s="235" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="235"/>
-      <c r="F8" s="234"/>
-    </row>
-    <row r="9" spans="1:9" s="3" customFormat="1" ht="17.399999999999999" customHeight="1" thickBot="1">
-      <c r="A9" s="224"/>
-      <c r="B9" s="225"/>
-      <c r="C9" s="228"/>
-      <c r="D9" s="237"/>
+      <c r="E8" s="234"/>
+      <c r="F8" s="233"/>
+    </row>
+    <row r="9" spans="1:9" s="3" customFormat="1" ht="17.45" customHeight="1" thickBot="1">
+      <c r="A9" s="223"/>
+      <c r="B9" s="224"/>
+      <c r="C9" s="227"/>
+      <c r="D9" s="236"/>
       <c r="E9" s="33" t="s">
         <v>75</v>
       </c>
@@ -7661,43 +7403,43 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A10" s="206">
+    <row r="10" spans="1:9" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A10" s="242">
         <v>1</v>
       </c>
-      <c r="B10" s="208" t="s">
+      <c r="B10" s="244" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="210">
+      <c r="C10" s="246">
         <v>15</v>
       </c>
       <c r="D10" s="60">
         <v>1888</v>
       </c>
-      <c r="E10" s="212">
+      <c r="E10" s="211">
         <f>SUM(D10:D10)</f>
         <v>1888</v>
       </c>
-      <c r="F10" s="214">
+      <c r="F10" s="213">
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A11" s="207"/>
-      <c r="B11" s="209"/>
-      <c r="C11" s="211"/>
+    <row r="11" spans="1:9" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A11" s="243"/>
+      <c r="B11" s="245"/>
+      <c r="C11" s="247"/>
       <c r="D11" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="E11" s="213"/>
-      <c r="F11" s="215"/>
+      <c r="E11" s="212"/>
+      <c r="F11" s="214"/>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" ht="39" customHeight="1" thickBot="1">
-      <c r="A12" s="201" t="s">
+      <c r="A12" s="237" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="202"/>
-      <c r="C12" s="203"/>
+      <c r="B12" s="238"/>
+      <c r="C12" s="239"/>
       <c r="D12" s="44">
         <v>126</v>
       </c>
@@ -7711,7 +7453,7 @@
       <c r="G12" s="25"/>
       <c r="H12" s="25"/>
     </row>
-    <row r="13" spans="1:9" s="3" customFormat="1" ht="17.399999999999999" customHeight="1" thickBot="1">
+    <row r="13" spans="1:9" s="3" customFormat="1" ht="17.45" customHeight="1" thickBot="1">
       <c r="A13" s="24"/>
       <c r="B13" s="24"/>
       <c r="C13" s="24"/>
@@ -7722,10 +7464,10 @@
       <c r="H13" s="25"/>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A14" s="204" t="s">
+      <c r="A14" s="240" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="205"/>
+      <c r="B14" s="241"/>
       <c r="C14" s="50" t="s">
         <v>53</v>
       </c>
@@ -7737,7 +7479,7 @@
       </c>
       <c r="F14" s="26"/>
     </row>
-    <row r="15" spans="1:9" s="3" customFormat="1" ht="28.2" customHeight="1" thickBot="1">
+    <row r="15" spans="1:9" s="3" customFormat="1" ht="28.15" customHeight="1" thickBot="1">
       <c r="A15" s="36" t="s">
         <v>78</v>
       </c>
@@ -7747,7 +7489,7 @@
       <c r="E15" s="37"/>
       <c r="F15" s="26"/>
     </row>
-    <row r="16" spans="1:9" s="3" customFormat="1" ht="28.2" customHeight="1" thickBot="1">
+    <row r="16" spans="1:9" s="3" customFormat="1" ht="28.15" customHeight="1" thickBot="1">
       <c r="A16" s="36" t="s">
         <v>80</v>
       </c>
@@ -7757,7 +7499,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="26"/>
     </row>
-    <row r="17" spans="1:6" s="3" customFormat="1" ht="28.2" customHeight="1" thickBot="1">
+    <row r="17" spans="1:6" s="3" customFormat="1" ht="28.15" customHeight="1" thickBot="1">
       <c r="A17" s="53" t="s">
         <v>82</v>
       </c>
@@ -7790,14 +7532,14 @@
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+    <row r="20" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
       <c r="D20" s="40"/>
       <c r="E20" s="28" t="s">
         <v>79</v>
       </c>
       <c r="F20" s="28"/>
     </row>
-    <row r="21" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+    <row r="21" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
       <c r="D21" s="26"/>
       <c r="E21" s="29" t="s">
         <v>81</v>
@@ -7806,12 +7548,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+    <row r="22" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
       <c r="D22" s="26"/>
       <c r="E22" s="29"/>
       <c r="F22" s="29"/>
     </row>
-    <row r="23" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
+    <row r="23" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
       <c r="D23" s="39"/>
       <c r="E23" s="28"/>
       <c r="F23" s="28"/>
@@ -7830,6 +7572,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
     <mergeCell ref="E10:E11"/>
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="G3:I4"/>
@@ -7839,11 +7586,6 @@
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="E6:F8"/>
     <mergeCell ref="D8:D9"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>
@@ -7854,29 +7596,29 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A2:I49"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="51.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" customWidth="1"/>
+    <col min="6" max="6" width="13.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:9" s="3" customFormat="1" ht="15" customHeight="1"/>
     <row r="3" spans="1:9" s="3" customFormat="1" ht="30.75" customHeight="1">
       <c r="D3" s="43"/>
       <c r="E3" s="43"/>
-      <c r="G3" s="216"/>
-      <c r="H3" s="216"/>
-      <c r="I3" s="216"/>
+      <c r="G3" s="215"/>
+      <c r="H3" s="215"/>
+      <c r="I3" s="215"/>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
       <c r="D4" s="42"/>
       <c r="E4" s="42"/>
       <c r="F4" s="41"/>
-      <c r="G4" s="216"/>
-      <c r="H4" s="216"/>
-      <c r="I4" s="216"/>
+      <c r="G4" s="215"/>
+      <c r="H4" s="215"/>
+      <c r="I4" s="215"/>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" ht="56.25" customHeight="1" thickBot="1">
       <c r="A5" s="51" t="s">
@@ -7885,52 +7627,52 @@
       <c r="B5" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="217" t="s">
+      <c r="C5" s="216" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="218"/>
-      <c r="E5" s="218"/>
-      <c r="F5" s="219"/>
+      <c r="D5" s="217"/>
+      <c r="E5" s="217"/>
+      <c r="F5" s="218"/>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A6" s="220" t="s">
+      <c r="A6" s="219" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="221"/>
-      <c r="C6" s="226" t="s">
+      <c r="B6" s="220"/>
+      <c r="C6" s="225" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="229" t="s">
+      <c r="D6" s="228" t="s">
         <v>94</v>
       </c>
-      <c r="E6" s="231" t="s">
+      <c r="E6" s="230" t="s">
         <v>72</v>
       </c>
-      <c r="F6" s="232"/>
+      <c r="F6" s="231"/>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" ht="30.6" customHeight="1" thickBot="1">
-      <c r="A7" s="222"/>
-      <c r="B7" s="223"/>
-      <c r="C7" s="227"/>
-      <c r="D7" s="230"/>
-      <c r="E7" s="233"/>
-      <c r="F7" s="234"/>
+      <c r="A7" s="221"/>
+      <c r="B7" s="222"/>
+      <c r="C7" s="226"/>
+      <c r="D7" s="229"/>
+      <c r="E7" s="232"/>
+      <c r="F7" s="233"/>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A8" s="222"/>
-      <c r="B8" s="223"/>
-      <c r="C8" s="227"/>
-      <c r="D8" s="236" t="s">
+      <c r="A8" s="221"/>
+      <c r="B8" s="222"/>
+      <c r="C8" s="226"/>
+      <c r="D8" s="235" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="235"/>
-      <c r="F8" s="234"/>
-    </row>
-    <row r="9" spans="1:9" s="3" customFormat="1" ht="17.399999999999999" customHeight="1" thickBot="1">
-      <c r="A9" s="224"/>
-      <c r="B9" s="225"/>
-      <c r="C9" s="228"/>
-      <c r="D9" s="237"/>
+      <c r="E8" s="234"/>
+      <c r="F8" s="233"/>
+    </row>
+    <row r="9" spans="1:9" s="3" customFormat="1" ht="17.45" customHeight="1" thickBot="1">
+      <c r="A9" s="223"/>
+      <c r="B9" s="224"/>
+      <c r="C9" s="227"/>
+      <c r="D9" s="236"/>
       <c r="E9" s="33" t="s">
         <v>75</v>
       </c>
@@ -7938,416 +7680,416 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A10" s="206">
+    <row r="10" spans="1:9" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A10" s="242">
         <v>1</v>
       </c>
-      <c r="B10" s="241" t="s">
+      <c r="B10" s="248" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="206">
+      <c r="C10" s="242">
         <v>32</v>
       </c>
       <c r="D10" s="54">
         <v>566</v>
       </c>
-      <c r="E10" s="212">
+      <c r="E10" s="211">
         <f>SUM(D10:D10)</f>
         <v>566</v>
       </c>
-      <c r="F10" s="214">
+      <c r="F10" s="213">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A11" s="207"/>
-      <c r="B11" s="242"/>
-      <c r="C11" s="207"/>
+    <row r="11" spans="1:9" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A11" s="243"/>
+      <c r="B11" s="249"/>
+      <c r="C11" s="243"/>
       <c r="D11" s="55" t="s">
         <v>97</v>
       </c>
-      <c r="E11" s="213"/>
-      <c r="F11" s="215"/>
-    </row>
-    <row r="12" spans="1:9" s="3" customFormat="1" ht="29.4" hidden="1" customHeight="1">
-      <c r="A12" s="206">
+      <c r="E11" s="212"/>
+      <c r="F11" s="214"/>
+    </row>
+    <row r="12" spans="1:9" s="3" customFormat="1" ht="29.45" hidden="1" customHeight="1">
+      <c r="A12" s="242">
         <v>2</v>
       </c>
-      <c r="B12" s="208" t="s">
+      <c r="B12" s="244" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="210">
+      <c r="C12" s="246">
         <v>14</v>
       </c>
       <c r="D12" s="54"/>
-      <c r="E12" s="239">
+      <c r="E12" s="250">
         <f>SUM(D12:D12)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="214">
+      <c r="F12" s="213">
         <f>มหาชัย!C11</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="3" customFormat="1" ht="29.4" hidden="1" customHeight="1">
-      <c r="A13" s="207"/>
-      <c r="B13" s="209"/>
-      <c r="C13" s="238"/>
+    <row r="13" spans="1:9" s="3" customFormat="1" ht="29.45" hidden="1" customHeight="1">
+      <c r="A13" s="243"/>
+      <c r="B13" s="245"/>
+      <c r="C13" s="253"/>
       <c r="D13" s="56" t="str">
         <f>IF(D12=0, "", IF(MOD(D12, $C$11) = 0, D12 / $C$11, IF(INT(D12 / $C$11) = 0, MOD(D12, $C$11) &amp; " P", INT(D12 / $C$11) &amp; " + " &amp; MOD(D12, $C$11) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="E13" s="240"/>
-      <c r="F13" s="215"/>
-    </row>
-    <row r="14" spans="1:9" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A14" s="206">
+      <c r="E13" s="251"/>
+      <c r="F13" s="214"/>
+    </row>
+    <row r="14" spans="1:9" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A14" s="242">
         <v>2</v>
       </c>
-      <c r="B14" s="241" t="s">
+      <c r="B14" s="248" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="206">
+      <c r="C14" s="242">
         <v>32</v>
       </c>
       <c r="D14" s="54">
         <v>275</v>
       </c>
-      <c r="E14" s="239">
+      <c r="E14" s="250">
         <f>SUM(D14:D14)</f>
         <v>275</v>
       </c>
-      <c r="F14" s="214" t="e">
+      <c r="F14" s="213" t="e">
         <f>มหาชัย!#REF!</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A15" s="207"/>
-      <c r="B15" s="242"/>
-      <c r="C15" s="207"/>
+    <row r="15" spans="1:9" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A15" s="243"/>
+      <c r="B15" s="249"/>
+      <c r="C15" s="243"/>
       <c r="D15" s="56" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="240"/>
-      <c r="F15" s="215"/>
-    </row>
-    <row r="16" spans="1:9" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A16" s="206">
+      <c r="E15" s="251"/>
+      <c r="F15" s="214"/>
+    </row>
+    <row r="16" spans="1:9" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A16" s="242">
         <v>3</v>
       </c>
-      <c r="B16" s="241" t="s">
+      <c r="B16" s="248" t="s">
         <v>86</v>
       </c>
-      <c r="C16" s="243">
+      <c r="C16" s="252">
         <v>27</v>
       </c>
       <c r="D16" s="57">
         <v>228</v>
       </c>
-      <c r="E16" s="239">
+      <c r="E16" s="250">
         <f>SUM(D16:D16)</f>
         <v>228</v>
       </c>
-      <c r="F16" s="214">
+      <c r="F16" s="213">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A17" s="207"/>
-      <c r="B17" s="242"/>
-      <c r="C17" s="211"/>
+    <row r="17" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A17" s="243"/>
+      <c r="B17" s="249"/>
+      <c r="C17" s="247"/>
       <c r="D17" s="56" t="s">
         <v>99</v>
       </c>
-      <c r="E17" s="240"/>
-      <c r="F17" s="215"/>
-    </row>
-    <row r="18" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A18" s="206">
+      <c r="E17" s="251"/>
+      <c r="F17" s="214"/>
+    </row>
+    <row r="18" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A18" s="242">
         <v>4</v>
       </c>
-      <c r="B18" s="208" t="s">
+      <c r="B18" s="244" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="210">
+      <c r="C18" s="246">
         <v>36</v>
       </c>
       <c r="D18" s="54">
         <v>181</v>
       </c>
-      <c r="E18" s="239">
+      <c r="E18" s="250">
         <f>SUM(D18:D18)</f>
         <v>181</v>
       </c>
-      <c r="F18" s="214">
+      <c r="F18" s="213">
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A19" s="207"/>
-      <c r="B19" s="209"/>
-      <c r="C19" s="211"/>
+    <row r="19" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A19" s="243"/>
+      <c r="B19" s="245"/>
+      <c r="C19" s="247"/>
       <c r="D19" s="58" t="s">
         <v>100</v>
       </c>
-      <c r="E19" s="240"/>
-      <c r="F19" s="215"/>
-    </row>
-    <row r="20" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A20" s="206">
+      <c r="E19" s="251"/>
+      <c r="F19" s="214"/>
+    </row>
+    <row r="20" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A20" s="242">
         <v>5</v>
       </c>
-      <c r="B20" s="208" t="s">
+      <c r="B20" s="244" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="210">
+      <c r="C20" s="246">
         <v>15</v>
       </c>
       <c r="D20" s="54">
         <v>272</v>
       </c>
-      <c r="E20" s="239">
+      <c r="E20" s="250">
         <f>SUM(D20:D20)</f>
         <v>272</v>
       </c>
-      <c r="F20" s="214">
+      <c r="F20" s="213">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A21" s="207"/>
-      <c r="B21" s="209"/>
-      <c r="C21" s="211"/>
+    <row r="21" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A21" s="243"/>
+      <c r="B21" s="245"/>
+      <c r="C21" s="247"/>
       <c r="D21" s="58" t="s">
         <v>101</v>
       </c>
-      <c r="E21" s="240"/>
-      <c r="F21" s="215"/>
-    </row>
-    <row r="22" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A22" s="206">
+      <c r="E21" s="251"/>
+      <c r="F21" s="214"/>
+    </row>
+    <row r="22" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A22" s="242">
         <v>6</v>
       </c>
-      <c r="B22" s="208" t="s">
+      <c r="B22" s="244" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="210">
+      <c r="C22" s="246">
         <v>45</v>
       </c>
       <c r="D22" s="54">
         <v>24</v>
       </c>
-      <c r="E22" s="239">
+      <c r="E22" s="250">
         <f>SUM(D22:D22)</f>
         <v>24</v>
       </c>
-      <c r="F22" s="214">
+      <c r="F22" s="213">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A23" s="207"/>
-      <c r="B23" s="209"/>
-      <c r="C23" s="211"/>
+    <row r="23" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A23" s="243"/>
+      <c r="B23" s="245"/>
+      <c r="C23" s="247"/>
       <c r="D23" s="59" t="s">
         <v>102</v>
       </c>
-      <c r="E23" s="213"/>
-      <c r="F23" s="215"/>
-    </row>
-    <row r="24" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A24" s="206">
+      <c r="E23" s="212"/>
+      <c r="F23" s="214"/>
+    </row>
+    <row r="24" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A24" s="242">
         <v>7</v>
       </c>
-      <c r="B24" s="208" t="s">
+      <c r="B24" s="244" t="s">
         <v>93</v>
       </c>
-      <c r="C24" s="210">
+      <c r="C24" s="246">
         <v>27</v>
       </c>
       <c r="D24" s="60">
         <v>390</v>
       </c>
-      <c r="E24" s="212">
+      <c r="E24" s="211">
         <f>SUM(D24:D24)</f>
         <v>390</v>
       </c>
-      <c r="F24" s="214">
+      <c r="F24" s="213">
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A25" s="207"/>
-      <c r="B25" s="209"/>
-      <c r="C25" s="211"/>
+    <row r="25" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A25" s="243"/>
+      <c r="B25" s="245"/>
+      <c r="C25" s="247"/>
       <c r="D25" s="59" t="s">
         <v>103</v>
       </c>
-      <c r="E25" s="213"/>
-      <c r="F25" s="215"/>
-    </row>
-    <row r="26" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A26" s="206">
+      <c r="E25" s="212"/>
+      <c r="F25" s="214"/>
+    </row>
+    <row r="26" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A26" s="242">
         <v>8</v>
       </c>
-      <c r="B26" s="208" t="s">
+      <c r="B26" s="244" t="s">
         <v>66</v>
       </c>
-      <c r="C26" s="210">
+      <c r="C26" s="246">
         <v>15</v>
       </c>
       <c r="D26" s="60">
         <v>40</v>
       </c>
-      <c r="E26" s="212">
+      <c r="E26" s="211">
         <f>SUM(D26:D26)</f>
         <v>40</v>
       </c>
-      <c r="F26" s="214">
+      <c r="F26" s="213">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A27" s="207"/>
-      <c r="B27" s="209"/>
-      <c r="C27" s="211"/>
+    <row r="27" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A27" s="243"/>
+      <c r="B27" s="245"/>
+      <c r="C27" s="247"/>
       <c r="D27" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="E27" s="213"/>
-      <c r="F27" s="215"/>
-    </row>
-    <row r="28" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A28" s="206">
+      <c r="E27" s="212"/>
+      <c r="F27" s="214"/>
+    </row>
+    <row r="28" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A28" s="242">
         <v>9</v>
       </c>
-      <c r="B28" s="208" t="s">
+      <c r="B28" s="244" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="210">
+      <c r="C28" s="246">
         <v>27</v>
       </c>
       <c r="D28" s="60">
         <v>172</v>
       </c>
-      <c r="E28" s="212">
+      <c r="E28" s="211">
         <f>SUM(D28:D28)</f>
         <v>172</v>
       </c>
-      <c r="F28" s="214">
+      <c r="F28" s="213">
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A29" s="207"/>
-      <c r="B29" s="209"/>
-      <c r="C29" s="211"/>
+    <row r="29" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A29" s="243"/>
+      <c r="B29" s="245"/>
+      <c r="C29" s="247"/>
       <c r="D29" s="59" t="s">
         <v>105</v>
       </c>
-      <c r="E29" s="213"/>
-      <c r="F29" s="215"/>
-    </row>
-    <row r="30" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A30" s="206">
+      <c r="E29" s="212"/>
+      <c r="F29" s="214"/>
+    </row>
+    <row r="30" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A30" s="242">
         <v>10</v>
       </c>
-      <c r="B30" s="208" t="s">
+      <c r="B30" s="244" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="210">
+      <c r="C30" s="246">
         <v>20</v>
       </c>
       <c r="D30" s="60">
         <v>239</v>
       </c>
-      <c r="E30" s="212">
+      <c r="E30" s="211">
         <f>SUM(D30:D30)</f>
         <v>239</v>
       </c>
-      <c r="F30" s="214">
+      <c r="F30" s="213">
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A31" s="207"/>
-      <c r="B31" s="209"/>
-      <c r="C31" s="211"/>
+    <row r="31" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A31" s="243"/>
+      <c r="B31" s="245"/>
+      <c r="C31" s="247"/>
       <c r="D31" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="E31" s="213"/>
-      <c r="F31" s="215"/>
-    </row>
-    <row r="32" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A32" s="206">
+      <c r="E31" s="212"/>
+      <c r="F31" s="214"/>
+    </row>
+    <row r="32" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A32" s="242">
         <v>11</v>
       </c>
-      <c r="B32" s="208" t="s">
+      <c r="B32" s="244" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="210">
+      <c r="C32" s="246">
         <v>32</v>
       </c>
       <c r="D32" s="60">
         <v>121</v>
       </c>
-      <c r="E32" s="212">
+      <c r="E32" s="211">
         <f>SUM(D32:D32)</f>
         <v>121</v>
       </c>
-      <c r="F32" s="214">
+      <c r="F32" s="213">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:8" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A33" s="207"/>
-      <c r="B33" s="209"/>
-      <c r="C33" s="211"/>
+    <row r="33" spans="1:8" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A33" s="243"/>
+      <c r="B33" s="245"/>
+      <c r="C33" s="247"/>
       <c r="D33" s="59" t="s">
         <v>107</v>
       </c>
-      <c r="E33" s="213"/>
-      <c r="F33" s="215"/>
-    </row>
-    <row r="34" spans="1:8" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A34" s="206">
+      <c r="E33" s="212"/>
+      <c r="F33" s="214"/>
+    </row>
+    <row r="34" spans="1:8" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A34" s="242">
         <v>12</v>
       </c>
-      <c r="B34" s="241" t="s">
+      <c r="B34" s="248" t="s">
         <v>70</v>
       </c>
-      <c r="C34" s="206">
+      <c r="C34" s="242">
         <v>45</v>
       </c>
       <c r="D34" s="60">
         <v>54</v>
       </c>
-      <c r="E34" s="212">
+      <c r="E34" s="211">
         <f>SUM(D34:D34)</f>
         <v>54</v>
       </c>
-      <c r="F34" s="214">
+      <c r="F34" s="213">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:8" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A35" s="207"/>
-      <c r="B35" s="242"/>
-      <c r="C35" s="207"/>
+    <row r="35" spans="1:8" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A35" s="243"/>
+      <c r="B35" s="249"/>
+      <c r="C35" s="243"/>
       <c r="D35" s="59" t="s">
         <v>108</v>
       </c>
-      <c r="E35" s="213"/>
-      <c r="F35" s="215"/>
+      <c r="E35" s="212"/>
+      <c r="F35" s="214"/>
     </row>
     <row r="36" spans="1:8" s="3" customFormat="1" ht="39" customHeight="1" thickBot="1">
-      <c r="A36" s="201" t="s">
+      <c r="A36" s="237" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="202"/>
-      <c r="C36" s="203"/>
+      <c r="B36" s="238"/>
+      <c r="C36" s="239"/>
       <c r="D36" s="44">
         <v>105</v>
       </c>
@@ -8360,7 +8102,7 @@
       <c r="G36" s="25"/>
       <c r="H36" s="25"/>
     </row>
-    <row r="37" spans="1:8" s="3" customFormat="1" ht="17.399999999999999" customHeight="1" thickBot="1">
+    <row r="37" spans="1:8" s="3" customFormat="1" ht="17.45" customHeight="1" thickBot="1">
       <c r="A37" s="24"/>
       <c r="B37" s="24"/>
       <c r="C37" s="24"/>
@@ -8371,10 +8113,10 @@
       <c r="H37" s="25"/>
     </row>
     <row r="38" spans="1:8" s="3" customFormat="1" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A38" s="204" t="s">
+      <c r="A38" s="240" t="s">
         <v>49</v>
       </c>
-      <c r="B38" s="205"/>
+      <c r="B38" s="241"/>
       <c r="C38" s="50" t="s">
         <v>53</v>
       </c>
@@ -8386,7 +8128,7 @@
       </c>
       <c r="F38" s="26"/>
     </row>
-    <row r="39" spans="1:8" s="3" customFormat="1" ht="28.2" customHeight="1" thickBot="1">
+    <row r="39" spans="1:8" s="3" customFormat="1" ht="28.15" customHeight="1" thickBot="1">
       <c r="A39" s="36" t="s">
         <v>78</v>
       </c>
@@ -8396,7 +8138,7 @@
       <c r="E39" s="37"/>
       <c r="F39" s="26"/>
     </row>
-    <row r="40" spans="1:8" s="3" customFormat="1" ht="28.2" customHeight="1" thickBot="1">
+    <row r="40" spans="1:8" s="3" customFormat="1" ht="28.15" customHeight="1" thickBot="1">
       <c r="A40" s="36" t="s">
         <v>80</v>
       </c>
@@ -8406,7 +8148,7 @@
       <c r="E40" s="37"/>
       <c r="F40" s="26"/>
     </row>
-    <row r="41" spans="1:8" s="3" customFormat="1" ht="28.2" customHeight="1" thickBot="1">
+    <row r="41" spans="1:8" s="3" customFormat="1" ht="28.15" customHeight="1" thickBot="1">
       <c r="A41" s="53" t="s">
         <v>82</v>
       </c>
@@ -8439,14 +8181,14 @@
         <v>92</v>
       </c>
     </row>
-    <row r="44" spans="1:8" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+    <row r="44" spans="1:8" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
       <c r="D44" s="40"/>
       <c r="E44" s="28" t="s">
         <v>79</v>
       </c>
       <c r="F44" s="28"/>
     </row>
-    <row r="45" spans="1:8" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+    <row r="45" spans="1:8" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
       <c r="D45" s="26"/>
       <c r="E45" s="29" t="s">
         <v>81</v>
@@ -8455,12 +8197,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="1:8" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+    <row r="46" spans="1:8" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
       <c r="D46" s="26"/>
       <c r="E46" s="29"/>
       <c r="F46" s="29"/>
     </row>
-    <row r="47" spans="1:8" s="3" customFormat="1" ht="29.4" customHeight="1">
+    <row r="47" spans="1:8" s="3" customFormat="1" ht="29.45" customHeight="1">
       <c r="D47" s="39"/>
       <c r="E47" s="28"/>
       <c r="F47" s="28"/>
@@ -8479,11 +8221,68 @@
     </row>
   </sheetData>
   <mergeCells count="74">
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="G3:I4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="A6:B9"/>
+    <mergeCell ref="C6:C9"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:F8"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
     <mergeCell ref="E32:E33"/>
     <mergeCell ref="F32:F33"/>
     <mergeCell ref="A34:A35"/>
@@ -8491,68 +8290,11 @@
     <mergeCell ref="C34:C35"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="F34:F35"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G3:I4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="A6:B9"/>
-    <mergeCell ref="C6:C9"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:F8"/>
-    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="50" orientation="portrait" r:id="rId1"/>

--- a/customers/cpall/excel_templates/logistic_plan_มหาชัย.xlsx
+++ b/customers/cpall/excel_templates/logistic_plan_มหาชัย.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gtdit\Downloads\Fw_ แบบฟอร์ม 7-11+แพลนรถ ของ PO 08_09  ค่ะ\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User7\Desktop\PRD-Plan\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F64111-D6E6-4873-A950-0D54A2B8EFD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AAB3F39-B8D1-44D4-892A-7DCE732D9A24}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="399" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="399" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="มหาชัย-ผลิต" sheetId="5" r:id="rId1"/>
@@ -21,9 +21,9 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'คันที่ 1'!$A$2:$F$49</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'คันที่ 2'!$A$1:$F$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'มหาชัย-ผลิต'!$B$2:$H$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'มหาชัย-ผลิต'!$B$4:$H$56</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,10 +31,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -64,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="148">
   <si>
     <t>PO1</t>
   </si>
@@ -469,6 +466,12 @@
     <t xml:space="preserve">Pear 400g ( 8859388010284 )    </t>
   </si>
   <si>
+    <t>เชอร์รี่สดนำเข้า150 กรัม(อเมริกา)x36P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cherry 150 g ( 8859388008885 )    </t>
+  </si>
+  <si>
     <t>องุ่นไซน์มัสแคท 300 กรัม x 15 P</t>
   </si>
   <si>
@@ -511,6 +514,9 @@
     <t xml:space="preserve">สตรอเบอร์รี่ 250 กรัม x 27 P </t>
   </si>
   <si>
+    <t xml:space="preserve">      วันที่ 18/08/69  ส่งวันที่ PO. 19/08/69</t>
+  </si>
+  <si>
     <t>สาลี่ทอง แพ็ก 4 ผล (800g.) x 8 P</t>
   </si>
   <si>
@@ -520,10 +526,7 @@
     <t>สาลี่ทอง แพ็ก 2 ผล (400g.) x 8 P</t>
   </si>
   <si>
-    <t xml:space="preserve">      วันที่ 07/09/69  ส่งวันที่ PO. 08/09/69</t>
-  </si>
-  <si>
-    <t>ผู้ส่ง : 7-11 มหาชัย  4 ล้อ 2841 พี่เบ้น</t>
+    <t>ผู้ส่ง : 7-11 มหาชัย 6 ล้อ 83-8096 พี่ปาล์ม+คาย</t>
   </si>
 </sst>
 </file>
@@ -534,14 +537,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -549,14 +552,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -642,7 +645,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -1084,23 +1087,23 @@
     </font>
     <font>
       <b/>
-      <sz val="45"/>
-      <color theme="1"/>
-      <name val="CordiaUPC"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="45"/>
+      <sz val="41"/>
       <color rgb="FF0000FF"/>
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="45"/>
+      <sz val="41"/>
       <color rgb="FF7030A0"/>
       <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="45"/>
+      <color theme="1"/>
+      <name val="CordiaUPC"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1642,7 +1645,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="247">
+  <cellXfs count="254">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1941,6 +1944,9 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1951,6 +1957,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1968,19 +1977,25 @@
     <xf numFmtId="0" fontId="79" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1995,31 +2010,40 @@
     <xf numFmtId="0" fontId="73" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="29" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="81" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="30" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="13" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="30" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="29" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="82" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="30" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="13" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2094,10 +2118,10 @@
     <xf numFmtId="0" fontId="57" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="5" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2139,16 +2163,16 @@
     <xf numFmtId="0" fontId="73" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="83" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="83" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="82" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="82" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2414,9 +2438,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>291938</xdr:colOff>
+      <xdr:colOff>196688</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>253999</xdr:rowOff>
+      <xdr:rowOff>158749</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3079912" cy="1167260"/>
     <xdr:pic>
@@ -2440,7 +2464,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="291938" y="444499"/>
+          <a:off x="196688" y="361949"/>
           <a:ext cx="3079912" cy="1167260"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2554,7 +2578,7 @@
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <global>
     <keyFlags>
       <key name="_Self">
@@ -2580,9 +2604,6 @@
         <flag name="ExcludeFromCalcComparison" value="1"/>
       </key>
       <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
         <flag name="ExcludeFromCalcComparison" value="1"/>
       </key>
       <key name="_ClassificationId">
@@ -2934,22 +2955,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:J134"/>
-  <sheetFormatPr defaultColWidth="5.6640625" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="B2:J136"/>
+  <sheetFormatPr defaultColWidth="5.75" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" style="64"/>
-    <col min="2" max="2" width="19.77734375" style="64" customWidth="1"/>
-    <col min="3" max="3" width="158.5546875" style="72" customWidth="1"/>
-    <col min="4" max="4" width="29.88671875" style="64" customWidth="1"/>
-    <col min="5" max="5" width="116.109375" style="64" customWidth="1"/>
-    <col min="6" max="6" width="30.88671875" style="64" customWidth="1"/>
-    <col min="7" max="7" width="33.88671875" style="64" customWidth="1"/>
-    <col min="8" max="8" width="45.88671875" style="64" customWidth="1"/>
-    <col min="9" max="9" width="11.5546875" style="64" customWidth="1"/>
-    <col min="10" max="16384" width="5.6640625" style="64"/>
+    <col min="1" max="1" width="5.75" style="64"/>
+    <col min="2" max="2" width="15.625" style="64" customWidth="1"/>
+    <col min="3" max="3" width="135" style="72" customWidth="1"/>
+    <col min="4" max="4" width="28.25" style="64" customWidth="1"/>
+    <col min="5" max="5" width="116.125" style="64" customWidth="1"/>
+    <col min="6" max="6" width="30.875" style="64" customWidth="1"/>
+    <col min="7" max="7" width="33.875" style="64" customWidth="1"/>
+    <col min="8" max="8" width="45.875" style="64" customWidth="1"/>
+    <col min="9" max="9" width="11.625" style="64" customWidth="1"/>
+    <col min="10" max="16384" width="5.75" style="64"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="58.95" customHeight="1"/>
+    <row r="2" spans="2:10" ht="58.9" customHeight="1"/>
     <row r="3" spans="2:10" ht="30.75" customHeight="1" thickBot="1">
       <c r="E3" s="65"/>
       <c r="F3" s="65"/>
@@ -2957,841 +2978,870 @@
       <c r="I3" s="65"/>
       <c r="J3" s="65"/>
     </row>
-    <row r="4" spans="2:10" ht="103.95" customHeight="1" thickBot="1">
-      <c r="B4" s="168" t="s">
-        <v>145</v>
-      </c>
-      <c r="C4" s="169"/>
-      <c r="D4" s="153" t="s">
-        <v>144</v>
-      </c>
-      <c r="E4" s="154"/>
-      <c r="F4" s="154"/>
-      <c r="G4" s="154"/>
-      <c r="H4" s="155"/>
+    <row r="4" spans="2:10" ht="103.9" customHeight="1" thickBot="1">
+      <c r="B4" s="175" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" s="176"/>
+      <c r="D4" s="160" t="s">
+        <v>143</v>
+      </c>
+      <c r="E4" s="161"/>
+      <c r="F4" s="161"/>
+      <c r="G4" s="161"/>
+      <c r="H4" s="162"/>
     </row>
     <row r="5" spans="2:10" s="67" customFormat="1" ht="15" customHeight="1">
-      <c r="B5" s="172" t="s">
+      <c r="B5" s="179" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="173"/>
-      <c r="D5" s="176" t="s">
+      <c r="C5" s="180"/>
+      <c r="D5" s="183" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="158" t="s">
+      <c r="E5" s="165" t="s">
         <v>111</v>
       </c>
-      <c r="F5" s="160" t="s">
+      <c r="F5" s="167" t="s">
         <v>72</v>
       </c>
-      <c r="G5" s="161"/>
-      <c r="H5" s="156" t="s">
+      <c r="G5" s="168"/>
+      <c r="H5" s="163" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="6" spans="2:10" s="67" customFormat="1" ht="30.6" customHeight="1" thickBot="1">
-      <c r="B6" s="174"/>
-      <c r="C6" s="175"/>
-      <c r="D6" s="177"/>
-      <c r="E6" s="159"/>
-      <c r="F6" s="162"/>
-      <c r="G6" s="163"/>
-      <c r="H6" s="157"/>
+      <c r="B6" s="181"/>
+      <c r="C6" s="182"/>
+      <c r="D6" s="184"/>
+      <c r="E6" s="166"/>
+      <c r="F6" s="169"/>
+      <c r="G6" s="170"/>
+      <c r="H6" s="164"/>
     </row>
     <row r="7" spans="2:10" s="67" customFormat="1" ht="58.5" customHeight="1" thickBot="1">
-      <c r="B7" s="174"/>
-      <c r="C7" s="175"/>
-      <c r="D7" s="177"/>
-      <c r="E7" s="159"/>
+      <c r="B7" s="181"/>
+      <c r="C7" s="182"/>
+      <c r="D7" s="184"/>
+      <c r="E7" s="166"/>
       <c r="F7" s="73" t="s">
         <v>75</v>
       </c>
       <c r="G7" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="H7" s="157"/>
+      <c r="H7" s="164"/>
     </row>
     <row r="8" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B8" s="164">
+      <c r="B8" s="171">
         <v>1</v>
       </c>
-      <c r="C8" s="104" t="s">
+      <c r="C8" s="106" t="s">
         <v>115</v>
       </c>
-      <c r="D8" s="164">
+      <c r="D8" s="171">
         <v>36</v>
       </c>
-      <c r="E8" s="122"/>
-      <c r="F8" s="151">
+      <c r="E8" s="125"/>
+      <c r="F8" s="158">
         <f>SUM(E8:E8)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="127">
+      <c r="G8" s="134">
         <f>มหาชัย!C10</f>
         <v>0</v>
       </c>
-      <c r="H8" s="129"/>
+      <c r="H8" s="136"/>
     </row>
     <row r="9" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B9" s="165"/>
-      <c r="C9" s="108" t="s">
+      <c r="B9" s="172"/>
+      <c r="C9" s="110" t="s">
         <v>116</v>
       </c>
-      <c r="D9" s="165"/>
-      <c r="E9" s="123" t="str">
+      <c r="D9" s="172"/>
+      <c r="E9" s="126" t="str">
         <f>IF(E8=0, "", IF(MOD(E8, $D$8) = 0, E8 / $D$8, IF(INT(E8 / $D$8) = 0, MOD(E8, $D$8) &amp; " P", INT(E8 / $D$8) &amp; " + " &amp; MOD(E8, $D$8) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F9" s="152"/>
-      <c r="G9" s="128"/>
-      <c r="H9" s="130"/>
+      <c r="F9" s="159"/>
+      <c r="G9" s="135"/>
+      <c r="H9" s="137"/>
     </row>
     <row r="10" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B10" s="164">
+      <c r="B10" s="171">
         <v>2</v>
       </c>
-      <c r="C10" s="105" t="s">
+      <c r="C10" s="107" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="164">
+      <c r="D10" s="171">
         <v>32</v>
       </c>
-      <c r="E10" s="122"/>
-      <c r="F10" s="151">
+      <c r="E10" s="125"/>
+      <c r="F10" s="158">
         <f>SUM(E10:E10)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="127">
+      <c r="G10" s="134">
         <f>มหาชัย!C11</f>
         <v>0</v>
       </c>
-      <c r="H10" s="129"/>
+      <c r="H10" s="136"/>
     </row>
     <row r="11" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B11" s="165"/>
-      <c r="C11" s="108" t="s">
+      <c r="B11" s="172"/>
+      <c r="C11" s="110" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="165"/>
-      <c r="E11" s="123" t="str">
+      <c r="D11" s="172"/>
+      <c r="E11" s="126" t="str">
         <f>IF(E10=0, "", IF(MOD(E10, $D$10) = 0, E10 / $D$10, IF(INT(E10 / $D$10) = 0, MOD(E10, $D$10) &amp; " P", INT(E10 / $D$10) &amp; " + " &amp; MOD(E10, $D$10) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F11" s="152"/>
-      <c r="G11" s="128"/>
-      <c r="H11" s="130"/>
+      <c r="F11" s="159"/>
+      <c r="G11" s="135"/>
+      <c r="H11" s="137"/>
     </row>
     <row r="12" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B12" s="116">
+      <c r="B12" s="171">
         <v>3</v>
       </c>
-      <c r="C12" s="105" t="s">
-        <v>136</v>
-      </c>
-      <c r="D12" s="164">
-        <v>14</v>
-      </c>
-      <c r="E12" s="122"/>
-      <c r="F12" s="151">
+      <c r="C12" s="107" t="s">
+        <v>127</v>
+      </c>
+      <c r="D12" s="138">
+        <v>36</v>
+      </c>
+      <c r="E12" s="125"/>
+      <c r="F12" s="158">
         <f>SUM(E12:E12)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="127">
+      <c r="G12" s="134">
         <f>มหาชัย!C12</f>
         <v>0</v>
       </c>
-      <c r="H12" s="129"/>
+      <c r="H12" s="136"/>
     </row>
     <row r="13" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B13" s="117"/>
-      <c r="C13" s="108" t="s">
-        <v>137</v>
-      </c>
-      <c r="D13" s="165"/>
-      <c r="E13" s="123" t="str">
+      <c r="B13" s="172"/>
+      <c r="C13" s="110" t="s">
+        <v>128</v>
+      </c>
+      <c r="D13" s="139"/>
+      <c r="E13" s="126" t="str">
         <f>IF(E12=0, "", IF(MOD(E12, $D$12) = 0, E12/ $D$12, IF(INT(E12 / $D$12) = 0, MOD(E12, $D$12) &amp; " P", INT(E12 / $D$12) &amp; " + " &amp; MOD(E12, $D$12) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F13" s="152"/>
-      <c r="G13" s="128"/>
-      <c r="H13" s="130"/>
+      <c r="F13" s="159"/>
+      <c r="G13" s="135"/>
+      <c r="H13" s="137"/>
     </row>
     <row r="14" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B14" s="116">
+      <c r="B14" s="120">
         <v>4</v>
       </c>
-      <c r="C14" s="105" t="s">
+      <c r="C14" s="107" t="s">
         <v>138</v>
       </c>
-      <c r="D14" s="164">
+      <c r="D14" s="171">
         <v>14</v>
       </c>
-      <c r="E14" s="122"/>
-      <c r="F14" s="151">
+      <c r="E14" s="125"/>
+      <c r="F14" s="158">
         <f>SUM(E14:E14)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="127">
+      <c r="G14" s="134">
         <f>มหาชัย!C13</f>
         <v>0</v>
       </c>
-      <c r="H14" s="129"/>
+      <c r="H14" s="136"/>
     </row>
     <row r="15" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B15" s="117"/>
-      <c r="C15" s="108" t="s">
+      <c r="B15" s="121"/>
+      <c r="C15" s="110" t="s">
         <v>139</v>
       </c>
-      <c r="D15" s="165"/>
-      <c r="E15" s="123" t="str">
+      <c r="D15" s="172"/>
+      <c r="E15" s="126" t="str">
         <f>IF(E14=0, "", IF(MOD(E14, $D$14) = 0, E14/ $D$14, IF(INT(E14 / $D$14) = 0, MOD(E14, $D$14) &amp; " P", INT(E14 / $D$14) &amp; " + " &amp; MOD(E14, $D$14) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F15" s="152"/>
-      <c r="G15" s="128"/>
-      <c r="H15" s="130"/>
+      <c r="F15" s="159"/>
+      <c r="G15" s="135"/>
+      <c r="H15" s="137"/>
     </row>
     <row r="16" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B16" s="114">
+      <c r="B16" s="120">
         <v>5</v>
       </c>
-      <c r="C16" s="105" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" s="131">
-        <v>32</v>
-      </c>
-      <c r="E16" s="122"/>
-      <c r="F16" s="151">
+      <c r="C16" s="107" t="s">
+        <v>140</v>
+      </c>
+      <c r="D16" s="171">
+        <v>14</v>
+      </c>
+      <c r="E16" s="125"/>
+      <c r="F16" s="158">
         <f>SUM(E16:E16)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="127">
+      <c r="G16" s="134">
         <f>มหาชัย!C14</f>
         <v>0</v>
       </c>
-      <c r="H16" s="129"/>
+      <c r="H16" s="136"/>
     </row>
     <row r="17" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B17" s="115"/>
-      <c r="C17" s="108" t="s">
-        <v>120</v>
-      </c>
-      <c r="D17" s="132"/>
-      <c r="E17" s="123" t="str">
+      <c r="B17" s="121"/>
+      <c r="C17" s="110" t="s">
+        <v>141</v>
+      </c>
+      <c r="D17" s="172"/>
+      <c r="E17" s="126" t="str">
         <f>IF(E16=0, "", IF(MOD(E16, $D$16) = 0, E16/ $D$16, IF(INT(E16 / $D$16) = 0, MOD(E16, $D$16) &amp; " P", INT(E16 / $D$16) &amp; " + " &amp; MOD(E16, $D$16) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F17" s="152"/>
-      <c r="G17" s="128"/>
-      <c r="H17" s="130"/>
+      <c r="F17" s="159"/>
+      <c r="G17" s="135"/>
+      <c r="H17" s="137"/>
     </row>
     <row r="18" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1">
       <c r="B18" s="118">
         <v>6</v>
       </c>
-      <c r="C18" s="104" t="s">
-        <v>134</v>
-      </c>
-      <c r="D18" s="131">
-        <v>27</v>
-      </c>
-      <c r="E18" s="124"/>
-      <c r="F18" s="166">
+      <c r="C18" s="107" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="138">
+        <v>32</v>
+      </c>
+      <c r="E18" s="125"/>
+      <c r="F18" s="158">
         <f>SUM(E18:E18)</f>
         <v>0</v>
       </c>
-      <c r="G18" s="127">
+      <c r="G18" s="134">
         <f>มหาชัย!C15</f>
         <v>0</v>
       </c>
-      <c r="H18" s="129"/>
+      <c r="H18" s="136"/>
     </row>
     <row r="19" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
       <c r="B19" s="119"/>
-      <c r="C19" s="108" t="s">
-        <v>135</v>
-      </c>
-      <c r="D19" s="132"/>
-      <c r="E19" s="123" t="str">
+      <c r="C19" s="110" t="s">
+        <v>120</v>
+      </c>
+      <c r="D19" s="139"/>
+      <c r="E19" s="126" t="str">
         <f>IF(E18=0, "", IF(MOD(E18, $D$18) = 0, E18/ $D$18, IF(INT(E18 / $D$18) = 0, MOD(E18, $D$18) &amp; " P", INT(E18 / $D$18) &amp; " + " &amp; MOD(E18, $D$18) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F19" s="167"/>
-      <c r="G19" s="128"/>
-      <c r="H19" s="130"/>
+      <c r="F19" s="159"/>
+      <c r="G19" s="135"/>
+      <c r="H19" s="137"/>
     </row>
     <row r="20" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B20" s="116">
+      <c r="B20" s="123">
         <v>7</v>
       </c>
       <c r="C20" s="106" t="s">
-        <v>140</v>
-      </c>
-      <c r="D20" s="131">
+        <v>136</v>
+      </c>
+      <c r="D20" s="138">
         <v>27</v>
       </c>
-      <c r="E20" s="122"/>
-      <c r="F20" s="151">
+      <c r="E20" s="127"/>
+      <c r="F20" s="173">
         <f>SUM(E20:E20)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="127">
+      <c r="G20" s="134">
         <f>มหาชัย!C16</f>
         <v>0</v>
       </c>
-      <c r="H20" s="129"/>
+      <c r="H20" s="136"/>
     </row>
     <row r="21" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B21" s="117"/>
-      <c r="C21" s="108" t="s">
-        <v>122</v>
-      </c>
-      <c r="D21" s="132"/>
-      <c r="E21" s="123" t="str">
+      <c r="B21" s="124"/>
+      <c r="C21" s="110" t="s">
+        <v>137</v>
+      </c>
+      <c r="D21" s="139"/>
+      <c r="E21" s="126" t="str">
         <f>IF(E20=0, "", IF(MOD(E20, $D$20) = 0, E20/ $D$20, IF(INT(E20 / $D$20) = 0, MOD(E20, $D$20) &amp; " P", INT(E20 / $D$20) &amp; " + " &amp; MOD(E20, $D$20) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F21" s="152"/>
-      <c r="G21" s="128"/>
-      <c r="H21" s="130"/>
+      <c r="F21" s="174"/>
+      <c r="G21" s="135"/>
+      <c r="H21" s="137"/>
     </row>
     <row r="22" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B22" s="116">
+      <c r="B22" s="120">
         <v>8</v>
       </c>
-      <c r="C22" s="107" t="s">
-        <v>63</v>
-      </c>
-      <c r="D22" s="131">
-        <v>36</v>
-      </c>
-      <c r="E22" s="122"/>
-      <c r="F22" s="151">
+      <c r="C22" s="108" t="s">
+        <v>142</v>
+      </c>
+      <c r="D22" s="138">
+        <v>27</v>
+      </c>
+      <c r="E22" s="125"/>
+      <c r="F22" s="158">
         <f>SUM(E22:E22)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="127">
+      <c r="G22" s="134">
         <f>มหาชัย!C17</f>
         <v>0</v>
       </c>
-      <c r="H22" s="129"/>
+      <c r="H22" s="136"/>
     </row>
     <row r="23" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B23" s="117"/>
-      <c r="C23" s="120" t="s">
-        <v>119</v>
-      </c>
-      <c r="D23" s="132"/>
-      <c r="E23" s="123" t="str">
+      <c r="B23" s="121"/>
+      <c r="C23" s="110" t="s">
+        <v>122</v>
+      </c>
+      <c r="D23" s="139"/>
+      <c r="E23" s="126" t="str">
         <f>IF(E22=0, "", IF(MOD(E22, $D$22) = 0, E22/ $D$22, IF(INT(E22 / $D$22) = 0, MOD(E22, $D$22) &amp; " P", INT(E22 / $D$22) &amp; " + " &amp; MOD(E22, $D$22) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F23" s="152"/>
-      <c r="G23" s="128"/>
-      <c r="H23" s="130"/>
+      <c r="F23" s="159"/>
+      <c r="G23" s="135"/>
+      <c r="H23" s="137"/>
     </row>
     <row r="24" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B24" s="116">
+      <c r="B24" s="120">
         <v>9</v>
       </c>
-      <c r="C24" s="105" t="s">
-        <v>114</v>
-      </c>
-      <c r="D24" s="131">
-        <v>20</v>
-      </c>
-      <c r="E24" s="122"/>
-      <c r="F24" s="151">
+      <c r="C24" s="109" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="138">
+        <v>36</v>
+      </c>
+      <c r="E24" s="125"/>
+      <c r="F24" s="158">
         <f>SUM(E24:E24)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="127">
+      <c r="G24" s="134">
         <f>มหาชัย!C18</f>
         <v>0</v>
       </c>
-      <c r="H24" s="129"/>
+      <c r="H24" s="136"/>
     </row>
     <row r="25" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B25" s="117"/>
-      <c r="C25" s="108" t="s">
-        <v>117</v>
-      </c>
-      <c r="D25" s="132"/>
-      <c r="E25" s="123" t="str">
+      <c r="B25" s="121"/>
+      <c r="C25" s="128" t="s">
+        <v>119</v>
+      </c>
+      <c r="D25" s="139"/>
+      <c r="E25" s="126" t="str">
         <f>IF(E24=0, "", IF(MOD(E24, $D$24) = 0, E24/ $D$24, IF(INT(E24 / $D$24) = 0, MOD(E24, $D$24) &amp; " P", INT(E24 / $D$24) &amp; " + " &amp; MOD(E24, $D$24) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F25" s="152"/>
-      <c r="G25" s="128"/>
-      <c r="H25" s="130"/>
+      <c r="F25" s="159"/>
+      <c r="G25" s="135"/>
+      <c r="H25" s="137"/>
     </row>
     <row r="26" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B26" s="116">
+      <c r="B26" s="120">
         <v>10</v>
       </c>
       <c r="C26" s="107" t="s">
-        <v>127</v>
-      </c>
-      <c r="D26" s="170">
-        <v>15</v>
+        <v>114</v>
+      </c>
+      <c r="D26" s="138">
+        <v>20</v>
       </c>
       <c r="E26" s="125"/>
-      <c r="F26" s="151">
+      <c r="F26" s="158">
         <f>SUM(E26:E26)</f>
         <v>0</v>
       </c>
-      <c r="G26" s="127">
+      <c r="G26" s="134">
         <f>มหาชัย!C19</f>
         <v>0</v>
       </c>
-      <c r="H26" s="129"/>
+      <c r="H26" s="136"/>
     </row>
     <row r="27" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B27" s="117"/>
-      <c r="C27" s="108" t="s">
-        <v>128</v>
-      </c>
-      <c r="D27" s="171"/>
+      <c r="B27" s="121"/>
+      <c r="C27" s="110" t="s">
+        <v>117</v>
+      </c>
+      <c r="D27" s="139"/>
       <c r="E27" s="126" t="str">
         <f>IF(E26=0, "", IF(MOD(E26, $D$26) = 0, E26/ $D$26, IF(INT(E26 / $D$26) = 0, MOD(E26, $D$26) &amp; " P", INT(E26 / $D$26) &amp; " + " &amp; MOD(E26, $D$26) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F27" s="152"/>
-      <c r="G27" s="128"/>
-      <c r="H27" s="130"/>
+      <c r="F27" s="159"/>
+      <c r="G27" s="135"/>
+      <c r="H27" s="137"/>
     </row>
     <row r="28" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B28" s="116">
+      <c r="B28" s="120">
         <v>11</v>
       </c>
-      <c r="C28" s="107" t="s">
-        <v>65</v>
-      </c>
-      <c r="D28" s="131">
-        <v>45</v>
-      </c>
-      <c r="E28" s="125"/>
-      <c r="F28" s="151">
+      <c r="C28" s="109" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" s="177">
+        <v>15</v>
+      </c>
+      <c r="E28" s="129"/>
+      <c r="F28" s="158">
         <f>SUM(E28:E28)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="127">
+      <c r="G28" s="134">
         <f>มหาชัย!C20</f>
         <v>0</v>
       </c>
-      <c r="H28" s="129"/>
+      <c r="H28" s="136"/>
     </row>
     <row r="29" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B29" s="117"/>
-      <c r="C29" s="108" t="s">
-        <v>118</v>
-      </c>
-      <c r="D29" s="132"/>
-      <c r="E29" s="126" t="str">
+      <c r="B29" s="121"/>
+      <c r="C29" s="110" t="s">
+        <v>130</v>
+      </c>
+      <c r="D29" s="178"/>
+      <c r="E29" s="130" t="str">
         <f>IF(E28=0, "", IF(MOD(E28, $D$28) = 0, E28/ $D$28, IF(INT(E28 / $D$28) = 0, MOD(E28, $D$28) &amp; " P", INT(E28 / $D$28) &amp; " + " &amp; MOD(E28, $D$28) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F29" s="152"/>
-      <c r="G29" s="128"/>
-      <c r="H29" s="130"/>
+      <c r="F29" s="159"/>
+      <c r="G29" s="135"/>
+      <c r="H29" s="137"/>
     </row>
     <row r="30" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B30" s="116">
+      <c r="B30" s="120">
         <v>12</v>
       </c>
-      <c r="C30" s="107" t="s">
-        <v>132</v>
-      </c>
-      <c r="D30" s="131">
-        <v>15</v>
-      </c>
-      <c r="E30" s="125"/>
-      <c r="F30" s="151">
+      <c r="C30" s="109" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="138">
+        <v>45</v>
+      </c>
+      <c r="E30" s="131"/>
+      <c r="F30" s="158">
         <f>SUM(E30:E30)</f>
         <v>0</v>
       </c>
-      <c r="G30" s="127">
+      <c r="G30" s="134">
         <f>มหาชัย!C21</f>
         <v>0</v>
       </c>
-      <c r="H30" s="129"/>
+      <c r="H30" s="136"/>
     </row>
     <row r="31" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B31" s="117"/>
-      <c r="C31" s="108" t="s">
-        <v>133</v>
-      </c>
-      <c r="D31" s="132"/>
-      <c r="E31" s="126" t="str">
+      <c r="B31" s="121"/>
+      <c r="C31" s="110" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31" s="139"/>
+      <c r="E31" s="130" t="str">
         <f>IF(E30=0, "", IF(MOD(E30, $D$30) = 0, E30/ $D$30, IF(INT(E30 / $D$30) = 0, MOD(E30, $D$30) &amp; " P", INT(E30 / $D$30) &amp; " + " &amp; MOD(E30, $D$30) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F31" s="152"/>
-      <c r="G31" s="128"/>
-      <c r="H31" s="130"/>
+      <c r="F31" s="159"/>
+      <c r="G31" s="135"/>
+      <c r="H31" s="137"/>
     </row>
     <row r="32" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B32" s="121">
+      <c r="B32" s="120">
         <v>13</v>
       </c>
-      <c r="C32" s="105" t="s">
-        <v>66</v>
-      </c>
-      <c r="D32" s="131">
+      <c r="C32" s="109" t="s">
+        <v>134</v>
+      </c>
+      <c r="D32" s="138">
         <v>15</v>
       </c>
-      <c r="E32" s="125"/>
-      <c r="F32" s="151">
+      <c r="E32" s="131"/>
+      <c r="F32" s="158">
         <f>SUM(E32:E32)</f>
         <v>0</v>
       </c>
-      <c r="G32" s="127">
+      <c r="G32" s="134">
         <f>มหาชัย!C22</f>
         <v>0</v>
       </c>
-      <c r="H32" s="129"/>
+      <c r="H32" s="136"/>
     </row>
     <row r="33" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B33" s="119"/>
-      <c r="C33" s="108" t="s">
-        <v>123</v>
-      </c>
-      <c r="D33" s="132"/>
-      <c r="E33" s="126" t="str">
+      <c r="B33" s="121"/>
+      <c r="C33" s="110" t="s">
+        <v>135</v>
+      </c>
+      <c r="D33" s="139"/>
+      <c r="E33" s="130" t="str">
         <f>IF(E32=0, "", IF(MOD(E32, $D$32) = 0, E32/ $D$32, IF(INT(E32 / $D$32) = 0, MOD(E32, $D$32) &amp; " P", INT(E32 / $D$32) &amp; " + " &amp; MOD(E32, $D$32) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F33" s="152"/>
-      <c r="G33" s="128"/>
-      <c r="H33" s="130"/>
+      <c r="F33" s="159"/>
+      <c r="G33" s="135"/>
+      <c r="H33" s="137"/>
     </row>
     <row r="34" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B34" s="121">
+      <c r="B34" s="132">
         <v>14</v>
       </c>
       <c r="C34" s="107" t="s">
-        <v>130</v>
-      </c>
-      <c r="D34" s="131">
-        <v>27</v>
-      </c>
-      <c r="E34" s="125"/>
-      <c r="F34" s="151">
+        <v>66</v>
+      </c>
+      <c r="D34" s="138">
+        <v>15</v>
+      </c>
+      <c r="E34" s="131"/>
+      <c r="F34" s="158">
         <f>SUM(E34:E34)</f>
         <v>0</v>
       </c>
-      <c r="G34" s="127">
+      <c r="G34" s="134">
         <f>มหาชัย!C23</f>
         <v>0</v>
       </c>
-      <c r="H34" s="129"/>
+      <c r="H34" s="136"/>
     </row>
     <row r="35" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B35" s="119"/>
-      <c r="C35" s="108" t="s">
-        <v>131</v>
-      </c>
-      <c r="D35" s="132"/>
-      <c r="E35" s="126" t="str">
+      <c r="B35" s="124"/>
+      <c r="C35" s="110" t="s">
+        <v>123</v>
+      </c>
+      <c r="D35" s="139"/>
+      <c r="E35" s="130" t="str">
         <f>IF(E34=0, "", IF(MOD(E34, $D$34) = 0, E34/ $D$34, IF(INT(E34 / $D$34) = 0, MOD(E34, $D$34) &amp; " P", INT(E34 / $D$34) &amp; " + " &amp; MOD(E34, $D$34) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F35" s="152"/>
-      <c r="G35" s="128"/>
-      <c r="H35" s="130"/>
+      <c r="F35" s="159"/>
+      <c r="G35" s="135"/>
+      <c r="H35" s="137"/>
     </row>
     <row r="36" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B36" s="121">
+      <c r="B36" s="132">
         <v>15</v>
       </c>
-      <c r="C36" s="107" t="s">
-        <v>68</v>
-      </c>
-      <c r="D36" s="131">
-        <v>20</v>
-      </c>
-      <c r="E36" s="125"/>
-      <c r="F36" s="151">
+      <c r="C36" s="109" t="s">
+        <v>132</v>
+      </c>
+      <c r="D36" s="138">
+        <v>27</v>
+      </c>
+      <c r="E36" s="131"/>
+      <c r="F36" s="158">
         <f>SUM(E36:E36)</f>
         <v>0</v>
       </c>
-      <c r="G36" s="127">
+      <c r="G36" s="134">
         <f>มหาชัย!C24</f>
         <v>0</v>
       </c>
-      <c r="H36" s="129"/>
+      <c r="H36" s="136"/>
     </row>
     <row r="37" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B37" s="119"/>
-      <c r="C37" s="108" t="s">
-        <v>124</v>
-      </c>
-      <c r="D37" s="132"/>
-      <c r="E37" s="126" t="str">
+      <c r="B37" s="124"/>
+      <c r="C37" s="110" t="s">
+        <v>133</v>
+      </c>
+      <c r="D37" s="139"/>
+      <c r="E37" s="130" t="str">
         <f>IF(E36=0, "", IF(MOD(E36, $D$36) = 0, E36/ $D$36, IF(INT(E36 / $D$36) = 0, MOD(E36, $D$36) &amp; " P", INT(E36 / $D$36) &amp; " + " &amp; MOD(E36, $D$36) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F37" s="152"/>
-      <c r="G37" s="128"/>
-      <c r="H37" s="130"/>
+      <c r="F37" s="159"/>
+      <c r="G37" s="135"/>
+      <c r="H37" s="137"/>
     </row>
     <row r="38" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B38" s="121">
+      <c r="B38" s="132">
         <v>16</v>
       </c>
-      <c r="C38" s="106" t="s">
-        <v>69</v>
-      </c>
-      <c r="D38" s="131">
-        <v>32</v>
-      </c>
-      <c r="E38" s="125"/>
-      <c r="F38" s="151">
+      <c r="C38" s="109" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" s="138">
+        <v>20</v>
+      </c>
+      <c r="E38" s="131"/>
+      <c r="F38" s="158">
         <f>SUM(E38:E38)</f>
         <v>0</v>
       </c>
-      <c r="G38" s="127">
+      <c r="G38" s="134">
         <f>มหาชัย!C25</f>
         <v>0</v>
       </c>
-      <c r="H38" s="129"/>
+      <c r="H38" s="136"/>
     </row>
     <row r="39" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B39" s="119"/>
-      <c r="C39" s="108" t="s">
-        <v>125</v>
-      </c>
-      <c r="D39" s="132"/>
-      <c r="E39" s="126" t="str">
+      <c r="B39" s="124"/>
+      <c r="C39" s="110" t="s">
+        <v>124</v>
+      </c>
+      <c r="D39" s="139"/>
+      <c r="E39" s="130" t="str">
         <f>IF(E38=0, "", IF(MOD(E38, $D$38) = 0, E38/ $D$38, IF(INT(E38 / $D$38) = 0, MOD(E38, $D$38) &amp; " P", INT(E38 / $D$38) &amp; " + " &amp; MOD(E38, $D$38) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F39" s="152"/>
-      <c r="G39" s="128"/>
-      <c r="H39" s="130"/>
+      <c r="F39" s="159"/>
+      <c r="G39" s="135"/>
+      <c r="H39" s="137"/>
     </row>
     <row r="40" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B40" s="121">
+      <c r="B40" s="132">
         <v>17</v>
       </c>
-      <c r="C40" s="105" t="s">
-        <v>113</v>
-      </c>
-      <c r="D40" s="131">
-        <v>15</v>
-      </c>
-      <c r="E40" s="125"/>
-      <c r="F40" s="151">
+      <c r="C40" s="108" t="s">
+        <v>69</v>
+      </c>
+      <c r="D40" s="138">
+        <v>32</v>
+      </c>
+      <c r="E40" s="131"/>
+      <c r="F40" s="158">
         <f>SUM(E40:E40)</f>
         <v>0</v>
       </c>
-      <c r="G40" s="127">
+      <c r="G40" s="134">
         <f>มหาชัย!C26</f>
         <v>0</v>
       </c>
-      <c r="H40" s="129"/>
+      <c r="H40" s="136"/>
     </row>
     <row r="41" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B41" s="119"/>
-      <c r="C41" s="108" t="s">
-        <v>126</v>
-      </c>
-      <c r="D41" s="132"/>
-      <c r="E41" s="126" t="str">
+      <c r="B41" s="124"/>
+      <c r="C41" s="110" t="s">
+        <v>125</v>
+      </c>
+      <c r="D41" s="139"/>
+      <c r="E41" s="130" t="str">
         <f>IF(E40=0, "", IF(MOD(E40, $D$40) = 0, E40/ $D$40, IF(INT(E40 / $D$40) = 0, MOD(E40, $D$40) &amp; " P", INT(E40 / $D$40) &amp; " + " &amp; MOD(E40, $D$40) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F41" s="152"/>
-      <c r="G41" s="128"/>
-      <c r="H41" s="130"/>
+      <c r="F41" s="159"/>
+      <c r="G41" s="135"/>
+      <c r="H41" s="137"/>
     </row>
     <row r="42" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B42" s="121">
+      <c r="B42" s="132">
         <v>18</v>
       </c>
-      <c r="C42" s="105" t="s">
-        <v>141</v>
-      </c>
-      <c r="D42" s="131">
-        <v>8</v>
-      </c>
-      <c r="E42" s="125"/>
-      <c r="F42" s="151">
+      <c r="C42" s="107" t="s">
+        <v>113</v>
+      </c>
+      <c r="D42" s="138">
+        <v>15</v>
+      </c>
+      <c r="E42" s="131"/>
+      <c r="F42" s="158">
         <f>SUM(E42:E42)</f>
         <v>0</v>
       </c>
-      <c r="G42" s="127">
+      <c r="G42" s="134">
         <f>มหาชัย!C27</f>
         <v>0</v>
       </c>
-      <c r="H42" s="129"/>
+      <c r="H42" s="136"/>
     </row>
     <row r="43" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B43" s="119"/>
-      <c r="C43" s="108" t="s">
-        <v>142</v>
-      </c>
-      <c r="D43" s="132"/>
-      <c r="E43" s="126" t="str">
+      <c r="B43" s="124"/>
+      <c r="C43" s="110" t="s">
+        <v>126</v>
+      </c>
+      <c r="D43" s="139"/>
+      <c r="E43" s="130" t="str">
         <f>IF(E42=0, "", IF(MOD(E42, $D$42) = 0, E42/ $D$42, IF(INT(E42 / $D$42) = 0, MOD(E42, $D$42) &amp; " P", INT(E42 / $D$42) &amp; " + " &amp; MOD(E42, $D$42) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F43" s="152"/>
-      <c r="G43" s="128"/>
-      <c r="H43" s="130"/>
-    </row>
-    <row r="44" spans="2:9" s="67" customFormat="1" ht="102" customHeight="1" thickBot="1">
-      <c r="B44" s="148" t="s">
+      <c r="F43" s="159"/>
+      <c r="G43" s="135"/>
+      <c r="H43" s="137"/>
+    </row>
+    <row r="44" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
+      <c r="B44" s="132">
+        <v>19</v>
+      </c>
+      <c r="C44" s="107" t="s">
+        <v>144</v>
+      </c>
+      <c r="D44" s="138">
+        <v>8</v>
+      </c>
+      <c r="E44" s="131"/>
+      <c r="F44" s="158">
+        <f>SUM(E44:E44)</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="134">
+        <f>มหาชัย!C28</f>
+        <v>0</v>
+      </c>
+      <c r="H44" s="136"/>
+    </row>
+    <row r="45" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
+      <c r="B45" s="124"/>
+      <c r="C45" s="110" t="s">
+        <v>145</v>
+      </c>
+      <c r="D45" s="139"/>
+      <c r="E45" s="130" t="str">
+        <f>IF(E44=0, "", IF(MOD(E44, $D$44) = 0, E44/ $D$44, IF(INT(E44 / $D$44) = 0, MOD(E44, $D$44) &amp; " P", INT(E44 / $D$44) &amp; " + " &amp; MOD(E44, $D$44) &amp; " P")))</f>
+        <v/>
+      </c>
+      <c r="F45" s="159"/>
+      <c r="G45" s="135"/>
+      <c r="H45" s="137"/>
+    </row>
+    <row r="46" spans="2:9" s="67" customFormat="1" ht="102" customHeight="1" thickBot="1">
+      <c r="B46" s="155" t="s">
         <v>88</v>
       </c>
-      <c r="C44" s="149"/>
-      <c r="D44" s="150"/>
-      <c r="E44" s="77">
-        <f>G44</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="78" t="s">
+      <c r="C46" s="156"/>
+      <c r="D46" s="157"/>
+      <c r="E46" s="77">
+        <f>-SUM(ROUNDUP(E8/$D$8,0), ROUNDUP(E10/$D$10,0), ROUNDUP(E12/$D$12,0), ROUNDUP(E14/$D$14,0), ROUNDUP(E16/$D$16,0), ROUNDUP(E18/$D$18,0), ROUNDUP(E20/$D$20,0), ROUNDUP(E22/$D$22,0), ROUNDUP(E24/$D$24,0), ROUNDUP(E26/$D$26,0), ROUNDUP(E28/$D$28,0), ROUNDUP(E30/$D$30,0), ROUNDUP(E32/$D$32,0), ROUNDUP(E34/$D$34,0), ROUNDUP(E36/$D$36,0), ROUNDUP(E38/$D$38,0), ROUNDUP(E40/$D$40,0), ROUNDUP(E42/$D$42,0), ROUNDUP(E44/$D$44,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F46" s="78" t="s">
         <v>90</v>
       </c>
-      <c r="G44" s="79">
-        <f>SUM(G8:G43)</f>
-        <v>0</v>
-      </c>
-      <c r="H44" s="70"/>
-      <c r="I44" s="69"/>
-    </row>
-    <row r="45" spans="2:9" ht="17.399999999999999" customHeight="1" thickBot="1">
-      <c r="E45" s="80"/>
-      <c r="F45" s="81"/>
-      <c r="G45" s="82"/>
-      <c r="H45" s="66"/>
-      <c r="I45" s="66"/>
-    </row>
-    <row r="46" spans="2:9" ht="76.8" customHeight="1" thickBot="1">
-      <c r="B46" s="139" t="s">
+      <c r="G46" s="79">
+        <f>SUM(G8:G45)</f>
+        <v>0</v>
+      </c>
+      <c r="H46" s="70"/>
+      <c r="I46" s="69"/>
+    </row>
+    <row r="47" spans="2:9" ht="17.45" customHeight="1" thickBot="1">
+      <c r="E47" s="80"/>
+      <c r="F47" s="81"/>
+      <c r="G47" s="82"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="66"/>
+    </row>
+    <row r="48" spans="2:9" ht="105" customHeight="1" thickBot="1">
+      <c r="B48" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="C46" s="147"/>
-      <c r="D46" s="140"/>
-      <c r="E46" s="84" t="s">
+      <c r="C48" s="154"/>
+      <c r="D48" s="147"/>
+      <c r="E48" s="84" t="s">
         <v>53</v>
       </c>
-      <c r="F46" s="139" t="s">
+      <c r="F48" s="146" t="s">
         <v>54</v>
       </c>
-      <c r="G46" s="140"/>
-      <c r="H46" s="84" t="s">
+      <c r="G48" s="147"/>
+      <c r="H48" s="84" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="47" spans="2:9" ht="62.4" customHeight="1">
-      <c r="B47" s="92" t="s">
+    <row r="49" spans="2:8" ht="62.45" customHeight="1">
+      <c r="B49" s="92" t="s">
         <v>78</v>
       </c>
-      <c r="C47" s="145"/>
-      <c r="D47" s="146"/>
-      <c r="E47" s="93"/>
-      <c r="F47" s="137"/>
-      <c r="G47" s="138"/>
-      <c r="H47" s="93"/>
-    </row>
-    <row r="48" spans="2:9" ht="62.4" customHeight="1">
-      <c r="B48" s="94" t="s">
+      <c r="C49" s="152"/>
+      <c r="D49" s="153"/>
+      <c r="E49" s="93"/>
+      <c r="F49" s="144"/>
+      <c r="G49" s="145"/>
+      <c r="H49" s="93"/>
+    </row>
+    <row r="50" spans="2:8" ht="62.45" customHeight="1">
+      <c r="B50" s="94" t="s">
         <v>80</v>
       </c>
-      <c r="C48" s="143"/>
-      <c r="D48" s="144"/>
-      <c r="E48" s="95"/>
-      <c r="F48" s="135"/>
-      <c r="G48" s="136"/>
-      <c r="H48" s="95"/>
-    </row>
-    <row r="49" spans="2:8" ht="62.4" customHeight="1" thickBot="1">
-      <c r="B49" s="96" t="s">
+      <c r="C50" s="150"/>
+      <c r="D50" s="151"/>
+      <c r="E50" s="95"/>
+      <c r="F50" s="142"/>
+      <c r="G50" s="143"/>
+      <c r="H50" s="95"/>
+    </row>
+    <row r="51" spans="2:8" ht="62.45" customHeight="1" thickBot="1">
+      <c r="B51" s="96" t="s">
         <v>82</v>
       </c>
-      <c r="C49" s="141"/>
-      <c r="D49" s="142"/>
-      <c r="E49" s="97"/>
-      <c r="F49" s="133"/>
-      <c r="G49" s="134"/>
-      <c r="H49" s="97"/>
-    </row>
-    <row r="51" spans="2:8" ht="102.6" customHeight="1">
-      <c r="C51" s="85"/>
-      <c r="D51" s="86" t="s">
+      <c r="C51" s="148"/>
+      <c r="D51" s="149"/>
+      <c r="E51" s="97"/>
+      <c r="F51" s="140"/>
+      <c r="G51" s="141"/>
+      <c r="H51" s="97"/>
+    </row>
+    <row r="53" spans="2:8" ht="102.6" customHeight="1">
+      <c r="C53" s="85"/>
+      <c r="D53" s="86" t="s">
         <v>91</v>
       </c>
-      <c r="E51" s="86"/>
-      <c r="F51" s="76">
-        <f>SUM(G44)</f>
-        <v>0</v>
-      </c>
-      <c r="G51" s="87" t="s">
+      <c r="E53" s="86"/>
+      <c r="F53" s="76">
+        <f>SUM(G46)</f>
+        <v>0</v>
+      </c>
+      <c r="G53" s="87" t="s">
         <v>92</v>
       </c>
-      <c r="H51" s="85"/>
-    </row>
-    <row r="52" spans="2:8" ht="55.95" customHeight="1" thickBot="1">
-      <c r="C52" s="85"/>
-      <c r="D52" s="85"/>
-      <c r="E52" s="86"/>
-      <c r="F52" s="86" t="s">
+      <c r="H53" s="85"/>
+    </row>
+    <row r="54" spans="2:8" ht="55.9" customHeight="1" thickBot="1">
+      <c r="C54" s="85"/>
+      <c r="D54" s="85"/>
+      <c r="E54" s="86"/>
+      <c r="F54" s="86" t="s">
         <v>79</v>
       </c>
-      <c r="G52" s="86"/>
-      <c r="H52" s="85"/>
-    </row>
-    <row r="53" spans="2:8" ht="55.95" customHeight="1" thickBot="1">
-      <c r="C53" s="88"/>
-      <c r="D53" s="85"/>
-      <c r="E53" s="85"/>
-      <c r="F53" s="89" t="s">
+      <c r="G54" s="86"/>
+      <c r="H54" s="85"/>
+    </row>
+    <row r="55" spans="2:8" ht="55.9" customHeight="1" thickBot="1">
+      <c r="C55" s="88"/>
+      <c r="D55" s="85"/>
+      <c r="E55" s="85"/>
+      <c r="F55" s="89" t="s">
         <v>81</v>
       </c>
-      <c r="G53" s="89" t="s">
+      <c r="G55" s="89" t="s">
         <v>59</v>
       </c>
-      <c r="H53" s="85"/>
-    </row>
-    <row r="54" spans="2:8" ht="55.95" customHeight="1" thickBot="1">
-      <c r="C54" s="88"/>
-      <c r="D54" s="85"/>
-      <c r="E54" s="85"/>
-      <c r="F54" s="89"/>
-      <c r="G54" s="89"/>
-      <c r="H54" s="85"/>
-    </row>
-    <row r="55" spans="2:8" ht="108.6" customHeight="1" thickBot="1">
-      <c r="C55" s="85"/>
-      <c r="D55" s="85"/>
-      <c r="E55" s="90" t="s">
+      <c r="H55" s="85"/>
+    </row>
+    <row r="56" spans="2:8" ht="55.9" customHeight="1" thickBot="1">
+      <c r="C56" s="88"/>
+      <c r="D56" s="85"/>
+      <c r="E56" s="85"/>
+      <c r="F56" s="89"/>
+      <c r="G56" s="89"/>
+      <c r="H56" s="85"/>
+    </row>
+    <row r="57" spans="2:8" ht="108.6" customHeight="1" thickBot="1">
+      <c r="C57" s="85"/>
+      <c r="D57" s="85"/>
+      <c r="E57" s="90" t="s">
         <v>83</v>
       </c>
-      <c r="F55" s="91"/>
-      <c r="G55" s="91"/>
-      <c r="H55" s="85"/>
-    </row>
-    <row r="56" spans="2:8" ht="87.6" customHeight="1">
-      <c r="C56" s="74"/>
-      <c r="D56" s="74"/>
-      <c r="E56" s="74"/>
-      <c r="F56" s="75"/>
-      <c r="G56" s="75"/>
-      <c r="H56" s="67"/>
-    </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
-      <c r="E57" s="67"/>
-      <c r="F57" s="67"/>
-      <c r="G57" s="67"/>
-      <c r="H57" s="67"/>
-    </row>
-    <row r="73" spans="3:3" ht="15" customHeight="1">
-      <c r="C73" s="64"/>
-    </row>
-    <row r="74" spans="3:3" ht="15" customHeight="1">
-      <c r="C74" s="64"/>
+      <c r="F57" s="91"/>
+      <c r="G57" s="91"/>
+      <c r="H57" s="85"/>
+    </row>
+    <row r="58" spans="2:8" ht="87.6" customHeight="1">
+      <c r="C58" s="74"/>
+      <c r="D58" s="74"/>
+      <c r="E58" s="74"/>
+      <c r="F58" s="75"/>
+      <c r="G58" s="75"/>
+      <c r="H58" s="67"/>
+    </row>
+    <row r="59" spans="2:8" ht="15" customHeight="1">
+      <c r="E59" s="67"/>
+      <c r="F59" s="67"/>
+      <c r="G59" s="67"/>
+      <c r="H59" s="67"/>
     </row>
     <row r="75" spans="3:3" ht="15" customHeight="1">
       <c r="C75" s="64"/>
@@ -3973,70 +4023,79 @@
     <row r="134" spans="3:3" ht="15" customHeight="1">
       <c r="C134" s="64"/>
     </row>
+    <row r="135" spans="3:3" ht="15" customHeight="1">
+      <c r="C135" s="64"/>
+    </row>
+    <row r="136" spans="3:3" ht="15" customHeight="1">
+      <c r="C136" s="64"/>
+    </row>
   </sheetData>
-  <mergeCells count="90">
-    <mergeCell ref="F20:F21"/>
+  <mergeCells count="95">
     <mergeCell ref="F22:F23"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="G26:G27"/>
     <mergeCell ref="G24:G25"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="H24:H25"/>
     <mergeCell ref="G22:G23"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="G30:G31"/>
     <mergeCell ref="F34:F35"/>
     <mergeCell ref="G34:G35"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="G28:G29"/>
     <mergeCell ref="F32:F33"/>
     <mergeCell ref="G32:G33"/>
     <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="H32:H33"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D20:D21"/>
     <mergeCell ref="D22:D23"/>
     <mergeCell ref="D24:D25"/>
     <mergeCell ref="D26:D27"/>
+    <mergeCell ref="D28:D29"/>
     <mergeCell ref="B5:C7"/>
     <mergeCell ref="D5:D7"/>
     <mergeCell ref="D8:D9"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="D20:D21"/>
     <mergeCell ref="D16:D17"/>
-    <mergeCell ref="D18:D19"/>
     <mergeCell ref="D14:D15"/>
-    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="G20:G21"/>
     <mergeCell ref="F16:F17"/>
     <mergeCell ref="G16:G17"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H42:H43"/>
     <mergeCell ref="H40:H41"/>
-    <mergeCell ref="H38:H39"/>
     <mergeCell ref="D4:H4"/>
     <mergeCell ref="H5:H7"/>
     <mergeCell ref="H8:H9"/>
@@ -4048,29 +4107,31 @@
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="D10:D11"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="F50:G50"/>
     <mergeCell ref="F49:G49"/>
     <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C50:D50"/>
     <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="B48:D48"/>
     <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="F40:F41"/>
     <mergeCell ref="G40:G41"/>
-    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="F42:F43"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="20" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="F8 F16" formulaRange="1"/>
+    <ignoredError sqref="F8 F18 F12" formulaRange="1"/>
   </ignoredErrors>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -4079,45 +4140,45 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AV50"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:AV51"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="35.6640625" style="3" customWidth="1"/>
-    <col min="2" max="3" width="11.5546875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="7.21875" style="3" customWidth="1"/>
-    <col min="5" max="13" width="5.6640625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="20.109375" style="3" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="10.6640625" style="3" customWidth="1"/>
-    <col min="17" max="17" width="15.6640625" style="3" customWidth="1"/>
-    <col min="18" max="47" width="3.6640625" style="3" hidden="1" customWidth="1"/>
-    <col min="48" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="35.75" style="3" customWidth="1"/>
+    <col min="2" max="3" width="11.625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="7.25" style="3" customWidth="1"/>
+    <col min="5" max="13" width="5.75" style="3" customWidth="1"/>
+    <col min="14" max="14" width="20.125" style="3" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="10.75" style="3" customWidth="1"/>
+    <col min="17" max="17" width="15.75" style="3" customWidth="1"/>
+    <col min="18" max="47" width="3.75" style="3" hidden="1" customWidth="1"/>
+    <col min="48" max="16384" width="8.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" ht="49.95" customHeight="1">
+    <row r="1" spans="1:48" ht="49.9" customHeight="1">
       <c r="A1" s="3" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="199" t="s">
+      <c r="B1" s="206" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="193"/>
-      <c r="D1" s="193"/>
-      <c r="E1" s="193"/>
-      <c r="F1" s="193"/>
-      <c r="G1" s="193"/>
-      <c r="H1" s="193"/>
-      <c r="I1" s="193"/>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="O1" s="200" t="s">
+      <c r="C1" s="200"/>
+      <c r="D1" s="200"/>
+      <c r="E1" s="200"/>
+      <c r="F1" s="200"/>
+      <c r="G1" s="200"/>
+      <c r="H1" s="200"/>
+      <c r="I1" s="200"/>
+      <c r="J1" s="200"/>
+      <c r="K1" s="200"/>
+      <c r="L1" s="200"/>
+      <c r="M1" s="200"/>
+      <c r="O1" s="207" t="s">
         <v>18</v>
       </c>
-      <c r="P1" s="200"/>
-      <c r="Q1" s="200"/>
-    </row>
-    <row r="2" spans="1:48" ht="10.199999999999999" customHeight="1">
+      <c r="P1" s="207"/>
+      <c r="Q1" s="207"/>
+    </row>
+    <row r="2" spans="1:48" ht="10.15" customHeight="1">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -4139,23 +4200,23 @@
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="9"/>
-      <c r="O3" s="200" t="s">
+      <c r="O3" s="207" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="200"/>
-      <c r="Q3" s="200"/>
-    </row>
-    <row r="4" spans="1:48" ht="25.2" customHeight="1">
+      <c r="P3" s="207"/>
+      <c r="Q3" s="207"/>
+    </row>
+    <row r="4" spans="1:48" ht="25.15" customHeight="1">
       <c r="A4" s="63" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="O4" s="200"/>
-      <c r="P4" s="200"/>
-      <c r="Q4" s="200"/>
-    </row>
-    <row r="5" spans="1:48" ht="4.95" customHeight="1">
+      <c r="O4" s="207"/>
+      <c r="P4" s="207"/>
+      <c r="Q4" s="207"/>
+    </row>
+    <row r="5" spans="1:48" ht="4.9000000000000004" customHeight="1">
       <c r="A5" s="63"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -4163,171 +4224,171 @@
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
     </row>
-    <row r="6" spans="1:48" ht="25.2" customHeight="1">
-      <c r="A6" s="201" t="s">
+    <row r="6" spans="1:48" ht="25.15" customHeight="1">
+      <c r="A6" s="208" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="201"/>
-      <c r="C6" s="203" t="s">
+      <c r="B6" s="208"/>
+      <c r="C6" s="210" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="203"/>
-      <c r="E6" s="203"/>
-      <c r="F6" s="203"/>
-      <c r="G6" s="203"/>
-      <c r="H6" s="203"/>
-      <c r="I6" s="203"/>
-      <c r="J6" s="203"/>
-      <c r="K6" s="203"/>
-      <c r="L6" s="203"/>
-      <c r="M6" s="203"/>
-      <c r="N6" s="203"/>
-      <c r="O6" s="203"/>
-      <c r="P6" s="203"/>
-      <c r="Q6" s="203"/>
-    </row>
-    <row r="7" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A7" s="201"/>
-      <c r="B7" s="201"/>
-      <c r="C7" s="197" t="s">
+      <c r="D6" s="210"/>
+      <c r="E6" s="210"/>
+      <c r="F6" s="210"/>
+      <c r="G6" s="210"/>
+      <c r="H6" s="210"/>
+      <c r="I6" s="210"/>
+      <c r="J6" s="210"/>
+      <c r="K6" s="210"/>
+      <c r="L6" s="210"/>
+      <c r="M6" s="210"/>
+      <c r="N6" s="210"/>
+      <c r="O6" s="210"/>
+      <c r="P6" s="210"/>
+      <c r="Q6" s="210"/>
+    </row>
+    <row r="7" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A7" s="208"/>
+      <c r="B7" s="208"/>
+      <c r="C7" s="204" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="178" t="s">
+      <c r="D7" s="185" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="179"/>
-      <c r="F7" s="179"/>
-      <c r="G7" s="179"/>
-      <c r="H7" s="179"/>
-      <c r="I7" s="179"/>
-      <c r="J7" s="179"/>
-      <c r="K7" s="179"/>
-      <c r="L7" s="179"/>
-      <c r="M7" s="179"/>
-      <c r="N7" s="179"/>
-      <c r="O7" s="179"/>
-      <c r="P7" s="179"/>
-      <c r="Q7" s="180"/>
+      <c r="E7" s="186"/>
+      <c r="F7" s="186"/>
+      <c r="G7" s="186"/>
+      <c r="H7" s="186"/>
+      <c r="I7" s="186"/>
+      <c r="J7" s="186"/>
+      <c r="K7" s="186"/>
+      <c r="L7" s="186"/>
+      <c r="M7" s="186"/>
+      <c r="N7" s="186"/>
+      <c r="O7" s="186"/>
+      <c r="P7" s="186"/>
+      <c r="Q7" s="187"/>
     </row>
     <row r="8" spans="1:48" ht="15" customHeight="1">
-      <c r="A8" s="202"/>
-      <c r="B8" s="201"/>
-      <c r="C8" s="198"/>
-      <c r="D8" s="183" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="183" t="s">
+      <c r="A8" s="209"/>
+      <c r="B8" s="208"/>
+      <c r="C8" s="205"/>
+      <c r="D8" s="190" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="190" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="183" t="s">
+      <c r="F8" s="190" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="183" t="s">
+      <c r="G8" s="190" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="183" t="s">
+      <c r="H8" s="190" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="183" t="s">
+      <c r="I8" s="190" t="s">
         <v>28</v>
       </c>
-      <c r="J8" s="183" t="s">
+      <c r="J8" s="190" t="s">
         <v>29</v>
       </c>
-      <c r="K8" s="183" t="s">
+      <c r="K8" s="190" t="s">
         <v>30</v>
       </c>
-      <c r="L8" s="183" t="s">
+      <c r="L8" s="190" t="s">
         <v>31</v>
       </c>
-      <c r="M8" s="183" t="s">
+      <c r="M8" s="190" t="s">
         <v>32</v>
       </c>
       <c r="N8" s="10"/>
-      <c r="O8" s="183" t="s">
+      <c r="O8" s="190" t="s">
         <v>35</v>
       </c>
-      <c r="P8" s="183" t="s">
+      <c r="P8" s="190" t="s">
         <v>36</v>
       </c>
-      <c r="Q8" s="183" t="s">
+      <c r="Q8" s="190" t="s">
         <v>37</v>
       </c>
-      <c r="R8" s="193" t="s">
+      <c r="R8" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="S8" s="193"/>
-      <c r="T8" s="193"/>
-      <c r="U8" s="193" t="s">
+      <c r="S8" s="200"/>
+      <c r="T8" s="200"/>
+      <c r="U8" s="200" t="s">
         <v>5</v>
       </c>
-      <c r="V8" s="193"/>
-      <c r="W8" s="193"/>
-      <c r="X8" s="193" t="s">
+      <c r="V8" s="200"/>
+      <c r="W8" s="200"/>
+      <c r="X8" s="200" t="s">
         <v>7</v>
       </c>
-      <c r="Y8" s="193"/>
-      <c r="Z8" s="193"/>
-      <c r="AA8" s="193" t="s">
+      <c r="Y8" s="200"/>
+      <c r="Z8" s="200"/>
+      <c r="AA8" s="200" t="s">
         <v>8</v>
       </c>
-      <c r="AB8" s="193"/>
-      <c r="AC8" s="193"/>
-      <c r="AD8" s="193" t="s">
+      <c r="AB8" s="200"/>
+      <c r="AC8" s="200"/>
+      <c r="AD8" s="200" t="s">
         <v>9</v>
       </c>
-      <c r="AE8" s="193"/>
-      <c r="AF8" s="193"/>
-      <c r="AG8" s="193" t="s">
+      <c r="AE8" s="200"/>
+      <c r="AF8" s="200"/>
+      <c r="AG8" s="200" t="s">
         <v>10</v>
       </c>
-      <c r="AH8" s="193"/>
-      <c r="AI8" s="193"/>
-      <c r="AJ8" s="193" t="s">
+      <c r="AH8" s="200"/>
+      <c r="AI8" s="200"/>
+      <c r="AJ8" s="200" t="s">
         <v>11</v>
       </c>
-      <c r="AK8" s="193"/>
-      <c r="AL8" s="193"/>
-      <c r="AM8" s="193" t="s">
+      <c r="AK8" s="200"/>
+      <c r="AL8" s="200"/>
+      <c r="AM8" s="200" t="s">
         <v>12</v>
       </c>
-      <c r="AN8" s="193"/>
-      <c r="AO8" s="193"/>
-      <c r="AP8" s="193" t="s">
+      <c r="AN8" s="200"/>
+      <c r="AO8" s="200"/>
+      <c r="AP8" s="200" t="s">
         <v>13</v>
       </c>
-      <c r="AQ8" s="193"/>
-      <c r="AR8" s="193"/>
-      <c r="AS8" s="193" t="s">
+      <c r="AQ8" s="200"/>
+      <c r="AR8" s="200"/>
+      <c r="AS8" s="200" t="s">
         <v>14</v>
       </c>
-      <c r="AT8" s="193"/>
-      <c r="AU8" s="193"/>
-    </row>
-    <row r="9" spans="1:48" ht="25.2" customHeight="1">
-      <c r="A9" s="3" t="s">
+      <c r="AT8" s="200"/>
+      <c r="AU8" s="200"/>
+    </row>
+    <row r="9" spans="1:48" ht="25.15" customHeight="1">
+      <c r="A9" s="113" t="s">
         <v>38</v>
       </c>
       <c r="B9" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="198"/>
-      <c r="D9" s="184"/>
-      <c r="E9" s="184"/>
-      <c r="F9" s="184"/>
-      <c r="G9" s="184"/>
-      <c r="H9" s="184"/>
-      <c r="I9" s="184"/>
-      <c r="J9" s="184"/>
-      <c r="K9" s="184"/>
-      <c r="L9" s="184"/>
-      <c r="M9" s="184"/>
+      <c r="C9" s="205"/>
+      <c r="D9" s="191"/>
+      <c r="E9" s="191"/>
+      <c r="F9" s="191"/>
+      <c r="G9" s="191"/>
+      <c r="H9" s="191"/>
+      <c r="I9" s="191"/>
+      <c r="J9" s="191"/>
+      <c r="K9" s="191"/>
+      <c r="L9" s="191"/>
+      <c r="M9" s="191"/>
       <c r="N9" s="98" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="184"/>
-      <c r="P9" s="184"/>
-      <c r="Q9" s="184"/>
+      <c r="O9" s="191"/>
+      <c r="P9" s="191"/>
+      <c r="Q9" s="191"/>
       <c r="R9" s="2" t="s">
         <v>2</v>
       </c>
@@ -4419,11 +4480,11 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A10" s="110" t="s">
+    <row r="10" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A10" s="114" t="s">
         <v>115</v>
       </c>
-      <c r="B10" s="109">
+      <c r="B10" s="112">
         <v>36</v>
       </c>
       <c r="C10" s="83">
@@ -4435,152 +4496,152 @@
         <v>0</v>
       </c>
       <c r="E10" s="83"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11">
+      <c r="F10" s="100"/>
+      <c r="G10" s="100"/>
+      <c r="H10" s="100"/>
+      <c r="I10" s="100"/>
+      <c r="J10" s="100"/>
+      <c r="K10" s="100"/>
+      <c r="L10" s="100"/>
+      <c r="M10" s="100"/>
+      <c r="N10" s="100">
         <f>'มหาชัย-ผลิต'!F8</f>
         <v>0</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="101">
-        <f t="shared" ref="R10:R22" si="0">INT(D10/B10)</f>
-        <v>0</v>
-      </c>
-      <c r="S10" s="102">
-        <f t="shared" ref="S10:S22" si="1">IF(MOD(D10,B10)/B10&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T10" s="103">
-        <f t="shared" ref="T10:T22" si="2">IF(AND(MOD(D10,B10)/B10&lt;=0.5,MOD(D10,B10)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U10" s="101">
+      <c r="O10" s="100"/>
+      <c r="P10" s="100"/>
+      <c r="Q10" s="100"/>
+      <c r="R10" s="102">
+        <f t="shared" ref="R10:R23" si="0">INT(D10/B10)</f>
+        <v>0</v>
+      </c>
+      <c r="S10" s="103">
+        <f t="shared" ref="S10:S23" si="1">IF(MOD(D10,B10)/B10&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T10" s="104">
+        <f t="shared" ref="T10:T23" si="2">IF(AND(MOD(D10,B10)/B10&lt;=0.5,MOD(D10,B10)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U10" s="102">
         <f>INT(E10/B10)</f>
         <v>0</v>
       </c>
-      <c r="V10" s="102">
+      <c r="V10" s="103">
         <f>IF(MOD(E10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="W10" s="103">
+      <c r="W10" s="104">
         <f>IF(AND(MOD(E10,B10)/B10&lt;=0.5,MOD(E10,B10)&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X10" s="101">
-        <f t="shared" ref="X10:X23" si="3">INT(F10/B10)</f>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="102">
-        <f t="shared" ref="Y10:Y23" si="4">IF(MOD(F10,B10)/B10&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z10" s="103">
-        <f t="shared" ref="Z10:Z23" si="5">IF(AND(MOD(F10,B10)/B10&lt;=0.5,MOD(F10,B10)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AA10" s="101">
+      <c r="X10" s="102">
+        <f t="shared" ref="X10:X24" si="3">INT(F10/B10)</f>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="103">
+        <f t="shared" ref="Y10:Y24" si="4">IF(MOD(F10,B10)/B10&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="104">
+        <f t="shared" ref="Z10:Z24" si="5">IF(AND(MOD(F10,B10)/B10&lt;=0.5,MOD(F10,B10)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA10" s="102">
         <f>INT(G10/B10)</f>
         <v>0</v>
       </c>
-      <c r="AB10" s="102">
+      <c r="AB10" s="103">
         <f>IF(MOD(G10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AC10" s="103">
+      <c r="AC10" s="104">
         <f>IF(AND(MOD(G10,B10)/B10&lt;=0.5,MOD(G10,B10)&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="AD10" s="101">
+      <c r="AD10" s="102">
         <f>INT(H10/B10)</f>
         <v>0</v>
       </c>
-      <c r="AE10" s="102">
+      <c r="AE10" s="103">
         <f>IF(MOD(H10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AF10" s="103">
+      <c r="AF10" s="104">
         <f>IF(AND(MOD(H10,B10)/B10&lt;=0.5,MOD(H10,B10)&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="AG10" s="101">
+      <c r="AG10" s="102">
         <f>INT(I10/B10)</f>
         <v>0</v>
       </c>
-      <c r="AH10" s="102">
+      <c r="AH10" s="103">
         <f>IF(MOD(I10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AI10" s="103">
+      <c r="AI10" s="104">
         <f>IF(AND(MOD(I10,B10)/B10&lt;=0.5,MOD(I10,B10)&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="AJ10" s="101">
+      <c r="AJ10" s="102">
         <f>INT(J10/B10)</f>
         <v>0</v>
       </c>
-      <c r="AK10" s="102">
+      <c r="AK10" s="103">
         <f>IF(MOD(J10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AL10" s="103">
+      <c r="AL10" s="104">
         <f>IF(AND(MOD(J10,B10)/B10&lt;=0.5,MOD(J10,B10)&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="AM10" s="101">
+      <c r="AM10" s="102">
         <f>INT(K10/B10)</f>
         <v>0</v>
       </c>
-      <c r="AN10" s="102">
+      <c r="AN10" s="103">
         <f>IF(MOD(K10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO10" s="103">
+      <c r="AO10" s="104">
         <f>IF(AND(MOD(K10,B10)/B10&lt;=0.5,MOD(K10,B10)&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="AP10" s="101">
+      <c r="AP10" s="102">
         <f>INT(L10/B10)</f>
         <v>0</v>
       </c>
-      <c r="AQ10" s="102">
+      <c r="AQ10" s="103">
         <f>IF(MOD(L10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AR10" s="103">
+      <c r="AR10" s="104">
         <f>IF(AND(MOD(L10,B10)/B10&lt;=0.5,MOD(L10,B10)&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS10" s="101">
+      <c r="AS10" s="102">
         <f>INT(M10/B10)</f>
         <v>0</v>
       </c>
-      <c r="AT10" s="102">
+      <c r="AT10" s="103">
         <f>IF(MOD(M10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AU10" s="103">
+      <c r="AU10" s="104">
         <f>IF(AND(MOD(M10,B10)/B10&lt;=0.5,MOD(M10,B10)&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="AV10" s="11"/>
-    </row>
-    <row r="11" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A11" s="110" t="s">
+      <c r="AV10" s="100"/>
+    </row>
+    <row r="11" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A11" s="114" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="109">
+      <c r="B11" s="112">
         <v>32</v>
       </c>
       <c r="C11" s="83">
-        <f t="shared" ref="C11:C16" si="6">SUMPRODUCT(ROUNDUP(D11/B11,0))</f>
+        <f t="shared" ref="C11:C17" si="6">SUMPRODUCT(ROUNDUP(D11/B11,0))</f>
         <v>0</v>
       </c>
       <c r="D11" s="83">
@@ -4588,152 +4649,152 @@
         <v>0</v>
       </c>
       <c r="E11" s="83"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11" t="str">
-        <f t="shared" ref="N11:N17" si="7">INT(SUM(D11:M11)/B11) &amp; " full, " &amp; IF(MOD(SUM(D11:M11), B11)/B11 &lt;= 0.5, "1 less than half", IF(MOD(SUM(D11:M11), B11)/B11 &gt; 0.5, "1 more than half", ""))</f>
+      <c r="F11" s="100"/>
+      <c r="G11" s="100"/>
+      <c r="H11" s="100"/>
+      <c r="I11" s="100"/>
+      <c r="J11" s="100"/>
+      <c r="K11" s="100"/>
+      <c r="L11" s="100"/>
+      <c r="M11" s="100"/>
+      <c r="N11" s="100" t="str">
+        <f t="shared" ref="N11:N18" si="7">INT(SUM(D11:M11)/B11) &amp; " full, " &amp; IF(MOD(SUM(D11:M11), B11)/B11 &lt;= 0.5, "1 less than half", IF(MOD(SUM(D11:M11), B11)/B11 &gt; 0.5, "1 more than half", ""))</f>
         <v>0 full, 1 less than half</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="101">
+      <c r="O11" s="100"/>
+      <c r="P11" s="100"/>
+      <c r="Q11" s="100"/>
+      <c r="R11" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S11" s="102">
+      <c r="S11" s="103">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T11" s="103">
+      <c r="T11" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U11" s="101">
-        <f t="shared" ref="U11:U23" si="8">INT(E11/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="V11" s="102">
-        <f t="shared" ref="V11:V23" si="9">IF(MOD(E11,B11)/B11&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="W11" s="103">
-        <f t="shared" ref="W11:W23" si="10">IF(AND(MOD(E11,B11)/B11&lt;=0.5,MOD(E11,B11)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X11" s="101">
+      <c r="U11" s="102">
+        <f t="shared" ref="U11:U24" si="8">INT(E11/B11)</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="103">
+        <f t="shared" ref="V11:V24" si="9">IF(MOD(E11,B11)/B11&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="104">
+        <f t="shared" ref="W11:W24" si="10">IF(AND(MOD(E11,B11)/B11&lt;=0.5,MOD(E11,B11)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X11" s="102">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y11" s="102">
+      <c r="Y11" s="103">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Z11" s="103">
+      <c r="Z11" s="104">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA11" s="101">
-        <f t="shared" ref="AA11:AA23" si="11">INT(G11/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="AB11" s="102">
-        <f t="shared" ref="AB11:AB23" si="12">IF(MOD(G11,B11)/B11&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AC11" s="103">
-        <f t="shared" ref="AC11:AC23" si="13">IF(AND(MOD(G11,B11)/B11&lt;=0.5,MOD(G11,B11)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AD11" s="101">
-        <f t="shared" ref="AD11:AD23" si="14">INT(H11/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="AE11" s="102">
-        <f t="shared" ref="AE11:AE23" si="15">IF(MOD(H11,B11)/B11&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF11" s="103">
-        <f t="shared" ref="AF11:AF23" si="16">IF(AND(MOD(H11,B11)/B11&lt;=0.5,MOD(H11,B11)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AG11" s="101">
-        <f t="shared" ref="AG11:AG23" si="17">INT(I11/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="AH11" s="102">
-        <f t="shared" ref="AH11:AH23" si="18">IF(MOD(I11,B11)/B11&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AI11" s="103">
-        <f t="shared" ref="AI11:AI23" si="19">IF(AND(MOD(I11,B11)/B11&lt;=0.5,MOD(I11,B11)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ11" s="101">
-        <f t="shared" ref="AJ11:AJ23" si="20">INT(J11/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="AK11" s="102">
-        <f t="shared" ref="AK11:AK23" si="21">IF(MOD(J11,B11)/B11&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AL11" s="103">
-        <f t="shared" ref="AL11:AL23" si="22">IF(AND(MOD(J11,B11)/B11&lt;=0.5,MOD(J11,B11)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AM11" s="101">
-        <f t="shared" ref="AM11:AM23" si="23">INT(K11/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="AN11" s="102">
-        <f t="shared" ref="AN11:AN23" si="24">IF(MOD(K11,B11)/B11&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AO11" s="103">
-        <f t="shared" ref="AO11:AO23" si="25">IF(AND(MOD(K11,B11)/B11&lt;=0.5,MOD(K11,B11)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AP11" s="101">
-        <f t="shared" ref="AP11:AP23" si="26">INT(L11/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="102">
-        <f t="shared" ref="AQ11:AQ23" si="27">IF(MOD(L11,B11)/B11&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AR11" s="103">
-        <f t="shared" ref="AR11:AR23" si="28">IF(AND(MOD(L11,B11)/B11&lt;=0.5,MOD(L11,B11)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AS11" s="101">
-        <f t="shared" ref="AS11:AS23" si="29">INT(M11/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="AT11" s="102">
-        <f t="shared" ref="AT11:AT23" si="30">IF(MOD(M11,B11)/B11&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AU11" s="103">
-        <f t="shared" ref="AU11:AU23" si="31">IF(AND(MOD(M11,B11)/B11&lt;=0.5,MOD(M11,B11)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AV11" s="11"/>
-    </row>
-    <row r="12" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A12" s="110" t="s">
-        <v>136</v>
-      </c>
-      <c r="B12" s="109">
-        <v>14</v>
+      <c r="AA11" s="102">
+        <f t="shared" ref="AA11:AA24" si="11">INT(G11/B11)</f>
+        <v>0</v>
+      </c>
+      <c r="AB11" s="103">
+        <f t="shared" ref="AB11:AB24" si="12">IF(MOD(G11,B11)/B11&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC11" s="104">
+        <f t="shared" ref="AC11:AC24" si="13">IF(AND(MOD(G11,B11)/B11&lt;=0.5,MOD(G11,B11)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD11" s="102">
+        <f t="shared" ref="AD11:AD24" si="14">INT(H11/B11)</f>
+        <v>0</v>
+      </c>
+      <c r="AE11" s="103">
+        <f t="shared" ref="AE11:AE24" si="15">IF(MOD(H11,B11)/B11&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="104">
+        <f t="shared" ref="AF11:AF24" si="16">IF(AND(MOD(H11,B11)/B11&lt;=0.5,MOD(H11,B11)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG11" s="102">
+        <f t="shared" ref="AG11:AG24" si="17">INT(I11/B11)</f>
+        <v>0</v>
+      </c>
+      <c r="AH11" s="103">
+        <f t="shared" ref="AH11:AH24" si="18">IF(MOD(I11,B11)/B11&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI11" s="104">
+        <f t="shared" ref="AI11:AI24" si="19">IF(AND(MOD(I11,B11)/B11&lt;=0.5,MOD(I11,B11)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="102">
+        <f t="shared" ref="AJ11:AJ24" si="20">INT(J11/B11)</f>
+        <v>0</v>
+      </c>
+      <c r="AK11" s="103">
+        <f t="shared" ref="AK11:AK24" si="21">IF(MOD(J11,B11)/B11&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL11" s="104">
+        <f t="shared" ref="AL11:AL24" si="22">IF(AND(MOD(J11,B11)/B11&lt;=0.5,MOD(J11,B11)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM11" s="102">
+        <f t="shared" ref="AM11:AM24" si="23">INT(K11/B11)</f>
+        <v>0</v>
+      </c>
+      <c r="AN11" s="103">
+        <f t="shared" ref="AN11:AN24" si="24">IF(MOD(K11,B11)/B11&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO11" s="104">
+        <f t="shared" ref="AO11:AO24" si="25">IF(AND(MOD(K11,B11)/B11&lt;=0.5,MOD(K11,B11)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP11" s="102">
+        <f t="shared" ref="AP11:AP24" si="26">INT(L11/B11)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="103">
+        <f t="shared" ref="AQ11:AQ24" si="27">IF(MOD(L11,B11)/B11&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR11" s="104">
+        <f t="shared" ref="AR11:AR24" si="28">IF(AND(MOD(L11,B11)/B11&lt;=0.5,MOD(L11,B11)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS11" s="102">
+        <f t="shared" ref="AS11:AS24" si="29">INT(M11/B11)</f>
+        <v>0</v>
+      </c>
+      <c r="AT11" s="103">
+        <f t="shared" ref="AT11:AT24" si="30">IF(MOD(M11,B11)/B11&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU11" s="104">
+        <f t="shared" ref="AU11:AU24" si="31">IF(AND(MOD(M11,B11)/B11&lt;=0.5,MOD(M11,B11)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV11" s="100"/>
+    </row>
+    <row r="12" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A12" s="114" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="112">
+        <v>36</v>
       </c>
       <c r="C12" s="83">
-        <f t="shared" ref="C12:C13" si="32">SUMPRODUCT(ROUNDUP(D12/B12,0))</f>
+        <f>SUMPRODUCT(ROUNDUP(D12/B12,0))</f>
         <v>0</v>
       </c>
       <c r="D12" s="83">
@@ -4741,59 +4802,152 @@
         <v>0</v>
       </c>
       <c r="E12" s="83"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="101"/>
-      <c r="S12" s="102"/>
-      <c r="T12" s="103"/>
-      <c r="U12" s="101"/>
-      <c r="V12" s="102"/>
-      <c r="W12" s="103"/>
-      <c r="X12" s="101"/>
-      <c r="Y12" s="102"/>
-      <c r="Z12" s="103"/>
-      <c r="AA12" s="101"/>
-      <c r="AB12" s="102"/>
-      <c r="AC12" s="103"/>
-      <c r="AD12" s="101"/>
-      <c r="AE12" s="102"/>
-      <c r="AF12" s="103"/>
-      <c r="AG12" s="101"/>
-      <c r="AH12" s="102"/>
-      <c r="AI12" s="103"/>
-      <c r="AJ12" s="101"/>
-      <c r="AK12" s="102"/>
-      <c r="AL12" s="103"/>
-      <c r="AM12" s="101"/>
-      <c r="AN12" s="102"/>
-      <c r="AO12" s="103"/>
-      <c r="AP12" s="101"/>
-      <c r="AQ12" s="102"/>
-      <c r="AR12" s="103"/>
-      <c r="AS12" s="101"/>
-      <c r="AT12" s="102"/>
-      <c r="AU12" s="103"/>
-      <c r="AV12" s="11"/>
-    </row>
-    <row r="13" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A13" s="110" t="s">
+      <c r="F12" s="100"/>
+      <c r="G12" s="100"/>
+      <c r="H12" s="100"/>
+      <c r="I12" s="100"/>
+      <c r="J12" s="100"/>
+      <c r="K12" s="100"/>
+      <c r="L12" s="100"/>
+      <c r="M12" s="100"/>
+      <c r="N12" s="100" t="str">
+        <f t="shared" si="7"/>
+        <v>0 full, 1 less than half</v>
+      </c>
+      <c r="O12" s="100"/>
+      <c r="P12" s="100"/>
+      <c r="Q12" s="100"/>
+      <c r="R12" s="102">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="103">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="104">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="102">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V12" s="103">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="W12" s="104">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="102">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="104">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA12" s="102">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB12" s="103">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AC12" s="104">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AD12" s="102">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AE12" s="103">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AF12" s="104">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AG12" s="102">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AH12" s="103">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AI12" s="104">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="102">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AK12" s="103">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AL12" s="104">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AM12" s="102">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN12" s="103">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AO12" s="104">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AP12" s="102">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="103">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AR12" s="104">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AS12" s="102">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AT12" s="103">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AU12" s="104">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AV12" s="100"/>
+    </row>
+    <row r="13" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A13" s="114" t="s">
         <v>138</v>
       </c>
-      <c r="B13" s="109">
+      <c r="B13" s="112">
         <v>14</v>
       </c>
       <c r="C13" s="83">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="C13:C14" si="32">SUMPRODUCT(ROUNDUP(D13/B13,0))</f>
         <v>0</v>
       </c>
       <c r="D13" s="83">
@@ -4801,59 +4955,59 @@
         <v>0</v>
       </c>
       <c r="E13" s="83"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="101"/>
-      <c r="S13" s="102"/>
-      <c r="T13" s="103"/>
-      <c r="U13" s="101"/>
-      <c r="V13" s="102"/>
-      <c r="W13" s="103"/>
-      <c r="X13" s="101"/>
-      <c r="Y13" s="102"/>
-      <c r="Z13" s="103"/>
-      <c r="AA13" s="101"/>
-      <c r="AB13" s="102"/>
-      <c r="AC13" s="103"/>
-      <c r="AD13" s="101"/>
-      <c r="AE13" s="102"/>
-      <c r="AF13" s="103"/>
-      <c r="AG13" s="101"/>
-      <c r="AH13" s="102"/>
-      <c r="AI13" s="103"/>
-      <c r="AJ13" s="101"/>
-      <c r="AK13" s="102"/>
-      <c r="AL13" s="103"/>
-      <c r="AM13" s="101"/>
-      <c r="AN13" s="102"/>
-      <c r="AO13" s="103"/>
-      <c r="AP13" s="101"/>
-      <c r="AQ13" s="102"/>
-      <c r="AR13" s="103"/>
-      <c r="AS13" s="101"/>
-      <c r="AT13" s="102"/>
-      <c r="AU13" s="103"/>
-      <c r="AV13" s="11"/>
-    </row>
-    <row r="14" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A14" s="110" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" s="109">
-        <v>32</v>
+      <c r="F13" s="122"/>
+      <c r="G13" s="122"/>
+      <c r="H13" s="122"/>
+      <c r="I13" s="122"/>
+      <c r="J13" s="122"/>
+      <c r="K13" s="122"/>
+      <c r="L13" s="122"/>
+      <c r="M13" s="122"/>
+      <c r="N13" s="122"/>
+      <c r="O13" s="122"/>
+      <c r="P13" s="122"/>
+      <c r="Q13" s="122"/>
+      <c r="R13" s="102"/>
+      <c r="S13" s="103"/>
+      <c r="T13" s="104"/>
+      <c r="U13" s="102"/>
+      <c r="V13" s="103"/>
+      <c r="W13" s="104"/>
+      <c r="X13" s="102"/>
+      <c r="Y13" s="103"/>
+      <c r="Z13" s="104"/>
+      <c r="AA13" s="102"/>
+      <c r="AB13" s="103"/>
+      <c r="AC13" s="104"/>
+      <c r="AD13" s="102"/>
+      <c r="AE13" s="103"/>
+      <c r="AF13" s="104"/>
+      <c r="AG13" s="102"/>
+      <c r="AH13" s="103"/>
+      <c r="AI13" s="104"/>
+      <c r="AJ13" s="102"/>
+      <c r="AK13" s="103"/>
+      <c r="AL13" s="104"/>
+      <c r="AM13" s="102"/>
+      <c r="AN13" s="103"/>
+      <c r="AO13" s="104"/>
+      <c r="AP13" s="102"/>
+      <c r="AQ13" s="103"/>
+      <c r="AR13" s="104"/>
+      <c r="AS13" s="102"/>
+      <c r="AT13" s="103"/>
+      <c r="AU13" s="104"/>
+      <c r="AV13" s="122"/>
+    </row>
+    <row r="14" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A14" s="114" t="s">
+        <v>140</v>
+      </c>
+      <c r="B14" s="112">
+        <v>14</v>
       </c>
       <c r="C14" s="83">
-        <f t="shared" si="6"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="D14" s="83">
@@ -4861,289 +5015,208 @@
         <v>0</v>
       </c>
       <c r="E14" s="83"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11" t="str">
+      <c r="F14" s="122"/>
+      <c r="G14" s="122"/>
+      <c r="H14" s="122"/>
+      <c r="I14" s="122"/>
+      <c r="J14" s="122"/>
+      <c r="K14" s="122"/>
+      <c r="L14" s="122"/>
+      <c r="M14" s="122"/>
+      <c r="N14" s="122"/>
+      <c r="O14" s="122"/>
+      <c r="P14" s="122"/>
+      <c r="Q14" s="122"/>
+      <c r="R14" s="102"/>
+      <c r="S14" s="103"/>
+      <c r="T14" s="104"/>
+      <c r="U14" s="102"/>
+      <c r="V14" s="103"/>
+      <c r="W14" s="104"/>
+      <c r="X14" s="102"/>
+      <c r="Y14" s="103"/>
+      <c r="Z14" s="104"/>
+      <c r="AA14" s="102"/>
+      <c r="AB14" s="103"/>
+      <c r="AC14" s="104"/>
+      <c r="AD14" s="102"/>
+      <c r="AE14" s="103"/>
+      <c r="AF14" s="104"/>
+      <c r="AG14" s="102"/>
+      <c r="AH14" s="103"/>
+      <c r="AI14" s="104"/>
+      <c r="AJ14" s="102"/>
+      <c r="AK14" s="103"/>
+      <c r="AL14" s="104"/>
+      <c r="AM14" s="102"/>
+      <c r="AN14" s="103"/>
+      <c r="AO14" s="104"/>
+      <c r="AP14" s="102"/>
+      <c r="AQ14" s="103"/>
+      <c r="AR14" s="104"/>
+      <c r="AS14" s="102"/>
+      <c r="AT14" s="103"/>
+      <c r="AU14" s="104"/>
+      <c r="AV14" s="122"/>
+    </row>
+    <row r="15" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A15" s="114" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="112">
+        <v>32</v>
+      </c>
+      <c r="C15" s="83">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="D15" s="83">
+        <f>'มหาชัย-ผลิต'!E18</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="83"/>
+      <c r="F15" s="100"/>
+      <c r="G15" s="100"/>
+      <c r="H15" s="100"/>
+      <c r="I15" s="100"/>
+      <c r="J15" s="100"/>
+      <c r="K15" s="100"/>
+      <c r="L15" s="100"/>
+      <c r="M15" s="100"/>
+      <c r="N15" s="100" t="str">
         <f t="shared" si="7"/>
         <v>0 full, 1 less than half</v>
       </c>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="101">
+      <c r="O15" s="100"/>
+      <c r="P15" s="100"/>
+      <c r="Q15" s="100"/>
+      <c r="R15" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S14" s="102">
+      <c r="S15" s="103">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T14" s="103">
+      <c r="T15" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U14" s="101">
+      <c r="U15" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="V14" s="102">
+      <c r="V15" s="103">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="W14" s="103">
+      <c r="W15" s="104">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="X14" s="101">
+      <c r="X15" s="102">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y14" s="102">
+      <c r="Y15" s="103">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Z14" s="103">
+      <c r="Z15" s="104">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA14" s="101">
+      <c r="AA15" s="102">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AB14" s="102">
+      <c r="AB15" s="103">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AC14" s="103">
+      <c r="AC15" s="104">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AD14" s="101">
+      <c r="AD15" s="102">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AE14" s="102">
+      <c r="AE15" s="103">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AF14" s="103">
+      <c r="AF15" s="104">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AG14" s="101">
+      <c r="AG15" s="102">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AH14" s="102">
+      <c r="AH15" s="103">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AI14" s="103">
+      <c r="AI15" s="104">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AJ14" s="101">
+      <c r="AJ15" s="102">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AK14" s="102">
+      <c r="AK15" s="103">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="AL14" s="103">
+      <c r="AL15" s="104">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AM14" s="101">
+      <c r="AM15" s="102">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AN14" s="102">
+      <c r="AN15" s="103">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AO14" s="103">
+      <c r="AO15" s="104">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AP14" s="101">
+      <c r="AP15" s="102">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AQ14" s="102">
+      <c r="AQ15" s="103">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AR14" s="103">
+      <c r="AR15" s="104">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AS14" s="101">
+      <c r="AS15" s="102">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AT14" s="102">
+      <c r="AT15" s="103">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AU14" s="103">
+      <c r="AU15" s="104">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="AV14" s="11"/>
-    </row>
-    <row r="15" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A15" s="111" t="s">
-        <v>134</v>
-      </c>
-      <c r="B15" s="109">
-        <v>27</v>
-      </c>
-      <c r="C15" s="83">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="D15" s="83">
-        <f>'มหาชัย-ผลิต'!E18</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="83"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="101"/>
-      <c r="S15" s="102"/>
-      <c r="T15" s="103"/>
-      <c r="U15" s="101">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="102">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="W15" s="103">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X15" s="101">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="102">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Z15" s="103">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AA15" s="101">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AB15" s="102">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AC15" s="103">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AD15" s="101">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AE15" s="102">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AF15" s="103">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AG15" s="101">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AH15" s="102">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AI15" s="103">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="101">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AK15" s="102">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AL15" s="103">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AM15" s="101">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AN15" s="102">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AO15" s="103">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AP15" s="101">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="102">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AR15" s="103">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AS15" s="101">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AT15" s="102">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AU15" s="103">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="AV15" s="11"/>
-    </row>
-    <row r="16" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A16" s="112" t="s">
-        <v>140</v>
-      </c>
-      <c r="B16" s="109">
+      <c r="AV15" s="100"/>
+    </row>
+    <row r="16" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A16" s="115" t="s">
+        <v>136</v>
+      </c>
+      <c r="B16" s="112">
         <v>27</v>
       </c>
       <c r="C16" s="83">
@@ -5155,140 +5228,140 @@
         <v>0</v>
       </c>
       <c r="E16" s="83"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="101"/>
-      <c r="S16" s="102"/>
-      <c r="T16" s="103"/>
-      <c r="U16" s="101">
+      <c r="F16" s="111"/>
+      <c r="G16" s="111"/>
+      <c r="H16" s="111"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="111"/>
+      <c r="L16" s="111"/>
+      <c r="M16" s="111"/>
+      <c r="N16" s="111"/>
+      <c r="O16" s="111"/>
+      <c r="P16" s="111"/>
+      <c r="Q16" s="111"/>
+      <c r="R16" s="102"/>
+      <c r="S16" s="103"/>
+      <c r="T16" s="104"/>
+      <c r="U16" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="V16" s="102">
+      <c r="V16" s="103">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="W16" s="103">
+      <c r="W16" s="104">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="X16" s="101">
+      <c r="X16" s="102">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y16" s="102">
+      <c r="Y16" s="103">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Z16" s="103">
+      <c r="Z16" s="104">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA16" s="101">
+      <c r="AA16" s="102">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AB16" s="102">
+      <c r="AB16" s="103">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AC16" s="103">
+      <c r="AC16" s="104">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AD16" s="101">
+      <c r="AD16" s="102">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AE16" s="102">
+      <c r="AE16" s="103">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AF16" s="103">
+      <c r="AF16" s="104">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AG16" s="101">
+      <c r="AG16" s="102">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AH16" s="102">
+      <c r="AH16" s="103">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AI16" s="103">
+      <c r="AI16" s="104">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AJ16" s="101">
+      <c r="AJ16" s="102">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AK16" s="102">
+      <c r="AK16" s="103">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="AL16" s="103">
+      <c r="AL16" s="104">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AM16" s="101">
+      <c r="AM16" s="102">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AN16" s="102">
+      <c r="AN16" s="103">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AO16" s="103">
+      <c r="AO16" s="104">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AP16" s="101">
+      <c r="AP16" s="102">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AQ16" s="102">
+      <c r="AQ16" s="103">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AR16" s="103">
+      <c r="AR16" s="104">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AS16" s="101">
+      <c r="AS16" s="102">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AT16" s="102">
+      <c r="AT16" s="103">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AU16" s="103">
+      <c r="AU16" s="104">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="AV16" s="11"/>
-    </row>
-    <row r="17" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A17" s="113" t="s">
-        <v>63</v>
-      </c>
-      <c r="B17" s="109">
-        <v>36</v>
+      <c r="AV16" s="111"/>
+    </row>
+    <row r="17" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A17" s="116" t="s">
+        <v>142</v>
+      </c>
+      <c r="B17" s="112">
+        <v>27</v>
       </c>
       <c r="C17" s="83">
-        <f>SUMPRODUCT(ROUNDUP(D17/B17,0))</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="D17" s="83">
@@ -5296,446 +5369,446 @@
         <v>0</v>
       </c>
       <c r="E17" s="83"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11" t="str">
+      <c r="F17" s="100"/>
+      <c r="G17" s="100"/>
+      <c r="H17" s="100"/>
+      <c r="I17" s="100"/>
+      <c r="J17" s="100"/>
+      <c r="K17" s="100"/>
+      <c r="L17" s="100"/>
+      <c r="M17" s="100"/>
+      <c r="N17" s="100"/>
+      <c r="O17" s="100"/>
+      <c r="P17" s="100"/>
+      <c r="Q17" s="100"/>
+      <c r="R17" s="102"/>
+      <c r="S17" s="103"/>
+      <c r="T17" s="104"/>
+      <c r="U17" s="102">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="103">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="104">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="102">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z17" s="104">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA17" s="102">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB17" s="103">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AC17" s="104">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AD17" s="102">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AE17" s="103">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="104">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AG17" s="102">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AH17" s="103">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AI17" s="104">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="102">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AK17" s="103">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AL17" s="104">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AM17" s="102">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN17" s="103">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AO17" s="104">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AP17" s="102">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="103">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AR17" s="104">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AS17" s="102">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AT17" s="103">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AU17" s="104">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AV17" s="100"/>
+    </row>
+    <row r="18" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A18" s="117" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="112">
+        <v>36</v>
+      </c>
+      <c r="C18" s="83">
+        <f>SUMPRODUCT(ROUNDUP(D18/B18,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="83">
+        <f>'มหาชัย-ผลิต'!E24</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="83"/>
+      <c r="F18" s="100"/>
+      <c r="G18" s="100"/>
+      <c r="H18" s="100"/>
+      <c r="I18" s="100"/>
+      <c r="J18" s="100"/>
+      <c r="K18" s="100"/>
+      <c r="L18" s="100"/>
+      <c r="M18" s="100"/>
+      <c r="N18" s="100" t="str">
         <f t="shared" si="7"/>
         <v>0 full, 1 less than half</v>
       </c>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="101">
+      <c r="O18" s="100"/>
+      <c r="P18" s="100"/>
+      <c r="Q18" s="100"/>
+      <c r="R18" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S17" s="102">
+      <c r="S18" s="103">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T17" s="103">
+      <c r="T18" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U17" s="101">
+      <c r="U18" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="V17" s="102">
+      <c r="V18" s="103">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="W17" s="103">
+      <c r="W18" s="104">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="X17" s="101">
+      <c r="X18" s="102">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y17" s="102">
+      <c r="Y18" s="103">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Z17" s="103">
+      <c r="Z18" s="104">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA17" s="101">
+      <c r="AA18" s="102">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AB17" s="102">
+      <c r="AB18" s="103">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AC17" s="103">
+      <c r="AC18" s="104">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AD17" s="101">
+      <c r="AD18" s="102">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AE17" s="102">
+      <c r="AE18" s="103">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AF17" s="103">
+      <c r="AF18" s="104">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AG17" s="101">
+      <c r="AG18" s="102">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AH17" s="102">
+      <c r="AH18" s="103">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AI17" s="103">
+      <c r="AI18" s="104">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AJ17" s="101">
+      <c r="AJ18" s="102">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AK17" s="102">
+      <c r="AK18" s="103">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="AL17" s="103">
+      <c r="AL18" s="104">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AM17" s="101">
+      <c r="AM18" s="102">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AN17" s="102">
+      <c r="AN18" s="103">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AO17" s="103">
+      <c r="AO18" s="104">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AP17" s="101">
+      <c r="AP18" s="102">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AQ17" s="102">
+      <c r="AQ18" s="103">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AR17" s="103">
+      <c r="AR18" s="104">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AS17" s="101">
+      <c r="AS18" s="102">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AT17" s="102">
+      <c r="AT18" s="103">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AU17" s="103">
+      <c r="AU18" s="104">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="AV17" s="11"/>
-    </row>
-    <row r="18" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A18" s="110" t="s">
+      <c r="AV18" s="100"/>
+    </row>
+    <row r="19" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A19" s="114" t="s">
         <v>114</v>
       </c>
-      <c r="B18" s="109">
+      <c r="B19" s="112">
         <v>20</v>
       </c>
-      <c r="C18" s="83">
-        <f>SUMPRODUCT(ROUNDUP(D18/B18,0))</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="83">
-        <f>'มหาชัย-ผลิต'!E24</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="83"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11" t="e">
+      <c r="C19" s="83">
+        <f>SUMPRODUCT(ROUNDUP(D19/B19,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="83">
+        <f>'มหาชัย-ผลิต'!E26</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="83"/>
+      <c r="F19" s="100"/>
+      <c r="G19" s="100"/>
+      <c r="H19" s="100"/>
+      <c r="I19" s="100"/>
+      <c r="J19" s="100"/>
+      <c r="K19" s="100"/>
+      <c r="L19" s="100"/>
+      <c r="M19" s="100"/>
+      <c r="N19" s="100" t="e">
         <f>'มหาชัย-ผลิต'!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="101">
-        <f t="shared" ref="R18" si="33">INT(D18/B18)</f>
-        <v>0</v>
-      </c>
-      <c r="S18" s="102">
-        <f t="shared" ref="S18" si="34">IF(MOD(D18,B18)/B18&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T18" s="103">
-        <f t="shared" ref="T18" si="35">IF(AND(MOD(D18,B18)/B18&lt;=0.5,MOD(D18,B18)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U18" s="101">
-        <f t="shared" ref="U18:U20" si="36">INT(E18/B18)</f>
-        <v>0</v>
-      </c>
-      <c r="V18" s="102">
-        <f t="shared" ref="V18:V20" si="37">IF(MOD(E18,B18)/B18&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="W18" s="103">
-        <f t="shared" ref="W18:W20" si="38">IF(AND(MOD(E18,B18)/B18&lt;=0.5,MOD(E18,B18)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X18" s="101">
-        <f t="shared" ref="X18:X20" si="39">INT(F18/B18)</f>
-        <v>0</v>
-      </c>
-      <c r="Y18" s="102">
-        <f t="shared" ref="Y18:Y20" si="40">IF(MOD(F18,B18)/B18&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z18" s="103">
-        <f t="shared" ref="Z18:Z20" si="41">IF(AND(MOD(F18,B18)/B18&lt;=0.5,MOD(F18,B18)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AA18" s="101">
-        <f t="shared" ref="AA18:AA20" si="42">INT(G18/B18)</f>
-        <v>0</v>
-      </c>
-      <c r="AB18" s="102">
-        <f t="shared" ref="AB18:AB20" si="43">IF(MOD(G18,B18)/B18&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AC18" s="103">
-        <f t="shared" ref="AC18:AC20" si="44">IF(AND(MOD(G18,B18)/B18&lt;=0.5,MOD(G18,B18)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AD18" s="101">
-        <f t="shared" ref="AD18:AD20" si="45">INT(H18/B18)</f>
-        <v>0</v>
-      </c>
-      <c r="AE18" s="102">
-        <f t="shared" ref="AE18:AE20" si="46">IF(MOD(H18,B18)/B18&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF18" s="103">
-        <f t="shared" ref="AF18:AF20" si="47">IF(AND(MOD(H18,B18)/B18&lt;=0.5,MOD(H18,B18)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AG18" s="101">
-        <f t="shared" ref="AG18:AG20" si="48">INT(I18/B18)</f>
-        <v>0</v>
-      </c>
-      <c r="AH18" s="102">
-        <f t="shared" ref="AH18:AH20" si="49">IF(MOD(I18,B18)/B18&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AI18" s="103">
-        <f t="shared" ref="AI18:AI20" si="50">IF(AND(MOD(I18,B18)/B18&lt;=0.5,MOD(I18,B18)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ18" s="101">
-        <f t="shared" ref="AJ18:AJ20" si="51">INT(J18/B18)</f>
-        <v>0</v>
-      </c>
-      <c r="AK18" s="102">
-        <f t="shared" ref="AK18:AK20" si="52">IF(MOD(J18,B18)/B18&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AL18" s="103">
-        <f t="shared" ref="AL18:AL20" si="53">IF(AND(MOD(J18,B18)/B18&lt;=0.5,MOD(J18,B18)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AM18" s="101">
-        <f t="shared" ref="AM18:AM20" si="54">INT(K18/B18)</f>
-        <v>0</v>
-      </c>
-      <c r="AN18" s="102">
-        <f t="shared" ref="AN18:AN20" si="55">IF(MOD(K18,B18)/B18&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AO18" s="103">
-        <f t="shared" ref="AO18:AO20" si="56">IF(AND(MOD(K18,B18)/B18&lt;=0.5,MOD(K18,B18)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AP18" s="101">
-        <f t="shared" ref="AP18:AP20" si="57">INT(L18/B18)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ18" s="102">
-        <f t="shared" ref="AQ18:AQ20" si="58">IF(MOD(L18,B18)/B18&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AR18" s="103">
-        <f t="shared" ref="AR18:AR20" si="59">IF(AND(MOD(L18,B18)/B18&lt;=0.5,MOD(L18,B18)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AS18" s="101">
-        <f t="shared" ref="AS18:AS20" si="60">INT(M18/B18)</f>
-        <v>0</v>
-      </c>
-      <c r="AT18" s="102">
-        <f t="shared" ref="AT18:AT20" si="61">IF(MOD(M18,B18)/B18&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AU18" s="103">
-        <f t="shared" ref="AU18:AU20" si="62">IF(AND(MOD(M18,B18)/B18&lt;=0.5,MOD(M18,B18)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AV18" s="11"/>
-    </row>
-    <row r="19" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A19" s="113" t="s">
-        <v>129</v>
-      </c>
-      <c r="B19" s="109">
+      <c r="O19" s="100"/>
+      <c r="P19" s="100"/>
+      <c r="Q19" s="100"/>
+      <c r="R19" s="102">
+        <f t="shared" ref="R19" si="33">INT(D19/B19)</f>
+        <v>0</v>
+      </c>
+      <c r="S19" s="103">
+        <f t="shared" ref="S19" si="34">IF(MOD(D19,B19)/B19&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T19" s="104">
+        <f t="shared" ref="T19" si="35">IF(AND(MOD(D19,B19)/B19&lt;=0.5,MOD(D19,B19)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U19" s="102">
+        <f t="shared" ref="U19:U21" si="36">INT(E19/B19)</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="103">
+        <f t="shared" ref="V19:V21" si="37">IF(MOD(E19,B19)/B19&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W19" s="104">
+        <f t="shared" ref="W19:W21" si="38">IF(AND(MOD(E19,B19)/B19&lt;=0.5,MOD(E19,B19)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X19" s="102">
+        <f t="shared" ref="X19:X21" si="39">INT(F19/B19)</f>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="103">
+        <f t="shared" ref="Y19:Y21" si="40">IF(MOD(F19,B19)/B19&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="104">
+        <f t="shared" ref="Z19:Z21" si="41">IF(AND(MOD(F19,B19)/B19&lt;=0.5,MOD(F19,B19)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA19" s="102">
+        <f t="shared" ref="AA19:AA21" si="42">INT(G19/B19)</f>
+        <v>0</v>
+      </c>
+      <c r="AB19" s="103">
+        <f t="shared" ref="AB19:AB21" si="43">IF(MOD(G19,B19)/B19&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC19" s="104">
+        <f t="shared" ref="AC19:AC21" si="44">IF(AND(MOD(G19,B19)/B19&lt;=0.5,MOD(G19,B19)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD19" s="102">
+        <f t="shared" ref="AD19:AD21" si="45">INT(H19/B19)</f>
+        <v>0</v>
+      </c>
+      <c r="AE19" s="103">
+        <f t="shared" ref="AE19:AE21" si="46">IF(MOD(H19,B19)/B19&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="104">
+        <f t="shared" ref="AF19:AF21" si="47">IF(AND(MOD(H19,B19)/B19&lt;=0.5,MOD(H19,B19)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG19" s="102">
+        <f t="shared" ref="AG19:AG21" si="48">INT(I19/B19)</f>
+        <v>0</v>
+      </c>
+      <c r="AH19" s="103">
+        <f t="shared" ref="AH19:AH21" si="49">IF(MOD(I19,B19)/B19&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI19" s="104">
+        <f t="shared" ref="AI19:AI21" si="50">IF(AND(MOD(I19,B19)/B19&lt;=0.5,MOD(I19,B19)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="102">
+        <f t="shared" ref="AJ19:AJ21" si="51">INT(J19/B19)</f>
+        <v>0</v>
+      </c>
+      <c r="AK19" s="103">
+        <f t="shared" ref="AK19:AK21" si="52">IF(MOD(J19,B19)/B19&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL19" s="104">
+        <f t="shared" ref="AL19:AL21" si="53">IF(AND(MOD(J19,B19)/B19&lt;=0.5,MOD(J19,B19)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM19" s="102">
+        <f t="shared" ref="AM19:AM21" si="54">INT(K19/B19)</f>
+        <v>0</v>
+      </c>
+      <c r="AN19" s="103">
+        <f t="shared" ref="AN19:AN21" si="55">IF(MOD(K19,B19)/B19&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO19" s="104">
+        <f t="shared" ref="AO19:AO21" si="56">IF(AND(MOD(K19,B19)/B19&lt;=0.5,MOD(K19,B19)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP19" s="102">
+        <f t="shared" ref="AP19:AP21" si="57">INT(L19/B19)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ19" s="103">
+        <f t="shared" ref="AQ19:AQ21" si="58">IF(MOD(L19,B19)/B19&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR19" s="104">
+        <f t="shared" ref="AR19:AR21" si="59">IF(AND(MOD(L19,B19)/B19&lt;=0.5,MOD(L19,B19)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS19" s="102">
+        <f t="shared" ref="AS19:AS21" si="60">INT(M19/B19)</f>
+        <v>0</v>
+      </c>
+      <c r="AT19" s="103">
+        <f t="shared" ref="AT19:AT21" si="61">IF(MOD(M19,B19)/B19&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU19" s="104">
+        <f t="shared" ref="AU19:AU21" si="62">IF(AND(MOD(M19,B19)/B19&lt;=0.5,MOD(M19,B19)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV19" s="100"/>
+    </row>
+    <row r="20" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A20" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="B20" s="112">
         <v>15</v>
       </c>
-      <c r="C19" s="83">
-        <f>SUMPRODUCT(ROUNDUP(D19/B19,0))</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="83">
-        <f>'มหาชัย-ผลิต'!E26</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="83"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="101"/>
-      <c r="S19" s="102"/>
-      <c r="T19" s="103"/>
-      <c r="U19" s="101">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="V19" s="102">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="W19" s="103">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="X19" s="101">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="102">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="Z19" s="103">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AA19" s="101">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AB19" s="102">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="AC19" s="103">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="AD19" s="101">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="AE19" s="102">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="AF19" s="103">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="AG19" s="101">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="AH19" s="102">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="AI19" s="103">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="AJ19" s="101">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="AK19" s="102">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="AL19" s="103">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="AM19" s="101">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="AN19" s="102">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="AO19" s="103">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="AP19" s="101">
-        <f t="shared" si="57"/>
-        <v>0</v>
-      </c>
-      <c r="AQ19" s="102">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="AR19" s="103">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="AS19" s="101">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
-      <c r="AT19" s="102">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="AU19" s="103">
-        <f t="shared" si="62"/>
-        <v>0</v>
-      </c>
-      <c r="AV19" s="11"/>
-    </row>
-    <row r="20" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A20" s="113" t="s">
-        <v>65</v>
-      </c>
-      <c r="B20" s="109">
-        <v>45</v>
-      </c>
       <c r="C20" s="83">
-        <f t="shared" ref="C20" si="63">SUMPRODUCT(ROUNDUP(D20/B20,0))</f>
+        <f>SUMPRODUCT(ROUNDUP(D20/B20,0))</f>
         <v>0</v>
       </c>
       <c r="D20" s="83">
@@ -5743,140 +5816,140 @@
         <v>0</v>
       </c>
       <c r="E20" s="83"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="101"/>
-      <c r="S20" s="102"/>
-      <c r="T20" s="103"/>
-      <c r="U20" s="101">
+      <c r="F20" s="100"/>
+      <c r="G20" s="100"/>
+      <c r="H20" s="100"/>
+      <c r="I20" s="100"/>
+      <c r="J20" s="100"/>
+      <c r="K20" s="100"/>
+      <c r="L20" s="100"/>
+      <c r="M20" s="100"/>
+      <c r="N20" s="100"/>
+      <c r="O20" s="100"/>
+      <c r="P20" s="100"/>
+      <c r="Q20" s="100"/>
+      <c r="R20" s="102"/>
+      <c r="S20" s="103"/>
+      <c r="T20" s="104"/>
+      <c r="U20" s="102">
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="V20" s="102">
+      <c r="V20" s="103">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="W20" s="103">
+      <c r="W20" s="104">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="X20" s="101">
+      <c r="X20" s="102">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="Y20" s="102">
+      <c r="Y20" s="103">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="Z20" s="103">
+      <c r="Z20" s="104">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="AA20" s="101">
+      <c r="AA20" s="102">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="AB20" s="102">
+      <c r="AB20" s="103">
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="AC20" s="103">
+      <c r="AC20" s="104">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="AD20" s="101">
+      <c r="AD20" s="102">
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="AE20" s="102">
+      <c r="AE20" s="103">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="AF20" s="103">
+      <c r="AF20" s="104">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
-      <c r="AG20" s="101">
+      <c r="AG20" s="102">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="AH20" s="102">
+      <c r="AH20" s="103">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="AI20" s="103">
+      <c r="AI20" s="104">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="AJ20" s="101">
+      <c r="AJ20" s="102">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
-      <c r="AK20" s="102">
+      <c r="AK20" s="103">
         <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="AL20" s="103">
+      <c r="AL20" s="104">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="AM20" s="101">
+      <c r="AM20" s="102">
         <f t="shared" si="54"/>
         <v>0</v>
       </c>
-      <c r="AN20" s="102">
+      <c r="AN20" s="103">
         <f t="shared" si="55"/>
         <v>0</v>
       </c>
-      <c r="AO20" s="103">
+      <c r="AO20" s="104">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="AP20" s="101">
+      <c r="AP20" s="102">
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AQ20" s="102">
+      <c r="AQ20" s="103">
         <f t="shared" si="58"/>
         <v>0</v>
       </c>
-      <c r="AR20" s="103">
+      <c r="AR20" s="104">
         <f t="shared" si="59"/>
         <v>0</v>
       </c>
-      <c r="AS20" s="101">
+      <c r="AS20" s="102">
         <f t="shared" si="60"/>
         <v>0</v>
       </c>
-      <c r="AT20" s="102">
+      <c r="AT20" s="103">
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="AU20" s="103">
+      <c r="AU20" s="104">
         <f t="shared" si="62"/>
         <v>0</v>
       </c>
-      <c r="AV20" s="11"/>
-    </row>
-    <row r="21" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A21" s="113" t="s">
-        <v>132</v>
-      </c>
-      <c r="B21" s="109">
-        <v>15</v>
+      <c r="AV20" s="100"/>
+    </row>
+    <row r="21" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A21" s="117" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="112">
+        <v>45</v>
       </c>
       <c r="C21" s="83">
-        <f t="shared" ref="C21" si="64">SUMPRODUCT(ROUNDUP(D21/B21,0))</f>
+        <f t="shared" ref="C21" si="63">SUMPRODUCT(ROUNDUP(D21/B21,0))</f>
         <v>0</v>
       </c>
       <c r="D21" s="83">
@@ -5884,140 +5957,140 @@
         <v>0</v>
       </c>
       <c r="E21" s="83"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="11"/>
-      <c r="R21" s="101"/>
-      <c r="S21" s="102"/>
-      <c r="T21" s="103"/>
-      <c r="U21" s="101">
-        <f t="shared" ref="U21" si="65">INT(E21/B21)</f>
-        <v>0</v>
-      </c>
-      <c r="V21" s="102">
-        <f t="shared" ref="V21" si="66">IF(MOD(E21,B21)/B21&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="W21" s="103">
-        <f t="shared" ref="W21" si="67">IF(AND(MOD(E21,B21)/B21&lt;=0.5,MOD(E21,B21)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X21" s="101">
-        <f t="shared" ref="X21" si="68">INT(F21/B21)</f>
-        <v>0</v>
-      </c>
-      <c r="Y21" s="102">
-        <f t="shared" ref="Y21" si="69">IF(MOD(F21,B21)/B21&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z21" s="103">
-        <f t="shared" ref="Z21" si="70">IF(AND(MOD(F21,B21)/B21&lt;=0.5,MOD(F21,B21)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AA21" s="101">
-        <f t="shared" ref="AA21" si="71">INT(G21/B21)</f>
-        <v>0</v>
-      </c>
-      <c r="AB21" s="102">
-        <f t="shared" ref="AB21" si="72">IF(MOD(G21,B21)/B21&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AC21" s="103">
-        <f t="shared" ref="AC21" si="73">IF(AND(MOD(G21,B21)/B21&lt;=0.5,MOD(G21,B21)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AD21" s="101">
-        <f t="shared" ref="AD21" si="74">INT(H21/B21)</f>
-        <v>0</v>
-      </c>
-      <c r="AE21" s="102">
-        <f t="shared" ref="AE21" si="75">IF(MOD(H21,B21)/B21&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF21" s="103">
-        <f t="shared" ref="AF21" si="76">IF(AND(MOD(H21,B21)/B21&lt;=0.5,MOD(H21,B21)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AG21" s="101">
-        <f t="shared" ref="AG21" si="77">INT(I21/B21)</f>
-        <v>0</v>
-      </c>
-      <c r="AH21" s="102">
-        <f t="shared" ref="AH21" si="78">IF(MOD(I21,B21)/B21&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AI21" s="103">
-        <f t="shared" ref="AI21" si="79">IF(AND(MOD(I21,B21)/B21&lt;=0.5,MOD(I21,B21)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ21" s="101">
-        <f t="shared" ref="AJ21" si="80">INT(J21/B21)</f>
-        <v>0</v>
-      </c>
-      <c r="AK21" s="102">
-        <f t="shared" ref="AK21" si="81">IF(MOD(J21,B21)/B21&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AL21" s="103">
-        <f t="shared" ref="AL21" si="82">IF(AND(MOD(J21,B21)/B21&lt;=0.5,MOD(J21,B21)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AM21" s="101">
-        <f t="shared" ref="AM21" si="83">INT(K21/B21)</f>
-        <v>0</v>
-      </c>
-      <c r="AN21" s="102">
-        <f t="shared" ref="AN21" si="84">IF(MOD(K21,B21)/B21&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AO21" s="103">
-        <f t="shared" ref="AO21" si="85">IF(AND(MOD(K21,B21)/B21&lt;=0.5,MOD(K21,B21)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AP21" s="101">
-        <f t="shared" ref="AP21" si="86">INT(L21/B21)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ21" s="102">
-        <f t="shared" ref="AQ21" si="87">IF(MOD(L21,B21)/B21&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AR21" s="103">
-        <f t="shared" ref="AR21" si="88">IF(AND(MOD(L21,B21)/B21&lt;=0.5,MOD(L21,B21)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AS21" s="101">
-        <f t="shared" ref="AS21" si="89">INT(M21/B21)</f>
-        <v>0</v>
-      </c>
-      <c r="AT21" s="102">
-        <f t="shared" ref="AT21" si="90">IF(MOD(M21,B21)/B21&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AU21" s="103">
-        <f t="shared" ref="AU21" si="91">IF(AND(MOD(M21,B21)/B21&lt;=0.5,MOD(M21,B21)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AV21" s="11"/>
-    </row>
-    <row r="22" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A22" s="113" t="s">
-        <v>66</v>
-      </c>
-      <c r="B22" s="109">
+      <c r="F21" s="100"/>
+      <c r="G21" s="100"/>
+      <c r="H21" s="100"/>
+      <c r="I21" s="100"/>
+      <c r="J21" s="100"/>
+      <c r="K21" s="100"/>
+      <c r="L21" s="100"/>
+      <c r="M21" s="100"/>
+      <c r="N21" s="100"/>
+      <c r="O21" s="100"/>
+      <c r="P21" s="100"/>
+      <c r="Q21" s="100"/>
+      <c r="R21" s="102"/>
+      <c r="S21" s="103"/>
+      <c r="T21" s="104"/>
+      <c r="U21" s="102">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="103">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="104">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="X21" s="102">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="103">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z21" s="104">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="AA21" s="102">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB21" s="103">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AC21" s="104">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD21" s="102">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="AE21" s="103">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="104">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="AG21" s="102">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="AH21" s="103">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="AI21" s="104">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="102">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="AK21" s="103">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="AL21" s="104">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="AM21" s="102">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="AN21" s="103">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="AO21" s="104">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="AP21" s="102">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="AQ21" s="103">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="AR21" s="104">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="AS21" s="102">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="AT21" s="103">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="AU21" s="104">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="AV21" s="100"/>
+    </row>
+    <row r="22" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A22" s="117" t="s">
+        <v>134</v>
+      </c>
+      <c r="B22" s="112">
         <v>15</v>
       </c>
       <c r="C22" s="83">
-        <f t="shared" ref="C22:C23" si="92">SUMPRODUCT(ROUNDUP(D22/B22,0))</f>
+        <f t="shared" ref="C22" si="64">SUMPRODUCT(ROUNDUP(D22/B22,0))</f>
         <v>0</v>
       </c>
       <c r="D22" s="83">
@@ -6025,293 +6098,293 @@
         <v>0</v>
       </c>
       <c r="E22" s="83"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11" t="e">
+      <c r="F22" s="105"/>
+      <c r="G22" s="105"/>
+      <c r="H22" s="105"/>
+      <c r="I22" s="105"/>
+      <c r="J22" s="105"/>
+      <c r="K22" s="105"/>
+      <c r="L22" s="105"/>
+      <c r="M22" s="105"/>
+      <c r="N22" s="105"/>
+      <c r="O22" s="105"/>
+      <c r="P22" s="105"/>
+      <c r="Q22" s="105"/>
+      <c r="R22" s="102"/>
+      <c r="S22" s="103"/>
+      <c r="T22" s="104"/>
+      <c r="U22" s="102">
+        <f t="shared" ref="U22" si="65">INT(E22/B22)</f>
+        <v>0</v>
+      </c>
+      <c r="V22" s="103">
+        <f t="shared" ref="V22" si="66">IF(MOD(E22,B22)/B22&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W22" s="104">
+        <f t="shared" ref="W22" si="67">IF(AND(MOD(E22,B22)/B22&lt;=0.5,MOD(E22,B22)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X22" s="102">
+        <f t="shared" ref="X22" si="68">INT(F22/B22)</f>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="103">
+        <f t="shared" ref="Y22" si="69">IF(MOD(F22,B22)/B22&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z22" s="104">
+        <f t="shared" ref="Z22" si="70">IF(AND(MOD(F22,B22)/B22&lt;=0.5,MOD(F22,B22)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA22" s="102">
+        <f t="shared" ref="AA22" si="71">INT(G22/B22)</f>
+        <v>0</v>
+      </c>
+      <c r="AB22" s="103">
+        <f t="shared" ref="AB22" si="72">IF(MOD(G22,B22)/B22&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC22" s="104">
+        <f t="shared" ref="AC22" si="73">IF(AND(MOD(G22,B22)/B22&lt;=0.5,MOD(G22,B22)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD22" s="102">
+        <f t="shared" ref="AD22" si="74">INT(H22/B22)</f>
+        <v>0</v>
+      </c>
+      <c r="AE22" s="103">
+        <f t="shared" ref="AE22" si="75">IF(MOD(H22,B22)/B22&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF22" s="104">
+        <f t="shared" ref="AF22" si="76">IF(AND(MOD(H22,B22)/B22&lt;=0.5,MOD(H22,B22)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG22" s="102">
+        <f t="shared" ref="AG22" si="77">INT(I22/B22)</f>
+        <v>0</v>
+      </c>
+      <c r="AH22" s="103">
+        <f t="shared" ref="AH22" si="78">IF(MOD(I22,B22)/B22&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI22" s="104">
+        <f t="shared" ref="AI22" si="79">IF(AND(MOD(I22,B22)/B22&lt;=0.5,MOD(I22,B22)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="102">
+        <f t="shared" ref="AJ22" si="80">INT(J22/B22)</f>
+        <v>0</v>
+      </c>
+      <c r="AK22" s="103">
+        <f t="shared" ref="AK22" si="81">IF(MOD(J22,B22)/B22&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL22" s="104">
+        <f t="shared" ref="AL22" si="82">IF(AND(MOD(J22,B22)/B22&lt;=0.5,MOD(J22,B22)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM22" s="102">
+        <f t="shared" ref="AM22" si="83">INT(K22/B22)</f>
+        <v>0</v>
+      </c>
+      <c r="AN22" s="103">
+        <f t="shared" ref="AN22" si="84">IF(MOD(K22,B22)/B22&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO22" s="104">
+        <f t="shared" ref="AO22" si="85">IF(AND(MOD(K22,B22)/B22&lt;=0.5,MOD(K22,B22)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP22" s="102">
+        <f t="shared" ref="AP22" si="86">INT(L22/B22)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="103">
+        <f t="shared" ref="AQ22" si="87">IF(MOD(L22,B22)/B22&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR22" s="104">
+        <f t="shared" ref="AR22" si="88">IF(AND(MOD(L22,B22)/B22&lt;=0.5,MOD(L22,B22)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS22" s="102">
+        <f t="shared" ref="AS22" si="89">INT(M22/B22)</f>
+        <v>0</v>
+      </c>
+      <c r="AT22" s="103">
+        <f t="shared" ref="AT22" si="90">IF(MOD(M22,B22)/B22&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU22" s="104">
+        <f t="shared" ref="AU22" si="91">IF(AND(MOD(M22,B22)/B22&lt;=0.5,MOD(M22,B22)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV22" s="105"/>
+    </row>
+    <row r="23" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A23" s="117" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="112">
+        <v>15</v>
+      </c>
+      <c r="C23" s="83">
+        <f t="shared" ref="C23:C24" si="92">SUMPRODUCT(ROUNDUP(D23/B23,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="83">
+        <f>'มหาชัย-ผลิต'!E34</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="83"/>
+      <c r="F23" s="100"/>
+      <c r="G23" s="100"/>
+      <c r="H23" s="100"/>
+      <c r="I23" s="100"/>
+      <c r="J23" s="100"/>
+      <c r="K23" s="100"/>
+      <c r="L23" s="100"/>
+      <c r="M23" s="100"/>
+      <c r="N23" s="100" t="e">
         <f>'มหาชัย-ผลิต'!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="11"/>
-      <c r="R22" s="101">
+      <c r="O23" s="100"/>
+      <c r="P23" s="100"/>
+      <c r="Q23" s="100"/>
+      <c r="R23" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S22" s="102">
+      <c r="S23" s="103">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T22" s="103">
+      <c r="T23" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U22" s="101">
+      <c r="U23" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="V22" s="102">
+      <c r="V23" s="103">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="W22" s="103">
+      <c r="W23" s="104">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="X22" s="101">
+      <c r="X23" s="102">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y22" s="102">
+      <c r="Y23" s="103">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Z22" s="103">
+      <c r="Z23" s="104">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA22" s="101">
+      <c r="AA23" s="102">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AB22" s="102">
+      <c r="AB23" s="103">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AC22" s="103">
+      <c r="AC23" s="104">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AD22" s="101">
+      <c r="AD23" s="102">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AE22" s="102">
+      <c r="AE23" s="103">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AF22" s="103">
+      <c r="AF23" s="104">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AG22" s="101">
+      <c r="AG23" s="102">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AH22" s="102">
+      <c r="AH23" s="103">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AI22" s="103">
+      <c r="AI23" s="104">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AJ22" s="101">
+      <c r="AJ23" s="102">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AK22" s="102">
+      <c r="AK23" s="103">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="AL22" s="103">
+      <c r="AL23" s="104">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AM22" s="101">
+      <c r="AM23" s="102">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AN22" s="102">
+      <c r="AN23" s="103">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AO22" s="103">
+      <c r="AO23" s="104">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AP22" s="101">
+      <c r="AP23" s="102">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AQ22" s="102">
+      <c r="AQ23" s="103">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AR22" s="103">
+      <c r="AR23" s="104">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AS22" s="101">
+      <c r="AS23" s="102">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AT22" s="102">
+      <c r="AT23" s="103">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AU22" s="103">
+      <c r="AU23" s="104">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="AV22" s="11"/>
-    </row>
-    <row r="23" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A23" s="113" t="s">
-        <v>130</v>
-      </c>
-      <c r="B23" s="109">
+      <c r="AV23" s="100"/>
+    </row>
+    <row r="24" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A24" s="117" t="s">
+        <v>132</v>
+      </c>
+      <c r="B24" s="112">
         <v>27</v>
       </c>
-      <c r="C23" s="83">
+      <c r="C24" s="83">
         <f t="shared" si="92"/>
-        <v>0</v>
-      </c>
-      <c r="D23" s="83">
-        <f>'มหาชัย-ผลิต'!E34</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="83"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="11"/>
-      <c r="R23" s="101"/>
-      <c r="S23" s="102"/>
-      <c r="T23" s="103"/>
-      <c r="U23" s="101">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V23" s="102">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="W23" s="103">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X23" s="101">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Y23" s="102">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Z23" s="103">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AA23" s="101">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AB23" s="102">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AC23" s="103">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AD23" s="101">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AE23" s="102">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AF23" s="103">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AG23" s="101">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AH23" s="102">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AI23" s="103">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AJ23" s="101">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AK23" s="102">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AL23" s="103">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AM23" s="101">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AN23" s="102">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AO23" s="103">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AP23" s="101">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AQ23" s="102">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AR23" s="103">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AS23" s="101">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AT23" s="102">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AU23" s="103">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="AV23" s="11"/>
-    </row>
-    <row r="24" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A24" s="113" t="s">
-        <v>68</v>
-      </c>
-      <c r="B24" s="109">
-        <v>20</v>
-      </c>
-      <c r="C24" s="83">
-        <f t="shared" ref="C24:C26" si="93">SUMPRODUCT(ROUNDUP(D24/B24,0))</f>
         <v>0</v>
       </c>
       <c r="D24" s="83">
@@ -6319,140 +6392,140 @@
         <v>0</v>
       </c>
       <c r="E24" s="83"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="11"/>
-      <c r="R24" s="101"/>
-      <c r="S24" s="102"/>
-      <c r="T24" s="103"/>
-      <c r="U24" s="101">
-        <f t="shared" ref="U24" si="94">INT(E24/B24)</f>
-        <v>0</v>
-      </c>
-      <c r="V24" s="102">
-        <f t="shared" ref="V24" si="95">IF(MOD(E24,B24)/B24&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="W24" s="103">
-        <f t="shared" ref="W24" si="96">IF(AND(MOD(E24,B24)/B24&lt;=0.5,MOD(E24,B24)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X24" s="101">
-        <f t="shared" ref="X24" si="97">INT(F24/B24)</f>
-        <v>0</v>
-      </c>
-      <c r="Y24" s="102">
-        <f t="shared" ref="Y24" si="98">IF(MOD(F24,B24)/B24&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z24" s="103">
-        <f t="shared" ref="Z24" si="99">IF(AND(MOD(F24,B24)/B24&lt;=0.5,MOD(F24,B24)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AA24" s="101">
-        <f t="shared" ref="AA24" si="100">INT(G24/B24)</f>
-        <v>0</v>
-      </c>
-      <c r="AB24" s="102">
-        <f t="shared" ref="AB24" si="101">IF(MOD(G24,B24)/B24&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AC24" s="103">
-        <f t="shared" ref="AC24" si="102">IF(AND(MOD(G24,B24)/B24&lt;=0.5,MOD(G24,B24)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AD24" s="101">
-        <f t="shared" ref="AD24" si="103">INT(H24/B24)</f>
-        <v>0</v>
-      </c>
-      <c r="AE24" s="102">
-        <f t="shared" ref="AE24" si="104">IF(MOD(H24,B24)/B24&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF24" s="103">
-        <f t="shared" ref="AF24" si="105">IF(AND(MOD(H24,B24)/B24&lt;=0.5,MOD(H24,B24)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AG24" s="101">
-        <f t="shared" ref="AG24" si="106">INT(I24/B24)</f>
-        <v>0</v>
-      </c>
-      <c r="AH24" s="102">
-        <f t="shared" ref="AH24" si="107">IF(MOD(I24,B24)/B24&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AI24" s="103">
-        <f t="shared" ref="AI24" si="108">IF(AND(MOD(I24,B24)/B24&lt;=0.5,MOD(I24,B24)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ24" s="101">
-        <f t="shared" ref="AJ24" si="109">INT(J24/B24)</f>
-        <v>0</v>
-      </c>
-      <c r="AK24" s="102">
-        <f t="shared" ref="AK24" si="110">IF(MOD(J24,B24)/B24&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AL24" s="103">
-        <f t="shared" ref="AL24" si="111">IF(AND(MOD(J24,B24)/B24&lt;=0.5,MOD(J24,B24)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AM24" s="101">
-        <f t="shared" ref="AM24" si="112">INT(K24/B24)</f>
-        <v>0</v>
-      </c>
-      <c r="AN24" s="102">
-        <f t="shared" ref="AN24" si="113">IF(MOD(K24,B24)/B24&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AO24" s="103">
-        <f t="shared" ref="AO24" si="114">IF(AND(MOD(K24,B24)/B24&lt;=0.5,MOD(K24,B24)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AP24" s="101">
-        <f t="shared" ref="AP24" si="115">INT(L24/B24)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ24" s="102">
-        <f t="shared" ref="AQ24" si="116">IF(MOD(L24,B24)/B24&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AR24" s="103">
-        <f t="shared" ref="AR24" si="117">IF(AND(MOD(L24,B24)/B24&lt;=0.5,MOD(L24,B24)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AS24" s="101">
-        <f t="shared" ref="AS24" si="118">INT(M24/B24)</f>
-        <v>0</v>
-      </c>
-      <c r="AT24" s="102">
-        <f t="shared" ref="AT24" si="119">IF(MOD(M24,B24)/B24&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AU24" s="103">
-        <f t="shared" ref="AU24" si="120">IF(AND(MOD(M24,B24)/B24&lt;=0.5,MOD(M24,B24)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AV24" s="11"/>
-    </row>
-    <row r="25" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A25" s="112" t="s">
-        <v>69</v>
-      </c>
-      <c r="B25" s="109">
-        <v>32</v>
+      <c r="F24" s="100"/>
+      <c r="G24" s="100"/>
+      <c r="H24" s="100"/>
+      <c r="I24" s="100"/>
+      <c r="J24" s="100"/>
+      <c r="K24" s="100"/>
+      <c r="L24" s="100"/>
+      <c r="M24" s="100"/>
+      <c r="N24" s="100"/>
+      <c r="O24" s="100"/>
+      <c r="P24" s="100"/>
+      <c r="Q24" s="100"/>
+      <c r="R24" s="102"/>
+      <c r="S24" s="103"/>
+      <c r="T24" s="104"/>
+      <c r="U24" s="102">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="103">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="104">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X24" s="102">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z24" s="104">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA24" s="102">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB24" s="103">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AC24" s="104">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AD24" s="102">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AE24" s="103">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="104">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AG24" s="102">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AH24" s="103">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AI24" s="104">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="102">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AK24" s="103">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AL24" s="104">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AM24" s="102">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN24" s="103">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AO24" s="104">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AP24" s="102">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ24" s="103">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AR24" s="104">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AS24" s="102">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AT24" s="103">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AU24" s="104">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AV24" s="100"/>
+    </row>
+    <row r="25" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A25" s="117" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="112">
+        <v>20</v>
       </c>
       <c r="C25" s="83">
-        <f t="shared" si="93"/>
+        <f t="shared" ref="C25:C27" si="93">SUMPRODUCT(ROUNDUP(D25/B25,0))</f>
         <v>0</v>
       </c>
       <c r="D25" s="83">
@@ -6460,56 +6533,137 @@
         <v>0</v>
       </c>
       <c r="E25" s="83"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="11"/>
-      <c r="R25" s="101"/>
-      <c r="S25" s="102"/>
-      <c r="T25" s="103"/>
-      <c r="U25" s="101"/>
-      <c r="V25" s="102"/>
-      <c r="W25" s="103"/>
-      <c r="X25" s="101"/>
-      <c r="Y25" s="102"/>
-      <c r="Z25" s="103"/>
-      <c r="AA25" s="101"/>
-      <c r="AB25" s="102"/>
-      <c r="AC25" s="103"/>
-      <c r="AD25" s="101"/>
-      <c r="AE25" s="102"/>
-      <c r="AF25" s="103"/>
-      <c r="AG25" s="101"/>
-      <c r="AH25" s="102"/>
-      <c r="AI25" s="103"/>
-      <c r="AJ25" s="101"/>
-      <c r="AK25" s="102"/>
-      <c r="AL25" s="103"/>
-      <c r="AM25" s="101"/>
-      <c r="AN25" s="102"/>
-      <c r="AO25" s="103"/>
-      <c r="AP25" s="101"/>
-      <c r="AQ25" s="102"/>
-      <c r="AR25" s="103"/>
-      <c r="AS25" s="101"/>
-      <c r="AT25" s="102"/>
-      <c r="AU25" s="103"/>
-      <c r="AV25" s="11"/>
-    </row>
-    <row r="26" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A26" s="110" t="s">
-        <v>113</v>
-      </c>
-      <c r="B26" s="109">
-        <v>15</v>
+      <c r="F25" s="100"/>
+      <c r="G25" s="100"/>
+      <c r="H25" s="100"/>
+      <c r="I25" s="100"/>
+      <c r="J25" s="100"/>
+      <c r="K25" s="100"/>
+      <c r="L25" s="100"/>
+      <c r="M25" s="100"/>
+      <c r="N25" s="100"/>
+      <c r="O25" s="100"/>
+      <c r="P25" s="100"/>
+      <c r="Q25" s="100"/>
+      <c r="R25" s="102"/>
+      <c r="S25" s="103"/>
+      <c r="T25" s="104"/>
+      <c r="U25" s="102">
+        <f t="shared" ref="U25" si="94">INT(E25/B25)</f>
+        <v>0</v>
+      </c>
+      <c r="V25" s="103">
+        <f t="shared" ref="V25" si="95">IF(MOD(E25,B25)/B25&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W25" s="104">
+        <f t="shared" ref="W25" si="96">IF(AND(MOD(E25,B25)/B25&lt;=0.5,MOD(E25,B25)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X25" s="102">
+        <f t="shared" ref="X25" si="97">INT(F25/B25)</f>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="103">
+        <f t="shared" ref="Y25" si="98">IF(MOD(F25,B25)/B25&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z25" s="104">
+        <f t="shared" ref="Z25" si="99">IF(AND(MOD(F25,B25)/B25&lt;=0.5,MOD(F25,B25)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA25" s="102">
+        <f t="shared" ref="AA25" si="100">INT(G25/B25)</f>
+        <v>0</v>
+      </c>
+      <c r="AB25" s="103">
+        <f t="shared" ref="AB25" si="101">IF(MOD(G25,B25)/B25&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC25" s="104">
+        <f t="shared" ref="AC25" si="102">IF(AND(MOD(G25,B25)/B25&lt;=0.5,MOD(G25,B25)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD25" s="102">
+        <f t="shared" ref="AD25" si="103">INT(H25/B25)</f>
+        <v>0</v>
+      </c>
+      <c r="AE25" s="103">
+        <f t="shared" ref="AE25" si="104">IF(MOD(H25,B25)/B25&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF25" s="104">
+        <f t="shared" ref="AF25" si="105">IF(AND(MOD(H25,B25)/B25&lt;=0.5,MOD(H25,B25)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG25" s="102">
+        <f t="shared" ref="AG25" si="106">INT(I25/B25)</f>
+        <v>0</v>
+      </c>
+      <c r="AH25" s="103">
+        <f t="shared" ref="AH25" si="107">IF(MOD(I25,B25)/B25&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI25" s="104">
+        <f t="shared" ref="AI25" si="108">IF(AND(MOD(I25,B25)/B25&lt;=0.5,MOD(I25,B25)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="102">
+        <f t="shared" ref="AJ25" si="109">INT(J25/B25)</f>
+        <v>0</v>
+      </c>
+      <c r="AK25" s="103">
+        <f t="shared" ref="AK25" si="110">IF(MOD(J25,B25)/B25&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL25" s="104">
+        <f t="shared" ref="AL25" si="111">IF(AND(MOD(J25,B25)/B25&lt;=0.5,MOD(J25,B25)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM25" s="102">
+        <f t="shared" ref="AM25" si="112">INT(K25/B25)</f>
+        <v>0</v>
+      </c>
+      <c r="AN25" s="103">
+        <f t="shared" ref="AN25" si="113">IF(MOD(K25,B25)/B25&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO25" s="104">
+        <f t="shared" ref="AO25" si="114">IF(AND(MOD(K25,B25)/B25&lt;=0.5,MOD(K25,B25)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP25" s="102">
+        <f t="shared" ref="AP25" si="115">INT(L25/B25)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="103">
+        <f t="shared" ref="AQ25" si="116">IF(MOD(L25,B25)/B25&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR25" s="104">
+        <f t="shared" ref="AR25" si="117">IF(AND(MOD(L25,B25)/B25&lt;=0.5,MOD(L25,B25)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS25" s="102">
+        <f t="shared" ref="AS25" si="118">INT(M25/B25)</f>
+        <v>0</v>
+      </c>
+      <c r="AT25" s="103">
+        <f t="shared" ref="AT25" si="119">IF(MOD(M25,B25)/B25&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU25" s="104">
+        <f t="shared" ref="AU25" si="120">IF(AND(MOD(M25,B25)/B25&lt;=0.5,MOD(M25,B25)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV25" s="100"/>
+    </row>
+    <row r="26" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A26" s="116" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26" s="112">
+        <v>32</v>
       </c>
       <c r="C26" s="83">
         <f t="shared" si="93"/>
@@ -6520,59 +6674,59 @@
         <v>0</v>
       </c>
       <c r="E26" s="83"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
-      <c r="Q26" s="11"/>
-      <c r="R26" s="101"/>
-      <c r="S26" s="102"/>
-      <c r="T26" s="103"/>
-      <c r="U26" s="101"/>
-      <c r="V26" s="102"/>
-      <c r="W26" s="103"/>
-      <c r="X26" s="101"/>
-      <c r="Y26" s="102"/>
-      <c r="Z26" s="103"/>
-      <c r="AA26" s="101"/>
-      <c r="AB26" s="102"/>
-      <c r="AC26" s="103"/>
-      <c r="AD26" s="101"/>
-      <c r="AE26" s="102"/>
-      <c r="AF26" s="103"/>
-      <c r="AG26" s="101"/>
-      <c r="AH26" s="102"/>
-      <c r="AI26" s="103"/>
-      <c r="AJ26" s="101"/>
-      <c r="AK26" s="102"/>
-      <c r="AL26" s="103"/>
-      <c r="AM26" s="101"/>
-      <c r="AN26" s="102"/>
-      <c r="AO26" s="103"/>
-      <c r="AP26" s="101"/>
-      <c r="AQ26" s="102"/>
-      <c r="AR26" s="103"/>
-      <c r="AS26" s="101"/>
-      <c r="AT26" s="102"/>
-      <c r="AU26" s="103"/>
-      <c r="AV26" s="11"/>
-    </row>
-    <row r="27" spans="1:48" ht="19.95" customHeight="1">
-      <c r="A27" s="110" t="s">
-        <v>143</v>
-      </c>
-      <c r="B27" s="109">
-        <v>8</v>
+      <c r="F26" s="100"/>
+      <c r="G26" s="100"/>
+      <c r="H26" s="100"/>
+      <c r="I26" s="100"/>
+      <c r="J26" s="100"/>
+      <c r="K26" s="100"/>
+      <c r="L26" s="100"/>
+      <c r="M26" s="100"/>
+      <c r="N26" s="100"/>
+      <c r="O26" s="100"/>
+      <c r="P26" s="100"/>
+      <c r="Q26" s="100"/>
+      <c r="R26" s="102"/>
+      <c r="S26" s="103"/>
+      <c r="T26" s="104"/>
+      <c r="U26" s="102"/>
+      <c r="V26" s="103"/>
+      <c r="W26" s="104"/>
+      <c r="X26" s="102"/>
+      <c r="Y26" s="103"/>
+      <c r="Z26" s="104"/>
+      <c r="AA26" s="102"/>
+      <c r="AB26" s="103"/>
+      <c r="AC26" s="104"/>
+      <c r="AD26" s="102"/>
+      <c r="AE26" s="103"/>
+      <c r="AF26" s="104"/>
+      <c r="AG26" s="102"/>
+      <c r="AH26" s="103"/>
+      <c r="AI26" s="104"/>
+      <c r="AJ26" s="102"/>
+      <c r="AK26" s="103"/>
+      <c r="AL26" s="104"/>
+      <c r="AM26" s="102"/>
+      <c r="AN26" s="103"/>
+      <c r="AO26" s="104"/>
+      <c r="AP26" s="102"/>
+      <c r="AQ26" s="103"/>
+      <c r="AR26" s="104"/>
+      <c r="AS26" s="102"/>
+      <c r="AT26" s="103"/>
+      <c r="AU26" s="104"/>
+      <c r="AV26" s="100"/>
+    </row>
+    <row r="27" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A27" s="114" t="s">
+        <v>113</v>
+      </c>
+      <c r="B27" s="112">
+        <v>15</v>
       </c>
       <c r="C27" s="83">
-        <f t="shared" ref="C27" si="121">SUMPRODUCT(ROUNDUP(D27/B27,0))</f>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="D27" s="83">
@@ -6580,164 +6734,200 @@
         <v>0</v>
       </c>
       <c r="E27" s="83"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="11"/>
-      <c r="P27" s="11"/>
-      <c r="Q27" s="11"/>
-      <c r="R27" s="101"/>
-      <c r="S27" s="102"/>
-      <c r="T27" s="103"/>
-      <c r="U27" s="101"/>
-      <c r="V27" s="102"/>
-      <c r="W27" s="103"/>
-      <c r="X27" s="101"/>
-      <c r="Y27" s="102"/>
-      <c r="Z27" s="103"/>
-      <c r="AA27" s="101"/>
-      <c r="AB27" s="102"/>
-      <c r="AC27" s="103"/>
-      <c r="AD27" s="101"/>
-      <c r="AE27" s="102"/>
-      <c r="AF27" s="103"/>
-      <c r="AG27" s="101"/>
-      <c r="AH27" s="102"/>
-      <c r="AI27" s="103"/>
-      <c r="AJ27" s="101"/>
-      <c r="AK27" s="102"/>
-      <c r="AL27" s="103"/>
-      <c r="AM27" s="101"/>
-      <c r="AN27" s="102"/>
-      <c r="AO27" s="103"/>
-      <c r="AP27" s="101"/>
-      <c r="AQ27" s="102"/>
-      <c r="AR27" s="103"/>
-      <c r="AS27" s="101"/>
-      <c r="AT27" s="102"/>
-      <c r="AU27" s="103"/>
-      <c r="AV27" s="11"/>
-    </row>
-    <row r="28" spans="1:48" s="23" customFormat="1" ht="25.2" customHeight="1">
-      <c r="A28" s="194" t="s">
+      <c r="F27" s="100"/>
+      <c r="G27" s="100"/>
+      <c r="H27" s="100"/>
+      <c r="I27" s="100"/>
+      <c r="J27" s="100"/>
+      <c r="K27" s="100"/>
+      <c r="L27" s="100"/>
+      <c r="M27" s="100"/>
+      <c r="N27" s="100"/>
+      <c r="O27" s="100"/>
+      <c r="P27" s="100"/>
+      <c r="Q27" s="100"/>
+      <c r="R27" s="102"/>
+      <c r="S27" s="103"/>
+      <c r="T27" s="104"/>
+      <c r="U27" s="102"/>
+      <c r="V27" s="103"/>
+      <c r="W27" s="104"/>
+      <c r="X27" s="102"/>
+      <c r="Y27" s="103"/>
+      <c r="Z27" s="104"/>
+      <c r="AA27" s="102"/>
+      <c r="AB27" s="103"/>
+      <c r="AC27" s="104"/>
+      <c r="AD27" s="102"/>
+      <c r="AE27" s="103"/>
+      <c r="AF27" s="104"/>
+      <c r="AG27" s="102"/>
+      <c r="AH27" s="103"/>
+      <c r="AI27" s="104"/>
+      <c r="AJ27" s="102"/>
+      <c r="AK27" s="103"/>
+      <c r="AL27" s="104"/>
+      <c r="AM27" s="102"/>
+      <c r="AN27" s="103"/>
+      <c r="AO27" s="104"/>
+      <c r="AP27" s="102"/>
+      <c r="AQ27" s="103"/>
+      <c r="AR27" s="104"/>
+      <c r="AS27" s="102"/>
+      <c r="AT27" s="103"/>
+      <c r="AU27" s="104"/>
+      <c r="AV27" s="100"/>
+    </row>
+    <row r="28" spans="1:48" ht="19.899999999999999" customHeight="1">
+      <c r="A28" s="114" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" s="112">
+        <v>8</v>
+      </c>
+      <c r="C28" s="83">
+        <f t="shared" ref="C28" si="121">SUMPRODUCT(ROUNDUP(D28/B28,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="83">
+        <f>'มหาชัย-ผลิต'!E44</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="83"/>
+      <c r="F28" s="133"/>
+      <c r="G28" s="133"/>
+      <c r="H28" s="133"/>
+      <c r="I28" s="133"/>
+      <c r="J28" s="133"/>
+      <c r="K28" s="133"/>
+      <c r="L28" s="133"/>
+      <c r="M28" s="133"/>
+      <c r="N28" s="133"/>
+      <c r="O28" s="133"/>
+      <c r="P28" s="133"/>
+      <c r="Q28" s="133"/>
+      <c r="R28" s="102"/>
+      <c r="S28" s="103"/>
+      <c r="T28" s="104"/>
+      <c r="U28" s="102"/>
+      <c r="V28" s="103"/>
+      <c r="W28" s="104"/>
+      <c r="X28" s="102"/>
+      <c r="Y28" s="103"/>
+      <c r="Z28" s="104"/>
+      <c r="AA28" s="102"/>
+      <c r="AB28" s="103"/>
+      <c r="AC28" s="104"/>
+      <c r="AD28" s="102"/>
+      <c r="AE28" s="103"/>
+      <c r="AF28" s="104"/>
+      <c r="AG28" s="102"/>
+      <c r="AH28" s="103"/>
+      <c r="AI28" s="104"/>
+      <c r="AJ28" s="102"/>
+      <c r="AK28" s="103"/>
+      <c r="AL28" s="104"/>
+      <c r="AM28" s="102"/>
+      <c r="AN28" s="103"/>
+      <c r="AO28" s="104"/>
+      <c r="AP28" s="102"/>
+      <c r="AQ28" s="103"/>
+      <c r="AR28" s="104"/>
+      <c r="AS28" s="102"/>
+      <c r="AT28" s="103"/>
+      <c r="AU28" s="104"/>
+      <c r="AV28" s="133"/>
+    </row>
+    <row r="29" spans="1:48" s="23" customFormat="1" ht="25.15" customHeight="1">
+      <c r="A29" s="201" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="195"/>
-      <c r="C28" s="99">
-        <f>SUM(C10:C27)</f>
-        <v>0</v>
-      </c>
-      <c r="D28" s="61">
-        <f>SUM(D29:D31)*-1</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="21"/>
-      <c r="O28" s="22"/>
-      <c r="P28" s="22"/>
-      <c r="Q28" s="22"/>
-      <c r="R28" s="22"/>
-      <c r="S28" s="22"/>
-      <c r="T28" s="22"/>
-      <c r="U28" s="22"/>
-      <c r="V28" s="22"/>
-      <c r="W28" s="22"/>
-      <c r="X28" s="22"/>
-      <c r="Y28" s="22"/>
-      <c r="Z28" s="22"/>
-      <c r="AA28" s="22"/>
-      <c r="AB28" s="22"/>
-      <c r="AC28" s="22"/>
-      <c r="AD28" s="22"/>
-      <c r="AE28" s="22"/>
-      <c r="AF28" s="22"/>
-      <c r="AG28" s="22"/>
-      <c r="AH28" s="22"/>
-      <c r="AI28" s="22"/>
-      <c r="AJ28" s="22"/>
-      <c r="AK28" s="22"/>
-      <c r="AL28" s="22"/>
-      <c r="AM28" s="22"/>
-      <c r="AN28" s="22"/>
-      <c r="AO28" s="22"/>
-      <c r="AP28" s="22"/>
-      <c r="AQ28" s="22"/>
-      <c r="AR28" s="22"/>
-      <c r="AS28" s="22"/>
-      <c r="AT28" s="22"/>
-      <c r="AU28" s="22"/>
-      <c r="AV28" s="22"/>
-    </row>
-    <row r="29" spans="1:48" ht="21" customHeight="1">
-      <c r="A29" s="196" t="s">
+      <c r="B29" s="202"/>
+      <c r="C29" s="99">
+        <f>SUM(C10:C28)</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="61">
+        <f>SUM(D30:D32)*-1</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="21"/>
+      <c r="M29" s="21"/>
+      <c r="N29" s="21"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22"/>
+      <c r="R29" s="22"/>
+      <c r="S29" s="22"/>
+      <c r="T29" s="22"/>
+      <c r="U29" s="22"/>
+      <c r="V29" s="22"/>
+      <c r="W29" s="22"/>
+      <c r="X29" s="22"/>
+      <c r="Y29" s="22"/>
+      <c r="Z29" s="22"/>
+      <c r="AA29" s="22"/>
+      <c r="AB29" s="22"/>
+      <c r="AC29" s="22"/>
+      <c r="AD29" s="22"/>
+      <c r="AE29" s="22"/>
+      <c r="AF29" s="22"/>
+      <c r="AG29" s="22"/>
+      <c r="AH29" s="22"/>
+      <c r="AI29" s="22"/>
+      <c r="AJ29" s="22"/>
+      <c r="AK29" s="22"/>
+      <c r="AL29" s="22"/>
+      <c r="AM29" s="22"/>
+      <c r="AN29" s="22"/>
+      <c r="AO29" s="22"/>
+      <c r="AP29" s="22"/>
+      <c r="AQ29" s="22"/>
+      <c r="AR29" s="22"/>
+      <c r="AS29" s="22"/>
+      <c r="AT29" s="22"/>
+      <c r="AU29" s="22"/>
+      <c r="AV29" s="22"/>
+    </row>
+    <row r="30" spans="1:48" ht="21" customHeight="1">
+      <c r="A30" s="203" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="196"/>
-      <c r="C29" s="196"/>
-      <c r="D29" s="100">
-        <f>SUM(R10:R22)</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="100"/>
-      <c r="F29" s="100"/>
-      <c r="G29" s="100"/>
-      <c r="H29" s="100"/>
-      <c r="I29" s="100"/>
-      <c r="J29" s="100"/>
-      <c r="K29" s="100"/>
-      <c r="L29" s="100"/>
-      <c r="M29" s="100"/>
-      <c r="N29" s="100"/>
-      <c r="O29" s="100"/>
-      <c r="P29" s="100"/>
-      <c r="Q29" s="100"/>
-    </row>
-    <row r="30" spans="1:48" ht="21" customHeight="1">
-      <c r="A30" s="191" t="s">
+      <c r="B30" s="203"/>
+      <c r="C30" s="203"/>
+      <c r="D30" s="101">
+        <f>SUM(R10:R23)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="101"/>
+      <c r="F30" s="101"/>
+      <c r="G30" s="101"/>
+      <c r="H30" s="101"/>
+      <c r="I30" s="101"/>
+      <c r="J30" s="101"/>
+      <c r="K30" s="101"/>
+      <c r="L30" s="101"/>
+      <c r="M30" s="101"/>
+      <c r="N30" s="101"/>
+      <c r="O30" s="101"/>
+      <c r="P30" s="101"/>
+      <c r="Q30" s="101"/>
+    </row>
+    <row r="31" spans="1:48" ht="21" customHeight="1">
+      <c r="A31" s="198" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="191"/>
-      <c r="C30" s="191"/>
-      <c r="D30" s="11">
-        <f>SUM(S10:S22)</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="11"/>
-      <c r="O30" s="11"/>
-      <c r="P30" s="11"/>
-      <c r="Q30" s="11"/>
-    </row>
-    <row r="31" spans="1:48" ht="21" customHeight="1">
-      <c r="A31" s="191" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="191"/>
-      <c r="C31" s="191"/>
+      <c r="B31" s="198"/>
+      <c r="C31" s="198"/>
       <c r="D31" s="11">
-        <f>SUM(T10:T22)</f>
+        <f>SUM(S10:S23)</f>
         <v>0</v>
       </c>
       <c r="E31" s="11"/>
@@ -6754,44 +6944,52 @@
       <c r="P31" s="11"/>
       <c r="Q31" s="11"/>
     </row>
-    <row r="32" spans="1:48" ht="15" customHeight="1">
-      <c r="A32" s="62"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
+    <row r="32" spans="1:48" ht="21" customHeight="1">
+      <c r="A32" s="198" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="198"/>
+      <c r="C32" s="198"/>
+      <c r="D32" s="11">
+        <f>SUM(T10:T23)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="11"/>
+      <c r="P32" s="11"/>
+      <c r="Q32" s="11"/>
     </row>
     <row r="33" spans="1:17" ht="15" customHeight="1">
       <c r="A33" s="62"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
     </row>
-    <row r="34" spans="1:17" ht="18" customHeight="1">
-      <c r="A34" s="190" t="s">
+    <row r="34" spans="1:17" ht="15" customHeight="1">
+      <c r="A34" s="62"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+    </row>
+    <row r="35" spans="1:17" ht="18" customHeight="1">
+      <c r="A35" s="197" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B35" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C34" s="10">
+      <c r="C35" s="10">
         <v>134</v>
       </c>
-      <c r="D34" s="11">
-        <f>IF(C34=0, 0, ((SUM(D29:M29)+SUM(D30:M30))/C34)*100)</f>
-        <v>0</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="18" customHeight="1">
-      <c r="A35" s="190"/>
-      <c r="B35" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C35" s="10">
-        <v>242</v>
-      </c>
       <c r="D35" s="11">
-        <f>IF(C35=0, 0, ((SUM(D31:M31))/C35)*100)</f>
+        <f>IF(C35=0, 0, ((SUM(D30:M30)+SUM(D31:M31))/C35)*100)</f>
         <v>0</v>
       </c>
       <c r="E35" s="11" t="s">
@@ -6799,13 +6997,15 @@
       </c>
     </row>
     <row r="36" spans="1:17" ht="18" customHeight="1">
-      <c r="A36" s="190"/>
-      <c r="B36" s="191" t="s">
-        <v>48</v>
-      </c>
-      <c r="C36" s="191"/>
+      <c r="A36" s="197"/>
+      <c r="B36" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" s="10">
+        <v>242</v>
+      </c>
       <c r="D36" s="11">
-        <f>D34+D35</f>
+        <f>IF(C36=0, 0, ((SUM(D32:M32))/C36)*100)</f>
         <v>0</v>
       </c>
       <c r="E36" s="11" t="s">
@@ -6813,60 +7013,58 @@
       </c>
     </row>
     <row r="37" spans="1:17" ht="18" customHeight="1">
-      <c r="A37" s="190"/>
-      <c r="B37" s="191" t="s">
-        <v>47</v>
-      </c>
-      <c r="C37" s="191"/>
+      <c r="A37" s="197"/>
+      <c r="B37" s="198" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" s="198"/>
       <c r="D37" s="11">
-        <v>100</v>
+        <f>D35+D36</f>
+        <v>0</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="18" customHeight="1">
-      <c r="A38" s="190"/>
-      <c r="B38" s="191" t="s">
+      <c r="A38" s="197"/>
+      <c r="B38" s="198" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" s="198"/>
+      <c r="D38" s="11">
+        <v>100</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" ht="18" customHeight="1">
+      <c r="A39" s="197"/>
+      <c r="B39" s="198" t="s">
         <v>19</v>
       </c>
-      <c r="C38" s="191"/>
-      <c r="D38" s="11">
-        <f>CEILING(D36 /D37, 1)</f>
-        <v>0</v>
-      </c>
-      <c r="E38" s="13" t="s">
+      <c r="C39" s="198"/>
+      <c r="D39" s="11">
+        <f>CEILING(D37 /D38, 1)</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="13" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="18" customHeight="1">
-      <c r="A39" s="190" t="s">
+    <row r="40" spans="1:17" ht="18" customHeight="1">
+      <c r="A40" s="197" t="s">
         <v>45</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B40" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C39" s="10">
+      <c r="C40" s="10">
         <v>154</v>
       </c>
-      <c r="D39" s="11">
-        <f>IF(C39=0, 0, ((SUM(D29:M29)+SUM(D30:M30))/C39)*100)</f>
-        <v>0</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" ht="18" customHeight="1">
-      <c r="A40" s="190"/>
-      <c r="B40" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C40" s="10">
-        <v>278</v>
-      </c>
       <c r="D40" s="11">
-        <f>IF(C40=0, 0, ((SUM(D31:M31))/C40)*100)</f>
+        <f>IF(C40=0, 0, ((SUM(D30:M30)+SUM(D31:M31))/C40)*100)</f>
         <v>0</v>
       </c>
       <c r="E40" s="11" t="s">
@@ -6874,13 +7072,15 @@
       </c>
     </row>
     <row r="41" spans="1:17" ht="18" customHeight="1">
-      <c r="A41" s="190"/>
-      <c r="B41" s="191" t="s">
-        <v>48</v>
-      </c>
-      <c r="C41" s="191"/>
+      <c r="A41" s="197"/>
+      <c r="B41" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" s="10">
+        <v>278</v>
+      </c>
       <c r="D41" s="11">
-        <f>D39+D40</f>
+        <f>IF(C41=0, 0, ((SUM(D32:M32))/C41)*100)</f>
         <v>0</v>
       </c>
       <c r="E41" s="11" t="s">
@@ -6888,151 +7088,165 @@
       </c>
     </row>
     <row r="42" spans="1:17" ht="18" customHeight="1">
-      <c r="A42" s="190"/>
-      <c r="B42" s="191" t="s">
-        <v>47</v>
-      </c>
-      <c r="C42" s="191"/>
+      <c r="A42" s="197"/>
+      <c r="B42" s="198" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" s="198"/>
       <c r="D42" s="11">
-        <v>100</v>
+        <f>D40+D41</f>
+        <v>0</v>
       </c>
       <c r="E42" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="25.2" customHeight="1">
-      <c r="A43" s="190"/>
-      <c r="B43" s="191" t="s">
+    <row r="43" spans="1:17" ht="18" customHeight="1">
+      <c r="A43" s="197"/>
+      <c r="B43" s="198" t="s">
+        <v>47</v>
+      </c>
+      <c r="C43" s="198"/>
+      <c r="D43" s="11">
+        <v>100</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" ht="25.15" customHeight="1">
+      <c r="A44" s="197"/>
+      <c r="B44" s="198" t="s">
         <v>19</v>
       </c>
-      <c r="C43" s="191"/>
-      <c r="D43" s="11">
-        <f>CEILING(D41 /D42, 1)</f>
-        <v>0</v>
-      </c>
-      <c r="E43" s="13" t="s">
+      <c r="C44" s="198"/>
+      <c r="D44" s="11">
+        <f>CEILING(D42 /D43, 1)</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="13" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="25.2" customHeight="1">
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="E44" s="9"/>
-    </row>
-    <row r="45" spans="1:17" ht="4.95" customHeight="1">
+    <row r="45" spans="1:17" ht="25.15" customHeight="1">
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
       <c r="E45" s="9"/>
     </row>
-    <row r="46" spans="1:17" ht="21" customHeight="1">
-      <c r="A46" s="192" t="s">
+    <row r="46" spans="1:17" ht="4.9000000000000004" customHeight="1">
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="E46" s="9"/>
+    </row>
+    <row r="47" spans="1:17" ht="21" customHeight="1">
+      <c r="A47" s="199" t="s">
         <v>15</v>
       </c>
-      <c r="B46" s="190"/>
-      <c r="C46" s="10" t="s">
+      <c r="B47" s="197"/>
+      <c r="C47" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D46" s="192" t="s">
+      <c r="D47" s="199" t="s">
         <v>53</v>
       </c>
-      <c r="E46" s="192"/>
-      <c r="F46" s="192"/>
-      <c r="G46" s="192" t="s">
+      <c r="E47" s="199"/>
+      <c r="F47" s="199"/>
+      <c r="G47" s="199" t="s">
         <v>54</v>
       </c>
-      <c r="H46" s="192"/>
-      <c r="I46" s="192"/>
-      <c r="J46" s="178" t="s">
+      <c r="H47" s="199"/>
+      <c r="I47" s="199"/>
+      <c r="J47" s="185" t="s">
         <v>55</v>
       </c>
-      <c r="K46" s="179"/>
-      <c r="L46" s="179"/>
-      <c r="M46" s="180"/>
-      <c r="N46" s="14"/>
-      <c r="O46" s="181" t="s">
+      <c r="K47" s="186"/>
+      <c r="L47" s="186"/>
+      <c r="M47" s="187"/>
+      <c r="N47" s="14"/>
+      <c r="O47" s="188" t="s">
         <v>60</v>
       </c>
-      <c r="P46" s="182"/>
-    </row>
-    <row r="47" spans="1:17" ht="21" customHeight="1">
-      <c r="A47" s="185" t="s">
+      <c r="P47" s="189"/>
+    </row>
+    <row r="48" spans="1:17" ht="21" customHeight="1">
+      <c r="A48" s="192" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="186"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="178"/>
-      <c r="E47" s="179"/>
-      <c r="F47" s="180"/>
-      <c r="G47" s="178"/>
-      <c r="H47" s="179"/>
-      <c r="I47" s="180"/>
-      <c r="J47" s="187"/>
-      <c r="K47" s="188"/>
-      <c r="L47" s="188"/>
-      <c r="M47" s="189"/>
-      <c r="N47" s="15"/>
-      <c r="O47" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="P47" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q47" s="5"/>
-    </row>
-    <row r="48" spans="1:17" ht="21" customHeight="1">
-      <c r="A48" s="185" t="s">
-        <v>51</v>
-      </c>
-      <c r="B48" s="186"/>
+      <c r="B48" s="193"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="178"/>
-      <c r="E48" s="179"/>
-      <c r="F48" s="180"/>
-      <c r="G48" s="178"/>
-      <c r="H48" s="179"/>
-      <c r="I48" s="180"/>
-      <c r="J48" s="187"/>
-      <c r="K48" s="188"/>
-      <c r="L48" s="188"/>
-      <c r="M48" s="189"/>
+      <c r="D48" s="185"/>
+      <c r="E48" s="186"/>
+      <c r="F48" s="187"/>
+      <c r="G48" s="185"/>
+      <c r="H48" s="186"/>
+      <c r="I48" s="187"/>
+      <c r="J48" s="194"/>
+      <c r="K48" s="195"/>
+      <c r="L48" s="195"/>
+      <c r="M48" s="196"/>
       <c r="N48" s="15"/>
       <c r="O48" s="19" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="P48" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="Q48" s="16"/>
+      <c r="Q48" s="5"/>
     </row>
     <row r="49" spans="1:17" ht="21" customHeight="1">
-      <c r="A49" s="185" t="s">
+      <c r="A49" s="192" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49" s="193"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="185"/>
+      <c r="E49" s="186"/>
+      <c r="F49" s="187"/>
+      <c r="G49" s="185"/>
+      <c r="H49" s="186"/>
+      <c r="I49" s="187"/>
+      <c r="J49" s="194"/>
+      <c r="K49" s="195"/>
+      <c r="L49" s="195"/>
+      <c r="M49" s="196"/>
+      <c r="N49" s="15"/>
+      <c r="O49" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="P49" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q49" s="16"/>
+    </row>
+    <row r="50" spans="1:17" ht="21" customHeight="1">
+      <c r="A50" s="192" t="s">
         <v>52</v>
       </c>
-      <c r="B49" s="185"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="178"/>
-      <c r="E49" s="179"/>
-      <c r="F49" s="180"/>
-      <c r="G49" s="178"/>
-      <c r="H49" s="179"/>
-      <c r="I49" s="180"/>
-      <c r="J49" s="187"/>
-      <c r="K49" s="188"/>
-      <c r="L49" s="188"/>
-      <c r="M49" s="189"/>
-      <c r="N49" s="15"/>
-      <c r="O49" s="17" t="s">
+      <c r="B50" s="192"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="185"/>
+      <c r="E50" s="186"/>
+      <c r="F50" s="187"/>
+      <c r="G50" s="185"/>
+      <c r="H50" s="186"/>
+      <c r="I50" s="187"/>
+      <c r="J50" s="194"/>
+      <c r="K50" s="195"/>
+      <c r="L50" s="195"/>
+      <c r="M50" s="196"/>
+      <c r="N50" s="15"/>
+      <c r="O50" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="P49" s="18" t="s">
+      <c r="P50" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="Q49" s="16"/>
-    </row>
-    <row r="50" spans="1:17" ht="15" customHeight="1">
-      <c r="O50" s="16"/>
-      <c r="P50" s="16"/>
       <c r="Q50" s="16"/>
+    </row>
+    <row r="51" spans="1:17" ht="15" customHeight="1">
+      <c r="O51" s="16"/>
+      <c r="P51" s="16"/>
+      <c r="Q51" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="59">
@@ -7043,7 +7257,7 @@
     <mergeCell ref="C6:Q6"/>
     <mergeCell ref="L8:L9"/>
     <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="E8:E9"/>
@@ -7053,7 +7267,7 @@
     <mergeCell ref="AM8:AO8"/>
     <mergeCell ref="AP8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
-    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
     <mergeCell ref="R8:T8"/>
     <mergeCell ref="U8:W8"/>
     <mergeCell ref="X8:Z8"/>
@@ -7065,36 +7279,36 @@
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="K8:K9"/>
-    <mergeCell ref="A30:C30"/>
     <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A34:A38"/>
-    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A35:A39"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B38:C38"/>
-    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="B39:C39"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A49:B49"/>
-    <mergeCell ref="J49:M49"/>
-    <mergeCell ref="A39:A43"/>
-    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="J50:M50"/>
+    <mergeCell ref="A40:A44"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B43:C43"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="J47:M47"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="D47:F47"/>
     <mergeCell ref="J48:M48"/>
-    <mergeCell ref="G46:I46"/>
-    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="J49:M49"/>
+    <mergeCell ref="G47:I47"/>
     <mergeCell ref="D48:F48"/>
     <mergeCell ref="D49:F49"/>
-    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="D50:F50"/>
     <mergeCell ref="G48:I48"/>
     <mergeCell ref="G49:I49"/>
-    <mergeCell ref="O46:P46"/>
+    <mergeCell ref="G50:I50"/>
+    <mergeCell ref="O47:P47"/>
     <mergeCell ref="O8:O9"/>
     <mergeCell ref="P8:P9"/>
     <mergeCell ref="M8:M9"/>
-    <mergeCell ref="J46:M46"/>
+    <mergeCell ref="J47:M47"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7105,29 +7319,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:I25"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="51.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" customWidth="1"/>
+    <col min="2" max="2" width="51.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.125" customWidth="1"/>
+    <col min="6" max="6" width="11.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:9" s="3" customFormat="1" ht="15" customHeight="1"/>
     <row r="3" spans="1:9" s="3" customFormat="1" ht="30.75" customHeight="1">
       <c r="D3" s="43"/>
       <c r="E3" s="43"/>
-      <c r="G3" s="208"/>
-      <c r="H3" s="208"/>
-      <c r="I3" s="208"/>
+      <c r="G3" s="215"/>
+      <c r="H3" s="215"/>
+      <c r="I3" s="215"/>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
       <c r="D4" s="42"/>
       <c r="E4" s="42"/>
       <c r="F4" s="41"/>
-      <c r="G4" s="208"/>
-      <c r="H4" s="208"/>
-      <c r="I4" s="208"/>
+      <c r="G4" s="215"/>
+      <c r="H4" s="215"/>
+      <c r="I4" s="215"/>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" ht="56.25" customHeight="1" thickBot="1">
       <c r="A5" s="51" t="s">
@@ -7136,52 +7350,52 @@
       <c r="B5" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="209" t="s">
+      <c r="C5" s="216" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="210"/>
-      <c r="E5" s="210"/>
-      <c r="F5" s="211"/>
+      <c r="D5" s="217"/>
+      <c r="E5" s="217"/>
+      <c r="F5" s="218"/>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A6" s="212" t="s">
+      <c r="A6" s="219" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="213"/>
-      <c r="C6" s="218" t="s">
+      <c r="B6" s="220"/>
+      <c r="C6" s="225" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="221" t="s">
+      <c r="D6" s="228" t="s">
         <v>94</v>
       </c>
-      <c r="E6" s="223" t="s">
+      <c r="E6" s="230" t="s">
         <v>72</v>
       </c>
-      <c r="F6" s="224"/>
+      <c r="F6" s="231"/>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" ht="30.6" customHeight="1" thickBot="1">
-      <c r="A7" s="214"/>
-      <c r="B7" s="215"/>
-      <c r="C7" s="219"/>
-      <c r="D7" s="222"/>
-      <c r="E7" s="225"/>
-      <c r="F7" s="226"/>
+      <c r="A7" s="221"/>
+      <c r="B7" s="222"/>
+      <c r="C7" s="226"/>
+      <c r="D7" s="229"/>
+      <c r="E7" s="232"/>
+      <c r="F7" s="233"/>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A8" s="214"/>
-      <c r="B8" s="215"/>
-      <c r="C8" s="219"/>
-      <c r="D8" s="228" t="s">
+      <c r="A8" s="221"/>
+      <c r="B8" s="222"/>
+      <c r="C8" s="226"/>
+      <c r="D8" s="235" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="227"/>
-      <c r="F8" s="226"/>
-    </row>
-    <row r="9" spans="1:9" s="3" customFormat="1" ht="17.399999999999999" customHeight="1" thickBot="1">
-      <c r="A9" s="216"/>
-      <c r="B9" s="217"/>
-      <c r="C9" s="220"/>
-      <c r="D9" s="229"/>
+      <c r="E8" s="234"/>
+      <c r="F8" s="233"/>
+    </row>
+    <row r="9" spans="1:9" s="3" customFormat="1" ht="17.45" customHeight="1" thickBot="1">
+      <c r="A9" s="223"/>
+      <c r="B9" s="224"/>
+      <c r="C9" s="227"/>
+      <c r="D9" s="236"/>
       <c r="E9" s="33" t="s">
         <v>75</v>
       </c>
@@ -7189,43 +7403,43 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A10" s="235">
+    <row r="10" spans="1:9" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A10" s="242">
         <v>1</v>
       </c>
-      <c r="B10" s="237" t="s">
+      <c r="B10" s="244" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="239">
+      <c r="C10" s="246">
         <v>15</v>
       </c>
       <c r="D10" s="60">
         <v>1888</v>
       </c>
-      <c r="E10" s="204">
+      <c r="E10" s="211">
         <f>SUM(D10:D10)</f>
         <v>1888</v>
       </c>
-      <c r="F10" s="206">
+      <c r="F10" s="213">
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A11" s="236"/>
-      <c r="B11" s="238"/>
-      <c r="C11" s="240"/>
+    <row r="11" spans="1:9" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A11" s="243"/>
+      <c r="B11" s="245"/>
+      <c r="C11" s="247"/>
       <c r="D11" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="E11" s="205"/>
-      <c r="F11" s="207"/>
+      <c r="E11" s="212"/>
+      <c r="F11" s="214"/>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" ht="39" customHeight="1" thickBot="1">
-      <c r="A12" s="230" t="s">
+      <c r="A12" s="237" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="231"/>
-      <c r="C12" s="232"/>
+      <c r="B12" s="238"/>
+      <c r="C12" s="239"/>
       <c r="D12" s="44">
         <v>126</v>
       </c>
@@ -7239,7 +7453,7 @@
       <c r="G12" s="25"/>
       <c r="H12" s="25"/>
     </row>
-    <row r="13" spans="1:9" s="3" customFormat="1" ht="17.399999999999999" customHeight="1" thickBot="1">
+    <row r="13" spans="1:9" s="3" customFormat="1" ht="17.45" customHeight="1" thickBot="1">
       <c r="A13" s="24"/>
       <c r="B13" s="24"/>
       <c r="C13" s="24"/>
@@ -7250,10 +7464,10 @@
       <c r="H13" s="25"/>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A14" s="233" t="s">
+      <c r="A14" s="240" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="234"/>
+      <c r="B14" s="241"/>
       <c r="C14" s="50" t="s">
         <v>53</v>
       </c>
@@ -7265,7 +7479,7 @@
       </c>
       <c r="F14" s="26"/>
     </row>
-    <row r="15" spans="1:9" s="3" customFormat="1" ht="28.2" customHeight="1" thickBot="1">
+    <row r="15" spans="1:9" s="3" customFormat="1" ht="28.15" customHeight="1" thickBot="1">
       <c r="A15" s="36" t="s">
         <v>78</v>
       </c>
@@ -7275,7 +7489,7 @@
       <c r="E15" s="37"/>
       <c r="F15" s="26"/>
     </row>
-    <row r="16" spans="1:9" s="3" customFormat="1" ht="28.2" customHeight="1" thickBot="1">
+    <row r="16" spans="1:9" s="3" customFormat="1" ht="28.15" customHeight="1" thickBot="1">
       <c r="A16" s="36" t="s">
         <v>80</v>
       </c>
@@ -7285,7 +7499,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="26"/>
     </row>
-    <row r="17" spans="1:6" s="3" customFormat="1" ht="28.2" customHeight="1" thickBot="1">
+    <row r="17" spans="1:6" s="3" customFormat="1" ht="28.15" customHeight="1" thickBot="1">
       <c r="A17" s="53" t="s">
         <v>82</v>
       </c>
@@ -7318,14 +7532,14 @@
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+    <row r="20" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
       <c r="D20" s="40"/>
       <c r="E20" s="28" t="s">
         <v>79</v>
       </c>
       <c r="F20" s="28"/>
     </row>
-    <row r="21" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+    <row r="21" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
       <c r="D21" s="26"/>
       <c r="E21" s="29" t="s">
         <v>81</v>
@@ -7334,12 +7548,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+    <row r="22" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
       <c r="D22" s="26"/>
       <c r="E22" s="29"/>
       <c r="F22" s="29"/>
     </row>
-    <row r="23" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
+    <row r="23" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
       <c r="D23" s="39"/>
       <c r="E23" s="28"/>
       <c r="F23" s="28"/>
@@ -7382,29 +7596,29 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A2:I49"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="51.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" customWidth="1"/>
+    <col min="6" max="6" width="13.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:9" s="3" customFormat="1" ht="15" customHeight="1"/>
     <row r="3" spans="1:9" s="3" customFormat="1" ht="30.75" customHeight="1">
       <c r="D3" s="43"/>
       <c r="E3" s="43"/>
-      <c r="G3" s="208"/>
-      <c r="H3" s="208"/>
-      <c r="I3" s="208"/>
+      <c r="G3" s="215"/>
+      <c r="H3" s="215"/>
+      <c r="I3" s="215"/>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
       <c r="D4" s="42"/>
       <c r="E4" s="42"/>
       <c r="F4" s="41"/>
-      <c r="G4" s="208"/>
-      <c r="H4" s="208"/>
-      <c r="I4" s="208"/>
+      <c r="G4" s="215"/>
+      <c r="H4" s="215"/>
+      <c r="I4" s="215"/>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" ht="56.25" customHeight="1" thickBot="1">
       <c r="A5" s="51" t="s">
@@ -7413,52 +7627,52 @@
       <c r="B5" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="209" t="s">
+      <c r="C5" s="216" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="210"/>
-      <c r="E5" s="210"/>
-      <c r="F5" s="211"/>
+      <c r="D5" s="217"/>
+      <c r="E5" s="217"/>
+      <c r="F5" s="218"/>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A6" s="212" t="s">
+      <c r="A6" s="219" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="213"/>
-      <c r="C6" s="218" t="s">
+      <c r="B6" s="220"/>
+      <c r="C6" s="225" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="221" t="s">
+      <c r="D6" s="228" t="s">
         <v>94</v>
       </c>
-      <c r="E6" s="223" t="s">
+      <c r="E6" s="230" t="s">
         <v>72</v>
       </c>
-      <c r="F6" s="224"/>
+      <c r="F6" s="231"/>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" ht="30.6" customHeight="1" thickBot="1">
-      <c r="A7" s="214"/>
-      <c r="B7" s="215"/>
-      <c r="C7" s="219"/>
-      <c r="D7" s="222"/>
-      <c r="E7" s="225"/>
-      <c r="F7" s="226"/>
+      <c r="A7" s="221"/>
+      <c r="B7" s="222"/>
+      <c r="C7" s="226"/>
+      <c r="D7" s="229"/>
+      <c r="E7" s="232"/>
+      <c r="F7" s="233"/>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A8" s="214"/>
-      <c r="B8" s="215"/>
-      <c r="C8" s="219"/>
-      <c r="D8" s="228" t="s">
+      <c r="A8" s="221"/>
+      <c r="B8" s="222"/>
+      <c r="C8" s="226"/>
+      <c r="D8" s="235" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="227"/>
-      <c r="F8" s="226"/>
-    </row>
-    <row r="9" spans="1:9" s="3" customFormat="1" ht="17.399999999999999" customHeight="1" thickBot="1">
-      <c r="A9" s="216"/>
-      <c r="B9" s="217"/>
-      <c r="C9" s="220"/>
-      <c r="D9" s="229"/>
+      <c r="E8" s="234"/>
+      <c r="F8" s="233"/>
+    </row>
+    <row r="9" spans="1:9" s="3" customFormat="1" ht="17.45" customHeight="1" thickBot="1">
+      <c r="A9" s="223"/>
+      <c r="B9" s="224"/>
+      <c r="C9" s="227"/>
+      <c r="D9" s="236"/>
       <c r="E9" s="33" t="s">
         <v>75</v>
       </c>
@@ -7466,416 +7680,416 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A10" s="235">
+    <row r="10" spans="1:9" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A10" s="242">
         <v>1</v>
       </c>
-      <c r="B10" s="241" t="s">
+      <c r="B10" s="248" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="235">
+      <c r="C10" s="242">
         <v>32</v>
       </c>
       <c r="D10" s="54">
         <v>566</v>
       </c>
-      <c r="E10" s="204">
+      <c r="E10" s="211">
         <f>SUM(D10:D10)</f>
         <v>566</v>
       </c>
-      <c r="F10" s="206">
+      <c r="F10" s="213">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A11" s="236"/>
-      <c r="B11" s="242"/>
-      <c r="C11" s="236"/>
+    <row r="11" spans="1:9" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A11" s="243"/>
+      <c r="B11" s="249"/>
+      <c r="C11" s="243"/>
       <c r="D11" s="55" t="s">
         <v>97</v>
       </c>
-      <c r="E11" s="205"/>
-      <c r="F11" s="207"/>
-    </row>
-    <row r="12" spans="1:9" s="3" customFormat="1" ht="29.4" hidden="1" customHeight="1">
-      <c r="A12" s="235">
+      <c r="E11" s="212"/>
+      <c r="F11" s="214"/>
+    </row>
+    <row r="12" spans="1:9" s="3" customFormat="1" ht="29.45" hidden="1" customHeight="1">
+      <c r="A12" s="242">
         <v>2</v>
       </c>
-      <c r="B12" s="237" t="s">
+      <c r="B12" s="244" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="239">
+      <c r="C12" s="246">
         <v>14</v>
       </c>
       <c r="D12" s="54"/>
-      <c r="E12" s="243">
+      <c r="E12" s="250">
         <f>SUM(D12:D12)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="206">
+      <c r="F12" s="213">
         <f>มหาชัย!C11</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="3" customFormat="1" ht="29.4" hidden="1" customHeight="1">
-      <c r="A13" s="236"/>
-      <c r="B13" s="238"/>
-      <c r="C13" s="246"/>
+    <row r="13" spans="1:9" s="3" customFormat="1" ht="29.45" hidden="1" customHeight="1">
+      <c r="A13" s="243"/>
+      <c r="B13" s="245"/>
+      <c r="C13" s="253"/>
       <c r="D13" s="56" t="str">
         <f>IF(D12=0, "", IF(MOD(D12, $C$11) = 0, D12 / $C$11, IF(INT(D12 / $C$11) = 0, MOD(D12, $C$11) &amp; " P", INT(D12 / $C$11) &amp; " + " &amp; MOD(D12, $C$11) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="E13" s="244"/>
-      <c r="F13" s="207"/>
-    </row>
-    <row r="14" spans="1:9" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A14" s="235">
+      <c r="E13" s="251"/>
+      <c r="F13" s="214"/>
+    </row>
+    <row r="14" spans="1:9" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A14" s="242">
         <v>2</v>
       </c>
-      <c r="B14" s="241" t="s">
+      <c r="B14" s="248" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="235">
+      <c r="C14" s="242">
         <v>32</v>
       </c>
       <c r="D14" s="54">
         <v>275</v>
       </c>
-      <c r="E14" s="243">
+      <c r="E14" s="250">
         <f>SUM(D14:D14)</f>
         <v>275</v>
       </c>
-      <c r="F14" s="206" t="e">
+      <c r="F14" s="213" t="e">
         <f>มหาชัย!#REF!</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A15" s="236"/>
-      <c r="B15" s="242"/>
-      <c r="C15" s="236"/>
+    <row r="15" spans="1:9" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A15" s="243"/>
+      <c r="B15" s="249"/>
+      <c r="C15" s="243"/>
       <c r="D15" s="56" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="244"/>
-      <c r="F15" s="207"/>
-    </row>
-    <row r="16" spans="1:9" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A16" s="235">
+      <c r="E15" s="251"/>
+      <c r="F15" s="214"/>
+    </row>
+    <row r="16" spans="1:9" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A16" s="242">
         <v>3</v>
       </c>
-      <c r="B16" s="241" t="s">
+      <c r="B16" s="248" t="s">
         <v>86</v>
       </c>
-      <c r="C16" s="245">
+      <c r="C16" s="252">
         <v>27</v>
       </c>
       <c r="D16" s="57">
         <v>228</v>
       </c>
-      <c r="E16" s="243">
+      <c r="E16" s="250">
         <f>SUM(D16:D16)</f>
         <v>228</v>
       </c>
-      <c r="F16" s="206">
+      <c r="F16" s="213">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A17" s="236"/>
-      <c r="B17" s="242"/>
-      <c r="C17" s="240"/>
+    <row r="17" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A17" s="243"/>
+      <c r="B17" s="249"/>
+      <c r="C17" s="247"/>
       <c r="D17" s="56" t="s">
         <v>99</v>
       </c>
-      <c r="E17" s="244"/>
-      <c r="F17" s="207"/>
-    </row>
-    <row r="18" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A18" s="235">
+      <c r="E17" s="251"/>
+      <c r="F17" s="214"/>
+    </row>
+    <row r="18" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A18" s="242">
         <v>4</v>
       </c>
-      <c r="B18" s="237" t="s">
+      <c r="B18" s="244" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="239">
+      <c r="C18" s="246">
         <v>36</v>
       </c>
       <c r="D18" s="54">
         <v>181</v>
       </c>
-      <c r="E18" s="243">
+      <c r="E18" s="250">
         <f>SUM(D18:D18)</f>
         <v>181</v>
       </c>
-      <c r="F18" s="206">
+      <c r="F18" s="213">
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A19" s="236"/>
-      <c r="B19" s="238"/>
-      <c r="C19" s="240"/>
+    <row r="19" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A19" s="243"/>
+      <c r="B19" s="245"/>
+      <c r="C19" s="247"/>
       <c r="D19" s="58" t="s">
         <v>100</v>
       </c>
-      <c r="E19" s="244"/>
-      <c r="F19" s="207"/>
-    </row>
-    <row r="20" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A20" s="235">
+      <c r="E19" s="251"/>
+      <c r="F19" s="214"/>
+    </row>
+    <row r="20" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A20" s="242">
         <v>5</v>
       </c>
-      <c r="B20" s="237" t="s">
+      <c r="B20" s="244" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="239">
+      <c r="C20" s="246">
         <v>15</v>
       </c>
       <c r="D20" s="54">
         <v>272</v>
       </c>
-      <c r="E20" s="243">
+      <c r="E20" s="250">
         <f>SUM(D20:D20)</f>
         <v>272</v>
       </c>
-      <c r="F20" s="206">
+      <c r="F20" s="213">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A21" s="236"/>
-      <c r="B21" s="238"/>
-      <c r="C21" s="240"/>
+    <row r="21" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A21" s="243"/>
+      <c r="B21" s="245"/>
+      <c r="C21" s="247"/>
       <c r="D21" s="58" t="s">
         <v>101</v>
       </c>
-      <c r="E21" s="244"/>
-      <c r="F21" s="207"/>
-    </row>
-    <row r="22" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A22" s="235">
+      <c r="E21" s="251"/>
+      <c r="F21" s="214"/>
+    </row>
+    <row r="22" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A22" s="242">
         <v>6</v>
       </c>
-      <c r="B22" s="237" t="s">
+      <c r="B22" s="244" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="239">
+      <c r="C22" s="246">
         <v>45</v>
       </c>
       <c r="D22" s="54">
         <v>24</v>
       </c>
-      <c r="E22" s="243">
+      <c r="E22" s="250">
         <f>SUM(D22:D22)</f>
         <v>24</v>
       </c>
-      <c r="F22" s="206">
+      <c r="F22" s="213">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A23" s="236"/>
-      <c r="B23" s="238"/>
-      <c r="C23" s="240"/>
+    <row r="23" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A23" s="243"/>
+      <c r="B23" s="245"/>
+      <c r="C23" s="247"/>
       <c r="D23" s="59" t="s">
         <v>102</v>
       </c>
-      <c r="E23" s="205"/>
-      <c r="F23" s="207"/>
-    </row>
-    <row r="24" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A24" s="235">
+      <c r="E23" s="212"/>
+      <c r="F23" s="214"/>
+    </row>
+    <row r="24" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A24" s="242">
         <v>7</v>
       </c>
-      <c r="B24" s="237" t="s">
+      <c r="B24" s="244" t="s">
         <v>93</v>
       </c>
-      <c r="C24" s="239">
+      <c r="C24" s="246">
         <v>27</v>
       </c>
       <c r="D24" s="60">
         <v>390</v>
       </c>
-      <c r="E24" s="204">
+      <c r="E24" s="211">
         <f>SUM(D24:D24)</f>
         <v>390</v>
       </c>
-      <c r="F24" s="206">
+      <c r="F24" s="213">
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A25" s="236"/>
-      <c r="B25" s="238"/>
-      <c r="C25" s="240"/>
+    <row r="25" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A25" s="243"/>
+      <c r="B25" s="245"/>
+      <c r="C25" s="247"/>
       <c r="D25" s="59" t="s">
         <v>103</v>
       </c>
-      <c r="E25" s="205"/>
-      <c r="F25" s="207"/>
-    </row>
-    <row r="26" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A26" s="235">
+      <c r="E25" s="212"/>
+      <c r="F25" s="214"/>
+    </row>
+    <row r="26" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A26" s="242">
         <v>8</v>
       </c>
-      <c r="B26" s="237" t="s">
+      <c r="B26" s="244" t="s">
         <v>66</v>
       </c>
-      <c r="C26" s="239">
+      <c r="C26" s="246">
         <v>15</v>
       </c>
       <c r="D26" s="60">
         <v>40</v>
       </c>
-      <c r="E26" s="204">
+      <c r="E26" s="211">
         <f>SUM(D26:D26)</f>
         <v>40</v>
       </c>
-      <c r="F26" s="206">
+      <c r="F26" s="213">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A27" s="236"/>
-      <c r="B27" s="238"/>
-      <c r="C27" s="240"/>
+    <row r="27" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A27" s="243"/>
+      <c r="B27" s="245"/>
+      <c r="C27" s="247"/>
       <c r="D27" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="E27" s="205"/>
-      <c r="F27" s="207"/>
-    </row>
-    <row r="28" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A28" s="235">
+      <c r="E27" s="212"/>
+      <c r="F27" s="214"/>
+    </row>
+    <row r="28" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A28" s="242">
         <v>9</v>
       </c>
-      <c r="B28" s="237" t="s">
+      <c r="B28" s="244" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="239">
+      <c r="C28" s="246">
         <v>27</v>
       </c>
       <c r="D28" s="60">
         <v>172</v>
       </c>
-      <c r="E28" s="204">
+      <c r="E28" s="211">
         <f>SUM(D28:D28)</f>
         <v>172</v>
       </c>
-      <c r="F28" s="206">
+      <c r="F28" s="213">
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A29" s="236"/>
-      <c r="B29" s="238"/>
-      <c r="C29" s="240"/>
+    <row r="29" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A29" s="243"/>
+      <c r="B29" s="245"/>
+      <c r="C29" s="247"/>
       <c r="D29" s="59" t="s">
         <v>105</v>
       </c>
-      <c r="E29" s="205"/>
-      <c r="F29" s="207"/>
-    </row>
-    <row r="30" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A30" s="235">
+      <c r="E29" s="212"/>
+      <c r="F29" s="214"/>
+    </row>
+    <row r="30" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A30" s="242">
         <v>10</v>
       </c>
-      <c r="B30" s="237" t="s">
+      <c r="B30" s="244" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="239">
+      <c r="C30" s="246">
         <v>20</v>
       </c>
       <c r="D30" s="60">
         <v>239</v>
       </c>
-      <c r="E30" s="204">
+      <c r="E30" s="211">
         <f>SUM(D30:D30)</f>
         <v>239</v>
       </c>
-      <c r="F30" s="206">
+      <c r="F30" s="213">
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A31" s="236"/>
-      <c r="B31" s="238"/>
-      <c r="C31" s="240"/>
+    <row r="31" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A31" s="243"/>
+      <c r="B31" s="245"/>
+      <c r="C31" s="247"/>
       <c r="D31" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="E31" s="205"/>
-      <c r="F31" s="207"/>
-    </row>
-    <row r="32" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A32" s="235">
+      <c r="E31" s="212"/>
+      <c r="F31" s="214"/>
+    </row>
+    <row r="32" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A32" s="242">
         <v>11</v>
       </c>
-      <c r="B32" s="237" t="s">
+      <c r="B32" s="244" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="239">
+      <c r="C32" s="246">
         <v>32</v>
       </c>
       <c r="D32" s="60">
         <v>121</v>
       </c>
-      <c r="E32" s="204">
+      <c r="E32" s="211">
         <f>SUM(D32:D32)</f>
         <v>121</v>
       </c>
-      <c r="F32" s="206">
+      <c r="F32" s="213">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:8" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A33" s="236"/>
-      <c r="B33" s="238"/>
-      <c r="C33" s="240"/>
+    <row r="33" spans="1:8" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A33" s="243"/>
+      <c r="B33" s="245"/>
+      <c r="C33" s="247"/>
       <c r="D33" s="59" t="s">
         <v>107</v>
       </c>
-      <c r="E33" s="205"/>
-      <c r="F33" s="207"/>
-    </row>
-    <row r="34" spans="1:8" s="3" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A34" s="235">
+      <c r="E33" s="212"/>
+      <c r="F33" s="214"/>
+    </row>
+    <row r="34" spans="1:8" s="3" customFormat="1" ht="29.45" customHeight="1">
+      <c r="A34" s="242">
         <v>12</v>
       </c>
-      <c r="B34" s="241" t="s">
+      <c r="B34" s="248" t="s">
         <v>70</v>
       </c>
-      <c r="C34" s="235">
+      <c r="C34" s="242">
         <v>45</v>
       </c>
       <c r="D34" s="60">
         <v>54</v>
       </c>
-      <c r="E34" s="204">
+      <c r="E34" s="211">
         <f>SUM(D34:D34)</f>
         <v>54</v>
       </c>
-      <c r="F34" s="206">
+      <c r="F34" s="213">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:8" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
-      <c r="A35" s="236"/>
-      <c r="B35" s="242"/>
-      <c r="C35" s="236"/>
+    <row r="35" spans="1:8" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+      <c r="A35" s="243"/>
+      <c r="B35" s="249"/>
+      <c r="C35" s="243"/>
       <c r="D35" s="59" t="s">
         <v>108</v>
       </c>
-      <c r="E35" s="205"/>
-      <c r="F35" s="207"/>
+      <c r="E35" s="212"/>
+      <c r="F35" s="214"/>
     </row>
     <row r="36" spans="1:8" s="3" customFormat="1" ht="39" customHeight="1" thickBot="1">
-      <c r="A36" s="230" t="s">
+      <c r="A36" s="237" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="231"/>
-      <c r="C36" s="232"/>
+      <c r="B36" s="238"/>
+      <c r="C36" s="239"/>
       <c r="D36" s="44">
         <v>105</v>
       </c>
@@ -7888,7 +8102,7 @@
       <c r="G36" s="25"/>
       <c r="H36" s="25"/>
     </row>
-    <row r="37" spans="1:8" s="3" customFormat="1" ht="17.399999999999999" customHeight="1" thickBot="1">
+    <row r="37" spans="1:8" s="3" customFormat="1" ht="17.45" customHeight="1" thickBot="1">
       <c r="A37" s="24"/>
       <c r="B37" s="24"/>
       <c r="C37" s="24"/>
@@ -7899,10 +8113,10 @@
       <c r="H37" s="25"/>
     </row>
     <row r="38" spans="1:8" s="3" customFormat="1" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A38" s="233" t="s">
+      <c r="A38" s="240" t="s">
         <v>49</v>
       </c>
-      <c r="B38" s="234"/>
+      <c r="B38" s="241"/>
       <c r="C38" s="50" t="s">
         <v>53</v>
       </c>
@@ -7914,7 +8128,7 @@
       </c>
       <c r="F38" s="26"/>
     </row>
-    <row r="39" spans="1:8" s="3" customFormat="1" ht="28.2" customHeight="1" thickBot="1">
+    <row r="39" spans="1:8" s="3" customFormat="1" ht="28.15" customHeight="1" thickBot="1">
       <c r="A39" s="36" t="s">
         <v>78</v>
       </c>
@@ -7924,7 +8138,7 @@
       <c r="E39" s="37"/>
       <c r="F39" s="26"/>
     </row>
-    <row r="40" spans="1:8" s="3" customFormat="1" ht="28.2" customHeight="1" thickBot="1">
+    <row r="40" spans="1:8" s="3" customFormat="1" ht="28.15" customHeight="1" thickBot="1">
       <c r="A40" s="36" t="s">
         <v>80</v>
       </c>
@@ -7934,7 +8148,7 @@
       <c r="E40" s="37"/>
       <c r="F40" s="26"/>
     </row>
-    <row r="41" spans="1:8" s="3" customFormat="1" ht="28.2" customHeight="1" thickBot="1">
+    <row r="41" spans="1:8" s="3" customFormat="1" ht="28.15" customHeight="1" thickBot="1">
       <c r="A41" s="53" t="s">
         <v>82</v>
       </c>
@@ -7967,14 +8181,14 @@
         <v>92</v>
       </c>
     </row>
-    <row r="44" spans="1:8" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+    <row r="44" spans="1:8" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
       <c r="D44" s="40"/>
       <c r="E44" s="28" t="s">
         <v>79</v>
       </c>
       <c r="F44" s="28"/>
     </row>
-    <row r="45" spans="1:8" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+    <row r="45" spans="1:8" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
       <c r="D45" s="26"/>
       <c r="E45" s="29" t="s">
         <v>81</v>
@@ -7983,12 +8197,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="1:8" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+    <row r="46" spans="1:8" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
       <c r="D46" s="26"/>
       <c r="E46" s="29"/>
       <c r="F46" s="29"/>
     </row>
-    <row r="47" spans="1:8" s="3" customFormat="1" ht="29.4" customHeight="1">
+    <row r="47" spans="1:8" s="3" customFormat="1" ht="29.45" customHeight="1">
       <c r="D47" s="39"/>
       <c r="E47" s="28"/>
       <c r="F47" s="28"/>

--- a/customers/cpall/excel_templates/logistic_plan_มหาชัย.xlsx
+++ b/customers/cpall/excel_templates/logistic_plan_มหาชัย.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User7\Desktop\PRD-Plan\New folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gtdit\Downloads\Fw_ แบบฟอร์ม 7-11+แพลนรถ ของ PO 08_09  ค่ะ\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AAB3F39-B8D1-44D4-892A-7DCE732D9A24}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F64111-D6E6-4873-A950-0D54A2B8EFD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="399" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="399" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="มหาชัย-ผลิต" sheetId="5" r:id="rId1"/>
@@ -21,9 +21,9 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'คันที่ 1'!$A$2:$F$49</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'คันที่ 2'!$A$1:$F$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'มหาชัย-ผลิต'!$B$4:$H$56</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'มหาชัย-ผลิต'!$B$2:$H$55</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +31,10 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -61,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="146">
   <si>
     <t>PO1</t>
   </si>
@@ -466,12 +469,6 @@
     <t xml:space="preserve">Pear 400g ( 8859388010284 )    </t>
   </si>
   <si>
-    <t>เชอร์รี่สดนำเข้า150 กรัม(อเมริกา)x36P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cherry 150 g ( 8859388008885 )    </t>
-  </si>
-  <si>
     <t>องุ่นไซน์มัสแคท 300 กรัม x 15 P</t>
   </si>
   <si>
@@ -514,9 +511,6 @@
     <t xml:space="preserve">สตรอเบอร์รี่ 250 กรัม x 27 P </t>
   </si>
   <si>
-    <t xml:space="preserve">      วันที่ 18/08/69  ส่งวันที่ PO. 19/08/69</t>
-  </si>
-  <si>
     <t>สาลี่ทอง แพ็ก 4 ผล (800g.) x 8 P</t>
   </si>
   <si>
@@ -526,7 +520,10 @@
     <t>สาลี่ทอง แพ็ก 2 ผล (400g.) x 8 P</t>
   </si>
   <si>
-    <t>ผู้ส่ง : 7-11 มหาชัย 6 ล้อ 83-8096 พี่ปาล์ม+คาย</t>
+    <t xml:space="preserve">      วันที่ 07/09/69  ส่งวันที่ PO. 08/09/69</t>
+  </si>
+  <si>
+    <t>ผู้ส่ง : 7-11 มหาชัย  4 ล้อ 2841 พี่เบ้น</t>
   </si>
 </sst>
 </file>
@@ -537,14 +534,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -552,14 +549,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -645,7 +642,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -1087,23 +1084,23 @@
     </font>
     <font>
       <b/>
-      <sz val="41"/>
+      <sz val="45"/>
+      <color theme="1"/>
+      <name val="CordiaUPC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="45"/>
       <color rgb="FF0000FF"/>
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="41"/>
+      <sz val="45"/>
       <color rgb="FF7030A0"/>
       <name val="Arial Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="45"/>
-      <color theme="1"/>
-      <name val="CordiaUPC"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1645,7 +1642,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="254">
+  <cellXfs count="247">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1944,9 +1941,6 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1957,9 +1951,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1977,25 +1968,19 @@
     <xf numFmtId="0" fontId="79" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2010,40 +1995,31 @@
     <xf numFmtId="0" fontId="73" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="29" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="81" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="30" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="13" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="30" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="29" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="82" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="30" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="13" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2118,10 +2094,10 @@
     <xf numFmtId="0" fontId="57" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="5" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2163,16 +2139,16 @@
     <xf numFmtId="0" fontId="73" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="82" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="82" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="83" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="83" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2438,9 +2414,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>196688</xdr:colOff>
+      <xdr:colOff>291938</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>158749</xdr:rowOff>
+      <xdr:rowOff>253999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3079912" cy="1167260"/>
     <xdr:pic>
@@ -2464,7 +2440,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="196688" y="361949"/>
+          <a:off x="291938" y="444499"/>
           <a:ext cx="3079912" cy="1167260"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2578,7 +2554,7 @@
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
     <keyFlags>
       <key name="_Self">
@@ -2604,6 +2580,9 @@
         <flag name="ExcludeFromCalcComparison" value="1"/>
       </key>
       <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
         <flag name="ExcludeFromCalcComparison" value="1"/>
       </key>
       <key name="_ClassificationId">
@@ -2955,22 +2934,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:J136"/>
-  <sheetFormatPr defaultColWidth="5.75" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="B2:J134"/>
+  <sheetFormatPr defaultColWidth="5.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.75" style="64"/>
-    <col min="2" max="2" width="15.625" style="64" customWidth="1"/>
-    <col min="3" max="3" width="135" style="72" customWidth="1"/>
-    <col min="4" max="4" width="28.25" style="64" customWidth="1"/>
-    <col min="5" max="5" width="116.125" style="64" customWidth="1"/>
-    <col min="6" max="6" width="30.875" style="64" customWidth="1"/>
-    <col min="7" max="7" width="33.875" style="64" customWidth="1"/>
-    <col min="8" max="8" width="45.875" style="64" customWidth="1"/>
-    <col min="9" max="9" width="11.625" style="64" customWidth="1"/>
-    <col min="10" max="16384" width="5.75" style="64"/>
+    <col min="1" max="1" width="5.6640625" style="64"/>
+    <col min="2" max="2" width="19.77734375" style="64" customWidth="1"/>
+    <col min="3" max="3" width="158.5546875" style="72" customWidth="1"/>
+    <col min="4" max="4" width="29.88671875" style="64" customWidth="1"/>
+    <col min="5" max="5" width="116.109375" style="64" customWidth="1"/>
+    <col min="6" max="6" width="30.88671875" style="64" customWidth="1"/>
+    <col min="7" max="7" width="33.88671875" style="64" customWidth="1"/>
+    <col min="8" max="8" width="45.88671875" style="64" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" style="64" customWidth="1"/>
+    <col min="10" max="16384" width="5.6640625" style="64"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="58.9" customHeight="1"/>
+    <row r="2" spans="2:10" ht="58.95" customHeight="1"/>
     <row r="3" spans="2:10" ht="30.75" customHeight="1" thickBot="1">
       <c r="E3" s="65"/>
       <c r="F3" s="65"/>
@@ -2978,870 +2957,841 @@
       <c r="I3" s="65"/>
       <c r="J3" s="65"/>
     </row>
-    <row r="4" spans="2:10" ht="103.9" customHeight="1" thickBot="1">
-      <c r="B4" s="175" t="s">
-        <v>147</v>
-      </c>
-      <c r="C4" s="176"/>
-      <c r="D4" s="160" t="s">
-        <v>143</v>
-      </c>
-      <c r="E4" s="161"/>
-      <c r="F4" s="161"/>
-      <c r="G4" s="161"/>
-      <c r="H4" s="162"/>
+    <row r="4" spans="2:10" ht="103.95" customHeight="1" thickBot="1">
+      <c r="B4" s="168" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" s="169"/>
+      <c r="D4" s="153" t="s">
+        <v>144</v>
+      </c>
+      <c r="E4" s="154"/>
+      <c r="F4" s="154"/>
+      <c r="G4" s="154"/>
+      <c r="H4" s="155"/>
     </row>
     <row r="5" spans="2:10" s="67" customFormat="1" ht="15" customHeight="1">
-      <c r="B5" s="179" t="s">
+      <c r="B5" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="180"/>
-      <c r="D5" s="183" t="s">
+      <c r="C5" s="173"/>
+      <c r="D5" s="176" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="165" t="s">
+      <c r="E5" s="158" t="s">
         <v>111</v>
       </c>
-      <c r="F5" s="167" t="s">
+      <c r="F5" s="160" t="s">
         <v>72</v>
       </c>
-      <c r="G5" s="168"/>
-      <c r="H5" s="163" t="s">
+      <c r="G5" s="161"/>
+      <c r="H5" s="156" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="6" spans="2:10" s="67" customFormat="1" ht="30.6" customHeight="1" thickBot="1">
-      <c r="B6" s="181"/>
-      <c r="C6" s="182"/>
-      <c r="D6" s="184"/>
-      <c r="E6" s="166"/>
-      <c r="F6" s="169"/>
-      <c r="G6" s="170"/>
-      <c r="H6" s="164"/>
+      <c r="B6" s="174"/>
+      <c r="C6" s="175"/>
+      <c r="D6" s="177"/>
+      <c r="E6" s="159"/>
+      <c r="F6" s="162"/>
+      <c r="G6" s="163"/>
+      <c r="H6" s="157"/>
     </row>
     <row r="7" spans="2:10" s="67" customFormat="1" ht="58.5" customHeight="1" thickBot="1">
-      <c r="B7" s="181"/>
-      <c r="C7" s="182"/>
-      <c r="D7" s="184"/>
-      <c r="E7" s="166"/>
+      <c r="B7" s="174"/>
+      <c r="C7" s="175"/>
+      <c r="D7" s="177"/>
+      <c r="E7" s="159"/>
       <c r="F7" s="73" t="s">
         <v>75</v>
       </c>
       <c r="G7" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="H7" s="164"/>
+      <c r="H7" s="157"/>
     </row>
     <row r="8" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B8" s="171">
+      <c r="B8" s="164">
         <v>1</v>
       </c>
-      <c r="C8" s="106" t="s">
+      <c r="C8" s="104" t="s">
         <v>115</v>
       </c>
-      <c r="D8" s="171">
+      <c r="D8" s="164">
         <v>36</v>
       </c>
-      <c r="E8" s="125"/>
-      <c r="F8" s="158">
+      <c r="E8" s="122"/>
+      <c r="F8" s="151">
         <f>SUM(E8:E8)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="134">
+      <c r="G8" s="127">
         <f>มหาชัย!C10</f>
         <v>0</v>
       </c>
-      <c r="H8" s="136"/>
+      <c r="H8" s="129"/>
     </row>
     <row r="9" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B9" s="172"/>
-      <c r="C9" s="110" t="s">
+      <c r="B9" s="165"/>
+      <c r="C9" s="108" t="s">
         <v>116</v>
       </c>
-      <c r="D9" s="172"/>
-      <c r="E9" s="126" t="str">
+      <c r="D9" s="165"/>
+      <c r="E9" s="123" t="str">
         <f>IF(E8=0, "", IF(MOD(E8, $D$8) = 0, E8 / $D$8, IF(INT(E8 / $D$8) = 0, MOD(E8, $D$8) &amp; " P", INT(E8 / $D$8) &amp; " + " &amp; MOD(E8, $D$8) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F9" s="159"/>
-      <c r="G9" s="135"/>
-      <c r="H9" s="137"/>
+      <c r="F9" s="152"/>
+      <c r="G9" s="128"/>
+      <c r="H9" s="130"/>
     </row>
     <row r="10" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B10" s="171">
+      <c r="B10" s="164">
         <v>2</v>
       </c>
-      <c r="C10" s="107" t="s">
+      <c r="C10" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="171">
+      <c r="D10" s="164">
         <v>32</v>
       </c>
-      <c r="E10" s="125"/>
-      <c r="F10" s="158">
+      <c r="E10" s="122"/>
+      <c r="F10" s="151">
         <f>SUM(E10:E10)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="134">
+      <c r="G10" s="127">
         <f>มหาชัย!C11</f>
         <v>0</v>
       </c>
-      <c r="H10" s="136"/>
+      <c r="H10" s="129"/>
     </row>
     <row r="11" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B11" s="172"/>
-      <c r="C11" s="110" t="s">
+      <c r="B11" s="165"/>
+      <c r="C11" s="108" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="172"/>
-      <c r="E11" s="126" t="str">
+      <c r="D11" s="165"/>
+      <c r="E11" s="123" t="str">
         <f>IF(E10=0, "", IF(MOD(E10, $D$10) = 0, E10 / $D$10, IF(INT(E10 / $D$10) = 0, MOD(E10, $D$10) &amp; " P", INT(E10 / $D$10) &amp; " + " &amp; MOD(E10, $D$10) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F11" s="159"/>
-      <c r="G11" s="135"/>
-      <c r="H11" s="137"/>
+      <c r="F11" s="152"/>
+      <c r="G11" s="128"/>
+      <c r="H11" s="130"/>
     </row>
     <row r="12" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B12" s="171">
+      <c r="B12" s="116">
         <v>3</v>
       </c>
-      <c r="C12" s="107" t="s">
-        <v>127</v>
-      </c>
-      <c r="D12" s="138">
-        <v>36</v>
-      </c>
-      <c r="E12" s="125"/>
-      <c r="F12" s="158">
+      <c r="C12" s="105" t="s">
+        <v>136</v>
+      </c>
+      <c r="D12" s="164">
+        <v>14</v>
+      </c>
+      <c r="E12" s="122"/>
+      <c r="F12" s="151">
         <f>SUM(E12:E12)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="134">
+      <c r="G12" s="127">
         <f>มหาชัย!C12</f>
         <v>0</v>
       </c>
-      <c r="H12" s="136"/>
+      <c r="H12" s="129"/>
     </row>
     <row r="13" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B13" s="172"/>
-      <c r="C13" s="110" t="s">
-        <v>128</v>
-      </c>
-      <c r="D13" s="139"/>
-      <c r="E13" s="126" t="str">
+      <c r="B13" s="117"/>
+      <c r="C13" s="108" t="s">
+        <v>137</v>
+      </c>
+      <c r="D13" s="165"/>
+      <c r="E13" s="123" t="str">
         <f>IF(E12=0, "", IF(MOD(E12, $D$12) = 0, E12/ $D$12, IF(INT(E12 / $D$12) = 0, MOD(E12, $D$12) &amp; " P", INT(E12 / $D$12) &amp; " + " &amp; MOD(E12, $D$12) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F13" s="159"/>
-      <c r="G13" s="135"/>
-      <c r="H13" s="137"/>
+      <c r="F13" s="152"/>
+      <c r="G13" s="128"/>
+      <c r="H13" s="130"/>
     </row>
     <row r="14" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B14" s="120">
+      <c r="B14" s="116">
         <v>4</v>
       </c>
-      <c r="C14" s="107" t="s">
+      <c r="C14" s="105" t="s">
         <v>138</v>
       </c>
-      <c r="D14" s="171">
+      <c r="D14" s="164">
         <v>14</v>
       </c>
-      <c r="E14" s="125"/>
-      <c r="F14" s="158">
+      <c r="E14" s="122"/>
+      <c r="F14" s="151">
         <f>SUM(E14:E14)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="134">
+      <c r="G14" s="127">
         <f>มหาชัย!C13</f>
         <v>0</v>
       </c>
-      <c r="H14" s="136"/>
+      <c r="H14" s="129"/>
     </row>
     <row r="15" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B15" s="121"/>
-      <c r="C15" s="110" t="s">
+      <c r="B15" s="117"/>
+      <c r="C15" s="108" t="s">
         <v>139</v>
       </c>
-      <c r="D15" s="172"/>
-      <c r="E15" s="126" t="str">
+      <c r="D15" s="165"/>
+      <c r="E15" s="123" t="str">
         <f>IF(E14=0, "", IF(MOD(E14, $D$14) = 0, E14/ $D$14, IF(INT(E14 / $D$14) = 0, MOD(E14, $D$14) &amp; " P", INT(E14 / $D$14) &amp; " + " &amp; MOD(E14, $D$14) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F15" s="159"/>
-      <c r="G15" s="135"/>
-      <c r="H15" s="137"/>
+      <c r="F15" s="152"/>
+      <c r="G15" s="128"/>
+      <c r="H15" s="130"/>
     </row>
     <row r="16" spans="2:10" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B16" s="120">
+      <c r="B16" s="114">
         <v>5</v>
       </c>
-      <c r="C16" s="107" t="s">
-        <v>140</v>
-      </c>
-      <c r="D16" s="171">
-        <v>14</v>
-      </c>
-      <c r="E16" s="125"/>
-      <c r="F16" s="158">
+      <c r="C16" s="105" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="131">
+        <v>32</v>
+      </c>
+      <c r="E16" s="122"/>
+      <c r="F16" s="151">
         <f>SUM(E16:E16)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="134">
+      <c r="G16" s="127">
         <f>มหาชัย!C14</f>
         <v>0</v>
       </c>
-      <c r="H16" s="136"/>
+      <c r="H16" s="129"/>
     </row>
     <row r="17" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B17" s="121"/>
-      <c r="C17" s="110" t="s">
-        <v>141</v>
-      </c>
-      <c r="D17" s="172"/>
-      <c r="E17" s="126" t="str">
+      <c r="B17" s="115"/>
+      <c r="C17" s="108" t="s">
+        <v>120</v>
+      </c>
+      <c r="D17" s="132"/>
+      <c r="E17" s="123" t="str">
         <f>IF(E16=0, "", IF(MOD(E16, $D$16) = 0, E16/ $D$16, IF(INT(E16 / $D$16) = 0, MOD(E16, $D$16) &amp; " P", INT(E16 / $D$16) &amp; " + " &amp; MOD(E16, $D$16) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F17" s="159"/>
-      <c r="G17" s="135"/>
-      <c r="H17" s="137"/>
+      <c r="F17" s="152"/>
+      <c r="G17" s="128"/>
+      <c r="H17" s="130"/>
     </row>
     <row r="18" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1">
       <c r="B18" s="118">
         <v>6</v>
       </c>
-      <c r="C18" s="107" t="s">
-        <v>62</v>
-      </c>
-      <c r="D18" s="138">
-        <v>32</v>
-      </c>
-      <c r="E18" s="125"/>
-      <c r="F18" s="158">
+      <c r="C18" s="104" t="s">
+        <v>134</v>
+      </c>
+      <c r="D18" s="131">
+        <v>27</v>
+      </c>
+      <c r="E18" s="124"/>
+      <c r="F18" s="166">
         <f>SUM(E18:E18)</f>
         <v>0</v>
       </c>
-      <c r="G18" s="134">
+      <c r="G18" s="127">
         <f>มหาชัย!C15</f>
         <v>0</v>
       </c>
-      <c r="H18" s="136"/>
+      <c r="H18" s="129"/>
     </row>
     <row r="19" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
       <c r="B19" s="119"/>
-      <c r="C19" s="110" t="s">
-        <v>120</v>
-      </c>
-      <c r="D19" s="139"/>
-      <c r="E19" s="126" t="str">
+      <c r="C19" s="108" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="132"/>
+      <c r="E19" s="123" t="str">
         <f>IF(E18=0, "", IF(MOD(E18, $D$18) = 0, E18/ $D$18, IF(INT(E18 / $D$18) = 0, MOD(E18, $D$18) &amp; " P", INT(E18 / $D$18) &amp; " + " &amp; MOD(E18, $D$18) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F19" s="159"/>
-      <c r="G19" s="135"/>
-      <c r="H19" s="137"/>
+      <c r="F19" s="167"/>
+      <c r="G19" s="128"/>
+      <c r="H19" s="130"/>
     </row>
     <row r="20" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B20" s="123">
+      <c r="B20" s="116">
         <v>7</v>
       </c>
       <c r="C20" s="106" t="s">
-        <v>136</v>
-      </c>
-      <c r="D20" s="138">
+        <v>140</v>
+      </c>
+      <c r="D20" s="131">
         <v>27</v>
       </c>
-      <c r="E20" s="127"/>
-      <c r="F20" s="173">
+      <c r="E20" s="122"/>
+      <c r="F20" s="151">
         <f>SUM(E20:E20)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="134">
+      <c r="G20" s="127">
         <f>มหาชัย!C16</f>
         <v>0</v>
       </c>
-      <c r="H20" s="136"/>
+      <c r="H20" s="129"/>
     </row>
     <row r="21" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B21" s="124"/>
-      <c r="C21" s="110" t="s">
-        <v>137</v>
-      </c>
-      <c r="D21" s="139"/>
-      <c r="E21" s="126" t="str">
+      <c r="B21" s="117"/>
+      <c r="C21" s="108" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21" s="132"/>
+      <c r="E21" s="123" t="str">
         <f>IF(E20=0, "", IF(MOD(E20, $D$20) = 0, E20/ $D$20, IF(INT(E20 / $D$20) = 0, MOD(E20, $D$20) &amp; " P", INT(E20 / $D$20) &amp; " + " &amp; MOD(E20, $D$20) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F21" s="174"/>
-      <c r="G21" s="135"/>
-      <c r="H21" s="137"/>
+      <c r="F21" s="152"/>
+      <c r="G21" s="128"/>
+      <c r="H21" s="130"/>
     </row>
     <row r="22" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B22" s="120">
+      <c r="B22" s="116">
         <v>8</v>
       </c>
-      <c r="C22" s="108" t="s">
-        <v>142</v>
-      </c>
-      <c r="D22" s="138">
-        <v>27</v>
-      </c>
-      <c r="E22" s="125"/>
-      <c r="F22" s="158">
+      <c r="C22" s="107" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="131">
+        <v>36</v>
+      </c>
+      <c r="E22" s="122"/>
+      <c r="F22" s="151">
         <f>SUM(E22:E22)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="134">
+      <c r="G22" s="127">
         <f>มหาชัย!C17</f>
         <v>0</v>
       </c>
-      <c r="H22" s="136"/>
+      <c r="H22" s="129"/>
     </row>
     <row r="23" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B23" s="121"/>
-      <c r="C23" s="110" t="s">
-        <v>122</v>
-      </c>
-      <c r="D23" s="139"/>
-      <c r="E23" s="126" t="str">
+      <c r="B23" s="117"/>
+      <c r="C23" s="120" t="s">
+        <v>119</v>
+      </c>
+      <c r="D23" s="132"/>
+      <c r="E23" s="123" t="str">
         <f>IF(E22=0, "", IF(MOD(E22, $D$22) = 0, E22/ $D$22, IF(INT(E22 / $D$22) = 0, MOD(E22, $D$22) &amp; " P", INT(E22 / $D$22) &amp; " + " &amp; MOD(E22, $D$22) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F23" s="159"/>
-      <c r="G23" s="135"/>
-      <c r="H23" s="137"/>
+      <c r="F23" s="152"/>
+      <c r="G23" s="128"/>
+      <c r="H23" s="130"/>
     </row>
     <row r="24" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B24" s="120">
+      <c r="B24" s="116">
         <v>9</v>
       </c>
-      <c r="C24" s="109" t="s">
-        <v>63</v>
-      </c>
-      <c r="D24" s="138">
-        <v>36</v>
-      </c>
-      <c r="E24" s="125"/>
-      <c r="F24" s="158">
+      <c r="C24" s="105" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" s="131">
+        <v>20</v>
+      </c>
+      <c r="E24" s="122"/>
+      <c r="F24" s="151">
         <f>SUM(E24:E24)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="134">
+      <c r="G24" s="127">
         <f>มหาชัย!C18</f>
         <v>0</v>
       </c>
-      <c r="H24" s="136"/>
+      <c r="H24" s="129"/>
     </row>
     <row r="25" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B25" s="121"/>
-      <c r="C25" s="128" t="s">
-        <v>119</v>
-      </c>
-      <c r="D25" s="139"/>
-      <c r="E25" s="126" t="str">
+      <c r="B25" s="117"/>
+      <c r="C25" s="108" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25" s="132"/>
+      <c r="E25" s="123" t="str">
         <f>IF(E24=0, "", IF(MOD(E24, $D$24) = 0, E24/ $D$24, IF(INT(E24 / $D$24) = 0, MOD(E24, $D$24) &amp; " P", INT(E24 / $D$24) &amp; " + " &amp; MOD(E24, $D$24) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F25" s="159"/>
-      <c r="G25" s="135"/>
-      <c r="H25" s="137"/>
+      <c r="F25" s="152"/>
+      <c r="G25" s="128"/>
+      <c r="H25" s="130"/>
     </row>
     <row r="26" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B26" s="120">
+      <c r="B26" s="116">
         <v>10</v>
       </c>
       <c r="C26" s="107" t="s">
-        <v>114</v>
-      </c>
-      <c r="D26" s="138">
-        <v>20</v>
+        <v>127</v>
+      </c>
+      <c r="D26" s="170">
+        <v>15</v>
       </c>
       <c r="E26" s="125"/>
-      <c r="F26" s="158">
+      <c r="F26" s="151">
         <f>SUM(E26:E26)</f>
         <v>0</v>
       </c>
-      <c r="G26" s="134">
+      <c r="G26" s="127">
         <f>มหาชัย!C19</f>
         <v>0</v>
       </c>
-      <c r="H26" s="136"/>
+      <c r="H26" s="129"/>
     </row>
     <row r="27" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B27" s="121"/>
-      <c r="C27" s="110" t="s">
-        <v>117</v>
-      </c>
-      <c r="D27" s="139"/>
+      <c r="B27" s="117"/>
+      <c r="C27" s="108" t="s">
+        <v>128</v>
+      </c>
+      <c r="D27" s="171"/>
       <c r="E27" s="126" t="str">
         <f>IF(E26=0, "", IF(MOD(E26, $D$26) = 0, E26/ $D$26, IF(INT(E26 / $D$26) = 0, MOD(E26, $D$26) &amp; " P", INT(E26 / $D$26) &amp; " + " &amp; MOD(E26, $D$26) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F27" s="159"/>
-      <c r="G27" s="135"/>
-      <c r="H27" s="137"/>
+      <c r="F27" s="152"/>
+      <c r="G27" s="128"/>
+      <c r="H27" s="130"/>
     </row>
     <row r="28" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B28" s="120">
+      <c r="B28" s="116">
         <v>11</v>
       </c>
-      <c r="C28" s="109" t="s">
-        <v>129</v>
-      </c>
-      <c r="D28" s="177">
-        <v>15</v>
-      </c>
-      <c r="E28" s="129"/>
-      <c r="F28" s="158">
+      <c r="C28" s="107" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="131">
+        <v>45</v>
+      </c>
+      <c r="E28" s="125"/>
+      <c r="F28" s="151">
         <f>SUM(E28:E28)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="134">
+      <c r="G28" s="127">
         <f>มหาชัย!C20</f>
         <v>0</v>
       </c>
-      <c r="H28" s="136"/>
+      <c r="H28" s="129"/>
     </row>
     <row r="29" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B29" s="121"/>
-      <c r="C29" s="110" t="s">
-        <v>130</v>
-      </c>
-      <c r="D29" s="178"/>
-      <c r="E29" s="130" t="str">
+      <c r="B29" s="117"/>
+      <c r="C29" s="108" t="s">
+        <v>118</v>
+      </c>
+      <c r="D29" s="132"/>
+      <c r="E29" s="126" t="str">
         <f>IF(E28=0, "", IF(MOD(E28, $D$28) = 0, E28/ $D$28, IF(INT(E28 / $D$28) = 0, MOD(E28, $D$28) &amp; " P", INT(E28 / $D$28) &amp; " + " &amp; MOD(E28, $D$28) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F29" s="159"/>
-      <c r="G29" s="135"/>
-      <c r="H29" s="137"/>
+      <c r="F29" s="152"/>
+      <c r="G29" s="128"/>
+      <c r="H29" s="130"/>
     </row>
     <row r="30" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B30" s="120">
+      <c r="B30" s="116">
         <v>12</v>
       </c>
-      <c r="C30" s="109" t="s">
-        <v>65</v>
-      </c>
-      <c r="D30" s="138">
-        <v>45</v>
-      </c>
-      <c r="E30" s="131"/>
-      <c r="F30" s="158">
+      <c r="C30" s="107" t="s">
+        <v>132</v>
+      </c>
+      <c r="D30" s="131">
+        <v>15</v>
+      </c>
+      <c r="E30" s="125"/>
+      <c r="F30" s="151">
         <f>SUM(E30:E30)</f>
         <v>0</v>
       </c>
-      <c r="G30" s="134">
+      <c r="G30" s="127">
         <f>มหาชัย!C21</f>
         <v>0</v>
       </c>
-      <c r="H30" s="136"/>
+      <c r="H30" s="129"/>
     </row>
     <row r="31" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B31" s="121"/>
-      <c r="C31" s="110" t="s">
-        <v>118</v>
-      </c>
-      <c r="D31" s="139"/>
-      <c r="E31" s="130" t="str">
+      <c r="B31" s="117"/>
+      <c r="C31" s="108" t="s">
+        <v>133</v>
+      </c>
+      <c r="D31" s="132"/>
+      <c r="E31" s="126" t="str">
         <f>IF(E30=0, "", IF(MOD(E30, $D$30) = 0, E30/ $D$30, IF(INT(E30 / $D$30) = 0, MOD(E30, $D$30) &amp; " P", INT(E30 / $D$30) &amp; " + " &amp; MOD(E30, $D$30) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F31" s="159"/>
-      <c r="G31" s="135"/>
-      <c r="H31" s="137"/>
+      <c r="F31" s="152"/>
+      <c r="G31" s="128"/>
+      <c r="H31" s="130"/>
     </row>
     <row r="32" spans="2:8" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B32" s="120">
+      <c r="B32" s="121">
         <v>13</v>
       </c>
-      <c r="C32" s="109" t="s">
-        <v>134</v>
-      </c>
-      <c r="D32" s="138">
+      <c r="C32" s="105" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" s="131">
         <v>15</v>
       </c>
-      <c r="E32" s="131"/>
-      <c r="F32" s="158">
+      <c r="E32" s="125"/>
+      <c r="F32" s="151">
         <f>SUM(E32:E32)</f>
         <v>0</v>
       </c>
-      <c r="G32" s="134">
+      <c r="G32" s="127">
         <f>มหาชัย!C22</f>
         <v>0</v>
       </c>
-      <c r="H32" s="136"/>
+      <c r="H32" s="129"/>
     </row>
     <row r="33" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B33" s="121"/>
-      <c r="C33" s="110" t="s">
-        <v>135</v>
-      </c>
-      <c r="D33" s="139"/>
-      <c r="E33" s="130" t="str">
+      <c r="B33" s="119"/>
+      <c r="C33" s="108" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33" s="132"/>
+      <c r="E33" s="126" t="str">
         <f>IF(E32=0, "", IF(MOD(E32, $D$32) = 0, E32/ $D$32, IF(INT(E32 / $D$32) = 0, MOD(E32, $D$32) &amp; " P", INT(E32 / $D$32) &amp; " + " &amp; MOD(E32, $D$32) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F33" s="159"/>
-      <c r="G33" s="135"/>
-      <c r="H33" s="137"/>
+      <c r="F33" s="152"/>
+      <c r="G33" s="128"/>
+      <c r="H33" s="130"/>
     </row>
     <row r="34" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B34" s="132">
+      <c r="B34" s="121">
         <v>14</v>
       </c>
       <c r="C34" s="107" t="s">
-        <v>66</v>
-      </c>
-      <c r="D34" s="138">
-        <v>15</v>
-      </c>
-      <c r="E34" s="131"/>
-      <c r="F34" s="158">
+        <v>130</v>
+      </c>
+      <c r="D34" s="131">
+        <v>27</v>
+      </c>
+      <c r="E34" s="125"/>
+      <c r="F34" s="151">
         <f>SUM(E34:E34)</f>
         <v>0</v>
       </c>
-      <c r="G34" s="134">
+      <c r="G34" s="127">
         <f>มหาชัย!C23</f>
         <v>0</v>
       </c>
-      <c r="H34" s="136"/>
+      <c r="H34" s="129"/>
     </row>
     <row r="35" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B35" s="124"/>
-      <c r="C35" s="110" t="s">
-        <v>123</v>
-      </c>
-      <c r="D35" s="139"/>
-      <c r="E35" s="130" t="str">
+      <c r="B35" s="119"/>
+      <c r="C35" s="108" t="s">
+        <v>131</v>
+      </c>
+      <c r="D35" s="132"/>
+      <c r="E35" s="126" t="str">
         <f>IF(E34=0, "", IF(MOD(E34, $D$34) = 0, E34/ $D$34, IF(INT(E34 / $D$34) = 0, MOD(E34, $D$34) &amp; " P", INT(E34 / $D$34) &amp; " + " &amp; MOD(E34, $D$34) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F35" s="159"/>
-      <c r="G35" s="135"/>
-      <c r="H35" s="137"/>
+      <c r="F35" s="152"/>
+      <c r="G35" s="128"/>
+      <c r="H35" s="130"/>
     </row>
     <row r="36" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B36" s="132">
+      <c r="B36" s="121">
         <v>15</v>
       </c>
-      <c r="C36" s="109" t="s">
-        <v>132</v>
-      </c>
-      <c r="D36" s="138">
-        <v>27</v>
-      </c>
-      <c r="E36" s="131"/>
-      <c r="F36" s="158">
+      <c r="C36" s="107" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" s="131">
+        <v>20</v>
+      </c>
+      <c r="E36" s="125"/>
+      <c r="F36" s="151">
         <f>SUM(E36:E36)</f>
         <v>0</v>
       </c>
-      <c r="G36" s="134">
+      <c r="G36" s="127">
         <f>มหาชัย!C24</f>
         <v>0</v>
       </c>
-      <c r="H36" s="136"/>
+      <c r="H36" s="129"/>
     </row>
     <row r="37" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B37" s="124"/>
-      <c r="C37" s="110" t="s">
-        <v>133</v>
-      </c>
-      <c r="D37" s="139"/>
-      <c r="E37" s="130" t="str">
+      <c r="B37" s="119"/>
+      <c r="C37" s="108" t="s">
+        <v>124</v>
+      </c>
+      <c r="D37" s="132"/>
+      <c r="E37" s="126" t="str">
         <f>IF(E36=0, "", IF(MOD(E36, $D$36) = 0, E36/ $D$36, IF(INT(E36 / $D$36) = 0, MOD(E36, $D$36) &amp; " P", INT(E36 / $D$36) &amp; " + " &amp; MOD(E36, $D$36) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F37" s="159"/>
-      <c r="G37" s="135"/>
-      <c r="H37" s="137"/>
+      <c r="F37" s="152"/>
+      <c r="G37" s="128"/>
+      <c r="H37" s="130"/>
     </row>
     <row r="38" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B38" s="132">
+      <c r="B38" s="121">
         <v>16</v>
       </c>
-      <c r="C38" s="109" t="s">
-        <v>68</v>
-      </c>
-      <c r="D38" s="138">
-        <v>20</v>
-      </c>
-      <c r="E38" s="131"/>
-      <c r="F38" s="158">
+      <c r="C38" s="106" t="s">
+        <v>69</v>
+      </c>
+      <c r="D38" s="131">
+        <v>32</v>
+      </c>
+      <c r="E38" s="125"/>
+      <c r="F38" s="151">
         <f>SUM(E38:E38)</f>
         <v>0</v>
       </c>
-      <c r="G38" s="134">
+      <c r="G38" s="127">
         <f>มหาชัย!C25</f>
         <v>0</v>
       </c>
-      <c r="H38" s="136"/>
+      <c r="H38" s="129"/>
     </row>
     <row r="39" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B39" s="124"/>
-      <c r="C39" s="110" t="s">
-        <v>124</v>
-      </c>
-      <c r="D39" s="139"/>
-      <c r="E39" s="130" t="str">
+      <c r="B39" s="119"/>
+      <c r="C39" s="108" t="s">
+        <v>125</v>
+      </c>
+      <c r="D39" s="132"/>
+      <c r="E39" s="126" t="str">
         <f>IF(E38=0, "", IF(MOD(E38, $D$38) = 0, E38/ $D$38, IF(INT(E38 / $D$38) = 0, MOD(E38, $D$38) &amp; " P", INT(E38 / $D$38) &amp; " + " &amp; MOD(E38, $D$38) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F39" s="159"/>
-      <c r="G39" s="135"/>
-      <c r="H39" s="137"/>
+      <c r="F39" s="152"/>
+      <c r="G39" s="128"/>
+      <c r="H39" s="130"/>
     </row>
     <row r="40" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B40" s="132">
+      <c r="B40" s="121">
         <v>17</v>
       </c>
-      <c r="C40" s="108" t="s">
-        <v>69</v>
-      </c>
-      <c r="D40" s="138">
-        <v>32</v>
-      </c>
-      <c r="E40" s="131"/>
-      <c r="F40" s="158">
+      <c r="C40" s="105" t="s">
+        <v>113</v>
+      </c>
+      <c r="D40" s="131">
+        <v>15</v>
+      </c>
+      <c r="E40" s="125"/>
+      <c r="F40" s="151">
         <f>SUM(E40:E40)</f>
         <v>0</v>
       </c>
-      <c r="G40" s="134">
+      <c r="G40" s="127">
         <f>มหาชัย!C26</f>
         <v>0</v>
       </c>
-      <c r="H40" s="136"/>
+      <c r="H40" s="129"/>
     </row>
     <row r="41" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B41" s="124"/>
-      <c r="C41" s="110" t="s">
-        <v>125</v>
-      </c>
-      <c r="D41" s="139"/>
-      <c r="E41" s="130" t="str">
+      <c r="B41" s="119"/>
+      <c r="C41" s="108" t="s">
+        <v>126</v>
+      </c>
+      <c r="D41" s="132"/>
+      <c r="E41" s="126" t="str">
         <f>IF(E40=0, "", IF(MOD(E40, $D$40) = 0, E40/ $D$40, IF(INT(E40 / $D$40) = 0, MOD(E40, $D$40) &amp; " P", INT(E40 / $D$40) &amp; " + " &amp; MOD(E40, $D$40) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F41" s="159"/>
-      <c r="G41" s="135"/>
-      <c r="H41" s="137"/>
+      <c r="F41" s="152"/>
+      <c r="G41" s="128"/>
+      <c r="H41" s="130"/>
     </row>
     <row r="42" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B42" s="132">
+      <c r="B42" s="121">
         <v>18</v>
       </c>
-      <c r="C42" s="107" t="s">
-        <v>113</v>
-      </c>
-      <c r="D42" s="138">
-        <v>15</v>
-      </c>
-      <c r="E42" s="131"/>
-      <c r="F42" s="158">
+      <c r="C42" s="105" t="s">
+        <v>141</v>
+      </c>
+      <c r="D42" s="131">
+        <v>8</v>
+      </c>
+      <c r="E42" s="125"/>
+      <c r="F42" s="151">
         <f>SUM(E42:E42)</f>
         <v>0</v>
       </c>
-      <c r="G42" s="134">
+      <c r="G42" s="127">
         <f>มหาชัย!C27</f>
         <v>0</v>
       </c>
-      <c r="H42" s="136"/>
+      <c r="H42" s="129"/>
     </row>
     <row r="43" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B43" s="124"/>
-      <c r="C43" s="110" t="s">
-        <v>126</v>
-      </c>
-      <c r="D43" s="139"/>
-      <c r="E43" s="130" t="str">
+      <c r="B43" s="119"/>
+      <c r="C43" s="108" t="s">
+        <v>142</v>
+      </c>
+      <c r="D43" s="132"/>
+      <c r="E43" s="126" t="str">
         <f>IF(E42=0, "", IF(MOD(E42, $D$42) = 0, E42/ $D$42, IF(INT(E42 / $D$42) = 0, MOD(E42, $D$42) &amp; " P", INT(E42 / $D$42) &amp; " + " &amp; MOD(E42, $D$42) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="F43" s="159"/>
-      <c r="G43" s="135"/>
-      <c r="H43" s="137"/>
-    </row>
-    <row r="44" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1">
-      <c r="B44" s="132">
-        <v>19</v>
-      </c>
-      <c r="C44" s="107" t="s">
-        <v>144</v>
-      </c>
-      <c r="D44" s="138">
-        <v>8</v>
-      </c>
-      <c r="E44" s="131"/>
-      <c r="F44" s="158">
-        <f>SUM(E44:E44)</f>
-        <v>0</v>
-      </c>
-      <c r="G44" s="134">
-        <f>มหาชัย!C28</f>
-        <v>0</v>
-      </c>
-      <c r="H44" s="136"/>
-    </row>
-    <row r="45" spans="2:9" s="71" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B45" s="124"/>
-      <c r="C45" s="110" t="s">
-        <v>145</v>
-      </c>
-      <c r="D45" s="139"/>
-      <c r="E45" s="130" t="str">
-        <f>IF(E44=0, "", IF(MOD(E44, $D$44) = 0, E44/ $D$44, IF(INT(E44 / $D$44) = 0, MOD(E44, $D$44) &amp; " P", INT(E44 / $D$44) &amp; " + " &amp; MOD(E44, $D$44) &amp; " P")))</f>
-        <v/>
-      </c>
-      <c r="F45" s="159"/>
-      <c r="G45" s="135"/>
-      <c r="H45" s="137"/>
-    </row>
-    <row r="46" spans="2:9" s="67" customFormat="1" ht="102" customHeight="1" thickBot="1">
-      <c r="B46" s="155" t="s">
+      <c r="F43" s="152"/>
+      <c r="G43" s="128"/>
+      <c r="H43" s="130"/>
+    </row>
+    <row r="44" spans="2:9" s="67" customFormat="1" ht="102" customHeight="1" thickBot="1">
+      <c r="B44" s="148" t="s">
         <v>88</v>
       </c>
-      <c r="C46" s="156"/>
-      <c r="D46" s="157"/>
-      <c r="E46" s="77">
-        <f>-SUM(ROUNDUP(E8/$D$8,0), ROUNDUP(E10/$D$10,0), ROUNDUP(E12/$D$12,0), ROUNDUP(E14/$D$14,0), ROUNDUP(E16/$D$16,0), ROUNDUP(E18/$D$18,0), ROUNDUP(E20/$D$20,0), ROUNDUP(E22/$D$22,0), ROUNDUP(E24/$D$24,0), ROUNDUP(E26/$D$26,0), ROUNDUP(E28/$D$28,0), ROUNDUP(E30/$D$30,0), ROUNDUP(E32/$D$32,0), ROUNDUP(E34/$D$34,0), ROUNDUP(E36/$D$36,0), ROUNDUP(E38/$D$38,0), ROUNDUP(E40/$D$40,0), ROUNDUP(E42/$D$42,0), ROUNDUP(E44/$D$44,0))</f>
-        <v>0</v>
-      </c>
-      <c r="F46" s="78" t="s">
+      <c r="C44" s="149"/>
+      <c r="D44" s="150"/>
+      <c r="E44" s="77">
+        <f>G44</f>
+        <v>0</v>
+      </c>
+      <c r="F44" s="78" t="s">
         <v>90</v>
       </c>
-      <c r="G46" s="79">
-        <f>SUM(G8:G45)</f>
-        <v>0</v>
-      </c>
-      <c r="H46" s="70"/>
-      <c r="I46" s="69"/>
-    </row>
-    <row r="47" spans="2:9" ht="17.45" customHeight="1" thickBot="1">
-      <c r="E47" s="80"/>
-      <c r="F47" s="81"/>
-      <c r="G47" s="82"/>
-      <c r="H47" s="66"/>
-      <c r="I47" s="66"/>
-    </row>
-    <row r="48" spans="2:9" ht="105" customHeight="1" thickBot="1">
-      <c r="B48" s="146" t="s">
+      <c r="G44" s="79">
+        <f>SUM(G8:G43)</f>
+        <v>0</v>
+      </c>
+      <c r="H44" s="70"/>
+      <c r="I44" s="69"/>
+    </row>
+    <row r="45" spans="2:9" ht="17.399999999999999" customHeight="1" thickBot="1">
+      <c r="E45" s="80"/>
+      <c r="F45" s="81"/>
+      <c r="G45" s="82"/>
+      <c r="H45" s="66"/>
+      <c r="I45" s="66"/>
+    </row>
+    <row r="46" spans="2:9" ht="76.8" customHeight="1" thickBot="1">
+      <c r="B46" s="139" t="s">
         <v>49</v>
       </c>
-      <c r="C48" s="154"/>
-      <c r="D48" s="147"/>
-      <c r="E48" s="84" t="s">
+      <c r="C46" s="147"/>
+      <c r="D46" s="140"/>
+      <c r="E46" s="84" t="s">
         <v>53</v>
       </c>
-      <c r="F48" s="146" t="s">
+      <c r="F46" s="139" t="s">
         <v>54</v>
       </c>
-      <c r="G48" s="147"/>
-      <c r="H48" s="84" t="s">
+      <c r="G46" s="140"/>
+      <c r="H46" s="84" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="2:8" ht="62.45" customHeight="1">
-      <c r="B49" s="92" t="s">
+    <row r="47" spans="2:9" ht="62.4" customHeight="1">
+      <c r="B47" s="92" t="s">
         <v>78</v>
       </c>
-      <c r="C49" s="152"/>
-      <c r="D49" s="153"/>
-      <c r="E49" s="93"/>
-      <c r="F49" s="144"/>
-      <c r="G49" s="145"/>
-      <c r="H49" s="93"/>
-    </row>
-    <row r="50" spans="2:8" ht="62.45" customHeight="1">
-      <c r="B50" s="94" t="s">
+      <c r="C47" s="145"/>
+      <c r="D47" s="146"/>
+      <c r="E47" s="93"/>
+      <c r="F47" s="137"/>
+      <c r="G47" s="138"/>
+      <c r="H47" s="93"/>
+    </row>
+    <row r="48" spans="2:9" ht="62.4" customHeight="1">
+      <c r="B48" s="94" t="s">
         <v>80</v>
       </c>
-      <c r="C50" s="150"/>
-      <c r="D50" s="151"/>
-      <c r="E50" s="95"/>
-      <c r="F50" s="142"/>
-      <c r="G50" s="143"/>
-      <c r="H50" s="95"/>
-    </row>
-    <row r="51" spans="2:8" ht="62.45" customHeight="1" thickBot="1">
-      <c r="B51" s="96" t="s">
+      <c r="C48" s="143"/>
+      <c r="D48" s="144"/>
+      <c r="E48" s="95"/>
+      <c r="F48" s="135"/>
+      <c r="G48" s="136"/>
+      <c r="H48" s="95"/>
+    </row>
+    <row r="49" spans="2:8" ht="62.4" customHeight="1" thickBot="1">
+      <c r="B49" s="96" t="s">
         <v>82</v>
       </c>
-      <c r="C51" s="148"/>
-      <c r="D51" s="149"/>
-      <c r="E51" s="97"/>
-      <c r="F51" s="140"/>
-      <c r="G51" s="141"/>
-      <c r="H51" s="97"/>
-    </row>
-    <row r="53" spans="2:8" ht="102.6" customHeight="1">
-      <c r="C53" s="85"/>
-      <c r="D53" s="86" t="s">
+      <c r="C49" s="141"/>
+      <c r="D49" s="142"/>
+      <c r="E49" s="97"/>
+      <c r="F49" s="133"/>
+      <c r="G49" s="134"/>
+      <c r="H49" s="97"/>
+    </row>
+    <row r="51" spans="2:8" ht="102.6" customHeight="1">
+      <c r="C51" s="85"/>
+      <c r="D51" s="86" t="s">
         <v>91</v>
       </c>
-      <c r="E53" s="86"/>
-      <c r="F53" s="76">
-        <f>SUM(G46)</f>
-        <v>0</v>
-      </c>
-      <c r="G53" s="87" t="s">
+      <c r="E51" s="86"/>
+      <c r="F51" s="76">
+        <f>SUM(G44)</f>
+        <v>0</v>
+      </c>
+      <c r="G51" s="87" t="s">
         <v>92</v>
       </c>
+      <c r="H51" s="85"/>
+    </row>
+    <row r="52" spans="2:8" ht="55.95" customHeight="1" thickBot="1">
+      <c r="C52" s="85"/>
+      <c r="D52" s="85"/>
+      <c r="E52" s="86"/>
+      <c r="F52" s="86" t="s">
+        <v>79</v>
+      </c>
+      <c r="G52" s="86"/>
+      <c r="H52" s="85"/>
+    </row>
+    <row r="53" spans="2:8" ht="55.95" customHeight="1" thickBot="1">
+      <c r="C53" s="88"/>
+      <c r="D53" s="85"/>
+      <c r="E53" s="85"/>
+      <c r="F53" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="G53" s="89" t="s">
+        <v>59</v>
+      </c>
       <c r="H53" s="85"/>
     </row>
-    <row r="54" spans="2:8" ht="55.9" customHeight="1" thickBot="1">
-      <c r="C54" s="85"/>
+    <row r="54" spans="2:8" ht="55.95" customHeight="1" thickBot="1">
+      <c r="C54" s="88"/>
       <c r="D54" s="85"/>
-      <c r="E54" s="86"/>
-      <c r="F54" s="86" t="s">
-        <v>79</v>
-      </c>
-      <c r="G54" s="86"/>
+      <c r="E54" s="85"/>
+      <c r="F54" s="89"/>
+      <c r="G54" s="89"/>
       <c r="H54" s="85"/>
     </row>
-    <row r="55" spans="2:8" ht="55.9" customHeight="1" thickBot="1">
-      <c r="C55" s="88"/>
+    <row r="55" spans="2:8" ht="108.6" customHeight="1" thickBot="1">
+      <c r="C55" s="85"/>
       <c r="D55" s="85"/>
-      <c r="E55" s="85"/>
-      <c r="F55" s="89" t="s">
-        <v>81</v>
-      </c>
-      <c r="G55" s="89" t="s">
-        <v>59</v>
-      </c>
+      <c r="E55" s="90" t="s">
+        <v>83</v>
+      </c>
+      <c r="F55" s="91"/>
+      <c r="G55" s="91"/>
       <c r="H55" s="85"/>
     </row>
-    <row r="56" spans="2:8" ht="55.9" customHeight="1" thickBot="1">
-      <c r="C56" s="88"/>
-      <c r="D56" s="85"/>
-      <c r="E56" s="85"/>
-      <c r="F56" s="89"/>
-      <c r="G56" s="89"/>
-      <c r="H56" s="85"/>
-    </row>
-    <row r="57" spans="2:8" ht="108.6" customHeight="1" thickBot="1">
-      <c r="C57" s="85"/>
-      <c r="D57" s="85"/>
-      <c r="E57" s="90" t="s">
-        <v>83</v>
-      </c>
-      <c r="F57" s="91"/>
-      <c r="G57" s="91"/>
-      <c r="H57" s="85"/>
-    </row>
-    <row r="58" spans="2:8" ht="87.6" customHeight="1">
-      <c r="C58" s="74"/>
-      <c r="D58" s="74"/>
-      <c r="E58" s="74"/>
-      <c r="F58" s="75"/>
-      <c r="G58" s="75"/>
-      <c r="H58" s="67"/>
-    </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
-      <c r="E59" s="67"/>
-      <c r="F59" s="67"/>
-      <c r="G59" s="67"/>
-      <c r="H59" s="67"/>
+    <row r="56" spans="2:8" ht="87.6" customHeight="1">
+      <c r="C56" s="74"/>
+      <c r="D56" s="74"/>
+      <c r="E56" s="74"/>
+      <c r="F56" s="75"/>
+      <c r="G56" s="75"/>
+      <c r="H56" s="67"/>
+    </row>
+    <row r="57" spans="2:8" ht="15" customHeight="1">
+      <c r="E57" s="67"/>
+      <c r="F57" s="67"/>
+      <c r="G57" s="67"/>
+      <c r="H57" s="67"/>
+    </row>
+    <row r="73" spans="3:3" ht="15" customHeight="1">
+      <c r="C73" s="64"/>
+    </row>
+    <row r="74" spans="3:3" ht="15" customHeight="1">
+      <c r="C74" s="64"/>
     </row>
     <row r="75" spans="3:3" ht="15" customHeight="1">
       <c r="C75" s="64"/>
@@ -4023,79 +3973,70 @@
     <row r="134" spans="3:3" ht="15" customHeight="1">
       <c r="C134" s="64"/>
     </row>
-    <row r="135" spans="3:3" ht="15" customHeight="1">
-      <c r="C135" s="64"/>
-    </row>
-    <row r="136" spans="3:3" ht="15" customHeight="1">
-      <c r="C136" s="64"/>
-    </row>
   </sheetData>
-  <mergeCells count="95">
+  <mergeCells count="90">
+    <mergeCell ref="F20:F21"/>
     <mergeCell ref="F22:F23"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="H24:H25"/>
     <mergeCell ref="F24:F25"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
     <mergeCell ref="H20:H21"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="G20:G21"/>
     <mergeCell ref="H28:H29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="H32:H33"/>
     <mergeCell ref="F34:F35"/>
     <mergeCell ref="G34:G35"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="G28:G29"/>
     <mergeCell ref="F32:F33"/>
     <mergeCell ref="G32:G33"/>
     <mergeCell ref="F30:F31"/>
-    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="H30:H31"/>
     <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D20:D21"/>
     <mergeCell ref="D22:D23"/>
     <mergeCell ref="D24:D25"/>
     <mergeCell ref="D26:D27"/>
-    <mergeCell ref="D28:D29"/>
     <mergeCell ref="B5:C7"/>
     <mergeCell ref="D5:D7"/>
     <mergeCell ref="D8:D9"/>
-    <mergeCell ref="B12:B13"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D16:D17"/>
     <mergeCell ref="D18:D19"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="D16:D17"/>
     <mergeCell ref="D14:D15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
     <mergeCell ref="D38:D39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="F26:F27"/>
     <mergeCell ref="D36:D37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="D28:D29"/>
     <mergeCell ref="D34:D35"/>
     <mergeCell ref="D32:D33"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
     <mergeCell ref="H40:H41"/>
+    <mergeCell ref="H38:H39"/>
     <mergeCell ref="D4:H4"/>
     <mergeCell ref="H5:H7"/>
     <mergeCell ref="H8:H9"/>
@@ -4107,31 +4048,29 @@
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="D40:D41"/>
     <mergeCell ref="F49:G49"/>
     <mergeCell ref="F48:G48"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="F46:G46"/>
     <mergeCell ref="C49:D49"/>
-    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C47:D47"/>
     <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="G40:G41"/>
     <mergeCell ref="F40:F41"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="F42:F43"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="20" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="F8 F18 F12" formulaRange="1"/>
+    <ignoredError sqref="F8 F16" formulaRange="1"/>
   </ignoredErrors>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -4140,45 +4079,45 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AV51"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:AV50"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="35.75" style="3" customWidth="1"/>
-    <col min="2" max="3" width="11.625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="7.25" style="3" customWidth="1"/>
-    <col min="5" max="13" width="5.75" style="3" customWidth="1"/>
-    <col min="14" max="14" width="20.125" style="3" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="10.75" style="3" customWidth="1"/>
-    <col min="17" max="17" width="15.75" style="3" customWidth="1"/>
-    <col min="18" max="47" width="3.75" style="3" hidden="1" customWidth="1"/>
-    <col min="48" max="16384" width="8.875" style="3"/>
+    <col min="1" max="1" width="35.6640625" style="3" customWidth="1"/>
+    <col min="2" max="3" width="11.5546875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="7.21875" style="3" customWidth="1"/>
+    <col min="5" max="13" width="5.6640625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="20.109375" style="3" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="10.6640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="15.6640625" style="3" customWidth="1"/>
+    <col min="18" max="47" width="3.6640625" style="3" hidden="1" customWidth="1"/>
+    <col min="48" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" ht="49.9" customHeight="1">
+    <row r="1" spans="1:48" ht="49.95" customHeight="1">
       <c r="A1" s="3" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="206" t="s">
+      <c r="B1" s="199" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
-      <c r="G1" s="200"/>
-      <c r="H1" s="200"/>
-      <c r="I1" s="200"/>
-      <c r="J1" s="200"/>
-      <c r="K1" s="200"/>
-      <c r="L1" s="200"/>
-      <c r="M1" s="200"/>
-      <c r="O1" s="207" t="s">
+      <c r="C1" s="193"/>
+      <c r="D1" s="193"/>
+      <c r="E1" s="193"/>
+      <c r="F1" s="193"/>
+      <c r="G1" s="193"/>
+      <c r="H1" s="193"/>
+      <c r="I1" s="193"/>
+      <c r="J1" s="193"/>
+      <c r="K1" s="193"/>
+      <c r="L1" s="193"/>
+      <c r="M1" s="193"/>
+      <c r="O1" s="200" t="s">
         <v>18</v>
       </c>
-      <c r="P1" s="207"/>
-      <c r="Q1" s="207"/>
-    </row>
-    <row r="2" spans="1:48" ht="10.15" customHeight="1">
+      <c r="P1" s="200"/>
+      <c r="Q1" s="200"/>
+    </row>
+    <row r="2" spans="1:48" ht="10.199999999999999" customHeight="1">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -4200,23 +4139,23 @@
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="9"/>
-      <c r="O3" s="207" t="s">
+      <c r="O3" s="200" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="207"/>
-      <c r="Q3" s="207"/>
-    </row>
-    <row r="4" spans="1:48" ht="25.15" customHeight="1">
+      <c r="P3" s="200"/>
+      <c r="Q3" s="200"/>
+    </row>
+    <row r="4" spans="1:48" ht="25.2" customHeight="1">
       <c r="A4" s="63" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="O4" s="207"/>
-      <c r="P4" s="207"/>
-      <c r="Q4" s="207"/>
-    </row>
-    <row r="5" spans="1:48" ht="4.9000000000000004" customHeight="1">
+      <c r="O4" s="200"/>
+      <c r="P4" s="200"/>
+      <c r="Q4" s="200"/>
+    </row>
+    <row r="5" spans="1:48" ht="4.95" customHeight="1">
       <c r="A5" s="63"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -4224,171 +4163,171 @@
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
     </row>
-    <row r="6" spans="1:48" ht="25.15" customHeight="1">
-      <c r="A6" s="208" t="s">
+    <row r="6" spans="1:48" ht="25.2" customHeight="1">
+      <c r="A6" s="201" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="208"/>
-      <c r="C6" s="210" t="s">
+      <c r="B6" s="201"/>
+      <c r="C6" s="203" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="210"/>
-      <c r="E6" s="210"/>
-      <c r="F6" s="210"/>
-      <c r="G6" s="210"/>
-      <c r="H6" s="210"/>
-      <c r="I6" s="210"/>
-      <c r="J6" s="210"/>
-      <c r="K6" s="210"/>
-      <c r="L6" s="210"/>
-      <c r="M6" s="210"/>
-      <c r="N6" s="210"/>
-      <c r="O6" s="210"/>
-      <c r="P6" s="210"/>
-      <c r="Q6" s="210"/>
-    </row>
-    <row r="7" spans="1:48" ht="19.899999999999999" customHeight="1">
-      <c r="A7" s="208"/>
-      <c r="B7" s="208"/>
-      <c r="C7" s="204" t="s">
+      <c r="D6" s="203"/>
+      <c r="E6" s="203"/>
+      <c r="F6" s="203"/>
+      <c r="G6" s="203"/>
+      <c r="H6" s="203"/>
+      <c r="I6" s="203"/>
+      <c r="J6" s="203"/>
+      <c r="K6" s="203"/>
+      <c r="L6" s="203"/>
+      <c r="M6" s="203"/>
+      <c r="N6" s="203"/>
+      <c r="O6" s="203"/>
+      <c r="P6" s="203"/>
+      <c r="Q6" s="203"/>
+    </row>
+    <row r="7" spans="1:48" ht="19.95" customHeight="1">
+      <c r="A7" s="201"/>
+      <c r="B7" s="201"/>
+      <c r="C7" s="197" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="185" t="s">
+      <c r="D7" s="178" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="186"/>
-      <c r="F7" s="186"/>
-      <c r="G7" s="186"/>
-      <c r="H7" s="186"/>
-      <c r="I7" s="186"/>
-      <c r="J7" s="186"/>
-      <c r="K7" s="186"/>
-      <c r="L7" s="186"/>
-      <c r="M7" s="186"/>
-      <c r="N7" s="186"/>
-      <c r="O7" s="186"/>
-      <c r="P7" s="186"/>
-      <c r="Q7" s="187"/>
+      <c r="E7" s="179"/>
+      <c r="F7" s="179"/>
+      <c r="G7" s="179"/>
+      <c r="H7" s="179"/>
+      <c r="I7" s="179"/>
+      <c r="J7" s="179"/>
+      <c r="K7" s="179"/>
+      <c r="L7" s="179"/>
+      <c r="M7" s="179"/>
+      <c r="N7" s="179"/>
+      <c r="O7" s="179"/>
+      <c r="P7" s="179"/>
+      <c r="Q7" s="180"/>
     </row>
     <row r="8" spans="1:48" ht="15" customHeight="1">
-      <c r="A8" s="209"/>
-      <c r="B8" s="208"/>
-      <c r="C8" s="205"/>
-      <c r="D8" s="190" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="190" t="s">
+      <c r="A8" s="202"/>
+      <c r="B8" s="201"/>
+      <c r="C8" s="198"/>
+      <c r="D8" s="183" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="183" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="190" t="s">
+      <c r="F8" s="183" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="190" t="s">
+      <c r="G8" s="183" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="190" t="s">
+      <c r="H8" s="183" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="190" t="s">
+      <c r="I8" s="183" t="s">
         <v>28</v>
       </c>
-      <c r="J8" s="190" t="s">
+      <c r="J8" s="183" t="s">
         <v>29</v>
       </c>
-      <c r="K8" s="190" t="s">
+      <c r="K8" s="183" t="s">
         <v>30</v>
       </c>
-      <c r="L8" s="190" t="s">
+      <c r="L8" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="M8" s="190" t="s">
+      <c r="M8" s="183" t="s">
         <v>32</v>
       </c>
       <c r="N8" s="10"/>
-      <c r="O8" s="190" t="s">
+      <c r="O8" s="183" t="s">
         <v>35</v>
       </c>
-      <c r="P8" s="190" t="s">
+      <c r="P8" s="183" t="s">
         <v>36</v>
       </c>
-      <c r="Q8" s="190" t="s">
+      <c r="Q8" s="183" t="s">
         <v>37</v>
       </c>
-      <c r="R8" s="200" t="s">
+      <c r="R8" s="193" t="s">
         <v>4</v>
       </c>
-      <c r="S8" s="200"/>
-      <c r="T8" s="200"/>
-      <c r="U8" s="200" t="s">
+      <c r="S8" s="193"/>
+      <c r="T8" s="193"/>
+      <c r="U8" s="193" t="s">
         <v>5</v>
       </c>
-      <c r="V8" s="200"/>
-      <c r="W8" s="200"/>
-      <c r="X8" s="200" t="s">
+      <c r="V8" s="193"/>
+      <c r="W8" s="193"/>
+      <c r="X8" s="193" t="s">
         <v>7</v>
       </c>
-      <c r="Y8" s="200"/>
-      <c r="Z8" s="200"/>
-      <c r="AA8" s="200" t="s">
+      <c r="Y8" s="193"/>
+      <c r="Z8" s="193"/>
+      <c r="AA8" s="193" t="s">
         <v>8</v>
       </c>
-      <c r="AB8" s="200"/>
-      <c r="AC8" s="200"/>
-      <c r="AD8" s="200" t="s">
+      <c r="AB8" s="193"/>
+      <c r="AC8" s="193"/>
+      <c r="AD8" s="193" t="s">
         <v>9</v>
       </c>
-      <c r="AE8" s="200"/>
-      <c r="AF8" s="200"/>
-      <c r="AG8" s="200" t="s">
+      <c r="AE8" s="193"/>
+      <c r="AF8" s="193"/>
+      <c r="AG8" s="193" t="s">
         <v>10</v>
       </c>
-      <c r="AH8" s="200"/>
-      <c r="AI8" s="200"/>
-      <c r="AJ8" s="200" t="s">
+      <c r="AH8" s="193"/>
+      <c r="AI8" s="193"/>
+      <c r="AJ8" s="193" t="s">
         <v>11</v>
       </c>
-      <c r="AK8" s="200"/>
-      <c r="AL8" s="200"/>
-      <c r="AM8" s="200" t="s">
+      <c r="AK8" s="193"/>
+      <c r="AL8" s="193"/>
+      <c r="AM8" s="193" t="s">
         <v>12</v>
       </c>
-      <c r="AN8" s="200"/>
-      <c r="AO8" s="200"/>
-      <c r="AP8" s="200" t="s">
+      <c r="AN8" s="193"/>
+      <c r="AO8" s="193"/>
+      <c r="AP8" s="193" t="s">
         <v>13</v>
       </c>
-      <c r="AQ8" s="200"/>
-      <c r="AR8" s="200"/>
-      <c r="AS8" s="200" t="s">
+      <c r="AQ8" s="193"/>
+      <c r="AR8" s="193"/>
+      <c r="AS8" s="193" t="s">
         <v>14</v>
       </c>
-      <c r="AT8" s="200"/>
-      <c r="AU8" s="200"/>
-    </row>
-    <row r="9" spans="1:48" ht="25.15" customHeight="1">
-      <c r="A9" s="113" t="s">
+      <c r="AT8" s="193"/>
+      <c r="AU8" s="193"/>
+    </row>
+    <row r="9" spans="1:48" ht="25.2" customHeight="1">
+      <c r="A9" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B9" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="205"/>
-      <c r="D9" s="191"/>
-      <c r="E9" s="191"/>
-      <c r="F9" s="191"/>
-      <c r="G9" s="191"/>
-      <c r="H9" s="191"/>
-      <c r="I9" s="191"/>
-      <c r="J9" s="191"/>
-      <c r="K9" s="191"/>
-      <c r="L9" s="191"/>
-      <c r="M9" s="191"/>
+      <c r="C9" s="198"/>
+      <c r="D9" s="184"/>
+      <c r="E9" s="184"/>
+      <c r="F9" s="184"/>
+      <c r="G9" s="184"/>
+      <c r="H9" s="184"/>
+      <c r="I9" s="184"/>
+      <c r="J9" s="184"/>
+      <c r="K9" s="184"/>
+      <c r="L9" s="184"/>
+      <c r="M9" s="184"/>
       <c r="N9" s="98" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="191"/>
-      <c r="P9" s="191"/>
-      <c r="Q9" s="191"/>
+      <c r="O9" s="184"/>
+      <c r="P9" s="184"/>
+      <c r="Q9" s="184"/>
       <c r="R9" s="2" t="s">
         <v>2</v>
       </c>
@@ -4480,11 +4419,11 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:48" ht="19.899999999999999" customHeight="1">
-      <c r="A10" s="114" t="s">
+    <row r="10" spans="1:48" ht="19.95" customHeight="1">
+      <c r="A10" s="110" t="s">
         <v>115</v>
       </c>
-      <c r="B10" s="112">
+      <c r="B10" s="109">
         <v>36</v>
       </c>
       <c r="C10" s="83">
@@ -4496,152 +4435,152 @@
         <v>0</v>
       </c>
       <c r="E10" s="83"/>
-      <c r="F10" s="100"/>
-      <c r="G10" s="100"/>
-      <c r="H10" s="100"/>
-      <c r="I10" s="100"/>
-      <c r="J10" s="100"/>
-      <c r="K10" s="100"/>
-      <c r="L10" s="100"/>
-      <c r="M10" s="100"/>
-      <c r="N10" s="100">
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11">
         <f>'มหาชัย-ผลิต'!F8</f>
         <v>0</v>
       </c>
-      <c r="O10" s="100"/>
-      <c r="P10" s="100"/>
-      <c r="Q10" s="100"/>
-      <c r="R10" s="102">
-        <f t="shared" ref="R10:R23" si="0">INT(D10/B10)</f>
-        <v>0</v>
-      </c>
-      <c r="S10" s="103">
-        <f t="shared" ref="S10:S23" si="1">IF(MOD(D10,B10)/B10&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T10" s="104">
-        <f t="shared" ref="T10:T23" si="2">IF(AND(MOD(D10,B10)/B10&lt;=0.5,MOD(D10,B10)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U10" s="102">
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="101">
+        <f t="shared" ref="R10:R22" si="0">INT(D10/B10)</f>
+        <v>0</v>
+      </c>
+      <c r="S10" s="102">
+        <f t="shared" ref="S10:S22" si="1">IF(MOD(D10,B10)/B10&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T10" s="103">
+        <f t="shared" ref="T10:T22" si="2">IF(AND(MOD(D10,B10)/B10&lt;=0.5,MOD(D10,B10)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U10" s="101">
         <f>INT(E10/B10)</f>
         <v>0</v>
       </c>
-      <c r="V10" s="103">
+      <c r="V10" s="102">
         <f>IF(MOD(E10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="W10" s="104">
+      <c r="W10" s="103">
         <f>IF(AND(MOD(E10,B10)/B10&lt;=0.5,MOD(E10,B10)&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X10" s="102">
-        <f t="shared" ref="X10:X24" si="3">INT(F10/B10)</f>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="103">
-        <f t="shared" ref="Y10:Y24" si="4">IF(MOD(F10,B10)/B10&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z10" s="104">
-        <f t="shared" ref="Z10:Z24" si="5">IF(AND(MOD(F10,B10)/B10&lt;=0.5,MOD(F10,B10)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AA10" s="102">
+      <c r="X10" s="101">
+        <f t="shared" ref="X10:X23" si="3">INT(F10/B10)</f>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="102">
+        <f t="shared" ref="Y10:Y23" si="4">IF(MOD(F10,B10)/B10&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="103">
+        <f t="shared" ref="Z10:Z23" si="5">IF(AND(MOD(F10,B10)/B10&lt;=0.5,MOD(F10,B10)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA10" s="101">
         <f>INT(G10/B10)</f>
         <v>0</v>
       </c>
-      <c r="AB10" s="103">
+      <c r="AB10" s="102">
         <f>IF(MOD(G10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AC10" s="104">
+      <c r="AC10" s="103">
         <f>IF(AND(MOD(G10,B10)/B10&lt;=0.5,MOD(G10,B10)&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="AD10" s="102">
+      <c r="AD10" s="101">
         <f>INT(H10/B10)</f>
         <v>0</v>
       </c>
-      <c r="AE10" s="103">
+      <c r="AE10" s="102">
         <f>IF(MOD(H10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AF10" s="104">
+      <c r="AF10" s="103">
         <f>IF(AND(MOD(H10,B10)/B10&lt;=0.5,MOD(H10,B10)&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="AG10" s="102">
+      <c r="AG10" s="101">
         <f>INT(I10/B10)</f>
         <v>0</v>
       </c>
-      <c r="AH10" s="103">
+      <c r="AH10" s="102">
         <f>IF(MOD(I10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AI10" s="104">
+      <c r="AI10" s="103">
         <f>IF(AND(MOD(I10,B10)/B10&lt;=0.5,MOD(I10,B10)&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="AJ10" s="102">
+      <c r="AJ10" s="101">
         <f>INT(J10/B10)</f>
         <v>0</v>
       </c>
-      <c r="AK10" s="103">
+      <c r="AK10" s="102">
         <f>IF(MOD(J10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AL10" s="104">
+      <c r="AL10" s="103">
         <f>IF(AND(MOD(J10,B10)/B10&lt;=0.5,MOD(J10,B10)&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="AM10" s="102">
+      <c r="AM10" s="101">
         <f>INT(K10/B10)</f>
         <v>0</v>
       </c>
-      <c r="AN10" s="103">
+      <c r="AN10" s="102">
         <f>IF(MOD(K10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO10" s="104">
+      <c r="AO10" s="103">
         <f>IF(AND(MOD(K10,B10)/B10&lt;=0.5,MOD(K10,B10)&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="AP10" s="102">
+      <c r="AP10" s="101">
         <f>INT(L10/B10)</f>
         <v>0</v>
       </c>
-      <c r="AQ10" s="103">
+      <c r="AQ10" s="102">
         <f>IF(MOD(L10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AR10" s="104">
+      <c r="AR10" s="103">
         <f>IF(AND(MOD(L10,B10)/B10&lt;=0.5,MOD(L10,B10)&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS10" s="102">
+      <c r="AS10" s="101">
         <f>INT(M10/B10)</f>
         <v>0</v>
       </c>
-      <c r="AT10" s="103">
+      <c r="AT10" s="102">
         <f>IF(MOD(M10,B10)/B10&gt;0.5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AU10" s="104">
+      <c r="AU10" s="103">
         <f>IF(AND(MOD(M10,B10)/B10&lt;=0.5,MOD(M10,B10)&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="AV10" s="100"/>
-    </row>
-    <row r="11" spans="1:48" ht="19.899999999999999" customHeight="1">
-      <c r="A11" s="114" t="s">
+      <c r="AV10" s="11"/>
+    </row>
+    <row r="11" spans="1:48" ht="19.95" customHeight="1">
+      <c r="A11" s="110" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="112">
+      <c r="B11" s="109">
         <v>32</v>
       </c>
       <c r="C11" s="83">
-        <f t="shared" ref="C11:C17" si="6">SUMPRODUCT(ROUNDUP(D11/B11,0))</f>
+        <f t="shared" ref="C11:C16" si="6">SUMPRODUCT(ROUNDUP(D11/B11,0))</f>
         <v>0</v>
       </c>
       <c r="D11" s="83">
@@ -4649,152 +4588,152 @@
         <v>0</v>
       </c>
       <c r="E11" s="83"/>
-      <c r="F11" s="100"/>
-      <c r="G11" s="100"/>
-      <c r="H11" s="100"/>
-      <c r="I11" s="100"/>
-      <c r="J11" s="100"/>
-      <c r="K11" s="100"/>
-      <c r="L11" s="100"/>
-      <c r="M11" s="100"/>
-      <c r="N11" s="100" t="str">
-        <f t="shared" ref="N11:N18" si="7">INT(SUM(D11:M11)/B11) &amp; " full, " &amp; IF(MOD(SUM(D11:M11), B11)/B11 &lt;= 0.5, "1 less than half", IF(MOD(SUM(D11:M11), B11)/B11 &gt; 0.5, "1 more than half", ""))</f>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11" t="str">
+        <f t="shared" ref="N11:N17" si="7">INT(SUM(D11:M11)/B11) &amp; " full, " &amp; IF(MOD(SUM(D11:M11), B11)/B11 &lt;= 0.5, "1 less than half", IF(MOD(SUM(D11:M11), B11)/B11 &gt; 0.5, "1 more than half", ""))</f>
         <v>0 full, 1 less than half</v>
       </c>
-      <c r="O11" s="100"/>
-      <c r="P11" s="100"/>
-      <c r="Q11" s="100"/>
-      <c r="R11" s="102">
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="101">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S11" s="103">
+      <c r="S11" s="102">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T11" s="104">
+      <c r="T11" s="103">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U11" s="102">
-        <f t="shared" ref="U11:U24" si="8">INT(E11/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="V11" s="103">
-        <f t="shared" ref="V11:V24" si="9">IF(MOD(E11,B11)/B11&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="W11" s="104">
-        <f t="shared" ref="W11:W24" si="10">IF(AND(MOD(E11,B11)/B11&lt;=0.5,MOD(E11,B11)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X11" s="102">
+      <c r="U11" s="101">
+        <f t="shared" ref="U11:U23" si="8">INT(E11/B11)</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="102">
+        <f t="shared" ref="V11:V23" si="9">IF(MOD(E11,B11)/B11&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="103">
+        <f t="shared" ref="W11:W23" si="10">IF(AND(MOD(E11,B11)/B11&lt;=0.5,MOD(E11,B11)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X11" s="101">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y11" s="103">
+      <c r="Y11" s="102">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Z11" s="104">
+      <c r="Z11" s="103">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA11" s="102">
-        <f t="shared" ref="AA11:AA24" si="11">INT(G11/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="AB11" s="103">
-        <f t="shared" ref="AB11:AB24" si="12">IF(MOD(G11,B11)/B11&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AC11" s="104">
-        <f t="shared" ref="AC11:AC24" si="13">IF(AND(MOD(G11,B11)/B11&lt;=0.5,MOD(G11,B11)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AD11" s="102">
-        <f t="shared" ref="AD11:AD24" si="14">INT(H11/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="AE11" s="103">
-        <f t="shared" ref="AE11:AE24" si="15">IF(MOD(H11,B11)/B11&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF11" s="104">
-        <f t="shared" ref="AF11:AF24" si="16">IF(AND(MOD(H11,B11)/B11&lt;=0.5,MOD(H11,B11)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AG11" s="102">
-        <f t="shared" ref="AG11:AG24" si="17">INT(I11/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="AH11" s="103">
-        <f t="shared" ref="AH11:AH24" si="18">IF(MOD(I11,B11)/B11&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AI11" s="104">
-        <f t="shared" ref="AI11:AI24" si="19">IF(AND(MOD(I11,B11)/B11&lt;=0.5,MOD(I11,B11)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ11" s="102">
-        <f t="shared" ref="AJ11:AJ24" si="20">INT(J11/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="AK11" s="103">
-        <f t="shared" ref="AK11:AK24" si="21">IF(MOD(J11,B11)/B11&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AL11" s="104">
-        <f t="shared" ref="AL11:AL24" si="22">IF(AND(MOD(J11,B11)/B11&lt;=0.5,MOD(J11,B11)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AM11" s="102">
-        <f t="shared" ref="AM11:AM24" si="23">INT(K11/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="AN11" s="103">
-        <f t="shared" ref="AN11:AN24" si="24">IF(MOD(K11,B11)/B11&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AO11" s="104">
-        <f t="shared" ref="AO11:AO24" si="25">IF(AND(MOD(K11,B11)/B11&lt;=0.5,MOD(K11,B11)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AP11" s="102">
-        <f t="shared" ref="AP11:AP24" si="26">INT(L11/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="103">
-        <f t="shared" ref="AQ11:AQ24" si="27">IF(MOD(L11,B11)/B11&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AR11" s="104">
-        <f t="shared" ref="AR11:AR24" si="28">IF(AND(MOD(L11,B11)/B11&lt;=0.5,MOD(L11,B11)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AS11" s="102">
-        <f t="shared" ref="AS11:AS24" si="29">INT(M11/B11)</f>
-        <v>0</v>
-      </c>
-      <c r="AT11" s="103">
-        <f t="shared" ref="AT11:AT24" si="30">IF(MOD(M11,B11)/B11&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AU11" s="104">
-        <f t="shared" ref="AU11:AU24" si="31">IF(AND(MOD(M11,B11)/B11&lt;=0.5,MOD(M11,B11)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AV11" s="100"/>
-    </row>
-    <row r="12" spans="1:48" ht="19.899999999999999" customHeight="1">
-      <c r="A12" s="114" t="s">
-        <v>127</v>
-      </c>
-      <c r="B12" s="112">
-        <v>36</v>
+      <c r="AA11" s="101">
+        <f t="shared" ref="AA11:AA23" si="11">INT(G11/B11)</f>
+        <v>0</v>
+      </c>
+      <c r="AB11" s="102">
+        <f t="shared" ref="AB11:AB23" si="12">IF(MOD(G11,B11)/B11&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC11" s="103">
+        <f t="shared" ref="AC11:AC23" si="13">IF(AND(MOD(G11,B11)/B11&lt;=0.5,MOD(G11,B11)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD11" s="101">
+        <f t="shared" ref="AD11:AD23" si="14">INT(H11/B11)</f>
+        <v>0</v>
+      </c>
+      <c r="AE11" s="102">
+        <f t="shared" ref="AE11:AE23" si="15">IF(MOD(H11,B11)/B11&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="103">
+        <f t="shared" ref="AF11:AF23" si="16">IF(AND(MOD(H11,B11)/B11&lt;=0.5,MOD(H11,B11)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG11" s="101">
+        <f t="shared" ref="AG11:AG23" si="17">INT(I11/B11)</f>
+        <v>0</v>
+      </c>
+      <c r="AH11" s="102">
+        <f t="shared" ref="AH11:AH23" si="18">IF(MOD(I11,B11)/B11&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI11" s="103">
+        <f t="shared" ref="AI11:AI23" si="19">IF(AND(MOD(I11,B11)/B11&lt;=0.5,MOD(I11,B11)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="101">
+        <f t="shared" ref="AJ11:AJ23" si="20">INT(J11/B11)</f>
+        <v>0</v>
+      </c>
+      <c r="AK11" s="102">
+        <f t="shared" ref="AK11:AK23" si="21">IF(MOD(J11,B11)/B11&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL11" s="103">
+        <f t="shared" ref="AL11:AL23" si="22">IF(AND(MOD(J11,B11)/B11&lt;=0.5,MOD(J11,B11)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM11" s="101">
+        <f t="shared" ref="AM11:AM23" si="23">INT(K11/B11)</f>
+        <v>0</v>
+      </c>
+      <c r="AN11" s="102">
+        <f t="shared" ref="AN11:AN23" si="24">IF(MOD(K11,B11)/B11&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO11" s="103">
+        <f t="shared" ref="AO11:AO23" si="25">IF(AND(MOD(K11,B11)/B11&lt;=0.5,MOD(K11,B11)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP11" s="101">
+        <f t="shared" ref="AP11:AP23" si="26">INT(L11/B11)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="102">
+        <f t="shared" ref="AQ11:AQ23" si="27">IF(MOD(L11,B11)/B11&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR11" s="103">
+        <f t="shared" ref="AR11:AR23" si="28">IF(AND(MOD(L11,B11)/B11&lt;=0.5,MOD(L11,B11)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS11" s="101">
+        <f t="shared" ref="AS11:AS23" si="29">INT(M11/B11)</f>
+        <v>0</v>
+      </c>
+      <c r="AT11" s="102">
+        <f t="shared" ref="AT11:AT23" si="30">IF(MOD(M11,B11)/B11&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU11" s="103">
+        <f t="shared" ref="AU11:AU23" si="31">IF(AND(MOD(M11,B11)/B11&lt;=0.5,MOD(M11,B11)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV11" s="11"/>
+    </row>
+    <row r="12" spans="1:48" ht="19.95" customHeight="1">
+      <c r="A12" s="110" t="s">
+        <v>136</v>
+      </c>
+      <c r="B12" s="109">
+        <v>14</v>
       </c>
       <c r="C12" s="83">
-        <f>SUMPRODUCT(ROUNDUP(D12/B12,0))</f>
+        <f t="shared" ref="C12:C13" si="32">SUMPRODUCT(ROUNDUP(D12/B12,0))</f>
         <v>0</v>
       </c>
       <c r="D12" s="83">
@@ -4802,269 +4741,269 @@
         <v>0</v>
       </c>
       <c r="E12" s="83"/>
-      <c r="F12" s="100"/>
-      <c r="G12" s="100"/>
-      <c r="H12" s="100"/>
-      <c r="I12" s="100"/>
-      <c r="J12" s="100"/>
-      <c r="K12" s="100"/>
-      <c r="L12" s="100"/>
-      <c r="M12" s="100"/>
-      <c r="N12" s="100" t="str">
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="101"/>
+      <c r="S12" s="102"/>
+      <c r="T12" s="103"/>
+      <c r="U12" s="101"/>
+      <c r="V12" s="102"/>
+      <c r="W12" s="103"/>
+      <c r="X12" s="101"/>
+      <c r="Y12" s="102"/>
+      <c r="Z12" s="103"/>
+      <c r="AA12" s="101"/>
+      <c r="AB12" s="102"/>
+      <c r="AC12" s="103"/>
+      <c r="AD12" s="101"/>
+      <c r="AE12" s="102"/>
+      <c r="AF12" s="103"/>
+      <c r="AG12" s="101"/>
+      <c r="AH12" s="102"/>
+      <c r="AI12" s="103"/>
+      <c r="AJ12" s="101"/>
+      <c r="AK12" s="102"/>
+      <c r="AL12" s="103"/>
+      <c r="AM12" s="101"/>
+      <c r="AN12" s="102"/>
+      <c r="AO12" s="103"/>
+      <c r="AP12" s="101"/>
+      <c r="AQ12" s="102"/>
+      <c r="AR12" s="103"/>
+      <c r="AS12" s="101"/>
+      <c r="AT12" s="102"/>
+      <c r="AU12" s="103"/>
+      <c r="AV12" s="11"/>
+    </row>
+    <row r="13" spans="1:48" ht="19.95" customHeight="1">
+      <c r="A13" s="110" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" s="109">
+        <v>14</v>
+      </c>
+      <c r="C13" s="83">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="D13" s="83">
+        <f>'มหาชัย-ผลิต'!E14</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="83"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="101"/>
+      <c r="S13" s="102"/>
+      <c r="T13" s="103"/>
+      <c r="U13" s="101"/>
+      <c r="V13" s="102"/>
+      <c r="W13" s="103"/>
+      <c r="X13" s="101"/>
+      <c r="Y13" s="102"/>
+      <c r="Z13" s="103"/>
+      <c r="AA13" s="101"/>
+      <c r="AB13" s="102"/>
+      <c r="AC13" s="103"/>
+      <c r="AD13" s="101"/>
+      <c r="AE13" s="102"/>
+      <c r="AF13" s="103"/>
+      <c r="AG13" s="101"/>
+      <c r="AH13" s="102"/>
+      <c r="AI13" s="103"/>
+      <c r="AJ13" s="101"/>
+      <c r="AK13" s="102"/>
+      <c r="AL13" s="103"/>
+      <c r="AM13" s="101"/>
+      <c r="AN13" s="102"/>
+      <c r="AO13" s="103"/>
+      <c r="AP13" s="101"/>
+      <c r="AQ13" s="102"/>
+      <c r="AR13" s="103"/>
+      <c r="AS13" s="101"/>
+      <c r="AT13" s="102"/>
+      <c r="AU13" s="103"/>
+      <c r="AV13" s="11"/>
+    </row>
+    <row r="14" spans="1:48" ht="19.95" customHeight="1">
+      <c r="A14" s="110" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="109">
+        <v>32</v>
+      </c>
+      <c r="C14" s="83">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="D14" s="83">
+        <f>'มหาชัย-ผลิต'!E16</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="83"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11" t="str">
         <f t="shared" si="7"/>
         <v>0 full, 1 less than half</v>
       </c>
-      <c r="O12" s="100"/>
-      <c r="P12" s="100"/>
-      <c r="Q12" s="100"/>
-      <c r="R12" s="102">
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="101">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S12" s="103">
+      <c r="S14" s="102">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T12" s="104">
+      <c r="T14" s="103">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U12" s="102">
+      <c r="U14" s="101">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="V12" s="103">
+      <c r="V14" s="102">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="W12" s="104">
+      <c r="W14" s="103">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="X12" s="102">
+      <c r="X14" s="101">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y12" s="103">
+      <c r="Y14" s="102">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Z12" s="104">
+      <c r="Z14" s="103">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA12" s="102">
+      <c r="AA14" s="101">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AB12" s="103">
+      <c r="AB14" s="102">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AC12" s="104">
+      <c r="AC14" s="103">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AD12" s="102">
+      <c r="AD14" s="101">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AE12" s="103">
+      <c r="AE14" s="102">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AF12" s="104">
+      <c r="AF14" s="103">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AG12" s="102">
+      <c r="AG14" s="101">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AH12" s="103">
+      <c r="AH14" s="102">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AI12" s="104">
+      <c r="AI14" s="103">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AJ12" s="102">
+      <c r="AJ14" s="101">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AK12" s="103">
+      <c r="AK14" s="102">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="AL12" s="104">
+      <c r="AL14" s="103">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AM12" s="102">
+      <c r="AM14" s="101">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AN12" s="103">
+      <c r="AN14" s="102">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AO12" s="104">
+      <c r="AO14" s="103">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AP12" s="102">
+      <c r="AP14" s="101">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AQ12" s="103">
+      <c r="AQ14" s="102">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AR12" s="104">
+      <c r="AR14" s="103">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AS12" s="102">
+      <c r="AS14" s="101">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AT12" s="103">
+      <c r="AT14" s="102">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AU12" s="104">
+      <c r="AU14" s="103">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="AV12" s="100"/>
-    </row>
-    <row r="13" spans="1:48" ht="19.899999999999999" customHeight="1">
-      <c r="A13" s="114" t="s">
-        <v>138</v>
-      </c>
-      <c r="B13" s="112">
-        <v>14</v>
-      </c>
-      <c r="C13" s="83">
-        <f t="shared" ref="C13:C14" si="32">SUMPRODUCT(ROUNDUP(D13/B13,0))</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="83">
-        <f>'มหาชัย-ผลิต'!E14</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="83"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="122"/>
-      <c r="K13" s="122"/>
-      <c r="L13" s="122"/>
-      <c r="M13" s="122"/>
-      <c r="N13" s="122"/>
-      <c r="O13" s="122"/>
-      <c r="P13" s="122"/>
-      <c r="Q13" s="122"/>
-      <c r="R13" s="102"/>
-      <c r="S13" s="103"/>
-      <c r="T13" s="104"/>
-      <c r="U13" s="102"/>
-      <c r="V13" s="103"/>
-      <c r="W13" s="104"/>
-      <c r="X13" s="102"/>
-      <c r="Y13" s="103"/>
-      <c r="Z13" s="104"/>
-      <c r="AA13" s="102"/>
-      <c r="AB13" s="103"/>
-      <c r="AC13" s="104"/>
-      <c r="AD13" s="102"/>
-      <c r="AE13" s="103"/>
-      <c r="AF13" s="104"/>
-      <c r="AG13" s="102"/>
-      <c r="AH13" s="103"/>
-      <c r="AI13" s="104"/>
-      <c r="AJ13" s="102"/>
-      <c r="AK13" s="103"/>
-      <c r="AL13" s="104"/>
-      <c r="AM13" s="102"/>
-      <c r="AN13" s="103"/>
-      <c r="AO13" s="104"/>
-      <c r="AP13" s="102"/>
-      <c r="AQ13" s="103"/>
-      <c r="AR13" s="104"/>
-      <c r="AS13" s="102"/>
-      <c r="AT13" s="103"/>
-      <c r="AU13" s="104"/>
-      <c r="AV13" s="122"/>
-    </row>
-    <row r="14" spans="1:48" ht="19.899999999999999" customHeight="1">
-      <c r="A14" s="114" t="s">
-        <v>140</v>
-      </c>
-      <c r="B14" s="112">
-        <v>14</v>
-      </c>
-      <c r="C14" s="83">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="D14" s="83">
-        <f>'มหาชัย-ผลิต'!E16</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="83"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="122"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="122"/>
-      <c r="J14" s="122"/>
-      <c r="K14" s="122"/>
-      <c r="L14" s="122"/>
-      <c r="M14" s="122"/>
-      <c r="N14" s="122"/>
-      <c r="O14" s="122"/>
-      <c r="P14" s="122"/>
-      <c r="Q14" s="122"/>
-      <c r="R14" s="102"/>
-      <c r="S14" s="103"/>
-      <c r="T14" s="104"/>
-      <c r="U14" s="102"/>
-      <c r="V14" s="103"/>
-      <c r="W14" s="104"/>
-      <c r="X14" s="102"/>
-      <c r="Y14" s="103"/>
-      <c r="Z14" s="104"/>
-      <c r="AA14" s="102"/>
-      <c r="AB14" s="103"/>
-      <c r="AC14" s="104"/>
-      <c r="AD14" s="102"/>
-      <c r="AE14" s="103"/>
-      <c r="AF14" s="104"/>
-      <c r="AG14" s="102"/>
-      <c r="AH14" s="103"/>
-      <c r="AI14" s="104"/>
-      <c r="AJ14" s="102"/>
-      <c r="AK14" s="103"/>
-      <c r="AL14" s="104"/>
-      <c r="AM14" s="102"/>
-      <c r="AN14" s="103"/>
-      <c r="AO14" s="104"/>
-      <c r="AP14" s="102"/>
-      <c r="AQ14" s="103"/>
-      <c r="AR14" s="104"/>
-      <c r="AS14" s="102"/>
-      <c r="AT14" s="103"/>
-      <c r="AU14" s="104"/>
-      <c r="AV14" s="122"/>
-    </row>
-    <row r="15" spans="1:48" ht="19.899999999999999" customHeight="1">
-      <c r="A15" s="114" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="112">
-        <v>32</v>
+      <c r="AV14" s="11"/>
+    </row>
+    <row r="15" spans="1:48" ht="19.95" customHeight="1">
+      <c r="A15" s="111" t="s">
+        <v>134</v>
+      </c>
+      <c r="B15" s="109">
+        <v>27</v>
       </c>
       <c r="C15" s="83">
         <f t="shared" si="6"/>
@@ -5075,431 +5014,431 @@
         <v>0</v>
       </c>
       <c r="E15" s="83"/>
-      <c r="F15" s="100"/>
-      <c r="G15" s="100"/>
-      <c r="H15" s="100"/>
-      <c r="I15" s="100"/>
-      <c r="J15" s="100"/>
-      <c r="K15" s="100"/>
-      <c r="L15" s="100"/>
-      <c r="M15" s="100"/>
-      <c r="N15" s="100" t="str">
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="101"/>
+      <c r="S15" s="102"/>
+      <c r="T15" s="103"/>
+      <c r="U15" s="101">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="102">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="103">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="101">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="102">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z15" s="103">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA15" s="101">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB15" s="102">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AC15" s="103">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AD15" s="101">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AE15" s="102">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AG15" s="101">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AH15" s="102">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AI15" s="103">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="101">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AK15" s="102">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AL15" s="103">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AM15" s="101">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN15" s="102">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AO15" s="103">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AP15" s="101">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="102">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AR15" s="103">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AS15" s="101">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AT15" s="102">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AU15" s="103">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AV15" s="11"/>
+    </row>
+    <row r="16" spans="1:48" ht="19.95" customHeight="1">
+      <c r="A16" s="112" t="s">
+        <v>140</v>
+      </c>
+      <c r="B16" s="109">
+        <v>27</v>
+      </c>
+      <c r="C16" s="83">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="D16" s="83">
+        <f>'มหาชัย-ผลิต'!E20</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="83"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="101"/>
+      <c r="S16" s="102"/>
+      <c r="T16" s="103"/>
+      <c r="U16" s="101">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="102">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="103">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="101">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="102">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="103">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA16" s="101">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB16" s="102">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AC16" s="103">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AD16" s="101">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AE16" s="102">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AG16" s="101">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AH16" s="102">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AI16" s="103">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="101">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AK16" s="102">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AL16" s="103">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AM16" s="101">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN16" s="102">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AO16" s="103">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AP16" s="101">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="102">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AR16" s="103">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AS16" s="101">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AT16" s="102">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AU16" s="103">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AV16" s="11"/>
+    </row>
+    <row r="17" spans="1:48" ht="19.95" customHeight="1">
+      <c r="A17" s="113" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="109">
+        <v>36</v>
+      </c>
+      <c r="C17" s="83">
+        <f>SUMPRODUCT(ROUNDUP(D17/B17,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="83">
+        <f>'มหาชัย-ผลิต'!E22</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="83"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11" t="str">
         <f t="shared" si="7"/>
         <v>0 full, 1 less than half</v>
       </c>
-      <c r="O15" s="100"/>
-      <c r="P15" s="100"/>
-      <c r="Q15" s="100"/>
-      <c r="R15" s="102">
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="101">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S15" s="103">
+      <c r="S17" s="102">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T15" s="104">
+      <c r="T17" s="103">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U15" s="102">
+      <c r="U17" s="101">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="V15" s="103">
+      <c r="V17" s="102">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="W15" s="104">
+      <c r="W17" s="103">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="X15" s="102">
+      <c r="X17" s="101">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y15" s="103">
+      <c r="Y17" s="102">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Z15" s="104">
+      <c r="Z17" s="103">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA15" s="102">
+      <c r="AA17" s="101">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AB15" s="103">
+      <c r="AB17" s="102">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AC15" s="104">
+      <c r="AC17" s="103">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AD15" s="102">
+      <c r="AD17" s="101">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AE15" s="103">
+      <c r="AE17" s="102">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AF15" s="104">
+      <c r="AF17" s="103">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AG15" s="102">
+      <c r="AG17" s="101">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AH15" s="103">
+      <c r="AH17" s="102">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AI15" s="104">
+      <c r="AI17" s="103">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AJ15" s="102">
+      <c r="AJ17" s="101">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AK15" s="103">
+      <c r="AK17" s="102">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="AL15" s="104">
+      <c r="AL17" s="103">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AM15" s="102">
+      <c r="AM17" s="101">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AN15" s="103">
+      <c r="AN17" s="102">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AO15" s="104">
+      <c r="AO17" s="103">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AP15" s="102">
+      <c r="AP17" s="101">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AQ15" s="103">
+      <c r="AQ17" s="102">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AR15" s="104">
+      <c r="AR17" s="103">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AS15" s="102">
+      <c r="AS17" s="101">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AT15" s="103">
+      <c r="AT17" s="102">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AU15" s="104">
+      <c r="AU17" s="103">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="AV15" s="100"/>
-    </row>
-    <row r="16" spans="1:48" ht="19.899999999999999" customHeight="1">
-      <c r="A16" s="115" t="s">
-        <v>136</v>
-      </c>
-      <c r="B16" s="112">
-        <v>27</v>
-      </c>
-      <c r="C16" s="83">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="D16" s="83">
-        <f>'มหาชัย-ผลิต'!E20</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="83"/>
-      <c r="F16" s="111"/>
-      <c r="G16" s="111"/>
-      <c r="H16" s="111"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="111"/>
-      <c r="K16" s="111"/>
-      <c r="L16" s="111"/>
-      <c r="M16" s="111"/>
-      <c r="N16" s="111"/>
-      <c r="O16" s="111"/>
-      <c r="P16" s="111"/>
-      <c r="Q16" s="111"/>
-      <c r="R16" s="102"/>
-      <c r="S16" s="103"/>
-      <c r="T16" s="104"/>
-      <c r="U16" s="102">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="103">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="W16" s="104">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X16" s="102">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="103">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Z16" s="104">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AA16" s="102">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AB16" s="103">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AC16" s="104">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AD16" s="102">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AE16" s="103">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AF16" s="104">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AG16" s="102">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AH16" s="103">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AI16" s="104">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AJ16" s="102">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AK16" s="103">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AL16" s="104">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AM16" s="102">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AN16" s="103">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AO16" s="104">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AP16" s="102">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AQ16" s="103">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AR16" s="104">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AS16" s="102">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AT16" s="103">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AU16" s="104">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="AV16" s="111"/>
-    </row>
-    <row r="17" spans="1:48" ht="19.899999999999999" customHeight="1">
-      <c r="A17" s="116" t="s">
-        <v>142</v>
-      </c>
-      <c r="B17" s="112">
-        <v>27</v>
-      </c>
-      <c r="C17" s="83">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="D17" s="83">
-        <f>'มหาชัย-ผลิต'!E22</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="83"/>
-      <c r="F17" s="100"/>
-      <c r="G17" s="100"/>
-      <c r="H17" s="100"/>
-      <c r="I17" s="100"/>
-      <c r="J17" s="100"/>
-      <c r="K17" s="100"/>
-      <c r="L17" s="100"/>
-      <c r="M17" s="100"/>
-      <c r="N17" s="100"/>
-      <c r="O17" s="100"/>
-      <c r="P17" s="100"/>
-      <c r="Q17" s="100"/>
-      <c r="R17" s="102"/>
-      <c r="S17" s="103"/>
-      <c r="T17" s="104"/>
-      <c r="U17" s="102">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="103">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="W17" s="104">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X17" s="102">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Y17" s="103">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Z17" s="104">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AA17" s="102">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AB17" s="103">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AC17" s="104">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AD17" s="102">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AE17" s="103">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AF17" s="104">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AG17" s="102">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AH17" s="103">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AI17" s="104">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AJ17" s="102">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AK17" s="103">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AL17" s="104">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AM17" s="102">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AN17" s="103">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AO17" s="104">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AP17" s="102">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AQ17" s="103">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AR17" s="104">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AS17" s="102">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AT17" s="103">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AU17" s="104">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="AV17" s="100"/>
-    </row>
-    <row r="18" spans="1:48" ht="19.899999999999999" customHeight="1">
-      <c r="A18" s="117" t="s">
-        <v>63</v>
-      </c>
-      <c r="B18" s="112">
-        <v>36</v>
+      <c r="AV17" s="11"/>
+    </row>
+    <row r="18" spans="1:48" ht="19.95" customHeight="1">
+      <c r="A18" s="110" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" s="109">
+        <v>20</v>
       </c>
       <c r="C18" s="83">
         <f>SUMPRODUCT(ROUNDUP(D18/B18,0))</f>
@@ -5510,149 +5449,149 @@
         <v>0</v>
       </c>
       <c r="E18" s="83"/>
-      <c r="F18" s="100"/>
-      <c r="G18" s="100"/>
-      <c r="H18" s="100"/>
-      <c r="I18" s="100"/>
-      <c r="J18" s="100"/>
-      <c r="K18" s="100"/>
-      <c r="L18" s="100"/>
-      <c r="M18" s="100"/>
-      <c r="N18" s="100" t="str">
-        <f t="shared" si="7"/>
-        <v>0 full, 1 less than half</v>
-      </c>
-      <c r="O18" s="100"/>
-      <c r="P18" s="100"/>
-      <c r="Q18" s="100"/>
-      <c r="R18" s="102">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S18" s="103">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T18" s="104">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="U18" s="102">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V18" s="103">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="W18" s="104">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X18" s="102">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Y18" s="103">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Z18" s="104">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AA18" s="102">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AB18" s="103">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AC18" s="104">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AD18" s="102">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AE18" s="103">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AF18" s="104">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AG18" s="102">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AH18" s="103">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AI18" s="104">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AJ18" s="102">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AK18" s="103">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AL18" s="104">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AM18" s="102">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AN18" s="103">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AO18" s="104">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AP18" s="102">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AQ18" s="103">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AR18" s="104">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AS18" s="102">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AT18" s="103">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AU18" s="104">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="AV18" s="100"/>
-    </row>
-    <row r="19" spans="1:48" ht="19.899999999999999" customHeight="1">
-      <c r="A19" s="114" t="s">
-        <v>114</v>
-      </c>
-      <c r="B19" s="112">
-        <v>20</v>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11" t="e">
+        <f>'มหาชัย-ผลิต'!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="O18" s="11"/>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="101">
+        <f t="shared" ref="R18" si="33">INT(D18/B18)</f>
+        <v>0</v>
+      </c>
+      <c r="S18" s="102">
+        <f t="shared" ref="S18" si="34">IF(MOD(D18,B18)/B18&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T18" s="103">
+        <f t="shared" ref="T18" si="35">IF(AND(MOD(D18,B18)/B18&lt;=0.5,MOD(D18,B18)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U18" s="101">
+        <f t="shared" ref="U18:U20" si="36">INT(E18/B18)</f>
+        <v>0</v>
+      </c>
+      <c r="V18" s="102">
+        <f t="shared" ref="V18:V20" si="37">IF(MOD(E18,B18)/B18&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W18" s="103">
+        <f t="shared" ref="W18:W20" si="38">IF(AND(MOD(E18,B18)/B18&lt;=0.5,MOD(E18,B18)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X18" s="101">
+        <f t="shared" ref="X18:X20" si="39">INT(F18/B18)</f>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="102">
+        <f t="shared" ref="Y18:Y20" si="40">IF(MOD(F18,B18)/B18&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z18" s="103">
+        <f t="shared" ref="Z18:Z20" si="41">IF(AND(MOD(F18,B18)/B18&lt;=0.5,MOD(F18,B18)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA18" s="101">
+        <f t="shared" ref="AA18:AA20" si="42">INT(G18/B18)</f>
+        <v>0</v>
+      </c>
+      <c r="AB18" s="102">
+        <f t="shared" ref="AB18:AB20" si="43">IF(MOD(G18,B18)/B18&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC18" s="103">
+        <f t="shared" ref="AC18:AC20" si="44">IF(AND(MOD(G18,B18)/B18&lt;=0.5,MOD(G18,B18)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD18" s="101">
+        <f t="shared" ref="AD18:AD20" si="45">INT(H18/B18)</f>
+        <v>0</v>
+      </c>
+      <c r="AE18" s="102">
+        <f t="shared" ref="AE18:AE20" si="46">IF(MOD(H18,B18)/B18&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="103">
+        <f t="shared" ref="AF18:AF20" si="47">IF(AND(MOD(H18,B18)/B18&lt;=0.5,MOD(H18,B18)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG18" s="101">
+        <f t="shared" ref="AG18:AG20" si="48">INT(I18/B18)</f>
+        <v>0</v>
+      </c>
+      <c r="AH18" s="102">
+        <f t="shared" ref="AH18:AH20" si="49">IF(MOD(I18,B18)/B18&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI18" s="103">
+        <f t="shared" ref="AI18:AI20" si="50">IF(AND(MOD(I18,B18)/B18&lt;=0.5,MOD(I18,B18)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="101">
+        <f t="shared" ref="AJ18:AJ20" si="51">INT(J18/B18)</f>
+        <v>0</v>
+      </c>
+      <c r="AK18" s="102">
+        <f t="shared" ref="AK18:AK20" si="52">IF(MOD(J18,B18)/B18&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL18" s="103">
+        <f t="shared" ref="AL18:AL20" si="53">IF(AND(MOD(J18,B18)/B18&lt;=0.5,MOD(J18,B18)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM18" s="101">
+        <f t="shared" ref="AM18:AM20" si="54">INT(K18/B18)</f>
+        <v>0</v>
+      </c>
+      <c r="AN18" s="102">
+        <f t="shared" ref="AN18:AN20" si="55">IF(MOD(K18,B18)/B18&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO18" s="103">
+        <f t="shared" ref="AO18:AO20" si="56">IF(AND(MOD(K18,B18)/B18&lt;=0.5,MOD(K18,B18)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP18" s="101">
+        <f t="shared" ref="AP18:AP20" si="57">INT(L18/B18)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="102">
+        <f t="shared" ref="AQ18:AQ20" si="58">IF(MOD(L18,B18)/B18&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR18" s="103">
+        <f t="shared" ref="AR18:AR20" si="59">IF(AND(MOD(L18,B18)/B18&lt;=0.5,MOD(L18,B18)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS18" s="101">
+        <f t="shared" ref="AS18:AS20" si="60">INT(M18/B18)</f>
+        <v>0</v>
+      </c>
+      <c r="AT18" s="102">
+        <f t="shared" ref="AT18:AT20" si="61">IF(MOD(M18,B18)/B18&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU18" s="103">
+        <f t="shared" ref="AU18:AU20" si="62">IF(AND(MOD(M18,B18)/B18&lt;=0.5,MOD(M18,B18)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV18" s="11"/>
+    </row>
+    <row r="19" spans="1:48" ht="19.95" customHeight="1">
+      <c r="A19" s="113" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" s="109">
+        <v>15</v>
       </c>
       <c r="C19" s="83">
         <f>SUMPRODUCT(ROUNDUP(D19/B19,0))</f>
@@ -5663,575 +5602,575 @@
         <v>0</v>
       </c>
       <c r="E19" s="83"/>
-      <c r="F19" s="100"/>
-      <c r="G19" s="100"/>
-      <c r="H19" s="100"/>
-      <c r="I19" s="100"/>
-      <c r="J19" s="100"/>
-      <c r="K19" s="100"/>
-      <c r="L19" s="100"/>
-      <c r="M19" s="100"/>
-      <c r="N19" s="100" t="e">
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="101"/>
+      <c r="S19" s="102"/>
+      <c r="T19" s="103"/>
+      <c r="U19" s="101">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="102">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="103">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="101">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="102">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="103">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="AA19" s="101">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB19" s="102">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AC19" s="103">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD19" s="101">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="AE19" s="102">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="103">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="AG19" s="101">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="AH19" s="102">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="AI19" s="103">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="101">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="AK19" s="102">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="AL19" s="103">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="AM19" s="101">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="AN19" s="102">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="AO19" s="103">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="AP19" s="101">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="AQ19" s="102">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="AR19" s="103">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="AS19" s="101">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="AT19" s="102">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="AU19" s="103">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="AV19" s="11"/>
+    </row>
+    <row r="20" spans="1:48" ht="19.95" customHeight="1">
+      <c r="A20" s="113" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="109">
+        <v>45</v>
+      </c>
+      <c r="C20" s="83">
+        <f t="shared" ref="C20" si="63">SUMPRODUCT(ROUNDUP(D20/B20,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="83">
+        <f>'มหาชัย-ผลิต'!E28</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="83"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="11"/>
+      <c r="P20" s="11"/>
+      <c r="Q20" s="11"/>
+      <c r="R20" s="101"/>
+      <c r="S20" s="102"/>
+      <c r="T20" s="103"/>
+      <c r="U20" s="101">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="102">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="103">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="X20" s="101">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="102">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z20" s="103">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="AA20" s="101">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB20" s="102">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AC20" s="103">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD20" s="101">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="AE20" s="102">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="103">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="AG20" s="101">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="AH20" s="102">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="AI20" s="103">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="101">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="AK20" s="102">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="AL20" s="103">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="AM20" s="101">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="AN20" s="102">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="AO20" s="103">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="AP20" s="101">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="102">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="AR20" s="103">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="AS20" s="101">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="AT20" s="102">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="AU20" s="103">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="AV20" s="11"/>
+    </row>
+    <row r="21" spans="1:48" ht="19.95" customHeight="1">
+      <c r="A21" s="113" t="s">
+        <v>132</v>
+      </c>
+      <c r="B21" s="109">
+        <v>15</v>
+      </c>
+      <c r="C21" s="83">
+        <f t="shared" ref="C21" si="64">SUMPRODUCT(ROUNDUP(D21/B21,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="83">
+        <f>'มหาชัย-ผลิต'!E30</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="83"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11"/>
+      <c r="R21" s="101"/>
+      <c r="S21" s="102"/>
+      <c r="T21" s="103"/>
+      <c r="U21" s="101">
+        <f t="shared" ref="U21" si="65">INT(E21/B21)</f>
+        <v>0</v>
+      </c>
+      <c r="V21" s="102">
+        <f t="shared" ref="V21" si="66">IF(MOD(E21,B21)/B21&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W21" s="103">
+        <f t="shared" ref="W21" si="67">IF(AND(MOD(E21,B21)/B21&lt;=0.5,MOD(E21,B21)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X21" s="101">
+        <f t="shared" ref="X21" si="68">INT(F21/B21)</f>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="102">
+        <f t="shared" ref="Y21" si="69">IF(MOD(F21,B21)/B21&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z21" s="103">
+        <f t="shared" ref="Z21" si="70">IF(AND(MOD(F21,B21)/B21&lt;=0.5,MOD(F21,B21)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA21" s="101">
+        <f t="shared" ref="AA21" si="71">INT(G21/B21)</f>
+        <v>0</v>
+      </c>
+      <c r="AB21" s="102">
+        <f t="shared" ref="AB21" si="72">IF(MOD(G21,B21)/B21&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC21" s="103">
+        <f t="shared" ref="AC21" si="73">IF(AND(MOD(G21,B21)/B21&lt;=0.5,MOD(G21,B21)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD21" s="101">
+        <f t="shared" ref="AD21" si="74">INT(H21/B21)</f>
+        <v>0</v>
+      </c>
+      <c r="AE21" s="102">
+        <f t="shared" ref="AE21" si="75">IF(MOD(H21,B21)/B21&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="103">
+        <f t="shared" ref="AF21" si="76">IF(AND(MOD(H21,B21)/B21&lt;=0.5,MOD(H21,B21)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG21" s="101">
+        <f t="shared" ref="AG21" si="77">INT(I21/B21)</f>
+        <v>0</v>
+      </c>
+      <c r="AH21" s="102">
+        <f t="shared" ref="AH21" si="78">IF(MOD(I21,B21)/B21&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI21" s="103">
+        <f t="shared" ref="AI21" si="79">IF(AND(MOD(I21,B21)/B21&lt;=0.5,MOD(I21,B21)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="101">
+        <f t="shared" ref="AJ21" si="80">INT(J21/B21)</f>
+        <v>0</v>
+      </c>
+      <c r="AK21" s="102">
+        <f t="shared" ref="AK21" si="81">IF(MOD(J21,B21)/B21&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL21" s="103">
+        <f t="shared" ref="AL21" si="82">IF(AND(MOD(J21,B21)/B21&lt;=0.5,MOD(J21,B21)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM21" s="101">
+        <f t="shared" ref="AM21" si="83">INT(K21/B21)</f>
+        <v>0</v>
+      </c>
+      <c r="AN21" s="102">
+        <f t="shared" ref="AN21" si="84">IF(MOD(K21,B21)/B21&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO21" s="103">
+        <f t="shared" ref="AO21" si="85">IF(AND(MOD(K21,B21)/B21&lt;=0.5,MOD(K21,B21)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP21" s="101">
+        <f t="shared" ref="AP21" si="86">INT(L21/B21)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ21" s="102">
+        <f t="shared" ref="AQ21" si="87">IF(MOD(L21,B21)/B21&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR21" s="103">
+        <f t="shared" ref="AR21" si="88">IF(AND(MOD(L21,B21)/B21&lt;=0.5,MOD(L21,B21)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS21" s="101">
+        <f t="shared" ref="AS21" si="89">INT(M21/B21)</f>
+        <v>0</v>
+      </c>
+      <c r="AT21" s="102">
+        <f t="shared" ref="AT21" si="90">IF(MOD(M21,B21)/B21&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU21" s="103">
+        <f t="shared" ref="AU21" si="91">IF(AND(MOD(M21,B21)/B21&lt;=0.5,MOD(M21,B21)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV21" s="11"/>
+    </row>
+    <row r="22" spans="1:48" ht="19.95" customHeight="1">
+      <c r="A22" s="113" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="109">
+        <v>15</v>
+      </c>
+      <c r="C22" s="83">
+        <f t="shared" ref="C22:C23" si="92">SUMPRODUCT(ROUNDUP(D22/B22,0))</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="83">
+        <f>'มหาชัย-ผลิต'!E32</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="83"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11" t="e">
         <f>'มหาชัย-ผลิต'!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="O19" s="100"/>
-      <c r="P19" s="100"/>
-      <c r="Q19" s="100"/>
-      <c r="R19" s="102">
-        <f t="shared" ref="R19" si="33">INT(D19/B19)</f>
-        <v>0</v>
-      </c>
-      <c r="S19" s="103">
-        <f t="shared" ref="S19" si="34">IF(MOD(D19,B19)/B19&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T19" s="104">
-        <f t="shared" ref="T19" si="35">IF(AND(MOD(D19,B19)/B19&lt;=0.5,MOD(D19,B19)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U19" s="102">
-        <f t="shared" ref="U19:U21" si="36">INT(E19/B19)</f>
-        <v>0</v>
-      </c>
-      <c r="V19" s="103">
-        <f t="shared" ref="V19:V21" si="37">IF(MOD(E19,B19)/B19&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="W19" s="104">
-        <f t="shared" ref="W19:W21" si="38">IF(AND(MOD(E19,B19)/B19&lt;=0.5,MOD(E19,B19)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X19" s="102">
-        <f t="shared" ref="X19:X21" si="39">INT(F19/B19)</f>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="103">
-        <f t="shared" ref="Y19:Y21" si="40">IF(MOD(F19,B19)/B19&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z19" s="104">
-        <f t="shared" ref="Z19:Z21" si="41">IF(AND(MOD(F19,B19)/B19&lt;=0.5,MOD(F19,B19)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AA19" s="102">
-        <f t="shared" ref="AA19:AA21" si="42">INT(G19/B19)</f>
-        <v>0</v>
-      </c>
-      <c r="AB19" s="103">
-        <f t="shared" ref="AB19:AB21" si="43">IF(MOD(G19,B19)/B19&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AC19" s="104">
-        <f t="shared" ref="AC19:AC21" si="44">IF(AND(MOD(G19,B19)/B19&lt;=0.5,MOD(G19,B19)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AD19" s="102">
-        <f t="shared" ref="AD19:AD21" si="45">INT(H19/B19)</f>
-        <v>0</v>
-      </c>
-      <c r="AE19" s="103">
-        <f t="shared" ref="AE19:AE21" si="46">IF(MOD(H19,B19)/B19&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF19" s="104">
-        <f t="shared" ref="AF19:AF21" si="47">IF(AND(MOD(H19,B19)/B19&lt;=0.5,MOD(H19,B19)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AG19" s="102">
-        <f t="shared" ref="AG19:AG21" si="48">INT(I19/B19)</f>
-        <v>0</v>
-      </c>
-      <c r="AH19" s="103">
-        <f t="shared" ref="AH19:AH21" si="49">IF(MOD(I19,B19)/B19&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AI19" s="104">
-        <f t="shared" ref="AI19:AI21" si="50">IF(AND(MOD(I19,B19)/B19&lt;=0.5,MOD(I19,B19)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ19" s="102">
-        <f t="shared" ref="AJ19:AJ21" si="51">INT(J19/B19)</f>
-        <v>0</v>
-      </c>
-      <c r="AK19" s="103">
-        <f t="shared" ref="AK19:AK21" si="52">IF(MOD(J19,B19)/B19&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AL19" s="104">
-        <f t="shared" ref="AL19:AL21" si="53">IF(AND(MOD(J19,B19)/B19&lt;=0.5,MOD(J19,B19)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AM19" s="102">
-        <f t="shared" ref="AM19:AM21" si="54">INT(K19/B19)</f>
-        <v>0</v>
-      </c>
-      <c r="AN19" s="103">
-        <f t="shared" ref="AN19:AN21" si="55">IF(MOD(K19,B19)/B19&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AO19" s="104">
-        <f t="shared" ref="AO19:AO21" si="56">IF(AND(MOD(K19,B19)/B19&lt;=0.5,MOD(K19,B19)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AP19" s="102">
-        <f t="shared" ref="AP19:AP21" si="57">INT(L19/B19)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ19" s="103">
-        <f t="shared" ref="AQ19:AQ21" si="58">IF(MOD(L19,B19)/B19&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AR19" s="104">
-        <f t="shared" ref="AR19:AR21" si="59">IF(AND(MOD(L19,B19)/B19&lt;=0.5,MOD(L19,B19)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AS19" s="102">
-        <f t="shared" ref="AS19:AS21" si="60">INT(M19/B19)</f>
-        <v>0</v>
-      </c>
-      <c r="AT19" s="103">
-        <f t="shared" ref="AT19:AT21" si="61">IF(MOD(M19,B19)/B19&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AU19" s="104">
-        <f t="shared" ref="AU19:AU21" si="62">IF(AND(MOD(M19,B19)/B19&lt;=0.5,MOD(M19,B19)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AV19" s="100"/>
-    </row>
-    <row r="20" spans="1:48" ht="19.899999999999999" customHeight="1">
-      <c r="A20" s="117" t="s">
-        <v>131</v>
-      </c>
-      <c r="B20" s="112">
-        <v>15</v>
-      </c>
-      <c r="C20" s="83">
-        <f>SUMPRODUCT(ROUNDUP(D20/B20,0))</f>
-        <v>0</v>
-      </c>
-      <c r="D20" s="83">
-        <f>'มหาชัย-ผลิต'!E28</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="83"/>
-      <c r="F20" s="100"/>
-      <c r="G20" s="100"/>
-      <c r="H20" s="100"/>
-      <c r="I20" s="100"/>
-      <c r="J20" s="100"/>
-      <c r="K20" s="100"/>
-      <c r="L20" s="100"/>
-      <c r="M20" s="100"/>
-      <c r="N20" s="100"/>
-      <c r="O20" s="100"/>
-      <c r="P20" s="100"/>
-      <c r="Q20" s="100"/>
-      <c r="R20" s="102"/>
-      <c r="S20" s="103"/>
-      <c r="T20" s="104"/>
-      <c r="U20" s="102">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="V20" s="103">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="W20" s="104">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="X20" s="102">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="Y20" s="103">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="Z20" s="104">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AA20" s="102">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AB20" s="103">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="AC20" s="104">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="AD20" s="102">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="AE20" s="103">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="AF20" s="104">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="AG20" s="102">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="AH20" s="103">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="AI20" s="104">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="AJ20" s="102">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="AK20" s="103">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="AL20" s="104">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="AM20" s="102">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="AN20" s="103">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="AO20" s="104">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="AP20" s="102">
-        <f t="shared" si="57"/>
-        <v>0</v>
-      </c>
-      <c r="AQ20" s="103">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="AR20" s="104">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="AS20" s="102">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
-      <c r="AT20" s="103">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="AU20" s="104">
-        <f t="shared" si="62"/>
-        <v>0</v>
-      </c>
-      <c r="AV20" s="100"/>
-    </row>
-    <row r="21" spans="1:48" ht="19.899999999999999" customHeight="1">
-      <c r="A21" s="117" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" s="112">
-        <v>45</v>
-      </c>
-      <c r="C21" s="83">
-        <f t="shared" ref="C21" si="63">SUMPRODUCT(ROUNDUP(D21/B21,0))</f>
-        <v>0</v>
-      </c>
-      <c r="D21" s="83">
-        <f>'มหาชัย-ผลิต'!E30</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="83"/>
-      <c r="F21" s="100"/>
-      <c r="G21" s="100"/>
-      <c r="H21" s="100"/>
-      <c r="I21" s="100"/>
-      <c r="J21" s="100"/>
-      <c r="K21" s="100"/>
-      <c r="L21" s="100"/>
-      <c r="M21" s="100"/>
-      <c r="N21" s="100"/>
-      <c r="O21" s="100"/>
-      <c r="P21" s="100"/>
-      <c r="Q21" s="100"/>
-      <c r="R21" s="102"/>
-      <c r="S21" s="103"/>
-      <c r="T21" s="104"/>
-      <c r="U21" s="102">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="V21" s="103">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="W21" s="104">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="X21" s="102">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="Y21" s="103">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="Z21" s="104">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="AA21" s="102">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AB21" s="103">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="AC21" s="104">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="AD21" s="102">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="AE21" s="103">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="AF21" s="104">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="AG21" s="102">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="AH21" s="103">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="AI21" s="104">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="AJ21" s="102">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="AK21" s="103">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="AL21" s="104">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="AM21" s="102">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="AN21" s="103">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="AO21" s="104">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="AP21" s="102">
-        <f t="shared" si="57"/>
-        <v>0</v>
-      </c>
-      <c r="AQ21" s="103">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="AR21" s="104">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="AS21" s="102">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
-      <c r="AT21" s="103">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="AU21" s="104">
-        <f t="shared" si="62"/>
-        <v>0</v>
-      </c>
-      <c r="AV21" s="100"/>
-    </row>
-    <row r="22" spans="1:48" ht="19.899999999999999" customHeight="1">
-      <c r="A22" s="117" t="s">
-        <v>134</v>
-      </c>
-      <c r="B22" s="112">
-        <v>15</v>
-      </c>
-      <c r="C22" s="83">
-        <f t="shared" ref="C22" si="64">SUMPRODUCT(ROUNDUP(D22/B22,0))</f>
-        <v>0</v>
-      </c>
-      <c r="D22" s="83">
-        <f>'มหาชัย-ผลิต'!E32</f>
-        <v>0</v>
-      </c>
-      <c r="E22" s="83"/>
-      <c r="F22" s="105"/>
-      <c r="G22" s="105"/>
-      <c r="H22" s="105"/>
-      <c r="I22" s="105"/>
-      <c r="J22" s="105"/>
-      <c r="K22" s="105"/>
-      <c r="L22" s="105"/>
-      <c r="M22" s="105"/>
-      <c r="N22" s="105"/>
-      <c r="O22" s="105"/>
-      <c r="P22" s="105"/>
-      <c r="Q22" s="105"/>
-      <c r="R22" s="102"/>
-      <c r="S22" s="103"/>
-      <c r="T22" s="104"/>
-      <c r="U22" s="102">
-        <f t="shared" ref="U22" si="65">INT(E22/B22)</f>
-        <v>0</v>
-      </c>
-      <c r="V22" s="103">
-        <f t="shared" ref="V22" si="66">IF(MOD(E22,B22)/B22&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="W22" s="104">
-        <f t="shared" ref="W22" si="67">IF(AND(MOD(E22,B22)/B22&lt;=0.5,MOD(E22,B22)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X22" s="102">
-        <f t="shared" ref="X22" si="68">INT(F22/B22)</f>
-        <v>0</v>
-      </c>
-      <c r="Y22" s="103">
-        <f t="shared" ref="Y22" si="69">IF(MOD(F22,B22)/B22&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z22" s="104">
-        <f t="shared" ref="Z22" si="70">IF(AND(MOD(F22,B22)/B22&lt;=0.5,MOD(F22,B22)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AA22" s="102">
-        <f t="shared" ref="AA22" si="71">INT(G22/B22)</f>
-        <v>0</v>
-      </c>
-      <c r="AB22" s="103">
-        <f t="shared" ref="AB22" si="72">IF(MOD(G22,B22)/B22&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AC22" s="104">
-        <f t="shared" ref="AC22" si="73">IF(AND(MOD(G22,B22)/B22&lt;=0.5,MOD(G22,B22)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AD22" s="102">
-        <f t="shared" ref="AD22" si="74">INT(H22/B22)</f>
-        <v>0</v>
-      </c>
-      <c r="AE22" s="103">
-        <f t="shared" ref="AE22" si="75">IF(MOD(H22,B22)/B22&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF22" s="104">
-        <f t="shared" ref="AF22" si="76">IF(AND(MOD(H22,B22)/B22&lt;=0.5,MOD(H22,B22)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AG22" s="102">
-        <f t="shared" ref="AG22" si="77">INT(I22/B22)</f>
-        <v>0</v>
-      </c>
-      <c r="AH22" s="103">
-        <f t="shared" ref="AH22" si="78">IF(MOD(I22,B22)/B22&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AI22" s="104">
-        <f t="shared" ref="AI22" si="79">IF(AND(MOD(I22,B22)/B22&lt;=0.5,MOD(I22,B22)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ22" s="102">
-        <f t="shared" ref="AJ22" si="80">INT(J22/B22)</f>
-        <v>0</v>
-      </c>
-      <c r="AK22" s="103">
-        <f t="shared" ref="AK22" si="81">IF(MOD(J22,B22)/B22&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AL22" s="104">
-        <f t="shared" ref="AL22" si="82">IF(AND(MOD(J22,B22)/B22&lt;=0.5,MOD(J22,B22)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AM22" s="102">
-        <f t="shared" ref="AM22" si="83">INT(K22/B22)</f>
-        <v>0</v>
-      </c>
-      <c r="AN22" s="103">
-        <f t="shared" ref="AN22" si="84">IF(MOD(K22,B22)/B22&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AO22" s="104">
-        <f t="shared" ref="AO22" si="85">IF(AND(MOD(K22,B22)/B22&lt;=0.5,MOD(K22,B22)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AP22" s="102">
-        <f t="shared" ref="AP22" si="86">INT(L22/B22)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ22" s="103">
-        <f t="shared" ref="AQ22" si="87">IF(MOD(L22,B22)/B22&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AR22" s="104">
-        <f t="shared" ref="AR22" si="88">IF(AND(MOD(L22,B22)/B22&lt;=0.5,MOD(L22,B22)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AS22" s="102">
-        <f t="shared" ref="AS22" si="89">INT(M22/B22)</f>
-        <v>0</v>
-      </c>
-      <c r="AT22" s="103">
-        <f t="shared" ref="AT22" si="90">IF(MOD(M22,B22)/B22&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AU22" s="104">
-        <f t="shared" ref="AU22" si="91">IF(AND(MOD(M22,B22)/B22&lt;=0.5,MOD(M22,B22)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AV22" s="105"/>
-    </row>
-    <row r="23" spans="1:48" ht="19.899999999999999" customHeight="1">
-      <c r="A23" s="117" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23" s="112">
-        <v>15</v>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11"/>
+      <c r="R22" s="101">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="102">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="103">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="101">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="102">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="103">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="101">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="102">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z22" s="103">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA22" s="101">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB22" s="102">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AC22" s="103">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AD22" s="101">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AE22" s="102">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AF22" s="103">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AG22" s="101">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AH22" s="102">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AI22" s="103">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="101">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AK22" s="102">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AL22" s="103">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AM22" s="101">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AN22" s="102">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AO22" s="103">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AP22" s="101">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="102">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AR22" s="103">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AS22" s="101">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AT22" s="102">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AU22" s="103">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AV22" s="11"/>
+    </row>
+    <row r="23" spans="1:48" ht="19.95" customHeight="1">
+      <c r="A23" s="113" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" s="109">
+        <v>27</v>
       </c>
       <c r="C23" s="83">
-        <f t="shared" ref="C23:C24" si="92">SUMPRODUCT(ROUNDUP(D23/B23,0))</f>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="D23" s="83">
@@ -6239,152 +6178,140 @@
         <v>0</v>
       </c>
       <c r="E23" s="83"/>
-      <c r="F23" s="100"/>
-      <c r="G23" s="100"/>
-      <c r="H23" s="100"/>
-      <c r="I23" s="100"/>
-      <c r="J23" s="100"/>
-      <c r="K23" s="100"/>
-      <c r="L23" s="100"/>
-      <c r="M23" s="100"/>
-      <c r="N23" s="100" t="e">
-        <f>'มหาชัย-ผลิต'!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="O23" s="100"/>
-      <c r="P23" s="100"/>
-      <c r="Q23" s="100"/>
-      <c r="R23" s="102">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S23" s="103">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T23" s="104">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="U23" s="102">
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="101"/>
+      <c r="S23" s="102"/>
+      <c r="T23" s="103"/>
+      <c r="U23" s="101">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="V23" s="103">
+      <c r="V23" s="102">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="W23" s="104">
+      <c r="W23" s="103">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="X23" s="102">
+      <c r="X23" s="101">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y23" s="103">
+      <c r="Y23" s="102">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Z23" s="104">
+      <c r="Z23" s="103">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA23" s="102">
+      <c r="AA23" s="101">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AB23" s="103">
+      <c r="AB23" s="102">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AC23" s="104">
+      <c r="AC23" s="103">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AD23" s="102">
+      <c r="AD23" s="101">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AE23" s="103">
+      <c r="AE23" s="102">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AF23" s="104">
+      <c r="AF23" s="103">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AG23" s="102">
+      <c r="AG23" s="101">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AH23" s="103">
+      <c r="AH23" s="102">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AI23" s="104">
+      <c r="AI23" s="103">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AJ23" s="102">
+      <c r="AJ23" s="101">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AK23" s="103">
+      <c r="AK23" s="102">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="AL23" s="104">
+      <c r="AL23" s="103">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AM23" s="102">
+      <c r="AM23" s="101">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AN23" s="103">
+      <c r="AN23" s="102">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AO23" s="104">
+      <c r="AO23" s="103">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AP23" s="102">
+      <c r="AP23" s="101">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AQ23" s="103">
+      <c r="AQ23" s="102">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="AR23" s="104">
+      <c r="AR23" s="103">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AS23" s="102">
+      <c r="AS23" s="101">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AT23" s="103">
+      <c r="AT23" s="102">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="AU23" s="104">
+      <c r="AU23" s="103">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="AV23" s="100"/>
-    </row>
-    <row r="24" spans="1:48" ht="19.899999999999999" customHeight="1">
-      <c r="A24" s="117" t="s">
-        <v>132</v>
-      </c>
-      <c r="B24" s="112">
-        <v>27</v>
+      <c r="AV23" s="11"/>
+    </row>
+    <row r="24" spans="1:48" ht="19.95" customHeight="1">
+      <c r="A24" s="113" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" s="109">
+        <v>20</v>
       </c>
       <c r="C24" s="83">
-        <f t="shared" si="92"/>
+        <f t="shared" ref="C24:C26" si="93">SUMPRODUCT(ROUNDUP(D24/B24,0))</f>
         <v>0</v>
       </c>
       <c r="D24" s="83">
@@ -6392,140 +6319,140 @@
         <v>0</v>
       </c>
       <c r="E24" s="83"/>
-      <c r="F24" s="100"/>
-      <c r="G24" s="100"/>
-      <c r="H24" s="100"/>
-      <c r="I24" s="100"/>
-      <c r="J24" s="100"/>
-      <c r="K24" s="100"/>
-      <c r="L24" s="100"/>
-      <c r="M24" s="100"/>
-      <c r="N24" s="100"/>
-      <c r="O24" s="100"/>
-      <c r="P24" s="100"/>
-      <c r="Q24" s="100"/>
-      <c r="R24" s="102"/>
-      <c r="S24" s="103"/>
-      <c r="T24" s="104"/>
-      <c r="U24" s="102">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V24" s="103">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="W24" s="104">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X24" s="102">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Y24" s="103">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Z24" s="104">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AA24" s="102">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AB24" s="103">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AC24" s="104">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AD24" s="102">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AE24" s="103">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AF24" s="104">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AG24" s="102">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AH24" s="103">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AI24" s="104">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AJ24" s="102">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AK24" s="103">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AL24" s="104">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AM24" s="102">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AN24" s="103">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AO24" s="104">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AP24" s="102">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AQ24" s="103">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AR24" s="104">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AS24" s="102">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AT24" s="103">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="AU24" s="104">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="AV24" s="100"/>
-    </row>
-    <row r="25" spans="1:48" ht="19.899999999999999" customHeight="1">
-      <c r="A25" s="117" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" s="112">
-        <v>20</v>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="101"/>
+      <c r="S24" s="102"/>
+      <c r="T24" s="103"/>
+      <c r="U24" s="101">
+        <f t="shared" ref="U24" si="94">INT(E24/B24)</f>
+        <v>0</v>
+      </c>
+      <c r="V24" s="102">
+        <f t="shared" ref="V24" si="95">IF(MOD(E24,B24)/B24&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W24" s="103">
+        <f t="shared" ref="W24" si="96">IF(AND(MOD(E24,B24)/B24&lt;=0.5,MOD(E24,B24)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X24" s="101">
+        <f t="shared" ref="X24" si="97">INT(F24/B24)</f>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="102">
+        <f t="shared" ref="Y24" si="98">IF(MOD(F24,B24)/B24&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z24" s="103">
+        <f t="shared" ref="Z24" si="99">IF(AND(MOD(F24,B24)/B24&lt;=0.5,MOD(F24,B24)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA24" s="101">
+        <f t="shared" ref="AA24" si="100">INT(G24/B24)</f>
+        <v>0</v>
+      </c>
+      <c r="AB24" s="102">
+        <f t="shared" ref="AB24" si="101">IF(MOD(G24,B24)/B24&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC24" s="103">
+        <f t="shared" ref="AC24" si="102">IF(AND(MOD(G24,B24)/B24&lt;=0.5,MOD(G24,B24)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD24" s="101">
+        <f t="shared" ref="AD24" si="103">INT(H24/B24)</f>
+        <v>0</v>
+      </c>
+      <c r="AE24" s="102">
+        <f t="shared" ref="AE24" si="104">IF(MOD(H24,B24)/B24&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="103">
+        <f t="shared" ref="AF24" si="105">IF(AND(MOD(H24,B24)/B24&lt;=0.5,MOD(H24,B24)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG24" s="101">
+        <f t="shared" ref="AG24" si="106">INT(I24/B24)</f>
+        <v>0</v>
+      </c>
+      <c r="AH24" s="102">
+        <f t="shared" ref="AH24" si="107">IF(MOD(I24,B24)/B24&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI24" s="103">
+        <f t="shared" ref="AI24" si="108">IF(AND(MOD(I24,B24)/B24&lt;=0.5,MOD(I24,B24)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="101">
+        <f t="shared" ref="AJ24" si="109">INT(J24/B24)</f>
+        <v>0</v>
+      </c>
+      <c r="AK24" s="102">
+        <f t="shared" ref="AK24" si="110">IF(MOD(J24,B24)/B24&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL24" s="103">
+        <f t="shared" ref="AL24" si="111">IF(AND(MOD(J24,B24)/B24&lt;=0.5,MOD(J24,B24)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM24" s="101">
+        <f t="shared" ref="AM24" si="112">INT(K24/B24)</f>
+        <v>0</v>
+      </c>
+      <c r="AN24" s="102">
+        <f t="shared" ref="AN24" si="113">IF(MOD(K24,B24)/B24&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO24" s="103">
+        <f t="shared" ref="AO24" si="114">IF(AND(MOD(K24,B24)/B24&lt;=0.5,MOD(K24,B24)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP24" s="101">
+        <f t="shared" ref="AP24" si="115">INT(L24/B24)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ24" s="102">
+        <f t="shared" ref="AQ24" si="116">IF(MOD(L24,B24)/B24&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR24" s="103">
+        <f t="shared" ref="AR24" si="117">IF(AND(MOD(L24,B24)/B24&lt;=0.5,MOD(L24,B24)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS24" s="101">
+        <f t="shared" ref="AS24" si="118">INT(M24/B24)</f>
+        <v>0</v>
+      </c>
+      <c r="AT24" s="102">
+        <f t="shared" ref="AT24" si="119">IF(MOD(M24,B24)/B24&gt;0.5,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU24" s="103">
+        <f t="shared" ref="AU24" si="120">IF(AND(MOD(M24,B24)/B24&lt;=0.5,MOD(M24,B24)&lt;&gt;0),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV24" s="11"/>
+    </row>
+    <row r="25" spans="1:48" ht="19.95" customHeight="1">
+      <c r="A25" s="112" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" s="109">
+        <v>32</v>
       </c>
       <c r="C25" s="83">
-        <f t="shared" ref="C25:C27" si="93">SUMPRODUCT(ROUNDUP(D25/B25,0))</f>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="D25" s="83">
@@ -6533,137 +6460,56 @@
         <v>0</v>
       </c>
       <c r="E25" s="83"/>
-      <c r="F25" s="100"/>
-      <c r="G25" s="100"/>
-      <c r="H25" s="100"/>
-      <c r="I25" s="100"/>
-      <c r="J25" s="100"/>
-      <c r="K25" s="100"/>
-      <c r="L25" s="100"/>
-      <c r="M25" s="100"/>
-      <c r="N25" s="100"/>
-      <c r="O25" s="100"/>
-      <c r="P25" s="100"/>
-      <c r="Q25" s="100"/>
-      <c r="R25" s="102"/>
-      <c r="S25" s="103"/>
-      <c r="T25" s="104"/>
-      <c r="U25" s="102">
-        <f t="shared" ref="U25" si="94">INT(E25/B25)</f>
-        <v>0</v>
-      </c>
-      <c r="V25" s="103">
-        <f t="shared" ref="V25" si="95">IF(MOD(E25,B25)/B25&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="W25" s="104">
-        <f t="shared" ref="W25" si="96">IF(AND(MOD(E25,B25)/B25&lt;=0.5,MOD(E25,B25)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X25" s="102">
-        <f t="shared" ref="X25" si="97">INT(F25/B25)</f>
-        <v>0</v>
-      </c>
-      <c r="Y25" s="103">
-        <f t="shared" ref="Y25" si="98">IF(MOD(F25,B25)/B25&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z25" s="104">
-        <f t="shared" ref="Z25" si="99">IF(AND(MOD(F25,B25)/B25&lt;=0.5,MOD(F25,B25)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AA25" s="102">
-        <f t="shared" ref="AA25" si="100">INT(G25/B25)</f>
-        <v>0</v>
-      </c>
-      <c r="AB25" s="103">
-        <f t="shared" ref="AB25" si="101">IF(MOD(G25,B25)/B25&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AC25" s="104">
-        <f t="shared" ref="AC25" si="102">IF(AND(MOD(G25,B25)/B25&lt;=0.5,MOD(G25,B25)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AD25" s="102">
-        <f t="shared" ref="AD25" si="103">INT(H25/B25)</f>
-        <v>0</v>
-      </c>
-      <c r="AE25" s="103">
-        <f t="shared" ref="AE25" si="104">IF(MOD(H25,B25)/B25&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF25" s="104">
-        <f t="shared" ref="AF25" si="105">IF(AND(MOD(H25,B25)/B25&lt;=0.5,MOD(H25,B25)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AG25" s="102">
-        <f t="shared" ref="AG25" si="106">INT(I25/B25)</f>
-        <v>0</v>
-      </c>
-      <c r="AH25" s="103">
-        <f t="shared" ref="AH25" si="107">IF(MOD(I25,B25)/B25&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AI25" s="104">
-        <f t="shared" ref="AI25" si="108">IF(AND(MOD(I25,B25)/B25&lt;=0.5,MOD(I25,B25)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ25" s="102">
-        <f t="shared" ref="AJ25" si="109">INT(J25/B25)</f>
-        <v>0</v>
-      </c>
-      <c r="AK25" s="103">
-        <f t="shared" ref="AK25" si="110">IF(MOD(J25,B25)/B25&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AL25" s="104">
-        <f t="shared" ref="AL25" si="111">IF(AND(MOD(J25,B25)/B25&lt;=0.5,MOD(J25,B25)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AM25" s="102">
-        <f t="shared" ref="AM25" si="112">INT(K25/B25)</f>
-        <v>0</v>
-      </c>
-      <c r="AN25" s="103">
-        <f t="shared" ref="AN25" si="113">IF(MOD(K25,B25)/B25&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AO25" s="104">
-        <f t="shared" ref="AO25" si="114">IF(AND(MOD(K25,B25)/B25&lt;=0.5,MOD(K25,B25)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AP25" s="102">
-        <f t="shared" ref="AP25" si="115">INT(L25/B25)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ25" s="103">
-        <f t="shared" ref="AQ25" si="116">IF(MOD(L25,B25)/B25&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AR25" s="104">
-        <f t="shared" ref="AR25" si="117">IF(AND(MOD(L25,B25)/B25&lt;=0.5,MOD(L25,B25)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AS25" s="102">
-        <f t="shared" ref="AS25" si="118">INT(M25/B25)</f>
-        <v>0</v>
-      </c>
-      <c r="AT25" s="103">
-        <f t="shared" ref="AT25" si="119">IF(MOD(M25,B25)/B25&gt;0.5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AU25" s="104">
-        <f t="shared" ref="AU25" si="120">IF(AND(MOD(M25,B25)/B25&lt;=0.5,MOD(M25,B25)&lt;&gt;0),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AV25" s="100"/>
-    </row>
-    <row r="26" spans="1:48" ht="19.899999999999999" customHeight="1">
-      <c r="A26" s="116" t="s">
-        <v>69</v>
-      </c>
-      <c r="B26" s="112">
-        <v>32</v>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="11"/>
+      <c r="R25" s="101"/>
+      <c r="S25" s="102"/>
+      <c r="T25" s="103"/>
+      <c r="U25" s="101"/>
+      <c r="V25" s="102"/>
+      <c r="W25" s="103"/>
+      <c r="X25" s="101"/>
+      <c r="Y25" s="102"/>
+      <c r="Z25" s="103"/>
+      <c r="AA25" s="101"/>
+      <c r="AB25" s="102"/>
+      <c r="AC25" s="103"/>
+      <c r="AD25" s="101"/>
+      <c r="AE25" s="102"/>
+      <c r="AF25" s="103"/>
+      <c r="AG25" s="101"/>
+      <c r="AH25" s="102"/>
+      <c r="AI25" s="103"/>
+      <c r="AJ25" s="101"/>
+      <c r="AK25" s="102"/>
+      <c r="AL25" s="103"/>
+      <c r="AM25" s="101"/>
+      <c r="AN25" s="102"/>
+      <c r="AO25" s="103"/>
+      <c r="AP25" s="101"/>
+      <c r="AQ25" s="102"/>
+      <c r="AR25" s="103"/>
+      <c r="AS25" s="101"/>
+      <c r="AT25" s="102"/>
+      <c r="AU25" s="103"/>
+      <c r="AV25" s="11"/>
+    </row>
+    <row r="26" spans="1:48" ht="19.95" customHeight="1">
+      <c r="A26" s="110" t="s">
+        <v>113</v>
+      </c>
+      <c r="B26" s="109">
+        <v>15</v>
       </c>
       <c r="C26" s="83">
         <f t="shared" si="93"/>
@@ -6674,59 +6520,59 @@
         <v>0</v>
       </c>
       <c r="E26" s="83"/>
-      <c r="F26" s="100"/>
-      <c r="G26" s="100"/>
-      <c r="H26" s="100"/>
-      <c r="I26" s="100"/>
-      <c r="J26" s="100"/>
-      <c r="K26" s="100"/>
-      <c r="L26" s="100"/>
-      <c r="M26" s="100"/>
-      <c r="N26" s="100"/>
-      <c r="O26" s="100"/>
-      <c r="P26" s="100"/>
-      <c r="Q26" s="100"/>
-      <c r="R26" s="102"/>
-      <c r="S26" s="103"/>
-      <c r="T26" s="104"/>
-      <c r="U26" s="102"/>
-      <c r="V26" s="103"/>
-      <c r="W26" s="104"/>
-      <c r="X26" s="102"/>
-      <c r="Y26" s="103"/>
-      <c r="Z26" s="104"/>
-      <c r="AA26" s="102"/>
-      <c r="AB26" s="103"/>
-      <c r="AC26" s="104"/>
-      <c r="AD26" s="102"/>
-      <c r="AE26" s="103"/>
-      <c r="AF26" s="104"/>
-      <c r="AG26" s="102"/>
-      <c r="AH26" s="103"/>
-      <c r="AI26" s="104"/>
-      <c r="AJ26" s="102"/>
-      <c r="AK26" s="103"/>
-      <c r="AL26" s="104"/>
-      <c r="AM26" s="102"/>
-      <c r="AN26" s="103"/>
-      <c r="AO26" s="104"/>
-      <c r="AP26" s="102"/>
-      <c r="AQ26" s="103"/>
-      <c r="AR26" s="104"/>
-      <c r="AS26" s="102"/>
-      <c r="AT26" s="103"/>
-      <c r="AU26" s="104"/>
-      <c r="AV26" s="100"/>
-    </row>
-    <row r="27" spans="1:48" ht="19.899999999999999" customHeight="1">
-      <c r="A27" s="114" t="s">
-        <v>113</v>
-      </c>
-      <c r="B27" s="112">
-        <v>15</v>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="11"/>
+      <c r="Q26" s="11"/>
+      <c r="R26" s="101"/>
+      <c r="S26" s="102"/>
+      <c r="T26" s="103"/>
+      <c r="U26" s="101"/>
+      <c r="V26" s="102"/>
+      <c r="W26" s="103"/>
+      <c r="X26" s="101"/>
+      <c r="Y26" s="102"/>
+      <c r="Z26" s="103"/>
+      <c r="AA26" s="101"/>
+      <c r="AB26" s="102"/>
+      <c r="AC26" s="103"/>
+      <c r="AD26" s="101"/>
+      <c r="AE26" s="102"/>
+      <c r="AF26" s="103"/>
+      <c r="AG26" s="101"/>
+      <c r="AH26" s="102"/>
+      <c r="AI26" s="103"/>
+      <c r="AJ26" s="101"/>
+      <c r="AK26" s="102"/>
+      <c r="AL26" s="103"/>
+      <c r="AM26" s="101"/>
+      <c r="AN26" s="102"/>
+      <c r="AO26" s="103"/>
+      <c r="AP26" s="101"/>
+      <c r="AQ26" s="102"/>
+      <c r="AR26" s="103"/>
+      <c r="AS26" s="101"/>
+      <c r="AT26" s="102"/>
+      <c r="AU26" s="103"/>
+      <c r="AV26" s="11"/>
+    </row>
+    <row r="27" spans="1:48" ht="19.95" customHeight="1">
+      <c r="A27" s="110" t="s">
+        <v>143</v>
+      </c>
+      <c r="B27" s="109">
+        <v>8</v>
       </c>
       <c r="C27" s="83">
-        <f t="shared" si="93"/>
+        <f t="shared" ref="C27" si="121">SUMPRODUCT(ROUNDUP(D27/B27,0))</f>
         <v>0</v>
       </c>
       <c r="D27" s="83">
@@ -6734,200 +6580,164 @@
         <v>0</v>
       </c>
       <c r="E27" s="83"/>
-      <c r="F27" s="100"/>
-      <c r="G27" s="100"/>
-      <c r="H27" s="100"/>
-      <c r="I27" s="100"/>
-      <c r="J27" s="100"/>
-      <c r="K27" s="100"/>
-      <c r="L27" s="100"/>
-      <c r="M27" s="100"/>
-      <c r="N27" s="100"/>
-      <c r="O27" s="100"/>
-      <c r="P27" s="100"/>
-      <c r="Q27" s="100"/>
-      <c r="R27" s="102"/>
-      <c r="S27" s="103"/>
-      <c r="T27" s="104"/>
-      <c r="U27" s="102"/>
-      <c r="V27" s="103"/>
-      <c r="W27" s="104"/>
-      <c r="X27" s="102"/>
-      <c r="Y27" s="103"/>
-      <c r="Z27" s="104"/>
-      <c r="AA27" s="102"/>
-      <c r="AB27" s="103"/>
-      <c r="AC27" s="104"/>
-      <c r="AD27" s="102"/>
-      <c r="AE27" s="103"/>
-      <c r="AF27" s="104"/>
-      <c r="AG27" s="102"/>
-      <c r="AH27" s="103"/>
-      <c r="AI27" s="104"/>
-      <c r="AJ27" s="102"/>
-      <c r="AK27" s="103"/>
-      <c r="AL27" s="104"/>
-      <c r="AM27" s="102"/>
-      <c r="AN27" s="103"/>
-      <c r="AO27" s="104"/>
-      <c r="AP27" s="102"/>
-      <c r="AQ27" s="103"/>
-      <c r="AR27" s="104"/>
-      <c r="AS27" s="102"/>
-      <c r="AT27" s="103"/>
-      <c r="AU27" s="104"/>
-      <c r="AV27" s="100"/>
-    </row>
-    <row r="28" spans="1:48" ht="19.899999999999999" customHeight="1">
-      <c r="A28" s="114" t="s">
-        <v>146</v>
-      </c>
-      <c r="B28" s="112">
-        <v>8</v>
-      </c>
-      <c r="C28" s="83">
-        <f t="shared" ref="C28" si="121">SUMPRODUCT(ROUNDUP(D28/B28,0))</f>
-        <v>0</v>
-      </c>
-      <c r="D28" s="83">
-        <f>'มหาชัย-ผลิต'!E44</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="83"/>
-      <c r="F28" s="133"/>
-      <c r="G28" s="133"/>
-      <c r="H28" s="133"/>
-      <c r="I28" s="133"/>
-      <c r="J28" s="133"/>
-      <c r="K28" s="133"/>
-      <c r="L28" s="133"/>
-      <c r="M28" s="133"/>
-      <c r="N28" s="133"/>
-      <c r="O28" s="133"/>
-      <c r="P28" s="133"/>
-      <c r="Q28" s="133"/>
-      <c r="R28" s="102"/>
-      <c r="S28" s="103"/>
-      <c r="T28" s="104"/>
-      <c r="U28" s="102"/>
-      <c r="V28" s="103"/>
-      <c r="W28" s="104"/>
-      <c r="X28" s="102"/>
-      <c r="Y28" s="103"/>
-      <c r="Z28" s="104"/>
-      <c r="AA28" s="102"/>
-      <c r="AB28" s="103"/>
-      <c r="AC28" s="104"/>
-      <c r="AD28" s="102"/>
-      <c r="AE28" s="103"/>
-      <c r="AF28" s="104"/>
-      <c r="AG28" s="102"/>
-      <c r="AH28" s="103"/>
-      <c r="AI28" s="104"/>
-      <c r="AJ28" s="102"/>
-      <c r="AK28" s="103"/>
-      <c r="AL28" s="104"/>
-      <c r="AM28" s="102"/>
-      <c r="AN28" s="103"/>
-      <c r="AO28" s="104"/>
-      <c r="AP28" s="102"/>
-      <c r="AQ28" s="103"/>
-      <c r="AR28" s="104"/>
-      <c r="AS28" s="102"/>
-      <c r="AT28" s="103"/>
-      <c r="AU28" s="104"/>
-      <c r="AV28" s="133"/>
-    </row>
-    <row r="29" spans="1:48" s="23" customFormat="1" ht="25.15" customHeight="1">
-      <c r="A29" s="201" t="s">
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="11"/>
+      <c r="R27" s="101"/>
+      <c r="S27" s="102"/>
+      <c r="T27" s="103"/>
+      <c r="U27" s="101"/>
+      <c r="V27" s="102"/>
+      <c r="W27" s="103"/>
+      <c r="X27" s="101"/>
+      <c r="Y27" s="102"/>
+      <c r="Z27" s="103"/>
+      <c r="AA27" s="101"/>
+      <c r="AB27" s="102"/>
+      <c r="AC27" s="103"/>
+      <c r="AD27" s="101"/>
+      <c r="AE27" s="102"/>
+      <c r="AF27" s="103"/>
+      <c r="AG27" s="101"/>
+      <c r="AH27" s="102"/>
+      <c r="AI27" s="103"/>
+      <c r="AJ27" s="101"/>
+      <c r="AK27" s="102"/>
+      <c r="AL27" s="103"/>
+      <c r="AM27" s="101"/>
+      <c r="AN27" s="102"/>
+      <c r="AO27" s="103"/>
+      <c r="AP27" s="101"/>
+      <c r="AQ27" s="102"/>
+      <c r="AR27" s="103"/>
+      <c r="AS27" s="101"/>
+      <c r="AT27" s="102"/>
+      <c r="AU27" s="103"/>
+      <c r="AV27" s="11"/>
+    </row>
+    <row r="28" spans="1:48" s="23" customFormat="1" ht="25.2" customHeight="1">
+      <c r="A28" s="194" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="202"/>
-      <c r="C29" s="99">
-        <f>SUM(C10:C28)</f>
-        <v>0</v>
-      </c>
-      <c r="D29" s="61">
-        <f>SUM(D30:D32)*-1</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="21"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
-      <c r="M29" s="21"/>
-      <c r="N29" s="21"/>
-      <c r="O29" s="22"/>
-      <c r="P29" s="22"/>
-      <c r="Q29" s="22"/>
-      <c r="R29" s="22"/>
-      <c r="S29" s="22"/>
-      <c r="T29" s="22"/>
-      <c r="U29" s="22"/>
-      <c r="V29" s="22"/>
-      <c r="W29" s="22"/>
-      <c r="X29" s="22"/>
-      <c r="Y29" s="22"/>
-      <c r="Z29" s="22"/>
-      <c r="AA29" s="22"/>
-      <c r="AB29" s="22"/>
-      <c r="AC29" s="22"/>
-      <c r="AD29" s="22"/>
-      <c r="AE29" s="22"/>
-      <c r="AF29" s="22"/>
-      <c r="AG29" s="22"/>
-      <c r="AH29" s="22"/>
-      <c r="AI29" s="22"/>
-      <c r="AJ29" s="22"/>
-      <c r="AK29" s="22"/>
-      <c r="AL29" s="22"/>
-      <c r="AM29" s="22"/>
-      <c r="AN29" s="22"/>
-      <c r="AO29" s="22"/>
-      <c r="AP29" s="22"/>
-      <c r="AQ29" s="22"/>
-      <c r="AR29" s="22"/>
-      <c r="AS29" s="22"/>
-      <c r="AT29" s="22"/>
-      <c r="AU29" s="22"/>
-      <c r="AV29" s="22"/>
+      <c r="B28" s="195"/>
+      <c r="C28" s="99">
+        <f>SUM(C10:C27)</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="61">
+        <f>SUM(D29:D31)*-1</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="21"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22"/>
+      <c r="R28" s="22"/>
+      <c r="S28" s="22"/>
+      <c r="T28" s="22"/>
+      <c r="U28" s="22"/>
+      <c r="V28" s="22"/>
+      <c r="W28" s="22"/>
+      <c r="X28" s="22"/>
+      <c r="Y28" s="22"/>
+      <c r="Z28" s="22"/>
+      <c r="AA28" s="22"/>
+      <c r="AB28" s="22"/>
+      <c r="AC28" s="22"/>
+      <c r="AD28" s="22"/>
+      <c r="AE28" s="22"/>
+      <c r="AF28" s="22"/>
+      <c r="AG28" s="22"/>
+      <c r="AH28" s="22"/>
+      <c r="AI28" s="22"/>
+      <c r="AJ28" s="22"/>
+      <c r="AK28" s="22"/>
+      <c r="AL28" s="22"/>
+      <c r="AM28" s="22"/>
+      <c r="AN28" s="22"/>
+      <c r="AO28" s="22"/>
+      <c r="AP28" s="22"/>
+      <c r="AQ28" s="22"/>
+      <c r="AR28" s="22"/>
+      <c r="AS28" s="22"/>
+      <c r="AT28" s="22"/>
+      <c r="AU28" s="22"/>
+      <c r="AV28" s="22"/>
+    </row>
+    <row r="29" spans="1:48" ht="21" customHeight="1">
+      <c r="A29" s="196" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="196"/>
+      <c r="C29" s="196"/>
+      <c r="D29" s="100">
+        <f>SUM(R10:R22)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="100"/>
+      <c r="F29" s="100"/>
+      <c r="G29" s="100"/>
+      <c r="H29" s="100"/>
+      <c r="I29" s="100"/>
+      <c r="J29" s="100"/>
+      <c r="K29" s="100"/>
+      <c r="L29" s="100"/>
+      <c r="M29" s="100"/>
+      <c r="N29" s="100"/>
+      <c r="O29" s="100"/>
+      <c r="P29" s="100"/>
+      <c r="Q29" s="100"/>
     </row>
     <row r="30" spans="1:48" ht="21" customHeight="1">
-      <c r="A30" s="203" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="203"/>
-      <c r="C30" s="203"/>
-      <c r="D30" s="101">
-        <f>SUM(R10:R23)</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="101"/>
-      <c r="F30" s="101"/>
-      <c r="G30" s="101"/>
-      <c r="H30" s="101"/>
-      <c r="I30" s="101"/>
-      <c r="J30" s="101"/>
-      <c r="K30" s="101"/>
-      <c r="L30" s="101"/>
-      <c r="M30" s="101"/>
-      <c r="N30" s="101"/>
-      <c r="O30" s="101"/>
-      <c r="P30" s="101"/>
-      <c r="Q30" s="101"/>
+      <c r="A30" s="191" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="191"/>
+      <c r="C30" s="191"/>
+      <c r="D30" s="11">
+        <f>SUM(S10:S22)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="11"/>
+      <c r="P30" s="11"/>
+      <c r="Q30" s="11"/>
     </row>
     <row r="31" spans="1:48" ht="21" customHeight="1">
-      <c r="A31" s="198" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="198"/>
-      <c r="C31" s="198"/>
+      <c r="A31" s="191" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="191"/>
+      <c r="C31" s="191"/>
       <c r="D31" s="11">
-        <f>SUM(S10:S23)</f>
+        <f>SUM(T10:T22)</f>
         <v>0</v>
       </c>
       <c r="E31" s="11"/>
@@ -6944,52 +6754,44 @@
       <c r="P31" s="11"/>
       <c r="Q31" s="11"/>
     </row>
-    <row r="32" spans="1:48" ht="21" customHeight="1">
-      <c r="A32" s="198" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="198"/>
-      <c r="C32" s="198"/>
-      <c r="D32" s="11">
-        <f>SUM(T10:T23)</f>
-        <v>0</v>
-      </c>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="11"/>
-      <c r="O32" s="11"/>
-      <c r="P32" s="11"/>
-      <c r="Q32" s="11"/>
+    <row r="32" spans="1:48" ht="15" customHeight="1">
+      <c r="A32" s="62"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
     </row>
     <row r="33" spans="1:17" ht="15" customHeight="1">
       <c r="A33" s="62"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
     </row>
-    <row r="34" spans="1:17" ht="15" customHeight="1">
-      <c r="A34" s="62"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
+    <row r="34" spans="1:17" ht="18" customHeight="1">
+      <c r="A34" s="190" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="10">
+        <v>134</v>
+      </c>
+      <c r="D34" s="11">
+        <f>IF(C34=0, 0, ((SUM(D29:M29)+SUM(D30:M30))/C34)*100)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="35" spans="1:17" ht="18" customHeight="1">
-      <c r="A35" s="197" t="s">
-        <v>44</v>
-      </c>
+      <c r="A35" s="190"/>
       <c r="B35" s="12" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C35" s="10">
-        <v>134</v>
+        <v>242</v>
       </c>
       <c r="D35" s="11">
-        <f>IF(C35=0, 0, ((SUM(D30:M30)+SUM(D31:M31))/C35)*100)</f>
+        <f>IF(C35=0, 0, ((SUM(D31:M31))/C35)*100)</f>
         <v>0</v>
       </c>
       <c r="E35" s="11" t="s">
@@ -6997,15 +6799,13 @@
       </c>
     </row>
     <row r="36" spans="1:17" ht="18" customHeight="1">
-      <c r="A36" s="197"/>
-      <c r="B36" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36" s="10">
-        <v>242</v>
-      </c>
+      <c r="A36" s="190"/>
+      <c r="B36" s="191" t="s">
+        <v>48</v>
+      </c>
+      <c r="C36" s="191"/>
       <c r="D36" s="11">
-        <f>IF(C36=0, 0, ((SUM(D32:M32))/C36)*100)</f>
+        <f>D34+D35</f>
         <v>0</v>
       </c>
       <c r="E36" s="11" t="s">
@@ -7013,58 +6813,60 @@
       </c>
     </row>
     <row r="37" spans="1:17" ht="18" customHeight="1">
-      <c r="A37" s="197"/>
-      <c r="B37" s="198" t="s">
-        <v>48</v>
-      </c>
-      <c r="C37" s="198"/>
+      <c r="A37" s="190"/>
+      <c r="B37" s="191" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" s="191"/>
       <c r="D37" s="11">
-        <f>D35+D36</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="18" customHeight="1">
-      <c r="A38" s="197"/>
-      <c r="B38" s="198" t="s">
-        <v>47</v>
-      </c>
-      <c r="C38" s="198"/>
+      <c r="A38" s="190"/>
+      <c r="B38" s="191" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" s="191"/>
       <c r="D38" s="11">
-        <v>100</v>
-      </c>
-      <c r="E38" s="11" t="s">
+        <f>CEILING(D36 /D37, 1)</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" ht="18" customHeight="1">
+      <c r="A39" s="190" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" s="10">
+        <v>154</v>
+      </c>
+      <c r="D39" s="11">
+        <f>IF(C39=0, 0, ((SUM(D29:M29)+SUM(D30:M30))/C39)*100)</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="18" customHeight="1">
-      <c r="A39" s="197"/>
-      <c r="B39" s="198" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" s="198"/>
-      <c r="D39" s="11">
-        <f>CEILING(D37 /D38, 1)</f>
-        <v>0</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>20</v>
-      </c>
-    </row>
     <row r="40" spans="1:17" ht="18" customHeight="1">
-      <c r="A40" s="197" t="s">
-        <v>45</v>
-      </c>
+      <c r="A40" s="190"/>
       <c r="B40" s="12" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C40" s="10">
-        <v>154</v>
+        <v>278</v>
       </c>
       <c r="D40" s="11">
-        <f>IF(C40=0, 0, ((SUM(D30:M30)+SUM(D31:M31))/C40)*100)</f>
+        <f>IF(C40=0, 0, ((SUM(D31:M31))/C40)*100)</f>
         <v>0</v>
       </c>
       <c r="E40" s="11" t="s">
@@ -7072,15 +6874,13 @@
       </c>
     </row>
     <row r="41" spans="1:17" ht="18" customHeight="1">
-      <c r="A41" s="197"/>
-      <c r="B41" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41" s="10">
-        <v>278</v>
-      </c>
+      <c r="A41" s="190"/>
+      <c r="B41" s="191" t="s">
+        <v>48</v>
+      </c>
+      <c r="C41" s="191"/>
       <c r="D41" s="11">
-        <f>IF(C41=0, 0, ((SUM(D32:M32))/C41)*100)</f>
+        <f>D39+D40</f>
         <v>0</v>
       </c>
       <c r="E41" s="11" t="s">
@@ -7088,165 +6888,151 @@
       </c>
     </row>
     <row r="42" spans="1:17" ht="18" customHeight="1">
-      <c r="A42" s="197"/>
-      <c r="B42" s="198" t="s">
-        <v>48</v>
-      </c>
-      <c r="C42" s="198"/>
+      <c r="A42" s="190"/>
+      <c r="B42" s="191" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42" s="191"/>
       <c r="D42" s="11">
-        <f>D40+D41</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E42" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="18" customHeight="1">
-      <c r="A43" s="197"/>
-      <c r="B43" s="198" t="s">
-        <v>47</v>
-      </c>
-      <c r="C43" s="198"/>
+    <row r="43" spans="1:17" ht="25.2" customHeight="1">
+      <c r="A43" s="190"/>
+      <c r="B43" s="191" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="191"/>
       <c r="D43" s="11">
-        <v>100</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" ht="25.15" customHeight="1">
-      <c r="A44" s="197"/>
-      <c r="B44" s="198" t="s">
-        <v>19</v>
-      </c>
-      <c r="C44" s="198"/>
-      <c r="D44" s="11">
-        <f>CEILING(D42 /D43, 1)</f>
-        <v>0</v>
-      </c>
-      <c r="E44" s="13" t="s">
+        <f>CEILING(D41 /D42, 1)</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="13" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="25.15" customHeight="1">
+    <row r="44" spans="1:17" ht="25.2" customHeight="1">
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="E44" s="9"/>
+    </row>
+    <row r="45" spans="1:17" ht="4.95" customHeight="1">
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
       <c r="E45" s="9"/>
     </row>
-    <row r="46" spans="1:17" ht="4.9000000000000004" customHeight="1">
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="E46" s="9"/>
+    <row r="46" spans="1:17" ht="21" customHeight="1">
+      <c r="A46" s="192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" s="190"/>
+      <c r="C46" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D46" s="192" t="s">
+        <v>53</v>
+      </c>
+      <c r="E46" s="192"/>
+      <c r="F46" s="192"/>
+      <c r="G46" s="192" t="s">
+        <v>54</v>
+      </c>
+      <c r="H46" s="192"/>
+      <c r="I46" s="192"/>
+      <c r="J46" s="178" t="s">
+        <v>55</v>
+      </c>
+      <c r="K46" s="179"/>
+      <c r="L46" s="179"/>
+      <c r="M46" s="180"/>
+      <c r="N46" s="14"/>
+      <c r="O46" s="181" t="s">
+        <v>60</v>
+      </c>
+      <c r="P46" s="182"/>
     </row>
     <row r="47" spans="1:17" ht="21" customHeight="1">
-      <c r="A47" s="199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" s="197"/>
-      <c r="C47" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D47" s="199" t="s">
-        <v>53</v>
-      </c>
-      <c r="E47" s="199"/>
-      <c r="F47" s="199"/>
-      <c r="G47" s="199" t="s">
-        <v>54</v>
-      </c>
-      <c r="H47" s="199"/>
-      <c r="I47" s="199"/>
-      <c r="J47" s="185" t="s">
-        <v>55</v>
-      </c>
-      <c r="K47" s="186"/>
-      <c r="L47" s="186"/>
-      <c r="M47" s="187"/>
-      <c r="N47" s="14"/>
-      <c r="O47" s="188" t="s">
-        <v>60</v>
-      </c>
-      <c r="P47" s="189"/>
+      <c r="A47" s="185" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47" s="186"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="178"/>
+      <c r="E47" s="179"/>
+      <c r="F47" s="180"/>
+      <c r="G47" s="178"/>
+      <c r="H47" s="179"/>
+      <c r="I47" s="180"/>
+      <c r="J47" s="187"/>
+      <c r="K47" s="188"/>
+      <c r="L47" s="188"/>
+      <c r="M47" s="189"/>
+      <c r="N47" s="15"/>
+      <c r="O47" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="P47" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q47" s="5"/>
     </row>
     <row r="48" spans="1:17" ht="21" customHeight="1">
-      <c r="A48" s="192" t="s">
-        <v>50</v>
-      </c>
-      <c r="B48" s="193"/>
+      <c r="A48" s="185" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48" s="186"/>
       <c r="C48" s="11"/>
-      <c r="D48" s="185"/>
-      <c r="E48" s="186"/>
-      <c r="F48" s="187"/>
-      <c r="G48" s="185"/>
-      <c r="H48" s="186"/>
-      <c r="I48" s="187"/>
-      <c r="J48" s="194"/>
-      <c r="K48" s="195"/>
-      <c r="L48" s="195"/>
-      <c r="M48" s="196"/>
+      <c r="D48" s="178"/>
+      <c r="E48" s="179"/>
+      <c r="F48" s="180"/>
+      <c r="G48" s="178"/>
+      <c r="H48" s="179"/>
+      <c r="I48" s="180"/>
+      <c r="J48" s="187"/>
+      <c r="K48" s="188"/>
+      <c r="L48" s="188"/>
+      <c r="M48" s="189"/>
       <c r="N48" s="15"/>
       <c r="O48" s="19" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P48" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="Q48" s="5"/>
+      <c r="Q48" s="16"/>
     </row>
     <row r="49" spans="1:17" ht="21" customHeight="1">
-      <c r="A49" s="192" t="s">
-        <v>51</v>
-      </c>
-      <c r="B49" s="193"/>
+      <c r="A49" s="185" t="s">
+        <v>52</v>
+      </c>
+      <c r="B49" s="185"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="185"/>
-      <c r="E49" s="186"/>
-      <c r="F49" s="187"/>
-      <c r="G49" s="185"/>
-      <c r="H49" s="186"/>
-      <c r="I49" s="187"/>
-      <c r="J49" s="194"/>
-      <c r="K49" s="195"/>
-      <c r="L49" s="195"/>
-      <c r="M49" s="196"/>
+      <c r="D49" s="178"/>
+      <c r="E49" s="179"/>
+      <c r="F49" s="180"/>
+      <c r="G49" s="178"/>
+      <c r="H49" s="179"/>
+      <c r="I49" s="180"/>
+      <c r="J49" s="187"/>
+      <c r="K49" s="188"/>
+      <c r="L49" s="188"/>
+      <c r="M49" s="189"/>
       <c r="N49" s="15"/>
-      <c r="O49" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="P49" s="20" t="s">
+      <c r="O49" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="P49" s="18" t="s">
         <v>57</v>
       </c>
       <c r="Q49" s="16"/>
     </row>
-    <row r="50" spans="1:17" ht="21" customHeight="1">
-      <c r="A50" s="192" t="s">
-        <v>52</v>
-      </c>
-      <c r="B50" s="192"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="185"/>
-      <c r="E50" s="186"/>
-      <c r="F50" s="187"/>
-      <c r="G50" s="185"/>
-      <c r="H50" s="186"/>
-      <c r="I50" s="187"/>
-      <c r="J50" s="194"/>
-      <c r="K50" s="195"/>
-      <c r="L50" s="195"/>
-      <c r="M50" s="196"/>
-      <c r="N50" s="15"/>
-      <c r="O50" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="P50" s="18" t="s">
-        <v>57</v>
-      </c>
+    <row r="50" spans="1:17" ht="15" customHeight="1">
+      <c r="O50" s="16"/>
+      <c r="P50" s="16"/>
       <c r="Q50" s="16"/>
-    </row>
-    <row r="51" spans="1:17" ht="15" customHeight="1">
-      <c r="O51" s="16"/>
-      <c r="P51" s="16"/>
-      <c r="Q51" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="59">
@@ -7257,7 +7043,7 @@
     <mergeCell ref="C6:Q6"/>
     <mergeCell ref="L8:L9"/>
     <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A29:C29"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="E8:E9"/>
@@ -7267,7 +7053,7 @@
     <mergeCell ref="AM8:AO8"/>
     <mergeCell ref="AP8:AR8"/>
     <mergeCell ref="AS8:AU8"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A28:B28"/>
     <mergeCell ref="R8:T8"/>
     <mergeCell ref="U8:W8"/>
     <mergeCell ref="X8:Z8"/>
@@ -7279,36 +7065,36 @@
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="K8:K9"/>
+    <mergeCell ref="A30:C30"/>
     <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A35:A39"/>
+    <mergeCell ref="A34:A38"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="A47:B47"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="J50:M50"/>
-    <mergeCell ref="A40:A44"/>
+    <mergeCell ref="J49:M49"/>
+    <mergeCell ref="A39:A43"/>
+    <mergeCell ref="B41:C41"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="J47:M47"/>
+    <mergeCell ref="J48:M48"/>
+    <mergeCell ref="G46:I46"/>
     <mergeCell ref="D47:F47"/>
-    <mergeCell ref="J48:M48"/>
-    <mergeCell ref="J49:M49"/>
-    <mergeCell ref="G47:I47"/>
     <mergeCell ref="D48:F48"/>
     <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="G47:I47"/>
     <mergeCell ref="G48:I48"/>
     <mergeCell ref="G49:I49"/>
-    <mergeCell ref="G50:I50"/>
-    <mergeCell ref="O47:P47"/>
+    <mergeCell ref="O46:P46"/>
     <mergeCell ref="O8:O9"/>
     <mergeCell ref="P8:P9"/>
     <mergeCell ref="M8:M9"/>
-    <mergeCell ref="J47:M47"/>
+    <mergeCell ref="J46:M46"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7319,29 +7105,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:I25"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="51.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.125" customWidth="1"/>
-    <col min="6" max="6" width="11.75" customWidth="1"/>
+    <col min="2" max="2" width="51.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:9" s="3" customFormat="1" ht="15" customHeight="1"/>
     <row r="3" spans="1:9" s="3" customFormat="1" ht="30.75" customHeight="1">
       <c r="D3" s="43"/>
       <c r="E3" s="43"/>
-      <c r="G3" s="215"/>
-      <c r="H3" s="215"/>
-      <c r="I3" s="215"/>
+      <c r="G3" s="208"/>
+      <c r="H3" s="208"/>
+      <c r="I3" s="208"/>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
       <c r="D4" s="42"/>
       <c r="E4" s="42"/>
       <c r="F4" s="41"/>
-      <c r="G4" s="215"/>
-      <c r="H4" s="215"/>
-      <c r="I4" s="215"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="208"/>
+      <c r="I4" s="208"/>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" ht="56.25" customHeight="1" thickBot="1">
       <c r="A5" s="51" t="s">
@@ -7350,52 +7136,52 @@
       <c r="B5" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="216" t="s">
+      <c r="C5" s="209" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="217"/>
-      <c r="E5" s="217"/>
-      <c r="F5" s="218"/>
+      <c r="D5" s="210"/>
+      <c r="E5" s="210"/>
+      <c r="F5" s="211"/>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A6" s="219" t="s">
+      <c r="A6" s="212" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="220"/>
-      <c r="C6" s="225" t="s">
+      <c r="B6" s="213"/>
+      <c r="C6" s="218" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="228" t="s">
+      <c r="D6" s="221" t="s">
         <v>94</v>
       </c>
-      <c r="E6" s="230" t="s">
+      <c r="E6" s="223" t="s">
         <v>72</v>
       </c>
-      <c r="F6" s="231"/>
+      <c r="F6" s="224"/>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" ht="30.6" customHeight="1" thickBot="1">
-      <c r="A7" s="221"/>
-      <c r="B7" s="222"/>
-      <c r="C7" s="226"/>
-      <c r="D7" s="229"/>
-      <c r="E7" s="232"/>
-      <c r="F7" s="233"/>
+      <c r="A7" s="214"/>
+      <c r="B7" s="215"/>
+      <c r="C7" s="219"/>
+      <c r="D7" s="222"/>
+      <c r="E7" s="225"/>
+      <c r="F7" s="226"/>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A8" s="221"/>
-      <c r="B8" s="222"/>
-      <c r="C8" s="226"/>
-      <c r="D8" s="235" t="s">
+      <c r="A8" s="214"/>
+      <c r="B8" s="215"/>
+      <c r="C8" s="219"/>
+      <c r="D8" s="228" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="234"/>
-      <c r="F8" s="233"/>
-    </row>
-    <row r="9" spans="1:9" s="3" customFormat="1" ht="17.45" customHeight="1" thickBot="1">
-      <c r="A9" s="223"/>
-      <c r="B9" s="224"/>
-      <c r="C9" s="227"/>
-      <c r="D9" s="236"/>
+      <c r="E8" s="227"/>
+      <c r="F8" s="226"/>
+    </row>
+    <row r="9" spans="1:9" s="3" customFormat="1" ht="17.399999999999999" customHeight="1" thickBot="1">
+      <c r="A9" s="216"/>
+      <c r="B9" s="217"/>
+      <c r="C9" s="220"/>
+      <c r="D9" s="229"/>
       <c r="E9" s="33" t="s">
         <v>75</v>
       </c>
@@ -7403,43 +7189,43 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="3" customFormat="1" ht="29.45" customHeight="1">
-      <c r="A10" s="242">
+    <row r="10" spans="1:9" s="3" customFormat="1" ht="29.4" customHeight="1">
+      <c r="A10" s="235">
         <v>1</v>
       </c>
-      <c r="B10" s="244" t="s">
+      <c r="B10" s="237" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="246">
+      <c r="C10" s="239">
         <v>15</v>
       </c>
       <c r="D10" s="60">
         <v>1888</v>
       </c>
-      <c r="E10" s="211">
+      <c r="E10" s="204">
         <f>SUM(D10:D10)</f>
         <v>1888</v>
       </c>
-      <c r="F10" s="213">
+      <c r="F10" s="206">
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
-      <c r="A11" s="243"/>
-      <c r="B11" s="245"/>
-      <c r="C11" s="247"/>
+    <row r="11" spans="1:9" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+      <c r="A11" s="236"/>
+      <c r="B11" s="238"/>
+      <c r="C11" s="240"/>
       <c r="D11" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="E11" s="212"/>
-      <c r="F11" s="214"/>
+      <c r="E11" s="205"/>
+      <c r="F11" s="207"/>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" ht="39" customHeight="1" thickBot="1">
-      <c r="A12" s="237" t="s">
+      <c r="A12" s="230" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="238"/>
-      <c r="C12" s="239"/>
+      <c r="B12" s="231"/>
+      <c r="C12" s="232"/>
       <c r="D12" s="44">
         <v>126</v>
       </c>
@@ -7453,7 +7239,7 @@
       <c r="G12" s="25"/>
       <c r="H12" s="25"/>
     </row>
-    <row r="13" spans="1:9" s="3" customFormat="1" ht="17.45" customHeight="1" thickBot="1">
+    <row r="13" spans="1:9" s="3" customFormat="1" ht="17.399999999999999" customHeight="1" thickBot="1">
       <c r="A13" s="24"/>
       <c r="B13" s="24"/>
       <c r="C13" s="24"/>
@@ -7464,10 +7250,10 @@
       <c r="H13" s="25"/>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A14" s="240" t="s">
+      <c r="A14" s="233" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="241"/>
+      <c r="B14" s="234"/>
       <c r="C14" s="50" t="s">
         <v>53</v>
       </c>
@@ -7479,7 +7265,7 @@
       </c>
       <c r="F14" s="26"/>
     </row>
-    <row r="15" spans="1:9" s="3" customFormat="1" ht="28.15" customHeight="1" thickBot="1">
+    <row r="15" spans="1:9" s="3" customFormat="1" ht="28.2" customHeight="1" thickBot="1">
       <c r="A15" s="36" t="s">
         <v>78</v>
       </c>
@@ -7489,7 +7275,7 @@
       <c r="E15" s="37"/>
       <c r="F15" s="26"/>
     </row>
-    <row r="16" spans="1:9" s="3" customFormat="1" ht="28.15" customHeight="1" thickBot="1">
+    <row r="16" spans="1:9" s="3" customFormat="1" ht="28.2" customHeight="1" thickBot="1">
       <c r="A16" s="36" t="s">
         <v>80</v>
       </c>
@@ -7499,7 +7285,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="26"/>
     </row>
-    <row r="17" spans="1:6" s="3" customFormat="1" ht="28.15" customHeight="1" thickBot="1">
+    <row r="17" spans="1:6" s="3" customFormat="1" ht="28.2" customHeight="1" thickBot="1">
       <c r="A17" s="53" t="s">
         <v>82</v>
       </c>
@@ -7532,14 +7318,14 @@
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+    <row r="20" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
       <c r="D20" s="40"/>
       <c r="E20" s="28" t="s">
         <v>79</v>
       </c>
       <c r="F20" s="28"/>
     </row>
-    <row r="21" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+    <row r="21" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
       <c r="D21" s="26"/>
       <c r="E21" s="29" t="s">
         <v>81</v>
@@ -7548,12 +7334,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+    <row r="22" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
       <c r="D22" s="26"/>
       <c r="E22" s="29"/>
       <c r="F22" s="29"/>
     </row>
-    <row r="23" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
+    <row r="23" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
       <c r="D23" s="39"/>
       <c r="E23" s="28"/>
       <c r="F23" s="28"/>
@@ -7596,29 +7382,29 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A2:I49"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="51.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="13.875" customWidth="1"/>
+    <col min="6" max="6" width="13.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:9" s="3" customFormat="1" ht="15" customHeight="1"/>
     <row r="3" spans="1:9" s="3" customFormat="1" ht="30.75" customHeight="1">
       <c r="D3" s="43"/>
       <c r="E3" s="43"/>
-      <c r="G3" s="215"/>
-      <c r="H3" s="215"/>
-      <c r="I3" s="215"/>
+      <c r="G3" s="208"/>
+      <c r="H3" s="208"/>
+      <c r="I3" s="208"/>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
       <c r="D4" s="42"/>
       <c r="E4" s="42"/>
       <c r="F4" s="41"/>
-      <c r="G4" s="215"/>
-      <c r="H4" s="215"/>
-      <c r="I4" s="215"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="208"/>
+      <c r="I4" s="208"/>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" ht="56.25" customHeight="1" thickBot="1">
       <c r="A5" s="51" t="s">
@@ -7627,52 +7413,52 @@
       <c r="B5" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="216" t="s">
+      <c r="C5" s="209" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="217"/>
-      <c r="E5" s="217"/>
-      <c r="F5" s="218"/>
+      <c r="D5" s="210"/>
+      <c r="E5" s="210"/>
+      <c r="F5" s="211"/>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A6" s="219" t="s">
+      <c r="A6" s="212" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="220"/>
-      <c r="C6" s="225" t="s">
+      <c r="B6" s="213"/>
+      <c r="C6" s="218" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="228" t="s">
+      <c r="D6" s="221" t="s">
         <v>94</v>
       </c>
-      <c r="E6" s="230" t="s">
+      <c r="E6" s="223" t="s">
         <v>72</v>
       </c>
-      <c r="F6" s="231"/>
+      <c r="F6" s="224"/>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" ht="30.6" customHeight="1" thickBot="1">
-      <c r="A7" s="221"/>
-      <c r="B7" s="222"/>
-      <c r="C7" s="226"/>
-      <c r="D7" s="229"/>
-      <c r="E7" s="232"/>
-      <c r="F7" s="233"/>
+      <c r="A7" s="214"/>
+      <c r="B7" s="215"/>
+      <c r="C7" s="219"/>
+      <c r="D7" s="222"/>
+      <c r="E7" s="225"/>
+      <c r="F7" s="226"/>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A8" s="221"/>
-      <c r="B8" s="222"/>
-      <c r="C8" s="226"/>
-      <c r="D8" s="235" t="s">
+      <c r="A8" s="214"/>
+      <c r="B8" s="215"/>
+      <c r="C8" s="219"/>
+      <c r="D8" s="228" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="234"/>
-      <c r="F8" s="233"/>
-    </row>
-    <row r="9" spans="1:9" s="3" customFormat="1" ht="17.45" customHeight="1" thickBot="1">
-      <c r="A9" s="223"/>
-      <c r="B9" s="224"/>
-      <c r="C9" s="227"/>
-      <c r="D9" s="236"/>
+      <c r="E8" s="227"/>
+      <c r="F8" s="226"/>
+    </row>
+    <row r="9" spans="1:9" s="3" customFormat="1" ht="17.399999999999999" customHeight="1" thickBot="1">
+      <c r="A9" s="216"/>
+      <c r="B9" s="217"/>
+      <c r="C9" s="220"/>
+      <c r="D9" s="229"/>
       <c r="E9" s="33" t="s">
         <v>75</v>
       </c>
@@ -7680,416 +7466,416 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="3" customFormat="1" ht="29.45" customHeight="1">
-      <c r="A10" s="242">
+    <row r="10" spans="1:9" s="3" customFormat="1" ht="29.4" customHeight="1">
+      <c r="A10" s="235">
         <v>1</v>
       </c>
-      <c r="B10" s="248" t="s">
+      <c r="B10" s="241" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="242">
+      <c r="C10" s="235">
         <v>32</v>
       </c>
       <c r="D10" s="54">
         <v>566</v>
       </c>
-      <c r="E10" s="211">
+      <c r="E10" s="204">
         <f>SUM(D10:D10)</f>
         <v>566</v>
       </c>
-      <c r="F10" s="213">
+      <c r="F10" s="206">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
-      <c r="A11" s="243"/>
-      <c r="B11" s="249"/>
-      <c r="C11" s="243"/>
+    <row r="11" spans="1:9" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+      <c r="A11" s="236"/>
+      <c r="B11" s="242"/>
+      <c r="C11" s="236"/>
       <c r="D11" s="55" t="s">
         <v>97</v>
       </c>
-      <c r="E11" s="212"/>
-      <c r="F11" s="214"/>
-    </row>
-    <row r="12" spans="1:9" s="3" customFormat="1" ht="29.45" hidden="1" customHeight="1">
-      <c r="A12" s="242">
+      <c r="E11" s="205"/>
+      <c r="F11" s="207"/>
+    </row>
+    <row r="12" spans="1:9" s="3" customFormat="1" ht="29.4" hidden="1" customHeight="1">
+      <c r="A12" s="235">
         <v>2</v>
       </c>
-      <c r="B12" s="244" t="s">
+      <c r="B12" s="237" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="246">
+      <c r="C12" s="239">
         <v>14</v>
       </c>
       <c r="D12" s="54"/>
-      <c r="E12" s="250">
+      <c r="E12" s="243">
         <f>SUM(D12:D12)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="213">
+      <c r="F12" s="206">
         <f>มหาชัย!C11</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="3" customFormat="1" ht="29.45" hidden="1" customHeight="1">
-      <c r="A13" s="243"/>
-      <c r="B13" s="245"/>
-      <c r="C13" s="253"/>
+    <row r="13" spans="1:9" s="3" customFormat="1" ht="29.4" hidden="1" customHeight="1">
+      <c r="A13" s="236"/>
+      <c r="B13" s="238"/>
+      <c r="C13" s="246"/>
       <c r="D13" s="56" t="str">
         <f>IF(D12=0, "", IF(MOD(D12, $C$11) = 0, D12 / $C$11, IF(INT(D12 / $C$11) = 0, MOD(D12, $C$11) &amp; " P", INT(D12 / $C$11) &amp; " + " &amp; MOD(D12, $C$11) &amp; " P")))</f>
         <v/>
       </c>
-      <c r="E13" s="251"/>
-      <c r="F13" s="214"/>
-    </row>
-    <row r="14" spans="1:9" s="3" customFormat="1" ht="29.45" customHeight="1">
-      <c r="A14" s="242">
+      <c r="E13" s="244"/>
+      <c r="F13" s="207"/>
+    </row>
+    <row r="14" spans="1:9" s="3" customFormat="1" ht="29.4" customHeight="1">
+      <c r="A14" s="235">
         <v>2</v>
       </c>
-      <c r="B14" s="248" t="s">
+      <c r="B14" s="241" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="242">
+      <c r="C14" s="235">
         <v>32</v>
       </c>
       <c r="D14" s="54">
         <v>275</v>
       </c>
-      <c r="E14" s="250">
+      <c r="E14" s="243">
         <f>SUM(D14:D14)</f>
         <v>275</v>
       </c>
-      <c r="F14" s="213" t="e">
+      <c r="F14" s="206" t="e">
         <f>มหาชัย!#REF!</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
-      <c r="A15" s="243"/>
-      <c r="B15" s="249"/>
-      <c r="C15" s="243"/>
+    <row r="15" spans="1:9" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+      <c r="A15" s="236"/>
+      <c r="B15" s="242"/>
+      <c r="C15" s="236"/>
       <c r="D15" s="56" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="251"/>
-      <c r="F15" s="214"/>
-    </row>
-    <row r="16" spans="1:9" s="3" customFormat="1" ht="29.45" customHeight="1">
-      <c r="A16" s="242">
+      <c r="E15" s="244"/>
+      <c r="F15" s="207"/>
+    </row>
+    <row r="16" spans="1:9" s="3" customFormat="1" ht="29.4" customHeight="1">
+      <c r="A16" s="235">
         <v>3</v>
       </c>
-      <c r="B16" s="248" t="s">
+      <c r="B16" s="241" t="s">
         <v>86</v>
       </c>
-      <c r="C16" s="252">
+      <c r="C16" s="245">
         <v>27</v>
       </c>
       <c r="D16" s="57">
         <v>228</v>
       </c>
-      <c r="E16" s="250">
+      <c r="E16" s="243">
         <f>SUM(D16:D16)</f>
         <v>228</v>
       </c>
-      <c r="F16" s="213">
+      <c r="F16" s="206">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
-      <c r="A17" s="243"/>
-      <c r="B17" s="249"/>
-      <c r="C17" s="247"/>
+    <row r="17" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+      <c r="A17" s="236"/>
+      <c r="B17" s="242"/>
+      <c r="C17" s="240"/>
       <c r="D17" s="56" t="s">
         <v>99</v>
       </c>
-      <c r="E17" s="251"/>
-      <c r="F17" s="214"/>
-    </row>
-    <row r="18" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
-      <c r="A18" s="242">
+      <c r="E17" s="244"/>
+      <c r="F17" s="207"/>
+    </row>
+    <row r="18" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
+      <c r="A18" s="235">
         <v>4</v>
       </c>
-      <c r="B18" s="244" t="s">
+      <c r="B18" s="237" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="246">
+      <c r="C18" s="239">
         <v>36</v>
       </c>
       <c r="D18" s="54">
         <v>181</v>
       </c>
-      <c r="E18" s="250">
+      <c r="E18" s="243">
         <f>SUM(D18:D18)</f>
         <v>181</v>
       </c>
-      <c r="F18" s="213">
+      <c r="F18" s="206">
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
-      <c r="A19" s="243"/>
-      <c r="B19" s="245"/>
-      <c r="C19" s="247"/>
+    <row r="19" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+      <c r="A19" s="236"/>
+      <c r="B19" s="238"/>
+      <c r="C19" s="240"/>
       <c r="D19" s="58" t="s">
         <v>100</v>
       </c>
-      <c r="E19" s="251"/>
-      <c r="F19" s="214"/>
-    </row>
-    <row r="20" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
-      <c r="A20" s="242">
+      <c r="E19" s="244"/>
+      <c r="F19" s="207"/>
+    </row>
+    <row r="20" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
+      <c r="A20" s="235">
         <v>5</v>
       </c>
-      <c r="B20" s="244" t="s">
+      <c r="B20" s="237" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="246">
+      <c r="C20" s="239">
         <v>15</v>
       </c>
       <c r="D20" s="54">
         <v>272</v>
       </c>
-      <c r="E20" s="250">
+      <c r="E20" s="243">
         <f>SUM(D20:D20)</f>
         <v>272</v>
       </c>
-      <c r="F20" s="213">
+      <c r="F20" s="206">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
-      <c r="A21" s="243"/>
-      <c r="B21" s="245"/>
-      <c r="C21" s="247"/>
+    <row r="21" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+      <c r="A21" s="236"/>
+      <c r="B21" s="238"/>
+      <c r="C21" s="240"/>
       <c r="D21" s="58" t="s">
         <v>101</v>
       </c>
-      <c r="E21" s="251"/>
-      <c r="F21" s="214"/>
-    </row>
-    <row r="22" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
-      <c r="A22" s="242">
+      <c r="E21" s="244"/>
+      <c r="F21" s="207"/>
+    </row>
+    <row r="22" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
+      <c r="A22" s="235">
         <v>6</v>
       </c>
-      <c r="B22" s="244" t="s">
+      <c r="B22" s="237" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="246">
+      <c r="C22" s="239">
         <v>45</v>
       </c>
       <c r="D22" s="54">
         <v>24</v>
       </c>
-      <c r="E22" s="250">
+      <c r="E22" s="243">
         <f>SUM(D22:D22)</f>
         <v>24</v>
       </c>
-      <c r="F22" s="213">
+      <c r="F22" s="206">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
-      <c r="A23" s="243"/>
-      <c r="B23" s="245"/>
-      <c r="C23" s="247"/>
+    <row r="23" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+      <c r="A23" s="236"/>
+      <c r="B23" s="238"/>
+      <c r="C23" s="240"/>
       <c r="D23" s="59" t="s">
         <v>102</v>
       </c>
-      <c r="E23" s="212"/>
-      <c r="F23" s="214"/>
-    </row>
-    <row r="24" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
-      <c r="A24" s="242">
+      <c r="E23" s="205"/>
+      <c r="F23" s="207"/>
+    </row>
+    <row r="24" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
+      <c r="A24" s="235">
         <v>7</v>
       </c>
-      <c r="B24" s="244" t="s">
+      <c r="B24" s="237" t="s">
         <v>93</v>
       </c>
-      <c r="C24" s="246">
+      <c r="C24" s="239">
         <v>27</v>
       </c>
       <c r="D24" s="60">
         <v>390</v>
       </c>
-      <c r="E24" s="211">
+      <c r="E24" s="204">
         <f>SUM(D24:D24)</f>
         <v>390</v>
       </c>
-      <c r="F24" s="213">
+      <c r="F24" s="206">
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
-      <c r="A25" s="243"/>
-      <c r="B25" s="245"/>
-      <c r="C25" s="247"/>
+    <row r="25" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+      <c r="A25" s="236"/>
+      <c r="B25" s="238"/>
+      <c r="C25" s="240"/>
       <c r="D25" s="59" t="s">
         <v>103</v>
       </c>
-      <c r="E25" s="212"/>
-      <c r="F25" s="214"/>
-    </row>
-    <row r="26" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
-      <c r="A26" s="242">
+      <c r="E25" s="205"/>
+      <c r="F25" s="207"/>
+    </row>
+    <row r="26" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
+      <c r="A26" s="235">
         <v>8</v>
       </c>
-      <c r="B26" s="244" t="s">
+      <c r="B26" s="237" t="s">
         <v>66</v>
       </c>
-      <c r="C26" s="246">
+      <c r="C26" s="239">
         <v>15</v>
       </c>
       <c r="D26" s="60">
         <v>40</v>
       </c>
-      <c r="E26" s="211">
+      <c r="E26" s="204">
         <f>SUM(D26:D26)</f>
         <v>40</v>
       </c>
-      <c r="F26" s="213">
+      <c r="F26" s="206">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
-      <c r="A27" s="243"/>
-      <c r="B27" s="245"/>
-      <c r="C27" s="247"/>
+    <row r="27" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+      <c r="A27" s="236"/>
+      <c r="B27" s="238"/>
+      <c r="C27" s="240"/>
       <c r="D27" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="E27" s="212"/>
-      <c r="F27" s="214"/>
-    </row>
-    <row r="28" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
-      <c r="A28" s="242">
+      <c r="E27" s="205"/>
+      <c r="F27" s="207"/>
+    </row>
+    <row r="28" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
+      <c r="A28" s="235">
         <v>9</v>
       </c>
-      <c r="B28" s="244" t="s">
+      <c r="B28" s="237" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="246">
+      <c r="C28" s="239">
         <v>27</v>
       </c>
       <c r="D28" s="60">
         <v>172</v>
       </c>
-      <c r="E28" s="211">
+      <c r="E28" s="204">
         <f>SUM(D28:D28)</f>
         <v>172</v>
       </c>
-      <c r="F28" s="213">
+      <c r="F28" s="206">
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
-      <c r="A29" s="243"/>
-      <c r="B29" s="245"/>
-      <c r="C29" s="247"/>
+    <row r="29" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+      <c r="A29" s="236"/>
+      <c r="B29" s="238"/>
+      <c r="C29" s="240"/>
       <c r="D29" s="59" t="s">
         <v>105</v>
       </c>
-      <c r="E29" s="212"/>
-      <c r="F29" s="214"/>
-    </row>
-    <row r="30" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
-      <c r="A30" s="242">
+      <c r="E29" s="205"/>
+      <c r="F29" s="207"/>
+    </row>
+    <row r="30" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
+      <c r="A30" s="235">
         <v>10</v>
       </c>
-      <c r="B30" s="244" t="s">
+      <c r="B30" s="237" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="246">
+      <c r="C30" s="239">
         <v>20</v>
       </c>
       <c r="D30" s="60">
         <v>239</v>
       </c>
-      <c r="E30" s="211">
+      <c r="E30" s="204">
         <f>SUM(D30:D30)</f>
         <v>239</v>
       </c>
-      <c r="F30" s="213">
+      <c r="F30" s="206">
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
-      <c r="A31" s="243"/>
-      <c r="B31" s="245"/>
-      <c r="C31" s="247"/>
+    <row r="31" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+      <c r="A31" s="236"/>
+      <c r="B31" s="238"/>
+      <c r="C31" s="240"/>
       <c r="D31" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="E31" s="212"/>
-      <c r="F31" s="214"/>
-    </row>
-    <row r="32" spans="1:6" s="3" customFormat="1" ht="29.45" customHeight="1">
-      <c r="A32" s="242">
+      <c r="E31" s="205"/>
+      <c r="F31" s="207"/>
+    </row>
+    <row r="32" spans="1:6" s="3" customFormat="1" ht="29.4" customHeight="1">
+      <c r="A32" s="235">
         <v>11</v>
       </c>
-      <c r="B32" s="244" t="s">
+      <c r="B32" s="237" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="246">
+      <c r="C32" s="239">
         <v>32</v>
       </c>
       <c r="D32" s="60">
         <v>121</v>
       </c>
-      <c r="E32" s="211">
+      <c r="E32" s="204">
         <f>SUM(D32:D32)</f>
         <v>121</v>
       </c>
-      <c r="F32" s="213">
+      <c r="F32" s="206">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:8" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
-      <c r="A33" s="243"/>
-      <c r="B33" s="245"/>
-      <c r="C33" s="247"/>
+    <row r="33" spans="1:8" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+      <c r="A33" s="236"/>
+      <c r="B33" s="238"/>
+      <c r="C33" s="240"/>
       <c r="D33" s="59" t="s">
         <v>107</v>
       </c>
-      <c r="E33" s="212"/>
-      <c r="F33" s="214"/>
-    </row>
-    <row r="34" spans="1:8" s="3" customFormat="1" ht="29.45" customHeight="1">
-      <c r="A34" s="242">
+      <c r="E33" s="205"/>
+      <c r="F33" s="207"/>
+    </row>
+    <row r="34" spans="1:8" s="3" customFormat="1" ht="29.4" customHeight="1">
+      <c r="A34" s="235">
         <v>12</v>
       </c>
-      <c r="B34" s="248" t="s">
+      <c r="B34" s="241" t="s">
         <v>70</v>
       </c>
-      <c r="C34" s="242">
+      <c r="C34" s="235">
         <v>45</v>
       </c>
       <c r="D34" s="60">
         <v>54</v>
       </c>
-      <c r="E34" s="211">
+      <c r="E34" s="204">
         <f>SUM(D34:D34)</f>
         <v>54</v>
       </c>
-      <c r="F34" s="213">
+      <c r="F34" s="206">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:8" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
-      <c r="A35" s="243"/>
-      <c r="B35" s="249"/>
-      <c r="C35" s="243"/>
+    <row r="35" spans="1:8" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
+      <c r="A35" s="236"/>
+      <c r="B35" s="242"/>
+      <c r="C35" s="236"/>
       <c r="D35" s="59" t="s">
         <v>108</v>
       </c>
-      <c r="E35" s="212"/>
-      <c r="F35" s="214"/>
+      <c r="E35" s="205"/>
+      <c r="F35" s="207"/>
     </row>
     <row r="36" spans="1:8" s="3" customFormat="1" ht="39" customHeight="1" thickBot="1">
-      <c r="A36" s="237" t="s">
+      <c r="A36" s="230" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="238"/>
-      <c r="C36" s="239"/>
+      <c r="B36" s="231"/>
+      <c r="C36" s="232"/>
       <c r="D36" s="44">
         <v>105</v>
       </c>
@@ -8102,7 +7888,7 @@
       <c r="G36" s="25"/>
       <c r="H36" s="25"/>
     </row>
-    <row r="37" spans="1:8" s="3" customFormat="1" ht="17.45" customHeight="1" thickBot="1">
+    <row r="37" spans="1:8" s="3" customFormat="1" ht="17.399999999999999" customHeight="1" thickBot="1">
       <c r="A37" s="24"/>
       <c r="B37" s="24"/>
       <c r="C37" s="24"/>
@@ -8113,10 +7899,10 @@
       <c r="H37" s="25"/>
     </row>
     <row r="38" spans="1:8" s="3" customFormat="1" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A38" s="240" t="s">
+      <c r="A38" s="233" t="s">
         <v>49</v>
       </c>
-      <c r="B38" s="241"/>
+      <c r="B38" s="234"/>
       <c r="C38" s="50" t="s">
         <v>53</v>
       </c>
@@ -8128,7 +7914,7 @@
       </c>
       <c r="F38" s="26"/>
     </row>
-    <row r="39" spans="1:8" s="3" customFormat="1" ht="28.15" customHeight="1" thickBot="1">
+    <row r="39" spans="1:8" s="3" customFormat="1" ht="28.2" customHeight="1" thickBot="1">
       <c r="A39" s="36" t="s">
         <v>78</v>
       </c>
@@ -8138,7 +7924,7 @@
       <c r="E39" s="37"/>
       <c r="F39" s="26"/>
     </row>
-    <row r="40" spans="1:8" s="3" customFormat="1" ht="28.15" customHeight="1" thickBot="1">
+    <row r="40" spans="1:8" s="3" customFormat="1" ht="28.2" customHeight="1" thickBot="1">
       <c r="A40" s="36" t="s">
         <v>80</v>
       </c>
@@ -8148,7 +7934,7 @@
       <c r="E40" s="37"/>
       <c r="F40" s="26"/>
     </row>
-    <row r="41" spans="1:8" s="3" customFormat="1" ht="28.15" customHeight="1" thickBot="1">
+    <row r="41" spans="1:8" s="3" customFormat="1" ht="28.2" customHeight="1" thickBot="1">
       <c r="A41" s="53" t="s">
         <v>82</v>
       </c>
@@ -8181,14 +7967,14 @@
         <v>92</v>
       </c>
     </row>
-    <row r="44" spans="1:8" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+    <row r="44" spans="1:8" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
       <c r="D44" s="40"/>
       <c r="E44" s="28" t="s">
         <v>79</v>
       </c>
       <c r="F44" s="28"/>
     </row>
-    <row r="45" spans="1:8" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+    <row r="45" spans="1:8" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
       <c r="D45" s="26"/>
       <c r="E45" s="29" t="s">
         <v>81</v>
@@ -8197,12 +7983,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="1:8" s="3" customFormat="1" ht="29.45" customHeight="1" thickBot="1">
+    <row r="46" spans="1:8" s="3" customFormat="1" ht="29.4" customHeight="1" thickBot="1">
       <c r="D46" s="26"/>
       <c r="E46" s="29"/>
       <c r="F46" s="29"/>
     </row>
-    <row r="47" spans="1:8" s="3" customFormat="1" ht="29.45" customHeight="1">
+    <row r="47" spans="1:8" s="3" customFormat="1" ht="29.4" customHeight="1">
       <c r="D47" s="39"/>
       <c r="E47" s="28"/>
       <c r="F47" s="28"/>
